--- a/data/OP1/case33_1/case33_1_operational_data.xlsx
+++ b/data/OP1/case33_1/case33_1_operational_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\thesis-shared-resources-planning-no_esso-degradation\data\CS7\case33_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS7/case33_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BF1AD7-FFA8-4ECA-9F99-53B30C515317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C614731-E163-634C-8926-8FFCC4133114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38010" yWindow="-12540" windowWidth="23250" windowHeight="13890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="52180" yWindow="1260" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -442,13 +442,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59B7BE64-82AA-46B6-895E-9570C0781B75}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -468,15 +468,17 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>4</v>
+        <f>E2*3.5</f>
+        <v>14</v>
       </c>
       <c r="C2" s="1">
-        <v>2.88</v>
+        <f>F2*3.5</f>
+        <v>8.4</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -488,15 +490,17 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" ref="B3:B33" si="0">E3*3.5</f>
+        <v>12.599999999999998</v>
       </c>
       <c r="C3" s="1">
-        <v>1.92</v>
+        <f t="shared" ref="C3:C33" si="1">F3*3.5</f>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -508,15 +512,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>16.8</v>
       </c>
       <c r="C4" s="1">
-        <v>3.84</v>
+        <f t="shared" si="1"/>
+        <v>11.200000000000001</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -528,15 +534,17 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C5" s="1">
-        <v>1.44</v>
+        <f t="shared" si="1"/>
+        <v>4.2</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -548,15 +556,17 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C6" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -568,15 +578,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="C7" s="1">
-        <v>4.8</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -588,15 +600,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="C8" s="1">
-        <v>4.8</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -608,15 +622,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C9" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -628,15 +644,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C10" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -648,15 +666,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>1.7999999999999998</v>
+        <f t="shared" si="0"/>
+        <v>6.2999999999999989</v>
       </c>
       <c r="C11" s="1">
-        <v>1.44</v>
+        <f t="shared" si="1"/>
+        <v>4.2</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -668,15 +688,17 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C12" s="1">
-        <v>1.6800000000000002</v>
+        <f t="shared" si="1"/>
+        <v>4.9000000000000004</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -688,15 +710,17 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C13" s="1">
-        <v>1.6800000000000002</v>
+        <f t="shared" si="1"/>
+        <v>4.9000000000000004</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -708,15 +732,17 @@
         <v>1.4000000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>16.8</v>
       </c>
       <c r="C14" s="1">
-        <v>3.84</v>
+        <f t="shared" si="1"/>
+        <v>11.200000000000001</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -728,15 +754,17 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C15" s="1">
-        <v>0.48</v>
+        <f t="shared" si="1"/>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -748,15 +776,17 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C16" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -768,15 +798,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C17" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -788,15 +820,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C18" s="1">
-        <v>1.92</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -808,15 +842,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C19" s="1">
-        <v>1.92</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -828,15 +864,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C20" s="1">
-        <v>1.92</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -848,15 +886,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C21" s="1">
-        <v>1.92</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -868,15 +908,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C22" s="1">
-        <v>1.92</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -888,15 +930,17 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C23" s="1">
-        <v>2.4</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -908,15 +952,17 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>16.8</v>
+        <f t="shared" si="0"/>
+        <v>58.800000000000004</v>
       </c>
       <c r="C24" s="1">
-        <v>9.6</v>
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -928,15 +974,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>16.8</v>
+        <f t="shared" si="0"/>
+        <v>58.800000000000004</v>
       </c>
       <c r="C25" s="1">
-        <v>9.6</v>
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -948,15 +996,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C26" s="1">
-        <v>1.2</v>
+        <f t="shared" si="1"/>
+        <v>3.5</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -968,15 +1018,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C27" s="1">
-        <v>1.2</v>
+        <f t="shared" si="1"/>
+        <v>3.5</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -988,15 +1040,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C28" s="1">
-        <v>0.96</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1008,15 +1062,17 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>16.8</v>
       </c>
       <c r="C29" s="1">
-        <v>3.3600000000000003</v>
+        <f t="shared" si="1"/>
+        <v>9.8000000000000007</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1028,15 +1084,17 @@
         <v>2.8000000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="C30" s="1">
-        <v>6</v>
+        <f t="shared" si="1"/>
+        <v>84</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1048,15 +1106,17 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="C31" s="1">
-        <v>3.3600000000000003</v>
+        <f t="shared" si="1"/>
+        <v>9.8000000000000007</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1068,15 +1128,17 @@
         <v>2.8000000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <v>8.4</v>
+        <f t="shared" si="0"/>
+        <v>29.400000000000002</v>
       </c>
       <c r="C32" s="1">
-        <v>4.8</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1088,15 +1150,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C33" s="1">
-        <v>1.92</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1108,11 +1172,11 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
     </row>
@@ -1125,12 +1189,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD68AE75-D6B1-4AA7-B0E5-5751542FB30D}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1138,7 +1202,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1146,7 +1210,7 @@
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1154,10 +1218,10 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B6" s="2"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B7" s="2"/>
     </row>
   </sheetData>
@@ -1168,9 +1232,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{206E5596-3B52-412C-A9A4-71C002FACF4D}">
   <dimension ref="A1:AA385"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -1253,7 +1317,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1336,7 +1400,7 @@
         <v>0.30423493001908397</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1419,7 +1483,7 @@
         <v>0.12215315627057644</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1502,7 +1566,7 @@
         <v>0.28807338371711955</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1585,7 +1649,7 @@
         <v>5.140697371227413E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1668,7 +1732,7 @@
         <v>0.31988431141736134</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1751,7 +1815,7 @@
         <v>0.45601221277188941</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1834,7 +1898,7 @@
         <v>0.23212504519623703</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1917,7 +1981,7 @@
         <v>0.16447266993333343</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2000,7 +2064,7 @@
         <v>0.14884669085844837</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2083,7 +2147,7 @@
         <v>0.21182466623223417</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2166,7 +2230,7 @@
         <v>8.8097283050149661E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2249,7 +2313,7 @@
         <v>0.37751283536620156</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2332,7 +2396,7 @@
         <v>0.71253728546098483</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2415,7 +2479,7 @@
         <v>0.29519824892940821</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2498,7 +2562,7 @@
         <v>0.1208807275594246</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2581,7 +2645,7 @@
         <v>0.29717043793976544</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2664,7 +2728,7 @@
         <v>5.090787688011613E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2747,7 +2811,7 @@
         <v>0.33620493955090019</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2830,7 +2894,7 @@
         <v>0.47011568326998909</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2913,7 +2977,7 @@
         <v>0.22743565034378779</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2996,7 +3060,7 @@
         <v>0.16275941295486118</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -3079,7 +3143,7 @@
         <v>0.15970009540021024</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -3162,7 +3226,7 @@
         <v>0.21390137864627567</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -3245,7 +3309,7 @@
         <v>8.3063152590141104E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -3328,7 +3392,7 @@
         <v>0.38918849006824902</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -3411,7 +3475,7 @@
         <v>0.764493129192515</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -3494,7 +3558,7 @@
         <v>0.31025938407886783</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -3577,7 +3641,7 @@
         <v>0.12724287111518379</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3660,7 +3724,7 @@
         <v>0.28807338371711955</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3743,7 +3807,7 @@
         <v>5.240516737659013E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3826,7 +3890,7 @@
         <v>0.33620493955090019</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3909,7 +3973,7 @@
         <v>0.47951799693538888</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1</v>
       </c>
@@ -3992,7 +4056,7 @@
         <v>0.3164043272198474</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2</v>
       </c>
@@ -4075,7 +4139,7 @@
         <v>0.13497923767898695</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>3</v>
       </c>
@@ -4158,7 +4222,7 @@
         <v>0.32167183731275839</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>4</v>
       </c>
@@ -4241,7 +4305,7 @@
         <v>5.1387009838987807E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>5</v>
       </c>
@@ -4324,7 +4388,7 @@
         <v>0.33607437452583194</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -4407,7 +4471,7 @@
         <v>0.47914190438877291</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7</v>
       </c>
@@ -4490,7 +4554,7 @@
         <v>0.25360247362045452</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>8</v>
       </c>
@@ -4573,7 +4637,7 @@
         <v>0.17105157673066676</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>9</v>
       </c>
@@ -4656,7 +4720,7 @@
         <v>0.15480055849278632</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>10</v>
       </c>
@@ -4739,7 +4803,7 @@
         <v>0.20949874832850765</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>11</v>
       </c>
@@ -4822,7 +4886,7 @@
         <v>9.1621174372155653E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>12</v>
       </c>
@@ -4905,7 +4969,7 @@
         <v>0.40070846937426924</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>13</v>
       </c>
@@ -4988,7 +5052,7 @@
         <v>0.7796345465085609</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>14</v>
       </c>
@@ -5071,7 +5135,7 @@
         <v>0.32266975944202259</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>15</v>
       </c>
@@ -5154,7 +5218,7 @@
         <v>0.12968593424059532</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>16</v>
       </c>
@@ -5237,7 +5301,7 @@
         <v>0.31851819184890778</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>17</v>
       </c>
@@ -5320,7 +5384,7 @@
         <v>4.9310767017210523E-2</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>18</v>
       </c>
@@ -5403,7 +5467,7 @@
         <v>0.35644251843648839</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>19</v>
       </c>
@@ -5486,7 +5550,7 @@
         <v>0.51336632613082811</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>20</v>
       </c>
@@ -5569,7 +5633,7 @@
         <v>0.23653307635753931</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>21</v>
       </c>
@@ -5652,7 +5716,7 @@
         <v>0.17283336398827787</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>22</v>
       </c>
@@ -5735,7 +5799,7 @@
         <v>0.16286308758095228</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>23</v>
       </c>
@@ -5818,7 +5882,7 @@
         <v>0.213818310149714</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>24</v>
       </c>
@@ -5901,7 +5965,7 @@
         <v>8.2895348241474168E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>25</v>
       </c>
@@ -5984,7 +6048,7 @@
         <v>0.40880358996768879</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>26</v>
       </c>
@@ -6067,7 +6131,7 @@
         <v>0.81051116221187025</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>27</v>
       </c>
@@ -6150,7 +6214,7 @@
         <v>0.3070061788865846</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>28</v>
       </c>
@@ -6233,7 +6297,7 @@
         <v>0.12703928252139948</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>29</v>
       </c>
@@ -6316,7 +6380,7 @@
         <v>0.30905725545735607</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>30</v>
       </c>
@@ -6399,7 +6463,7 @@
         <v>5.0867949133543484E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>31</v>
       </c>
@@ -6482,7 +6546,7 @@
         <v>0.32589030257050366</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>32</v>
       </c>
@@ -6565,7 +6629,7 @@
         <v>0.47425270128276498</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>1</v>
       </c>
@@ -6648,7 +6712,7 @@
         <v>0.28043833648293781</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>2</v>
       </c>
@@ -6731,7 +6795,7 @@
         <v>0.12594499382980892</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>3</v>
       </c>
@@ -6814,7 +6878,7 @@
         <v>0.30014214231916309</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4</v>
       </c>
@@ -6897,7 +6961,7 @@
         <v>5.1357064029058326E-2</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>5</v>
       </c>
@@ -6980,7 +7044,7 @@
         <v>0.3134866251890141</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>6</v>
       </c>
@@ -7063,7 +7127,7 @@
         <v>0.47914190438877291</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>7</v>
       </c>
@@ -7146,7 +7210,7 @@
         <v>0.22518474081461215</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>8</v>
       </c>
@@ -7229,7 +7293,7 @@
         <v>0.1729361594069862</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>9</v>
       </c>
@@ -7312,7 +7376,7 @@
         <v>0.14435028040543274</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>10</v>
       </c>
@@ -7395,7 +7459,7 @@
         <v>0.2035178165760681</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>11</v>
       </c>
@@ -7478,7 +7542,7 @@
         <v>7.8112924304466036E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>12</v>
       </c>
@@ -7561,7 +7625,7 @@
         <v>0.38903281467222173</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>13</v>
       </c>
@@ -7644,7 +7708,7 @@
         <v>0.70556035787417926</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>14</v>
       </c>
@@ -7727,7 +7791,7 @@
         <v>0.29224626644011414</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>15</v>
       </c>
@@ -7810,7 +7874,7 @@
         <v>0.13093291437752413</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>16</v>
       </c>
@@ -7893,7 +7957,7 @@
         <v>0.29122702918097015</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>17</v>
       </c>
@@ -7976,7 +8040,7 @@
         <v>5.0378834238028643E-2</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>18</v>
       </c>
@@ -8059,7 +8123,7 @@
         <v>0.33587852698822945</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>19</v>
       </c>
@@ -8142,7 +8206,7 @@
         <v>0.4422848348204057</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>20</v>
       </c>
@@ -8225,7 +8289,7 @@
         <v>0.22748254429231229</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>21</v>
       </c>
@@ -8308,7 +8372,7 @@
         <v>0.17629414308479177</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>22</v>
       </c>
@@ -8391,7 +8455,7 @@
         <v>0.14890871031297273</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>23</v>
       </c>
@@ -8474,7 +8538,7 @@
         <v>0.20555299474182878</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>24</v>
       </c>
@@ -8557,7 +8621,7 @@
         <v>7.8112924304466036E-2</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>25</v>
       </c>
@@ -8640,7 +8704,7 @@
         <v>0.38521876746955291</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>26</v>
       </c>
@@ -8723,7 +8787,7 @@
         <v>0.72010799411900772</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>27</v>
       </c>
@@ -8806,7 +8870,7 @@
         <v>0.29519824892940821</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>28</v>
       </c>
@@ -8889,7 +8953,7 @@
         <v>0.1184631130082361</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>29</v>
       </c>
@@ -8972,7 +9036,7 @@
         <v>0.30311384669856073</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>30</v>
       </c>
@@ -9055,7 +9119,7 @@
         <v>4.9889719342513801E-2</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>31</v>
       </c>
@@ -9138,7 +9202,7 @@
         <v>0.3134866251890141</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>32</v>
       </c>
@@ -9221,7 +9285,7 @@
         <v>0.47914190438877291</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>1</v>
       </c>
@@ -9304,7 +9368,7 @@
         <v>0.40460512983649527</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>2</v>
       </c>
@@ -9387,7 +9451,7 @@
         <v>0.12531670023913216</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>3</v>
       </c>
@@ -9470,7 +9534,7 @@
         <v>0.29869072399109714</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>4</v>
       </c>
@@ -9553,7 +9617,7 @@
         <v>4.4140186966755215E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>5</v>
       </c>
@@ -9636,7 +9700,7 @@
         <v>0.31506655879445489</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>6</v>
       </c>
@@ -9719,7 +9783,7 @@
         <v>0.44456052640476812</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>7</v>
       </c>
@@ -9802,7 +9866,7 @@
         <v>0.24397437503436967</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>8</v>
       </c>
@@ -9885,7 +9949,7 @@
         <v>0.15382663214631914</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>9</v>
       </c>
@@ -9968,7 +10032,7 @@
         <v>0.14269317780774657</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>10</v>
       </c>
@@ -10051,7 +10115,7 @@
         <v>0.21685736810291287</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>11</v>
       </c>
@@ -10134,7 +10198,7 @@
         <v>7.9818120109252197E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>12</v>
       </c>
@@ -10217,7 +10281,7 @@
         <v>0.45025918839909279</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>13</v>
       </c>
@@ -10300,7 +10364,7 @@
         <v>0.78440506467065618</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>14</v>
       </c>
@@ -10383,7 +10447,7 @@
         <v>0.4349917738149664</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>15</v>
       </c>
@@ -10466,7 +10530,7 @@
         <v>0.12151477012193317</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>16</v>
       </c>
@@ -10549,7 +10613,7 @@
         <v>0.29988121067334794</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>17</v>
       </c>
@@ -10632,7 +10696,7 @@
         <v>4.4687934013653223E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>18</v>
       </c>
@@ -10715,7 +10779,7 @@
         <v>0.33018527981719359</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>19</v>
       </c>
@@ -10798,7 +10862,7 @@
         <v>0.42311155071818235</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>20</v>
       </c>
@@ -10881,7 +10945,7 @@
         <v>0.23439270222739572</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>21</v>
       </c>
@@ -10964,7 +11028,7 @@
         <v>0.15708373083840152</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>22</v>
       </c>
@@ -11047,7 +11111,7 @@
         <v>0.14033793264830885</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>23</v>
       </c>
@@ -11130,7 +11194,7 @@
         <v>0.19882125121158906</v>
       </c>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>24</v>
       </c>
@@ -11213,7 +11277,7 @@
         <v>7.9720383742063805E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>25</v>
       </c>
@@ -11296,7 +11360,7 @@
         <v>0.42271478599915069</v>
       </c>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>26</v>
       </c>
@@ -11379,7 +11443,7 @@
         <v>0.7719433123864361</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>27</v>
       </c>
@@ -11462,7 +11526,7 @@
         <v>0.42260815392379569</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>28</v>
       </c>
@@ -11545,7 +11609,7 @@
         <v>0.12503041680988139</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>29</v>
       </c>
@@ -11628,7 +11692,7 @@
         <v>0.30983513447948846</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>30</v>
       </c>
@@ -11711,7 +11775,7 @@
         <v>4.7369169177349381E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>31</v>
       </c>
@@ -11794,7 +11858,7 @@
         <v>0.29376889231153613</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>32</v>
       </c>
@@ -11877,7 +11941,7 @@
         <v>0.40276293406267627</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>1</v>
       </c>
@@ -11960,7 +12024,7 @@
         <v>0.42689047219041887</v>
       </c>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>2</v>
       </c>
@@ -12043,7 +12107,7 @@
         <v>0.12033783871790973</v>
       </c>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>3</v>
       </c>
@@ -12126,7 +12190,7 @@
         <v>0.29665445719231714</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>4</v>
       </c>
@@ -12209,7 +12273,7 @@
         <v>4.2953112347665981E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>5</v>
       </c>
@@ -12292,7 +12356,7 @@
         <v>0.3215536643614364</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>6</v>
       </c>
@@ -12375,7 +12439,7 @@
         <v>0.44732388733607209</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>7</v>
       </c>
@@ -12458,7 +12522,7 @@
         <v>0.21766051836345818</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>8</v>
       </c>
@@ -12541,7 +12605,7 @@
         <v>0.13917647670381256</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>9</v>
       </c>
@@ -12624,7 +12688,7 @@
         <v>0.13581314695342595</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>10</v>
       </c>
@@ -12707,7 +12771,7 @@
         <v>0.18744030886223878</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>11</v>
       </c>
@@ -12790,7 +12854,7 @@
         <v>7.5711443802736714E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>12</v>
       </c>
@@ -12873,7 +12937,7 @@
         <v>0.45877795420658402</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>13</v>
       </c>
@@ -12956,7 +13020,7 @@
         <v>0.72691636268398796</v>
       </c>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>14</v>
       </c>
@@ -13039,7 +13103,7 @@
         <v>0.40804281413635179</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>15</v>
       </c>
@@ -13122,7 +13186,7 @@
         <v>0.11968020682142257</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>16</v>
       </c>
@@ -13205,7 +13269,7 @@
         <v>0.2817710283800931</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>17</v>
       </c>
@@ -13288,7 +13352,7 @@
         <v>4.7180765681348061E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>18</v>
       </c>
@@ -13371,7 +13435,7 @@
         <v>0.3246823184506501</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>19</v>
       </c>
@@ -13454,7 +13518,7 @@
         <v>0.4378654235287498</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>20</v>
       </c>
@@ -13537,7 +13601,7 @@
         <v>0.2315525622208352</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>21</v>
       </c>
@@ -13620,7 +13684,7 @@
         <v>0.15065394992841988</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>22</v>
       </c>
@@ -13703,7 +13767,7 @@
         <v>0.13333519255883414</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>23</v>
       </c>
@@ -13786,7 +13850,7 @@
         <v>0.2201848013021738</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>24</v>
       </c>
@@ -13869,7 +13933,7 @@
         <v>7.5208128585683348E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>25</v>
       </c>
@@ -13952,7 +14016,7 @@
         <v>0.42885448722957481</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>26</v>
       </c>
@@ -14035,7 +14099,7 @@
         <v>0.75957708235256871</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>27</v>
       </c>
@@ -14118,7 +14182,7 @@
         <v>0.41003335984872546</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>28</v>
       </c>
@@ -14201,7 +14265,7 @@
         <v>0.12746094767742908</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>29</v>
       </c>
@@ -14284,7 +14348,7 @@
         <v>0.31004400592124742</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>30</v>
       </c>
@@ -14367,7 +14431,7 @@
         <v>4.6176909736852456E-2</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>31</v>
       </c>
@@ -14450,7 +14514,7 @@
         <v>0.31071405402795677</v>
       </c>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>32</v>
       </c>
@@ -14533,7 +14597,7 @@
         <v>0.44091942255282457</v>
       </c>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>1</v>
       </c>
@@ -14616,7 +14680,7 @@
         <v>0.42965036203221812</v>
       </c>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>2</v>
       </c>
@@ -14699,7 +14763,7 @@
         <v>0.12289737753343244</v>
       </c>
     </row>
-    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>3</v>
       </c>
@@ -14782,7 +14846,7 @@
         <v>0.28273252588643172</v>
       </c>
     </row>
-    <row r="165" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>4</v>
       </c>
@@ -14865,7 +14929,7 @@
         <v>4.083949069934821E-2</v>
       </c>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>5</v>
       </c>
@@ -14948,7 +15012,7 @@
         <v>0.32221764217060544</v>
       </c>
     </row>
-    <row r="167" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>6</v>
       </c>
@@ -15031,7 +15095,7 @@
         <v>0.46171304926561546</v>
       </c>
     </row>
-    <row r="168" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>7</v>
       </c>
@@ -15114,7 +15178,7 @@
         <v>0.24146630603376001</v>
       </c>
     </row>
-    <row r="169" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>8</v>
       </c>
@@ -15197,7 +15261,7 @@
         <v>0.16428246479929443</v>
       </c>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>9</v>
       </c>
@@ -15280,7 +15344,7 @@
         <v>0.13144036344599996</v>
       </c>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>10</v>
       </c>
@@ -15363,7 +15427,7 @@
         <v>0.19702677154429635</v>
       </c>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>11</v>
       </c>
@@ -15446,7 +15510,7 @@
         <v>7.2314319481827663E-2</v>
       </c>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>12</v>
       </c>
@@ -15529,7 +15593,7 @@
         <v>0.46001998724932369</v>
       </c>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>13</v>
       </c>
@@ -15612,7 +15676,7 @@
         <v>0.72622447296762938</v>
       </c>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>14</v>
       </c>
@@ -15695,7 +15759,7 @@
         <v>0.4010627508493424</v>
       </c>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>15</v>
       </c>
@@ -15778,7 +15842,7 @@
         <v>0.12537432575955593</v>
       </c>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>16</v>
       </c>
@@ -15861,7 +15925,7 @@
         <v>0.31273459745725996</v>
       </c>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>17</v>
       </c>
@@ -15944,7 +16008,7 @@
         <v>4.4051037967967832E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>18</v>
       </c>
@@ -16027,7 +16091,7 @@
         <v>0.29278258429582177</v>
       </c>
     </row>
-    <row r="180" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>19</v>
       </c>
@@ -16110,7 +16174,7 @@
         <v>0.43040774612253258</v>
       </c>
     </row>
-    <row r="181" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>20</v>
       </c>
@@ -16193,7 +16257,7 @@
         <v>0.22549174696111235</v>
       </c>
     </row>
-    <row r="182" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>21</v>
       </c>
@@ -16276,7 +16340,7 @@
         <v>0.14289138994230252</v>
       </c>
     </row>
-    <row r="183" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>22</v>
       </c>
@@ -16359,7 +16423,7 @@
         <v>0.13544434056330421</v>
       </c>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>23</v>
       </c>
@@ -16442,7 +16506,7 @@
         <v>0.21582499841669786</v>
       </c>
     </row>
-    <row r="185" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>24</v>
       </c>
@@ -16525,7 +16589,7 @@
         <v>8.3930712813533967E-2</v>
       </c>
     </row>
-    <row r="186" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>25</v>
       </c>
@@ -16608,7 +16672,7 @@
         <v>0.45973303128551724</v>
       </c>
     </row>
-    <row r="187" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>26</v>
       </c>
@@ -16691,7 +16755,7 @@
         <v>0.73190418906602639</v>
       </c>
     </row>
-    <row r="188" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>27</v>
       </c>
@@ -16774,7 +16838,7 @@
         <v>0.39427768777634509</v>
       </c>
     </row>
-    <row r="189" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>28</v>
       </c>
@@ -16857,7 +16921,7 @@
         <v>0.12672797661677199</v>
       </c>
     </row>
-    <row r="190" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>29</v>
       </c>
@@ -16940,7 +17004,7 @@
         <v>0.29363456677379773</v>
       </c>
     </row>
-    <row r="191" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>30</v>
       </c>
@@ -17023,7 +17087,7 @@
         <v>4.8685903486685111E-2</v>
       </c>
     </row>
-    <row r="192" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>31</v>
       </c>
@@ -17106,7 +17170,7 @@
         <v>0.31338468480191034</v>
       </c>
     </row>
-    <row r="193" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>32</v>
       </c>
@@ -17189,7 +17253,7 @@
         <v>0.45918880408260448</v>
       </c>
     </row>
-    <row r="194" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>1</v>
       </c>
@@ -17272,7 +17336,7 @@
         <v>0.56850363147764293</v>
       </c>
     </row>
-    <row r="195" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>2</v>
       </c>
@@ -17355,7 +17419,7 @@
         <v>0.1409055153001664</v>
       </c>
     </row>
-    <row r="196" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>3</v>
       </c>
@@ -17438,7 +17502,7 @@
         <v>0.33597021620982936</v>
       </c>
     </row>
-    <row r="197" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>4</v>
       </c>
@@ -17521,7 +17585,7 @@
         <v>4.6885646565674503E-2</v>
       </c>
     </row>
-    <row r="198" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>5</v>
       </c>
@@ -17604,7 +17668,7 @@
         <v>0.32717567035626965</v>
       </c>
     </row>
-    <row r="199" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>6</v>
       </c>
@@ -17687,7 +17751,7 @@
         <v>0.45982461493547749</v>
       </c>
     </row>
-    <row r="200" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>7</v>
       </c>
@@ -17770,7 +17834,7 @@
         <v>0.23184769316557399</v>
       </c>
     </row>
-    <row r="201" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>8</v>
       </c>
@@ -17853,7 +17917,7 @@
         <v>0.15918020101075309</v>
       </c>
     </row>
-    <row r="202" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>9</v>
       </c>
@@ -17936,7 +18000,7 @@
         <v>0.13313519014660974</v>
       </c>
     </row>
-    <row r="203" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>10</v>
       </c>
@@ -18019,7 +18083,7 @@
         <v>0.22892824212080104</v>
       </c>
     </row>
-    <row r="204" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>11</v>
       </c>
@@ -18102,7 +18166,7 @@
         <v>7.7288570783292224E-2</v>
       </c>
     </row>
-    <row r="205" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>12</v>
       </c>
@@ -18185,7 +18249,7 @@
         <v>0.55794241306146164</v>
       </c>
     </row>
-    <row r="206" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>13</v>
       </c>
@@ -18268,7 +18332,7 @@
         <v>0.81989931552599016</v>
       </c>
     </row>
-    <row r="207" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>14</v>
       </c>
@@ -18351,7 +18415,7 @@
         <v>0.55226067057828165</v>
       </c>
     </row>
-    <row r="208" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>15</v>
       </c>
@@ -18434,7 +18498,7 @@
         <v>0.13819579385208627</v>
       </c>
     </row>
-    <row r="209" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>16</v>
       </c>
@@ -18517,7 +18581,7 @@
         <v>0.33597021620982936</v>
       </c>
     </row>
-    <row r="210" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>17</v>
       </c>
@@ -18600,7 +18664,7 @@
         <v>4.6425983364050238E-2</v>
       </c>
     </row>
-    <row r="211" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>18</v>
       </c>
@@ -18683,7 +18747,7 @@
         <v>0.33699094046695777</v>
       </c>
     </row>
-    <row r="212" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>19</v>
       </c>
@@ -18766,7 +18830,7 @@
         <v>0.4733488683159327</v>
       </c>
     </row>
-    <row r="213" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>20</v>
       </c>
@@ -18849,7 +18913,7 @@
         <v>0.25137170943214865</v>
       </c>
     </row>
-    <row r="214" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>21</v>
       </c>
@@ -18932,7 +18996,7 @@
         <v>0.15454388447645931</v>
       </c>
     </row>
-    <row r="215" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>22</v>
       </c>
@@ -19015,7 +19079,7 @@
         <v>0.13176266241313953</v>
       </c>
     </row>
-    <row r="216" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>23</v>
       </c>
@@ -19098,7 +19162,7 @@
         <v>0.22443945305960886</v>
       </c>
     </row>
-    <row r="217" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>24</v>
       </c>
@@ -19181,7 +19245,7 @@
         <v>8.0542826395220313E-2</v>
       </c>
     </row>
-    <row r="218" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>25</v>
       </c>
@@ -19264,7 +19328,7 @@
         <v>0.56341243671892705</v>
       </c>
     </row>
-    <row r="219" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>26</v>
       </c>
@@ -19347,7 +19411,7 @@
         <v>0.75621781529096177</v>
       </c>
     </row>
-    <row r="220" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>27</v>
       </c>
@@ -19430,7 +19494,7 @@
         <v>0.52518906907934626</v>
       </c>
     </row>
-    <row r="221" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>28</v>
       </c>
@@ -19513,7 +19577,7 @@
         <v>0.14226037602420646</v>
       </c>
     </row>
-    <row r="222" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>29</v>
       </c>
@@ -19596,7 +19660,7 @@
         <v>0.30717276910612967</v>
       </c>
     </row>
-    <row r="223" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>30</v>
       </c>
@@ -19679,7 +19743,7 @@
         <v>4.5046993759177457E-2</v>
       </c>
     </row>
-    <row r="224" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>31</v>
       </c>
@@ -19762,7 +19826,7 @@
         <v>0.33044742705983238</v>
       </c>
     </row>
-    <row r="225" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>32</v>
       </c>
@@ -19845,7 +19909,7 @@
         <v>0.46884078385578098</v>
       </c>
     </row>
-    <row r="226" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>1</v>
       </c>
@@ -19928,7 +19992,7 @@
         <v>0.53601770967892048</v>
       </c>
     </row>
-    <row r="227" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>2</v>
       </c>
@@ -20011,7 +20075,7 @@
         <v>0.13006662950784589</v>
       </c>
     </row>
-    <row r="228" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>3</v>
       </c>
@@ -20094,7 +20158,7 @@
         <v>0.31037248545098522</v>
       </c>
     </row>
-    <row r="229" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>4</v>
       </c>
@@ -20177,7 +20241,7 @@
         <v>4.5506656960801722E-2</v>
       </c>
     </row>
-    <row r="230" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>5</v>
       </c>
@@ -20260,7 +20324,7 @@
         <v>0.33699094046695777</v>
       </c>
     </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>6</v>
       </c>
@@ -20343,7 +20407,7 @@
         <v>0.450808446015174</v>
       </c>
     </row>
-    <row r="232" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>7</v>
       </c>
@@ -20426,7 +20490,7 @@
         <v>0.24405020333218316</v>
       </c>
     </row>
-    <row r="233" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>8</v>
       </c>
@@ -20509,7 +20573,7 @@
         <v>0.15454388447645931</v>
       </c>
     </row>
-    <row r="234" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>9</v>
       </c>
@@ -20592,7 +20656,7 @@
         <v>0.14137035654743096</v>
       </c>
     </row>
-    <row r="235" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>10</v>
       </c>
@@ -20675,7 +20739,7 @@
         <v>0.22892824212080104</v>
       </c>
     </row>
-    <row r="236" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>11</v>
       </c>
@@ -20758,7 +20822,7 @@
         <v>8.0542826395220313E-2</v>
       </c>
     </row>
-    <row r="237" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>12</v>
       </c>
@@ -20841,7 +20905,7 @@
         <v>0.53606231843160046</v>
       </c>
     </row>
-    <row r="238" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>13</v>
       </c>
@@ -20924,7 +20988,7 @@
         <v>0.78009837787909742</v>
       </c>
     </row>
-    <row r="239" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>14</v>
       </c>
@@ -21007,7 +21071,7 @@
         <v>0.52518906907934626</v>
       </c>
     </row>
-    <row r="240" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>15</v>
       </c>
@@ -21090,7 +21154,7 @@
         <v>0.1409055153001664</v>
       </c>
     </row>
-    <row r="241" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>16</v>
       </c>
@@ -21173,7 +21237,7 @@
         <v>0.30397305276127418</v>
       </c>
     </row>
-    <row r="242" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>17</v>
       </c>
@@ -21256,7 +21320,7 @@
         <v>4.5046993759177457E-2</v>
       </c>
     </row>
-    <row r="243" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>18</v>
       </c>
@@ -21339,7 +21403,7 @@
         <v>0.32390391365270693</v>
       </c>
     </row>
-    <row r="244" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>19</v>
       </c>
@@ -21422,7 +21486,7 @@
         <v>0.4282680237144153</v>
       </c>
     </row>
-    <row r="245" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>20</v>
       </c>
@@ -21505,7 +21569,7 @@
         <v>0.23916919926553951</v>
       </c>
     </row>
-    <row r="246" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>21</v>
       </c>
@@ -21588,7 +21652,7 @@
         <v>0.15918020101075309</v>
       </c>
     </row>
-    <row r="247" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>22</v>
       </c>
@@ -21671,7 +21735,7 @@
         <v>0.13999782881396075</v>
       </c>
     </row>
-    <row r="248" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>23</v>
       </c>
@@ -21754,7 +21818,7 @@
         <v>0.2177062694678206</v>
       </c>
     </row>
-    <row r="249" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>24</v>
       </c>
@@ -21837,7 +21901,7 @@
         <v>8.1356390298202338E-2</v>
       </c>
     </row>
-    <row r="250" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>25</v>
       </c>
@@ -21920,7 +21984,7 @@
         <v>0.54700236574653105</v>
       </c>
     </row>
-    <row r="251" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>26</v>
       </c>
@@ -22003,7 +22067,7 @@
         <v>0.79601875293785451</v>
       </c>
     </row>
-    <row r="252" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>27</v>
       </c>
@@ -22086,7 +22150,7 @@
         <v>0.5197747487795592</v>
       </c>
     </row>
-    <row r="253" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>28</v>
       </c>
@@ -22169,7 +22233,7 @@
         <v>0.13006662950784589</v>
       </c>
     </row>
-    <row r="254" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>29</v>
       </c>
@@ -22252,7 +22316,7 @@
         <v>0.31997163448555177</v>
       </c>
     </row>
-    <row r="255" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>30</v>
       </c>
@@ -22335,7 +22399,7 @@
         <v>4.7345309767298761E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>31</v>
       </c>
@@ -22418,7 +22482,7 @@
         <v>0.31736040024558154</v>
       </c>
     </row>
-    <row r="257" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>32</v>
       </c>
@@ -22501,7 +22565,7 @@
         <v>0.4282680237144153</v>
       </c>
     </row>
-    <row r="258" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>1</v>
       </c>
@@ -22584,7 +22648,7 @@
         <v>0.52979124133416533</v>
       </c>
     </row>
-    <row r="259" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>2</v>
       </c>
@@ -22667,7 +22731,7 @@
         <v>0.1299988864716439</v>
       </c>
     </row>
-    <row r="260" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>3</v>
       </c>
@@ -22750,7 +22814,7 @@
         <v>0.30701278328888693</v>
       </c>
     </row>
-    <row r="261" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>4</v>
       </c>
@@ -22833,7 +22897,7 @@
         <v>4.1921283988132489E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>5</v>
       </c>
@@ -22916,7 +22980,7 @@
         <v>0.31081688683845615</v>
       </c>
     </row>
-    <row r="263" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>6</v>
       </c>
@@ -22999,7 +23063,7 @@
         <v>0.41970266324012701</v>
       </c>
     </row>
-    <row r="264" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>7</v>
       </c>
@@ -23082,7 +23146,7 @@
         <v>0.23416617009722973</v>
       </c>
     </row>
-    <row r="265" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>8</v>
       </c>
@@ -23165,7 +23229,7 @@
         <v>0.14975302405768906</v>
       </c>
     </row>
-    <row r="266" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>9</v>
       </c>
@@ -23248,7 +23312,7 @@
         <v>0.13169403602646604</v>
       </c>
     </row>
-    <row r="267" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>10</v>
       </c>
@@ -23331,7 +23395,7 @@
         <v>0.20682095599442957</v>
       </c>
     </row>
-    <row r="268" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>11</v>
       </c>
@@ -23414,7 +23478,7 @@
         <v>7.9607227906790992E-2</v>
       </c>
     </row>
-    <row r="269" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>12</v>
       </c>
@@ -23497,7 +23561,7 @@
         <v>0.51965224745920446</v>
       </c>
     </row>
-    <row r="270" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>13</v>
       </c>
@@ -23580,7 +23644,7 @@
         <v>0.76377999344387137</v>
       </c>
     </row>
-    <row r="271" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>14</v>
       </c>
@@ -23663,7 +23727,7 @@
         <v>0.52979124133416533</v>
       </c>
     </row>
-    <row r="272" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>15</v>
       </c>
@@ -23746,7 +23810,7 @@
         <v>0.13257312184732001</v>
       </c>
     </row>
-    <row r="273" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>16</v>
       </c>
@@ -23829,7 +23893,7 @@
         <v>0.30397305276127418</v>
       </c>
     </row>
-    <row r="274" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>17</v>
       </c>
@@ -23912,7 +23976,7 @@
         <v>4.1484603946589441E-2</v>
       </c>
     </row>
-    <row r="275" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>18</v>
       </c>
@@ -23995,7 +24059,7 @@
         <v>0.32324956231199442</v>
       </c>
     </row>
-    <row r="276" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>19</v>
       </c>
@@ -24078,7 +24142,7 @@
         <v>0.44968142490013607</v>
       </c>
     </row>
-    <row r="277" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>20</v>
       </c>
@@ -24161,7 +24225,7 @@
         <v>0.23648464702888547</v>
       </c>
     </row>
-    <row r="278" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>21</v>
       </c>
@@ -24244,7 +24308,7 @@
         <v>0.15122119096021541</v>
       </c>
     </row>
-    <row r="279" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>22</v>
       </c>
@@ -24327,7 +24391,7 @@
         <v>0.13169403602646604</v>
       </c>
     </row>
-    <row r="280" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>23</v>
       </c>
@@ -24410,7 +24474,7 @@
         <v>0.21748183001476099</v>
       </c>
     </row>
-    <row r="281" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>24</v>
       </c>
@@ -24493,7 +24557,7 @@
         <v>7.5742799367626373E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>25</v>
       </c>
@@ -24576,7 +24640,7 @@
         <v>0.5300452924083886</v>
       </c>
     </row>
-    <row r="283" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>26</v>
       </c>
@@ -24659,7 +24723,7 @@
         <v>0.77134217159678098</v>
       </c>
     </row>
-    <row r="284" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>27</v>
       </c>
@@ -24742,7 +24806,7 @@
         <v>0.50921682419497438</v>
       </c>
     </row>
-    <row r="285" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>28</v>
       </c>
@@ -24825,7 +24889,7 @@
         <v>0.13386023953515808</v>
       </c>
     </row>
-    <row r="286" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>29</v>
       </c>
@@ -24908,7 +24972,7 @@
         <v>0.29789359170604868</v>
       </c>
     </row>
-    <row r="287" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>30</v>
       </c>
@@ -24991,7 +25055,7 @@
         <v>4.4978044278933815E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>31</v>
       </c>
@@ -25074,7 +25138,7 @@
         <v>0.31392505570684071</v>
       </c>
     </row>
-    <row r="289" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>32</v>
       </c>
@@ -25157,7 +25221,7 @@
         <v>0.40685462252869453</v>
       </c>
     </row>
-    <row r="290" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>1</v>
       </c>
@@ -25240,7 +25304,7 @@
         <v>0.38991367175680802</v>
       </c>
     </row>
-    <row r="291" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>2</v>
       </c>
@@ -25323,7 +25387,7 @@
         <v>0.12626746373434408</v>
       </c>
     </row>
-    <row r="292" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>3</v>
       </c>
@@ -25406,7 +25470,7 @@
         <v>0.29748174575997999</v>
       </c>
     </row>
-    <row r="293" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>4</v>
       </c>
@@ -25489,7 +25553,7 @@
         <v>4.5989104722610467E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>5</v>
       </c>
@@ -25572,7 +25636,7 @@
         <v>0.29758364319182595</v>
       </c>
     </row>
-    <row r="295" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>6</v>
       </c>
@@ -25655,7 +25719,7 @@
         <v>0.46963632109024683</v>
       </c>
     </row>
-    <row r="296" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>7</v>
       </c>
@@ -25738,7 +25802,7 @@
         <v>0.23346439779015135</v>
       </c>
     </row>
-    <row r="297" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>8</v>
       </c>
@@ -25821,7 +25885,7 @@
         <v>0.1479600323897812</v>
       </c>
     </row>
-    <row r="298" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>9</v>
       </c>
@@ -25904,7 +25968,7 @@
         <v>0.14914807358193835</v>
       </c>
     </row>
-    <row r="299" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>10</v>
       </c>
@@ -25987,7 +26051,7 @@
         <v>0.21630483374172366</v>
       </c>
     </row>
-    <row r="300" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>11</v>
       </c>
@@ -26070,7 +26134,7 @@
         <v>7.7467480970060482E-2</v>
       </c>
     </row>
-    <row r="301" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>12</v>
       </c>
@@ -26153,7 +26217,7 @@
         <v>0.42050493603836914</v>
       </c>
     </row>
-    <row r="302" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>13</v>
       </c>
@@ -26236,7 +26300,7 @@
         <v>0.71913619665267769</v>
       </c>
     </row>
-    <row r="303" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>14</v>
       </c>
@@ -26319,7 +26383,7 @@
         <v>0.38462437459764404</v>
       </c>
     </row>
-    <row r="304" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>15</v>
       </c>
@@ -26402,7 +26466,7 @@
         <v>0.11771851435202564</v>
       </c>
     </row>
-    <row r="305" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>16</v>
       </c>
@@ -26485,7 +26549,7 @@
         <v>0.30105279375407817</v>
       </c>
     </row>
-    <row r="306" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>17</v>
       </c>
@@ -26568,7 +26632,7 @@
         <v>4.6766775035971847E-2</v>
       </c>
     </row>
-    <row r="307" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>18</v>
       </c>
@@ -26651,7 +26715,7 @@
         <v>0.30864966612628669</v>
       </c>
     </row>
-    <row r="308" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>19</v>
       </c>
@@ -26734,7 +26798,7 @@
         <v>0.46092865073350575</v>
       </c>
     </row>
-    <row r="309" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>20</v>
       </c>
@@ -26817,7 +26881,7 @@
         <v>0.22107520885198301</v>
       </c>
     </row>
-    <row r="310" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>21</v>
       </c>
@@ -26900,7 +26964,7 @@
         <v>0.14942932593407893</v>
       </c>
     </row>
-    <row r="311" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>22</v>
       </c>
@@ -26983,7 +27047,7 @@
         <v>0.14580624846449972</v>
       </c>
     </row>
-    <row r="312" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>23</v>
       </c>
@@ -27066,7 +27130,7 @@
         <v>0.20833483292938207</v>
       </c>
     </row>
-    <row r="313" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>24</v>
       </c>
@@ -27149,7 +27213,7 @@
         <v>7.6075164377009091E-2</v>
       </c>
     </row>
-    <row r="314" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>25</v>
       </c>
@@ -27232,7 +27296,7 @@
         <v>0.46772855744554459</v>
       </c>
     </row>
-    <row r="315" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>26</v>
       </c>
@@ -27315,7 +27379,7 @@
         <v>0.69763343251953736</v>
       </c>
     </row>
-    <row r="316" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>27</v>
       </c>
@@ -27398,7 +27462,7 @@
         <v>0.38316213563756696</v>
       </c>
     </row>
-    <row r="317" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>28</v>
       </c>
@@ -27481,7 +27545,7 @@
         <v>0.1289304828276106</v>
       </c>
     </row>
-    <row r="318" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>29</v>
       </c>
@@ -27564,7 +27628,7 @@
         <v>0.28713789806851081</v>
       </c>
     </row>
-    <row r="319" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>30</v>
       </c>
@@ -27647,7 +27711,7 @@
         <v>4.4676910970780283E-2</v>
       </c>
     </row>
-    <row r="320" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>31</v>
       </c>
@@ -27730,7 +27794,7 @@
         <v>0.30928644336699423</v>
       </c>
     </row>
-    <row r="321" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>32</v>
       </c>
@@ -27813,7 +27877,7 @@
         <v>0.45203518990861852</v>
       </c>
     </row>
-    <row r="322" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>1</v>
       </c>
@@ -27896,7 +27960,7 @@
         <v>0.37538367038182924</v>
       </c>
     </row>
-    <row r="323" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>2</v>
       </c>
@@ -27979,7 +28043,7 @@
         <v>0.12018811300212001</v>
       </c>
     </row>
-    <row r="324" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>3</v>
       </c>
@@ -28062,7 +28126,7 @@
         <v>0.28154725817896198</v>
       </c>
     </row>
-    <row r="325" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>4</v>
       </c>
@@ -28145,7 +28209,7 @@
         <v>4.6882367854616955E-2</v>
       </c>
     </row>
-    <row r="326" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>5</v>
       </c>
@@ -28228,7 +28292,7 @@
         <v>0.30259669914399334</v>
       </c>
     </row>
-    <row r="327" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>6</v>
       </c>
@@ -28311,7 +28375,7 @@
         <v>0.43565833319397973</v>
       </c>
     </row>
-    <row r="328" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>7</v>
       </c>
@@ -28394,7 +28458,7 @@
         <v>0.21772304768995185</v>
       </c>
     </row>
-    <row r="329" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>8</v>
       </c>
@@ -28477,7 +28541,7 @@
         <v>0.16035307422661751</v>
       </c>
     </row>
-    <row r="330" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>9</v>
       </c>
@@ -28560,7 +28624,7 @@
         <v>0.1386796906061204</v>
       </c>
     </row>
-    <row r="331" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>10</v>
       </c>
@@ -28643,7 +28707,7 @@
         <v>0.2130218266585143</v>
       </c>
     </row>
-    <row r="332" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>11</v>
       </c>
@@ -28726,7 +28790,7 @@
         <v>7.7051441060587519E-2</v>
       </c>
     </row>
-    <row r="333" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>12</v>
       </c>
@@ -28809,7 +28873,7 @@
         <v>0.41695009600600685</v>
       </c>
     </row>
-    <row r="334" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>13</v>
       </c>
@@ -28892,7 +28956,7 @@
         <v>0.71830057796525593</v>
       </c>
     </row>
-    <row r="335" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>14</v>
       </c>
@@ -28975,7 +29039,7 @@
         <v>0.35771485362760636</v>
       </c>
     </row>
-    <row r="336" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>15</v>
       </c>
@@ -29058,7 +29122,7 @@
         <v>0.11720366727689044</v>
       </c>
     </row>
-    <row r="337" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>16</v>
       </c>
@@ -29141,7 +29205,7 @@
         <v>0.29742669809320632</v>
       </c>
     </row>
-    <row r="338" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>17</v>
       </c>
@@ -29224,7 +29288,7 @@
         <v>4.3774702556512855E-2</v>
       </c>
     </row>
-    <row r="339" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>18</v>
       </c>
@@ -29307,7 +29371,7 @@
         <v>0.31479827545539374</v>
       </c>
     </row>
-    <row r="340" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>19</v>
       </c>
@@ -29390,7 +29454,7 @@
         <v>0.4436653899862828</v>
       </c>
     </row>
-    <row r="341" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>20</v>
       </c>
@@ -29473,7 +29537,7 @@
         <v>0.23657711677899329</v>
       </c>
     </row>
-    <row r="342" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>21</v>
       </c>
@@ -29556,7 +29620,7 @@
         <v>0.15822983535940957</v>
       </c>
     </row>
-    <row r="343" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>22</v>
       </c>
@@ -29639,7 +29703,7 @@
         <v>0.14485334106993131</v>
       </c>
     </row>
-    <row r="344" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>23</v>
       </c>
@@ -29722,7 +29786,7 @@
         <v>0.20046621042375082</v>
       </c>
     </row>
-    <row r="345" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>24</v>
       </c>
@@ -29805,7 +29869,7 @@
         <v>8.1244140608213222E-2</v>
       </c>
     </row>
-    <row r="346" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>25</v>
       </c>
@@ -29888,7 +29952,7 @@
         <v>0.42038347631675754</v>
       </c>
     </row>
-    <row r="347" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>26</v>
       </c>
@@ -29971,7 +30035,7 @@
         <v>0.76319264462658776</v>
       </c>
     </row>
-    <row r="348" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>27</v>
       </c>
@@ -30054,7 +30118,7 @@
         <v>0.40699492683503591</v>
       </c>
     </row>
-    <row r="349" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>28</v>
       </c>
@@ -30137,7 +30201,7 @@
         <v>0.12384606230212507</v>
       </c>
     </row>
-    <row r="350" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>29</v>
       </c>
@@ -30220,7 +30284,7 @@
         <v>0.29237113682890775</v>
       </c>
     </row>
-    <row r="351" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>30</v>
       </c>
@@ -30303,7 +30367,7 @@
         <v>5.043452388991345E-2</v>
       </c>
     </row>
-    <row r="352" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>31</v>
       </c>
@@ -30386,7 +30450,7 @@
         <v>0.33298126403136252</v>
       </c>
     </row>
-    <row r="353" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>32</v>
       </c>
@@ -30469,7 +30533,7 @@
         <v>0.43966360856781511</v>
       </c>
     </row>
-    <row r="354" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>1</v>
       </c>
@@ -30552,7 +30616,7 @@
         <v>0.36542259844303537</v>
       </c>
     </row>
-    <row r="355" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>2</v>
       </c>
@@ -30635,7 +30699,7 @@
         <v>0.11993956495672245</v>
       </c>
     </row>
-    <row r="356" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>3</v>
       </c>
@@ -30718,7 +30782,7 @@
         <v>0.29133395395230999</v>
       </c>
     </row>
-    <row r="357" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>4</v>
       </c>
@@ -30801,7 +30865,7 @@
         <v>4.6491627052506763E-2</v>
       </c>
     </row>
-    <row r="358" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>5</v>
       </c>
@@ -30884,7 +30948,7 @@
         <v>0.33094444964029684</v>
       </c>
     </row>
-    <row r="359" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>6</v>
       </c>
@@ -30967,7 +31031,7 @@
         <v>0.44131775373106019</v>
       </c>
     </row>
-    <row r="360" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>7</v>
       </c>
@@ -31050,7 +31114,7 @@
         <v>0.21940458410267669</v>
       </c>
     </row>
-    <row r="361" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>8</v>
       </c>
@@ -31133,7 +31197,7 @@
         <v>0.14882351390693122</v>
       </c>
     </row>
-    <row r="362" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>9</v>
       </c>
@@ -31216,7 +31280,7 @@
         <v>0.14232419957901937</v>
       </c>
     </row>
-    <row r="363" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>10</v>
       </c>
@@ -31299,7 +31363,7 @@
         <v>0.1987066051117635</v>
       </c>
     </row>
-    <row r="364" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>11</v>
       </c>
@@ -31382,7 +31446,7 @@
         <v>8.2968124911176055E-2</v>
       </c>
     </row>
-    <row r="365" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>12</v>
       </c>
@@ -31465,7 +31529,7 @@
         <v>0.44534195487828471</v>
       </c>
     </row>
-    <row r="366" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>13</v>
       </c>
@@ -31548,7 +31612,7 @@
         <v>0.72046342351678183</v>
       </c>
     </row>
-    <row r="367" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>14</v>
       </c>
@@ -31631,7 +31695,7 @@
         <v>0.3905046989223474</v>
       </c>
     </row>
-    <row r="368" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>15</v>
       </c>
@@ -31714,7 +31778,7 @@
         <v>0.12557691115573524</v>
       </c>
     </row>
-    <row r="369" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>16</v>
       </c>
@@ -31797,7 +31861,7 @@
         <v>0.29689256902968525</v>
       </c>
     </row>
-    <row r="370" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>17</v>
       </c>
@@ -31880,7 +31944,7 @@
         <v>4.5766371175294397E-2</v>
       </c>
     </row>
-    <row r="371" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>18</v>
       </c>
@@ -31963,7 +32027,7 @@
         <v>0.32149215231149958</v>
       </c>
     </row>
-    <row r="372" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>19</v>
       </c>
@@ -32046,7 +32110,7 @@
         <v>0.43026063286055011</v>
       </c>
     </row>
-    <row r="373" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>20</v>
       </c>
@@ -32129,7 +32193,7 @@
         <v>0.21739521351587132</v>
       </c>
     </row>
-    <row r="374" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>21</v>
       </c>
@@ -32212,7 +32276,7 @@
         <v>0.14757998683067833</v>
       </c>
     </row>
-    <row r="375" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>22</v>
       </c>
@@ -32295,7 +32359,7 @@
         <v>0.13246396666318053</v>
       </c>
     </row>
-    <row r="376" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>23</v>
       </c>
@@ -32378,7 +32442,7 @@
         <v>0.19190004695921983</v>
       </c>
     </row>
-    <row r="377" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>24</v>
       </c>
@@ -32461,7 +32525,7 @@
         <v>8.0102468745015948E-2</v>
       </c>
     </row>
-    <row r="378" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>25</v>
       </c>
@@ -32544,7 +32608,7 @@
         <v>0.41896012228240564</v>
       </c>
     </row>
-    <row r="379" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>26</v>
       </c>
@@ -32627,7 +32691,7 @@
         <v>0.68614524604916194</v>
       </c>
     </row>
-    <row r="380" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>27</v>
       </c>
@@ -32710,7 +32774,7 @@
         <v>0.38248935213953739</v>
       </c>
     </row>
-    <row r="381" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>28</v>
       </c>
@@ -32793,7 +32857,7 @@
         <v>0.12614241732230266</v>
       </c>
     </row>
-    <row r="382" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>29</v>
       </c>
@@ -32876,7 +32940,7 @@
         <v>0.30007397257087931</v>
       </c>
     </row>
-    <row r="383" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>30</v>
       </c>
@@ -32959,7 +33023,7 @@
         <v>4.6078634270013533E-2</v>
       </c>
     </row>
-    <row r="384" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>31</v>
       </c>
@@ -33042,7 +33106,7 @@
         <v>0.29177639938549099</v>
       </c>
     </row>
-    <row r="385" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>32</v>
       </c>
@@ -33133,9 +33197,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBB35780-D2A8-4868-BC60-ED161DD3DC9F}">
   <dimension ref="A1:AA385"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -33218,7 +33282,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -33301,7 +33365,7 @@
         <v>0.10440066304416196</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -33384,7 +33448,7 @@
         <v>-0.10503458241230207</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -33467,7 +33531,7 @@
         <v>-0.28973750613877669</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -33550,7 +33614,7 @@
         <v>-0.29715603926547057</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -33633,7 +33697,7 @@
         <v>-0.25022140873816789</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -33716,7 +33780,7 @@
         <v>0.22534376338021103</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -33799,7 +33863,7 @@
         <v>-0.22749198791228348</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -33882,7 +33946,7 @@
         <v>-0.72083640057428056</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -33965,7 +34029,7 @@
         <v>-2.726202685746134E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -34048,7 +34112,7 @@
         <v>-0.28544317332426927</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -34131,7 +34195,7 @@
         <v>-0.17665658184026775</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -34214,7 +34278,7 @@
         <v>0.29053667590828686</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -34297,7 +34361,7 @@
         <v>0.16425412952137319</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -34380,7 +34444,7 @@
         <v>0.10239295798562037</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -34463,7 +34527,7 @@
         <v>-0.10503458241230207</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -34546,7 +34610,7 @@
         <v>-0.27318107721656087</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -34629,7 +34693,7 @@
         <v>-0.32843562234604645</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -34712,7 +34776,7 @@
         <v>-0.26827862380174705</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -34795,7 +34859,7 @@
         <v>0.2392825528676468</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -34878,7 +34942,7 @@
         <v>-0.21882562646800599</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -34961,7 +35025,7 @@
         <v>-0.75118740691425023</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -35044,7 +35108,7 @@
         <v>-2.4902812994796415E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -35127,7 +35191,7 @@
         <v>-0.30309945208659528</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -35210,7 +35274,7 @@
         <v>-0.17308776200511083</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -35293,7 +35357,7 @@
         <v>0.27925369820311069</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -35376,7 +35440,7 @@
         <v>0.16267476289135999</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -35459,7 +35523,7 @@
         <v>9.9381400397808003E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -35542,7 +35606,7 @@
         <v>-0.10003293563076388</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -35625,7 +35689,7 @@
         <v>-0.27318107721656087</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -35708,7 +35772,7 @@
         <v>-0.32843562234604645</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -35791,7 +35855,7 @@
         <v>-0.25796021519398754</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -35874,7 +35938,7 @@
         <v>0.2346362897051682</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>1</v>
       </c>
@@ -35957,7 +36021,7 @@
         <v>0.10546474672518899</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2</v>
       </c>
@@ -36040,7 +36104,7 @@
         <v>-9.9942905988696193E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>3</v>
       </c>
@@ -36123,7 +36187,7 @@
         <v>-0.2842186964980381</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>4</v>
       </c>
@@ -36206,7 +36270,7 @@
         <v>-0.3060707204434347</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>5</v>
       </c>
@@ -36289,7 +36353,7 @@
         <v>-0.26569902164980719</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>6</v>
       </c>
@@ -36372,7 +36436,7 @@
         <v>0.24646102945367621</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>7</v>
       </c>
@@ -36455,7 +36519,7 @@
         <v>-0.21869563104634182</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>8</v>
       </c>
@@ -36538,7 +36602,7 @@
         <v>-0.75027687672405119</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>9</v>
       </c>
@@ -36621,7 +36685,7 @@
         <v>-2.5919896304478624E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>10</v>
       </c>
@@ -36704,7 +36768,7 @@
         <v>-0.30916144112832716</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>11</v>
       </c>
@@ -36787,7 +36851,7 @@
         <v>-0.18747010594079325</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>12</v>
       </c>
@@ -36870,7 +36934,7 @@
         <v>0.29053667590828686</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>13</v>
       </c>
@@ -36953,7 +37017,7 @@
         <v>0.15454102474679199</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>14</v>
       </c>
@@ -37036,7 +37100,7 @@
         <v>0.10753268293548682</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>15</v>
       </c>
@@ -37119,7 +37183,7 @@
         <v>-0.10715528064767427</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>16</v>
       </c>
@@ -37202,7 +37266,7 @@
         <v>-0.27284994863811657</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>17</v>
       </c>
@@ -37285,7 +37349,7 @@
         <v>-0.31895790867263196</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>18</v>
       </c>
@@ -37368,7 +37432,7 @@
         <v>-0.26038504121681105</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>19</v>
       </c>
@@ -37451,7 +37515,7 @@
         <v>0.22731842522426446</v>
       </c>
     </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>20</v>
       </c>
@@ -37534,7 +37598,7 @@
         <v>-0.22762198333394762</v>
       </c>
     </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>21</v>
       </c>
@@ -37617,7 +37681,7 @@
         <v>-0.75027687672405119</v>
       </c>
     </row>
-    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>22</v>
       </c>
@@ -37700,7 +37764,7 @@
         <v>-2.7539889823508541E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>23</v>
       </c>
@@ -37783,7 +37847,7 @@
         <v>-0.29703746304486339</v>
       </c>
     </row>
-    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>24</v>
       </c>
@@ -37866,7 +37930,7 @@
         <v>-0.17644245265015834</v>
       </c>
     </row>
-    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>25</v>
       </c>
@@ -37949,7 +38013,7 @@
         <v>0.27891520887195537</v>
       </c>
     </row>
-    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>26</v>
       </c>
@@ -38032,7 +38096,7 @@
         <v>0.16592825814918719</v>
       </c>
     </row>
-    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>27</v>
       </c>
@@ -38115,7 +38179,7 @@
         <v>0.10029490619944442</v>
       </c>
     </row>
-    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>28</v>
       </c>
@@ -38198,7 +38262,7 @@
         <v>-0.10715528064767427</v>
       </c>
     </row>
-    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>29</v>
       </c>
@@ -38281,7 +38345,7 @@
         <v>-0.27284994863811657</v>
       </c>
     </row>
-    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>30</v>
       </c>
@@ -38364,7 +38428,7 @@
         <v>-0.32217970572993126</v>
       </c>
     </row>
-    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>31</v>
       </c>
@@ -38447,7 +38511,7 @@
         <v>-0.25772805100031299</v>
       </c>
     </row>
-    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>32</v>
       </c>
@@ -38530,7 +38594,7 @@
         <v>0.23210407628161739</v>
       </c>
     </row>
-    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>1</v>
       </c>
@@ -38613,7 +38677,7 @@
         <v>0.10329642526196409</v>
       </c>
     </row>
-    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>2</v>
       </c>
@@ -38696,7 +38760,7 @@
         <v>-9.9012599687330088E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>3</v>
       </c>
@@ -38779,7 +38843,7 @@
         <v>-0.26230902222430585</v>
       </c>
     </row>
-    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4</v>
       </c>
@@ -38862,7 +38926,7 @@
         <v>-0.30347451504774686</v>
       </c>
     </row>
-    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>5</v>
       </c>
@@ -38945,7 +39009,7 @@
         <v>-0.25280101089010776</v>
       </c>
     </row>
-    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>6</v>
       </c>
@@ -39028,7 +39092,7 @@
         <v>0.23677357075990837</v>
       </c>
     </row>
-    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>7</v>
       </c>
@@ -39111,7 +39175,7 @@
         <v>-0.21869563104634185</v>
       </c>
     </row>
-    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>8</v>
       </c>
@@ -39194,7 +39258,7 @@
         <v>-0.75847164843584303</v>
       </c>
     </row>
-    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>9</v>
       </c>
@@ -39277,7 +39341,7 @@
         <v>-2.5175433263371027E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>10</v>
       </c>
@@ -39360,7 +39424,7 @@
         <v>-0.29703746304486334</v>
       </c>
     </row>
-    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>11</v>
       </c>
@@ -39443,7 +39507,7 @@
         <v>-0.17662089364191619</v>
       </c>
     </row>
-    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>12</v>
       </c>
@@ -39526,7 +39590,7 @@
         <v>0.26813996516351213</v>
       </c>
     </row>
-    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>13</v>
       </c>
@@ -39609,7 +39673,7 @@
         <v>0.14703903325422923</v>
       </c>
     </row>
-    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>14</v>
       </c>
@@ -39692,7 +39756,7 @@
         <v>9.7393772389851849E-2</v>
       </c>
     </row>
-    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>15</v>
       </c>
@@ -39775,7 +39839,7 @@
         <v>-0.10195356799487455</v>
       </c>
     </row>
-    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>16</v>
       </c>
@@ -39858,7 +39922,7 @@
         <v>-0.27853432256807731</v>
       </c>
     </row>
-    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>17</v>
       </c>
@@ -39941,7 +40005,7 @@
         <v>-0.30960531333153979</v>
       </c>
     </row>
-    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>18</v>
       </c>
@@ -40024,7 +40088,7 @@
         <v>-0.25280101089010776</v>
       </c>
     </row>
-    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>19</v>
       </c>
@@ -40107,7 +40171,7 @@
         <v>0.23222023286067936</v>
       </c>
     </row>
-    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>20</v>
       </c>
@@ -40190,7 +40254,7 @@
         <v>-0.21444911393864588</v>
       </c>
     </row>
-    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>21</v>
       </c>
@@ -40273,7 +40337,7 @@
         <v>-0.72872766222267271</v>
       </c>
     </row>
-    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>22</v>
       </c>
@@ -40356,7 +40420,7 @@
         <v>-2.5689217615684722E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>23</v>
       </c>
@@ -40439,7 +40503,7 @@
         <v>-0.29703746304486334</v>
       </c>
     </row>
-    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>24</v>
       </c>
@@ -40522,7 +40586,7 @@
         <v>-0.17137472848423552</v>
       </c>
     </row>
-    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>25</v>
       </c>
@@ -40605,7 +40669,7 @@
         <v>0.26813996516351213</v>
       </c>
     </row>
-    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>26</v>
       </c>
@@ -40688,7 +40752,7 @@
         <v>0.14703903325422923</v>
       </c>
     </row>
-    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>27</v>
       </c>
@@ -40771,7 +40835,7 @@
         <v>0.10231264978327871</v>
       </c>
     </row>
-    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>28</v>
       </c>
@@ -40854,7 +40918,7 @@
         <v>-9.6071631379785624E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>29</v>
       </c>
@@ -40937,7 +41001,7 @@
         <v>-0.27042167239619158</v>
       </c>
     </row>
-    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>30</v>
       </c>
@@ -41020,7 +41084,7 @@
         <v>-0.31573611161533266</v>
       </c>
     </row>
-    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>31</v>
       </c>
@@ -41103,7 +41167,7 @@
         <v>-0.25785703110790992</v>
       </c>
     </row>
-    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>32</v>
       </c>
@@ -41186,7 +41250,7 @@
         <v>0.22311355706222133</v>
       </c>
     </row>
-    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>1</v>
       </c>
@@ -41269,7 +41333,7 @@
         <v>0.23760749463551797</v>
       </c>
     </row>
-    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>2</v>
       </c>
@@ -41352,7 +41416,7 @@
         <v>-3.5905771033493038E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>3</v>
       </c>
@@ -41435,7 +41499,7 @@
         <v>-0.20578658689322218</v>
       </c>
     </row>
-    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>4</v>
       </c>
@@ -41518,7 +41582,7 @@
         <v>-0.28962811170780051</v>
       </c>
     </row>
-    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>5</v>
       </c>
@@ -41601,7 +41665,7 @@
         <v>-0.12389553246065828</v>
       </c>
     </row>
-    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>6</v>
       </c>
@@ -41684,7 +41748,7 @@
         <v>0.33237688508273816</v>
       </c>
     </row>
-    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>7</v>
       </c>
@@ -41767,7 +41831,7 @@
         <v>-0.15590387379103984</v>
       </c>
     </row>
-    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>8</v>
       </c>
@@ -41850,7 +41914,7 @@
         <v>-0.828655542709546</v>
       </c>
     </row>
-    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>9</v>
       </c>
@@ -41933,7 +41997,7 @@
         <v>-1.6089547589897894E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>10</v>
       </c>
@@ -42016,7 +42080,7 @@
         <v>-0.15731781796771568</v>
       </c>
     </row>
-    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>11</v>
       </c>
@@ -42099,7 +42163,7 @@
         <v>-0.13524649072189965</v>
       </c>
     </row>
-    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>12</v>
       </c>
@@ -42182,7 +42246,7 @@
         <v>0.38975295617822353</v>
       </c>
     </row>
-    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>13</v>
       </c>
@@ -42265,7 +42329,7 @@
         <v>0.18031544078576742</v>
       </c>
     </row>
-    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>14</v>
       </c>
@@ -42348,7 +42412,7 @@
         <v>0.22202818712711603</v>
       </c>
     </row>
-    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>15</v>
       </c>
@@ -42431,7 +42495,7 @@
         <v>-3.5986237224313211E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>16</v>
       </c>
@@ -42514,7 +42578,7 @@
         <v>-0.19719024690254594</v>
       </c>
     </row>
-    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>17</v>
       </c>
@@ -42597,7 +42661,7 @@
         <v>-0.26353988069316525</v>
       </c>
     </row>
-    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>18</v>
       </c>
@@ -42680,7 +42744,7 @@
         <v>-0.114817589943775</v>
       </c>
     </row>
-    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>19</v>
       </c>
@@ -42763,7 +42827,7 @@
         <v>0.34470553774825213</v>
       </c>
     </row>
-    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>20</v>
       </c>
@@ -42846,7 +42910,7 @@
         <v>-0.16614510917506134</v>
       </c>
     </row>
-    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>21</v>
       </c>
@@ -42929,7 +42993,7 @@
         <v>-0.75903892741456302</v>
       </c>
     </row>
-    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>22</v>
       </c>
@@ -43012,7 +43076,7 @@
         <v>-1.4912564087038236E-2</v>
       </c>
     </row>
-    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>23</v>
       </c>
@@ -43095,7 +43159,7 @@
         <v>-0.17396207697380037</v>
       </c>
     </row>
-    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>24</v>
       </c>
@@ -43178,7 +43242,7 @@
         <v>-0.13971909935658441</v>
       </c>
     </row>
-    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>25</v>
       </c>
@@ -43261,7 +43325,7 @@
         <v>0.40211757717383378</v>
       </c>
     </row>
-    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>26</v>
       </c>
@@ -43344,7 +43408,7 @@
         <v>0.18313533440208066</v>
       </c>
     </row>
-    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>27</v>
       </c>
@@ -43427,7 +43491,7 @@
         <v>0.22566608737329294</v>
       </c>
     </row>
-    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>28</v>
       </c>
@@ -43510,7 +43574,7 @@
         <v>-3.7456848986658464E-2</v>
       </c>
     </row>
-    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>29</v>
       </c>
@@ -43593,7 +43657,7 @@
         <v>-0.21267994555977024</v>
       </c>
     </row>
-    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>30</v>
       </c>
@@ -43676,7 +43740,7 @@
         <v>-0.2674527790746834</v>
       </c>
     </row>
-    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>31</v>
       </c>
@@ -43759,7 +43823,7 @@
         <v>-0.11245437744379867</v>
       </c>
     </row>
-    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>32</v>
       </c>
@@ -43842,7 +43906,7 @@
         <v>0.3109013348788397</v>
       </c>
     </row>
-    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>1</v>
       </c>
@@ -43925,7 +43989,7 @@
         <v>0.2307535183084562</v>
       </c>
     </row>
-    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>2</v>
       </c>
@@ -44008,7 +44072,7 @@
         <v>-3.531095206826363E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>3</v>
       </c>
@@ -44091,7 +44155,7 @@
         <v>-0.2146930384344056</v>
       </c>
     </row>
-    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>4</v>
       </c>
@@ -44174,7 +44238,7 @@
         <v>-0.2546406723509716</v>
       </c>
     </row>
-    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>5</v>
       </c>
@@ -44257,7 +44321,7 @@
         <v>-0.12220395679471781</v>
       </c>
     </row>
-    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>6</v>
       </c>
@@ -44340,7 +44404,7 @@
         <v>0.30166028657189642</v>
       </c>
     </row>
-    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>7</v>
       </c>
@@ -44423,7 +44487,7 @@
         <v>-0.18167805818432164</v>
       </c>
     </row>
-    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>8</v>
       </c>
@@ -44506,7 +44570,7 @@
         <v>-0.73052453371612514</v>
       </c>
     </row>
-    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>9</v>
       </c>
@@ -44589,7 +44653,7 @@
         <v>-1.5009826760444123E-2</v>
       </c>
     </row>
-    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>10</v>
       </c>
@@ -44672,7 +44736,7 @@
         <v>-0.15860070411137861</v>
       </c>
     </row>
-    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>11</v>
       </c>
@@ -44755,7 +44819,7 @@
         <v>-0.13730456798862051</v>
       </c>
     </row>
-    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>12</v>
       </c>
@@ -44838,7 +44902,7 @@
         <v>0.36839082356962832</v>
       </c>
     </row>
-    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>13</v>
       </c>
@@ -44921,7 +44985,7 @@
         <v>0.18245761903417482</v>
       </c>
     </row>
-    <row r="143" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>14</v>
       </c>
@@ -45004,7 +45068,7 @@
         <v>0.22742473480474143</v>
       </c>
     </row>
-    <row r="144" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>15</v>
       </c>
@@ -45087,7 +45151,7 @@
         <v>-3.2943145724916648E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>16</v>
       </c>
@@ -45170,7 +45234,7 @@
         <v>-0.22637920635014494</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>17</v>
       </c>
@@ -45253,7 +45317,7 @@
         <v>-0.26054650878898294</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>18</v>
       </c>
@@ -45336,7 +45400,7 @@
         <v>-0.11699798865364913</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>19</v>
       </c>
@@ -45419,7 +45483,7 @@
         <v>0.34963630090064257</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>20</v>
       </c>
@@ -45502,7 +45566,7 @@
         <v>-0.17279007194861853</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>21</v>
       </c>
@@ -45585,7 +45649,7 @@
         <v>-0.78430854703951447</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>22</v>
       </c>
@@ -45668,7 +45732,7 @@
         <v>-1.5923976692796063E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>23</v>
       </c>
@@ -45751,7 +45815,7 @@
         <v>-0.16803320521638915</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>24</v>
       </c>
@@ -45834,7 +45898,7 @@
         <v>-0.13354300735013738</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>25</v>
       </c>
@@ -45917,7 +45981,7 @@
         <v>0.40066736701528766</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>26</v>
       </c>
@@ -46000,7 +46064,7 @@
         <v>0.18382947054603144</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>27</v>
       </c>
@@ -46083,7 +46147,7 @@
         <v>0.2406992658908256</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>28</v>
       </c>
@@ -46166,7 +46230,7 @@
         <v>-3.5585336327689121E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>29</v>
       </c>
@@ -46249,7 +46313,7 @@
         <v>-0.20896388103592764</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>30</v>
       </c>
@@ -46332,7 +46396,7 @@
         <v>-0.27406735598634852</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>31</v>
       </c>
@@ -46415,7 +46479,7 @@
         <v>-0.11233777161752428</v>
       </c>
     </row>
-    <row r="161" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>32</v>
       </c>
@@ -46498,7 +46562,7 @@
         <v>0.32548686065234889</v>
       </c>
     </row>
-    <row r="162" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>1</v>
       </c>
@@ -46581,7 +46645,7 @@
         <v>0.21888830163862186</v>
       </c>
     </row>
-    <row r="163" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>2</v>
       </c>
@@ -46664,7 +46728,7 @@
         <v>-3.5272270856435729E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>3</v>
       </c>
@@ -46747,7 +46811,7 @@
         <v>-0.20031496104475072</v>
       </c>
     </row>
-    <row r="165" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>4</v>
       </c>
@@ -46830,7 +46894,7 @@
         <v>-0.28323005944518853</v>
       </c>
     </row>
-    <row r="166" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>5</v>
       </c>
@@ -46913,7 +46977,7 @@
         <v>-0.12143617811566067</v>
       </c>
     </row>
-    <row r="167" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>6</v>
       </c>
@@ -46996,7 +47060,7 @@
         <v>0.33277688952051449</v>
       </c>
     </row>
-    <row r="168" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>7</v>
       </c>
@@ -47079,7 +47143,7 @@
         <v>-0.16502112180551265</v>
       </c>
     </row>
-    <row r="169" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>8</v>
       </c>
@@ -47162,7 +47226,7 @@
         <v>-0.80624253037920024</v>
       </c>
     </row>
-    <row r="170" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>9</v>
       </c>
@@ -47245,7 +47309,7 @@
         <v>-1.5421612694464655E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>10</v>
       </c>
@@ -47328,7 +47392,7 @@
         <v>-0.16208131145492288</v>
       </c>
     </row>
-    <row r="172" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>11</v>
       </c>
@@ -47411,7 +47475,7 @@
         <v>-0.13091245446272495</v>
       </c>
     </row>
-    <row r="173" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>12</v>
       </c>
@@ -47494,7 +47558,7 @@
         <v>0.35947356602414998</v>
       </c>
     </row>
-    <row r="174" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>13</v>
       </c>
@@ -47577,7 +47641,7 @@
         <v>0.16985537032829737</v>
       </c>
     </row>
-    <row r="175" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>14</v>
       </c>
@@ -47660,7 +47724,7 @@
         <v>0.22507598645748134</v>
       </c>
     </row>
-    <row r="176" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>15</v>
       </c>
@@ -47743,7 +47807,7 @@
         <v>-3.1997908184051932E-2</v>
       </c>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>16</v>
       </c>
@@ -47826,7 +47890,7 @@
         <v>-0.20988415174255701</v>
       </c>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>17</v>
       </c>
@@ -47909,7 +47973,7 @@
         <v>-0.2796749754294815</v>
       </c>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>18</v>
       </c>
@@ -47992,7 +48056,7 @@
         <v>-0.11288777572189508</v>
       </c>
     </row>
-    <row r="180" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>19</v>
       </c>
@@ -48075,7 +48139,7 @@
         <v>0.32229740285695407</v>
       </c>
     </row>
-    <row r="181" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>20</v>
       </c>
@@ -48158,7 +48222,7 @@
         <v>-0.16773482769106485</v>
       </c>
     </row>
-    <row r="182" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>21</v>
       </c>
@@ -48241,7 +48305,7 @@
         <v>-0.82928999105755041</v>
       </c>
     </row>
-    <row r="183" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>22</v>
       </c>
@@ -48324,7 +48388,7 @@
         <v>-1.4860788120205935E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>23</v>
       </c>
@@ -48407,7 +48471,7 @@
         <v>-0.16161192709571529</v>
       </c>
     </row>
-    <row r="185" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>24</v>
       </c>
@@ -48490,7 +48554,7 @@
         <v>-0.13035772393242473</v>
       </c>
     </row>
-    <row r="186" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>25</v>
       </c>
@@ -48573,7 +48637,7 @@
         <v>0.36650325620326013</v>
       </c>
     </row>
-    <row r="187" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>26</v>
       </c>
@@ -48656,7 +48720,7 @@
         <v>0.19318789433785161</v>
       </c>
     </row>
-    <row r="188" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>27</v>
       </c>
@@ -48739,7 +48803,7 @@
         <v>0.22473047552438052</v>
       </c>
     </row>
-    <row r="189" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>28</v>
       </c>
@@ -48822,7 +48886,7 @@
         <v>-3.206094483016203E-2</v>
       </c>
     </row>
-    <row r="190" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>29</v>
       </c>
@@ -48905,7 +48969,7 @@
         <v>-0.20327853343157756</v>
       </c>
     </row>
-    <row r="191" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>30</v>
       </c>
@@ -48988,7 +49052,7 @@
         <v>-0.26648446469407749</v>
       </c>
     </row>
-    <row r="192" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>31</v>
       </c>
@@ -49071,7 +49135,7 @@
         <v>-0.1122573573137703</v>
       </c>
     </row>
-    <row r="193" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>32</v>
       </c>
@@ -49154,7 +49218,7 @@
         <v>0.33023862951028665</v>
       </c>
     </row>
-    <row r="194" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>1</v>
       </c>
@@ -49237,7 +49301,7 @@
         <v>0.34129538164225937</v>
       </c>
     </row>
-    <row r="195" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>2</v>
       </c>
@@ -49320,7 +49384,7 @@
         <v>5.3833481319321141E-3</v>
       </c>
     </row>
-    <row r="196" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>3</v>
       </c>
@@ -49403,7 +49467,7 @@
         <v>-0.178702442907301</v>
       </c>
     </row>
-    <row r="197" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>4</v>
       </c>
@@ -49486,7 +49550,7 @@
         <v>-0.25843427198662428</v>
       </c>
     </row>
-    <row r="198" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>5</v>
       </c>
@@ -49569,7 +49633,7 @@
         <v>-3.3323073312274763E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>6</v>
       </c>
@@ -49652,7 +49716,7 @@
         <v>0.40320032542354517</v>
       </c>
     </row>
-    <row r="200" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>7</v>
       </c>
@@ -49735,7 +49799,7 @@
         <v>-0.15263910926371257</v>
       </c>
     </row>
-    <row r="201" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>8</v>
       </c>
@@ -49818,7 +49882,7 @@
         <v>-0.82565871664279178</v>
       </c>
     </row>
-    <row r="202" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>9</v>
       </c>
@@ -49901,7 +49965,7 @@
         <v>-9.0170305740912161E-3</v>
       </c>
     </row>
-    <row r="203" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>10</v>
       </c>
@@ -49984,7 +50048,7 @@
         <v>-8.9625737462220023E-2</v>
       </c>
     </row>
-    <row r="204" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>11</v>
       </c>
@@ -50067,7 +50131,7 @@
         <v>-0.12162824610174412</v>
       </c>
     </row>
-    <row r="205" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>12</v>
       </c>
@@ -50150,7 +50214,7 @@
         <v>0.46297428949727881</v>
       </c>
     </row>
-    <row r="206" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>13</v>
       </c>
@@ -50233,7 +50297,7 @@
         <v>0.20938376872673248</v>
       </c>
     </row>
-    <row r="207" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>14</v>
       </c>
@@ -50316,7 +50380,7 @@
         <v>0.32791124902883739</v>
       </c>
     </row>
-    <row r="208" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>15</v>
       </c>
@@ -50399,7 +50463,7 @@
         <v>5.6053418693313766E-3</v>
       </c>
     </row>
-    <row r="209" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>16</v>
       </c>
@@ -50482,7 +50546,7 @@
         <v>-0.18246459960008629</v>
       </c>
     </row>
-    <row r="210" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>17</v>
       </c>
@@ -50565,7 +50629,7 @@
         <v>-0.25316010317057075</v>
       </c>
     </row>
-    <row r="211" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>18</v>
       </c>
@@ -50648,7 +50712,7 @@
         <v>-3.0784172488482395E-2</v>
       </c>
     </row>
-    <row r="212" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>19</v>
       </c>
@@ -50731,7 +50795,7 @@
         <v>0.42377177059821586</v>
       </c>
     </row>
-    <row r="213" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>20</v>
       </c>
@@ -50814,7 +50878,7 @@
         <v>-0.14522944376547409</v>
       </c>
     </row>
-    <row r="214" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>21</v>
       </c>
@@ -50897,7 +50961,7 @@
         <v>-0.8686617748012706</v>
       </c>
     </row>
-    <row r="215" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>22</v>
       </c>
@@ -50980,7 +51044,7 @@
         <v>-8.7569239229155077E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>23</v>
       </c>
@@ -51063,7 +51127,7 @@
         <v>-9.6027575852378602E-2</v>
       </c>
     </row>
-    <row r="217" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>24</v>
       </c>
@@ -51146,7 +51210,7 @@
         <v>-0.11461123190356658</v>
       </c>
     </row>
-    <row r="218" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>25</v>
       </c>
@@ -51229,7 +51293,7 @@
         <v>0.49604388160422735</v>
       </c>
     </row>
-    <row r="219" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>26</v>
       </c>
@@ -51312,7 +51376,7 @@
         <v>0.20523755548461897</v>
       </c>
     </row>
-    <row r="220" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>27</v>
       </c>
@@ -51395,7 +51459,7 @@
         <v>0.32791124902883739</v>
       </c>
     </row>
-    <row r="221" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>28</v>
       </c>
@@ -51478,7 +51542,7 @@
         <v>5.6608403036811925E-3</v>
       </c>
     </row>
-    <row r="222" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>29</v>
       </c>
@@ -51561,7 +51625,7 @@
         <v>-0.19751322637122745</v>
       </c>
     </row>
-    <row r="223" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>30</v>
       </c>
@@ -51644,7 +51708,7 @@
         <v>-0.27425677843478496</v>
       </c>
     </row>
-    <row r="224" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>31</v>
       </c>
@@ -51727,7 +51791,7 @@
         <v>-3.0784172488482395E-2</v>
       </c>
     </row>
-    <row r="225" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>32</v>
       </c>
@@ -51810,7 +51874,7 @@
         <v>0.4196574815632817</v>
       </c>
     </row>
-    <row r="226" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>1</v>
       </c>
@@ -51893,7 +51957,7 @@
         <v>0.34119500064765867</v>
       </c>
     </row>
-    <row r="227" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>2</v>
       </c>
@@ -51976,7 +52040,7 @@
         <v>5.4876851885097668E-3</v>
       </c>
     </row>
-    <row r="228" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>3</v>
       </c>
@@ -52059,7 +52123,7 @@
         <v>-0.19181355898165775</v>
       </c>
     </row>
-    <row r="229" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>4</v>
       </c>
@@ -52142,7 +52206,7 @@
         <v>-0.28248448178782853</v>
       </c>
     </row>
-    <row r="230" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>5</v>
       </c>
@@ -52225,7 +52289,7 @@
         <v>-3.1053930701010334E-2</v>
       </c>
     </row>
-    <row r="231" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>6</v>
       </c>
@@ -52308,7 +52372,7 @@
         <v>0.43648492371616232</v>
       </c>
     </row>
-    <row r="232" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>7</v>
       </c>
@@ -52391,7 +52455,7 @@
         <v>-0.15569189144898682</v>
       </c>
     </row>
-    <row r="233" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>8</v>
       </c>
@@ -52474,7 +52538,7 @@
         <v>-0.92129751798724857</v>
       </c>
     </row>
-    <row r="234" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>9</v>
       </c>
@@ -52557,7 +52621,7 @@
         <v>-8.4838119391810133E-3</v>
       </c>
     </row>
-    <row r="235" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>10</v>
       </c>
@@ -52640,7 +52704,7 @@
         <v>-9.6082448752865673E-2</v>
       </c>
     </row>
-    <row r="236" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>11</v>
       </c>
@@ -52723,7 +52787,7 @@
         <v>-0.12166333117273501</v>
       </c>
     </row>
-    <row r="237" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>12</v>
       </c>
@@ -52806,7 +52870,7 @@
         <v>0.46713160964786665</v>
       </c>
     </row>
-    <row r="238" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>13</v>
       </c>
@@ -52889,7 +52953,7 @@
         <v>0.21780058160822294</v>
       </c>
     </row>
-    <row r="239" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>14</v>
       </c>
@@ -52972,7 +53036,7 @@
         <v>0.33774858649970252</v>
       </c>
     </row>
-    <row r="240" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>15</v>
       </c>
@@ -53055,7 +53119,7 @@
         <v>5.4876851885097668E-3</v>
       </c>
     </row>
-    <row r="241" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>16</v>
       </c>
@@ -53138,7 +53202,7 @@
         <v>-0.19375106967844216</v>
       </c>
     </row>
-    <row r="242" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>17</v>
       </c>
@@ -53221,7 +53285,7 @@
         <v>-0.26618730014622299</v>
       </c>
     </row>
-    <row r="243" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>18</v>
       </c>
@@ -53304,7 +53368,7 @@
         <v>-3.1707697663136865E-2</v>
       </c>
     </row>
-    <row r="244" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>19</v>
       </c>
@@ -53387,7 +53451,7 @@
         <v>0.43648492371616232</v>
       </c>
     </row>
-    <row r="245" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>20</v>
       </c>
@@ -53470,7 +53534,7 @@
         <v>-0.14653354489316406</v>
       </c>
     </row>
-    <row r="246" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>21</v>
       </c>
@@ -53553,7 +53617,7 @@
         <v>-0.93015614796789525</v>
       </c>
     </row>
-    <row r="247" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>22</v>
       </c>
@@ -53636,7 +53700,7 @@
         <v>-8.4838119391810133E-3</v>
       </c>
     </row>
-    <row r="248" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>23</v>
       </c>
@@ -53719,7 +53783,7 @@
         <v>-9.7024433544560432E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>24</v>
       </c>
@@ -53802,7 +53866,7 @@
         <v>-0.12407250604744263</v>
       </c>
     </row>
-    <row r="250" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>25</v>
       </c>
@@ -53885,7 +53949,7 @@
         <v>0.49632733525085837</v>
       </c>
     </row>
-    <row r="251" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>26</v>
       </c>
@@ -53968,7 +54032,7 @@
         <v>0.21352998196884601</v>
       </c>
     </row>
-    <row r="252" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>27</v>
       </c>
@@ -54051,7 +54115,7 @@
         <v>0.3549806572394833</v>
       </c>
     </row>
-    <row r="253" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>28</v>
       </c>
@@ -54134,7 +54198,7 @@
         <v>5.8878289001719382E-3</v>
       </c>
     </row>
-    <row r="254" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>29</v>
       </c>
@@ -54217,7 +54281,7 @@
         <v>-0.19181355898165775</v>
       </c>
     </row>
-    <row r="255" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>30</v>
       </c>
@@ -54300,7 +54364,7 @@
         <v>-0.28248448178782853</v>
       </c>
     </row>
-    <row r="256" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>31</v>
       </c>
@@ -54383,7 +54447,7 @@
         <v>-3.33421150684532E-2</v>
       </c>
     </row>
-    <row r="257" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>32</v>
       </c>
@@ -54466,7 +54530,7 @@
         <v>0.4068208997742872</v>
       </c>
     </row>
-    <row r="258" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>1</v>
       </c>
@@ -54549,7 +54613,7 @@
         <v>0.33446947400941418</v>
       </c>
     </row>
-    <row r="259" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>2</v>
       </c>
@@ -54632,7 +54696,7 @@
         <v>5.6042319006443797E-3</v>
       </c>
     </row>
-    <row r="260" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>3</v>
       </c>
@@ -54715,7 +54779,7 @@
         <v>-0.182276491765447</v>
       </c>
     </row>
-    <row r="261" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>4</v>
       </c>
@@ -54798,7 +54862,7 @@
         <v>-0.27699934621913286</v>
       </c>
     </row>
-    <row r="262" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>5</v>
       </c>
@@ -54881,7 +54945,7 @@
         <v>-3.2361464625263403E-2</v>
       </c>
     </row>
-    <row r="263" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>6</v>
       </c>
@@ -54964,7 +55028,7 @@
         <v>0.39908603638861101</v>
       </c>
     </row>
-    <row r="264" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>7</v>
       </c>
@@ -55047,7 +55111,7 @@
         <v>-0.15115717616406488</v>
       </c>
     </row>
-    <row r="265" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>8</v>
       </c>
@@ -55130,7 +55194,7 @@
         <v>-0.80914554230993596</v>
       </c>
     </row>
-    <row r="266" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>9</v>
       </c>
@@ -55213,7 +55277,7 @@
         <v>-8.406646965998887E-3</v>
       </c>
     </row>
-    <row r="267" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>10</v>
       </c>
@@ -55296,7 +55360,7 @@
         <v>-8.7824077229561093E-2</v>
       </c>
     </row>
-    <row r="268" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>11</v>
       </c>
@@ -55379,7 +55443,7 @@
         <v>-0.12048213378270846</v>
       </c>
     </row>
-    <row r="269" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>12</v>
       </c>
@@ -55462,7 +55526,7 @@
         <v>0.46769851694112857</v>
       </c>
     </row>
-    <row r="270" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>13</v>
       </c>
@@ -55545,7 +55609,7 @@
         <v>0.1970280532652342</v>
       </c>
     </row>
-    <row r="271" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>14</v>
       </c>
@@ -55628,7 +55692,7 @@
         <v>0.33125728218219291</v>
       </c>
     </row>
-    <row r="272" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>15</v>
       </c>
@@ -55711,7 +55775,7 @@
         <v>5.6042319006443797E-3</v>
       </c>
     </row>
-    <row r="273" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>16</v>
       </c>
@@ -55794,7 +55858,7 @@
         <v>-0.18611389159208799</v>
       </c>
     </row>
-    <row r="274" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>17</v>
       </c>
@@ -55877,7 +55941,7 @@
         <v>-0.25068124382702556</v>
       </c>
     </row>
-    <row r="275" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>18</v>
       </c>
@@ -55960,7 +56024,7 @@
         <v>-3.2688348106326669E-2</v>
       </c>
     </row>
-    <row r="276" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>19</v>
       </c>
@@ -56043,7 +56107,7 @@
         <v>0.39497174735367691</v>
       </c>
     </row>
-    <row r="277" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>20</v>
       </c>
@@ -56126,7 +56190,7 @@
         <v>-0.148178490633773</v>
       </c>
     </row>
-    <row r="278" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>21</v>
       </c>
@@ -56209,7 +56273,7 @@
         <v>-0.85971713870430699</v>
       </c>
     </row>
-    <row r="279" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>22</v>
       </c>
@@ -56292,7 +56356,7 @@
         <v>-8.6667536171745954E-3</v>
       </c>
     </row>
-    <row r="280" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>23</v>
       </c>
@@ -56375,7 +56439,7 @@
         <v>-8.8674607187110732E-2</v>
       </c>
     </row>
-    <row r="281" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>24</v>
       </c>
@@ -56458,7 +56522,7 @@
         <v>-0.1134651195845309</v>
       </c>
     </row>
-    <row r="282" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>25</v>
       </c>
@@ -56541,7 +56605,7 @@
         <v>0.46741506329449761</v>
       </c>
     </row>
-    <row r="283" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>26</v>
       </c>
@@ -56624,7 +56688,7 @@
         <v>0.20731066210567572</v>
       </c>
     </row>
-    <row r="284" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>27</v>
       </c>
@@ -56707,7 +56771,7 @@
         <v>0.33105652019299159</v>
       </c>
     </row>
-    <row r="285" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>28</v>
       </c>
@@ -56790,7 +56854,7 @@
         <v>5.6042319006443797E-3</v>
       </c>
     </row>
-    <row r="286" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>29</v>
       </c>
@@ -56873,7 +56937,7 @@
         <v>-0.18434567794647894</v>
       </c>
     </row>
-    <row r="287" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>30</v>
       </c>
@@ -56956,7 +57020,7 @@
         <v>-0.25068124382702556</v>
       </c>
     </row>
-    <row r="288" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>31</v>
       </c>
@@ -57039,7 +57103,7 @@
         <v>-3.265661184602927E-2</v>
       </c>
     </row>
-    <row r="289" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>32</v>
       </c>
@@ -57122,7 +57186,7 @@
         <v>0.41126433193201606</v>
       </c>
     </row>
-    <row r="290" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>1</v>
       </c>
@@ -57205,7 +57269,7 @@
         <v>0.19741312877482328</v>
       </c>
     </row>
-    <row r="291" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>2</v>
       </c>
@@ -57288,7 +57352,7 @@
         <v>-5.5509142443077385E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>3</v>
       </c>
@@ -57371,7 +57435,7 @@
         <v>-0.23134604557356478</v>
       </c>
     </row>
-    <row r="293" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>4</v>
       </c>
@@ -57454,7 +57518,7 @@
         <v>-0.25544176041861333</v>
       </c>
     </row>
-    <row r="294" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>5</v>
       </c>
@@ -57537,7 +57601,7 @@
         <v>-0.16270967775809597</v>
       </c>
     </row>
-    <row r="295" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>6</v>
       </c>
@@ -57620,7 +57684,7 @@
         <v>0.28175225412934646</v>
       </c>
     </row>
-    <row r="296" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>7</v>
       </c>
@@ -57703,7 +57767,7 @@
         <v>-0.16598751427602706</v>
       </c>
     </row>
-    <row r="297" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>8</v>
       </c>
@@ -57786,7 +57850,7 @@
         <v>-0.78959093885493115</v>
       </c>
     </row>
-    <row r="298" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>9</v>
       </c>
@@ -57869,7 +57933,7 @@
         <v>-1.7461412185552319E-2</v>
       </c>
     </row>
-    <row r="299" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>10</v>
       </c>
@@ -57952,7 +58016,7 @@
         <v>-0.20535899678772981</v>
       </c>
     </row>
-    <row r="300" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>11</v>
       </c>
@@ -58035,7 +58099,7 @@
         <v>-0.15839849252461777</v>
       </c>
     </row>
-    <row r="301" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>12</v>
       </c>
@@ -58118,7 +58182,7 @@
         <v>0.35245854912687019</v>
       </c>
     </row>
-    <row r="302" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>13</v>
       </c>
@@ -58201,7 +58265,7 @@
         <v>0.16081225716204761</v>
       </c>
     </row>
-    <row r="303" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>14</v>
       </c>
@@ -58284,7 +58348,7 @@
         <v>0.18153397104662145</v>
       </c>
     </row>
-    <row r="304" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>15</v>
       </c>
@@ -58367,7 +58431,7 @@
         <v>-5.3909329683069378E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>16</v>
       </c>
@@ -58450,7 +58514,7 @@
         <v>-0.23080100618241389</v>
       </c>
     </row>
-    <row r="306" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>17</v>
       </c>
@@ -58533,7 +58597,7 @@
         <v>-0.27885065903039274</v>
       </c>
     </row>
-    <row r="307" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>18</v>
       </c>
@@ -58616,7 +58680,7 @@
         <v>-0.16569544452305959</v>
       </c>
     </row>
-    <row r="308" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>19</v>
       </c>
@@ -58699,7 +58763,7 @@
         <v>0.28621185639236219</v>
       </c>
     </row>
-    <row r="309" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>20</v>
       </c>
@@ -58782,7 +58846,7 @@
         <v>-0.17556626662073285</v>
       </c>
     </row>
-    <row r="310" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>21</v>
       </c>
@@ -58865,7 +58929,7 @@
         <v>-0.81163218696209283</v>
       </c>
     </row>
-    <row r="311" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>22</v>
       </c>
@@ -58948,7 +59012,7 @@
         <v>-1.8636473990565453E-2</v>
       </c>
     </row>
-    <row r="312" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>23</v>
       </c>
@@ -59031,7 +59095,7 @@
         <v>-0.20315565508373407</v>
       </c>
     </row>
-    <row r="313" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>24</v>
       </c>
@@ -59114,7 +59178,7 @@
         <v>-0.1452795221048481</v>
       </c>
     </row>
-    <row r="314" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>25</v>
       </c>
@@ -59197,7 +59261,7 @@
         <v>0.33261161368040337</v>
       </c>
     </row>
-    <row r="315" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>26</v>
       </c>
@@ -59280,7 +59344,7 @@
         <v>0.15937158615163902</v>
       </c>
     </row>
-    <row r="316" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>27</v>
       </c>
@@ -59363,7 +59427,7 @@
         <v>0.18582768868086444</v>
       </c>
     </row>
-    <row r="317" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>28</v>
       </c>
@@ -59446,7 +59510,7 @@
         <v>-5.5020829672942043E-2</v>
       </c>
     </row>
-    <row r="318" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>29</v>
       </c>
@@ -59529,7 +59593,7 @@
         <v>-0.23222911792352124</v>
       </c>
     </row>
-    <row r="319" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>30</v>
       </c>
@@ -59612,7 +59676,7 @@
         <v>-0.30671134309338133</v>
       </c>
     </row>
-    <row r="320" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>31</v>
       </c>
@@ -59695,7 +59759,7 @@
         <v>-0.14803193051300698</v>
       </c>
     </row>
-    <row r="321" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>32</v>
       </c>
@@ -59778,7 +59842,7 @@
         <v>0.28914801574595983</v>
       </c>
     </row>
-    <row r="322" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>1</v>
       </c>
@@ -59861,7 +59925,7 @@
         <v>0.17598171361019971</v>
       </c>
     </row>
-    <row r="323" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>2</v>
       </c>
@@ -59944,7 +60008,7 @@
         <v>-4.9841411421543011E-2</v>
       </c>
     </row>
-    <row r="324" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>3</v>
       </c>
@@ -60027,7 +60091,7 @@
         <v>-0.22467411938961626</v>
       </c>
     </row>
-    <row r="325" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>4</v>
       </c>
@@ -60110,7 +60174,7 @@
         <v>-0.26521910394337467</v>
       </c>
     </row>
-    <row r="326" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>5</v>
       </c>
@@ -60193,7 +60257,7 @@
         <v>-0.15892035534779669</v>
       </c>
     </row>
-    <row r="327" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>6</v>
       </c>
@@ -60276,7 +60340,7 @@
         <v>0.28807906682082157</v>
       </c>
     </row>
-    <row r="328" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>7</v>
       </c>
@@ -60359,7 +60423,7 @@
         <v>-0.18183163125384061</v>
       </c>
     </row>
-    <row r="329" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>8</v>
       </c>
@@ -60442,7 +60506,7 @@
         <v>-0.77397826887815169</v>
       </c>
     </row>
-    <row r="330" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>9</v>
       </c>
@@ -60525,7 +60589,7 @@
         <v>-1.7694522489840651E-2</v>
       </c>
     </row>
-    <row r="331" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>10</v>
       </c>
@@ -60608,7 +60672,7 @@
         <v>-0.21201497421934132</v>
       </c>
     </row>
-    <row r="332" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>11</v>
       </c>
@@ -60691,7 +60755,7 @@
         <v>-0.14546822093702438</v>
       </c>
     </row>
-    <row r="333" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>12</v>
       </c>
@@ -60774,7 +60838,7 @@
         <v>0.33574541709400801</v>
       </c>
     </row>
-    <row r="334" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>13</v>
       </c>
@@ -60857,7 +60921,7 @@
         <v>0.17012409886981447</v>
       </c>
     </row>
-    <row r="335" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>14</v>
       </c>
@@ -60940,7 +61004,7 @@
         <v>0.19069977867171825</v>
       </c>
     </row>
-    <row r="336" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>15</v>
       </c>
@@ -61023,7 +61087,7 @@
         <v>-5.7210265799620144E-2</v>
       </c>
     </row>
-    <row r="337" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>16</v>
       </c>
@@ -61106,7 +61170,7 @@
         <v>-0.21563720722343019</v>
       </c>
     </row>
-    <row r="338" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>17</v>
       </c>
@@ -61189,7 +61253,7 @@
         <v>-0.26837877793199727</v>
       </c>
     </row>
-    <row r="339" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>18</v>
       </c>
@@ -61272,7 +61336,7 @@
         <v>-0.14771910888517525</v>
       </c>
     </row>
-    <row r="340" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>19</v>
       </c>
@@ -61355,7 +61419,7 @@
         <v>0.28083148365021204</v>
       </c>
     </row>
-    <row r="341" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>20</v>
       </c>
@@ -61438,7 +61502,7 @@
         <v>-0.17585624758952306</v>
       </c>
     </row>
-    <row r="342" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>21</v>
       </c>
@@ -61521,7 +61585,7 @@
         <v>-0.78804596031672758</v>
       </c>
     </row>
-    <row r="343" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>22</v>
       </c>
@@ -61604,7 +61668,7 @@
         <v>-1.835223675063001E-2</v>
       </c>
     </row>
-    <row r="344" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>23</v>
       </c>
@@ -61687,7 +61751,7 @@
         <v>-0.21786598903212359</v>
       </c>
     </row>
-    <row r="345" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>24</v>
       </c>
@@ -61770,7 +61834,7 @@
         <v>-0.14572406395195864</v>
       </c>
     </row>
-    <row r="346" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>25</v>
       </c>
@@ -61853,7 +61917,7 @@
         <v>0.31752753790946048</v>
       </c>
     </row>
-    <row r="347" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>26</v>
       </c>
@@ -61936,7 +62000,7 @@
         <v>0.17169500899641987</v>
       </c>
     </row>
-    <row r="348" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>27</v>
       </c>
@@ -62019,7 +62083,7 @@
         <v>0.18796596099810325</v>
       </c>
     </row>
-    <row r="349" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>28</v>
       </c>
@@ -62102,7 +62166,7 @@
         <v>-5.952263758544904E-2</v>
       </c>
     </row>
-    <row r="350" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>29</v>
       </c>
@@ -62185,7 +62249,7 @@
         <v>-0.23767692657785158</v>
       </c>
     </row>
-    <row r="351" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>30</v>
       </c>
@@ -62268,7 +62332,7 @@
         <v>-0.28650404464498619</v>
       </c>
     </row>
-    <row r="352" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>31</v>
       </c>
@@ -62351,7 +62415,7 @@
         <v>-0.15915432150812536</v>
       </c>
     </row>
-    <row r="353" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>32</v>
       </c>
@@ -62434,7 +62498,7 @@
         <v>0.2731966527474296</v>
       </c>
     </row>
-    <row r="354" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>1</v>
       </c>
@@ -62517,7 +62581,7 @@
         <v>0.19501476988237185</v>
       </c>
     </row>
-    <row r="355" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>2</v>
       </c>
@@ -62600,7 +62664,7 @@
         <v>-5.0348330939479588E-2</v>
       </c>
     </row>
-    <row r="356" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>3</v>
       </c>
@@ -62683,7 +62747,7 @@
         <v>-0.22990682674428603</v>
       </c>
     </row>
-    <row r="357" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>4</v>
       </c>
@@ -62766,7 +62830,7 @@
         <v>-0.28824220798069622</v>
       </c>
     </row>
-    <row r="358" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>5</v>
       </c>
@@ -62849,7 +62913,7 @@
         <v>-0.16801064454174258</v>
       </c>
     </row>
-    <row r="359" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>6</v>
       </c>
@@ -62932,7 +62996,7 @@
         <v>0.28146715869081351</v>
       </c>
     </row>
-    <row r="360" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>7</v>
       </c>
@@ -63015,7 +63079,7 @@
         <v>-0.19289441956836567</v>
       </c>
     </row>
-    <row r="361" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>8</v>
       </c>
@@ -63098,7 +63162,7 @@
         <v>-0.69388881502398359</v>
       </c>
     </row>
-    <row r="362" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>9</v>
       </c>
@@ -63181,7 +63245,7 @@
         <v>-1.9607210627353693E-2</v>
       </c>
     </row>
-    <row r="363" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>10</v>
       </c>
@@ -63264,7 +63328,7 @@
         <v>-0.20218513468733235</v>
       </c>
     </row>
-    <row r="364" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>11</v>
       </c>
@@ -63347,7 +63411,7 @@
         <v>-0.15405864171055272</v>
       </c>
     </row>
-    <row r="365" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>12</v>
       </c>
@@ -63430,7 +63494,7 @@
         <v>0.35124673238676496</v>
       </c>
     </row>
-    <row r="366" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>13</v>
       </c>
@@ -63513,7 +63577,7 @@
         <v>0.17259242942294106</v>
       </c>
     </row>
-    <row r="367" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>14</v>
       </c>
@@ -63596,7 +63660,7 @@
         <v>0.18638460350136357</v>
       </c>
     </row>
-    <row r="368" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>15</v>
       </c>
@@ -63679,7 +63743,7 @@
         <v>-5.2206519974136147E-2</v>
       </c>
     </row>
-    <row r="369" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>16</v>
       </c>
@@ -63762,7 +63826,7 @@
         <v>-0.22911942200885815</v>
       </c>
     </row>
-    <row r="370" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>17</v>
       </c>
@@ -63845,7 +63909,7 @@
         <v>-0.27316100913376912</v>
       </c>
     </row>
-    <row r="371" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>18</v>
       </c>
@@ -63928,7 +63992,7 @@
         <v>-0.16040620618731405</v>
       </c>
     </row>
-    <row r="372" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>19</v>
       </c>
@@ -64011,7 +64075,7 @@
         <v>0.2995399215497494</v>
       </c>
     </row>
-    <row r="373" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>20</v>
       </c>
@@ -64094,7 +64158,7 @@
         <v>-0.1733083373249055</v>
       </c>
     </row>
-    <row r="374" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>21</v>
       </c>
@@ -64177,7 +64241,7 @@
         <v>-0.74294745728710343</v>
       </c>
     </row>
-    <row r="375" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>22</v>
       </c>
@@ -64260,7 +64324,7 @@
         <v>-1.7942174565296207E-2</v>
       </c>
     </row>
-    <row r="376" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>23</v>
       </c>
@@ -64343,7 +64407,7 @@
         <v>-0.21312340680918018</v>
       </c>
     </row>
-    <row r="377" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>24</v>
       </c>
@@ -64426,7 +64490,7 @@
         <v>-0.14504668087687686</v>
       </c>
     </row>
-    <row r="378" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>25</v>
       </c>
@@ -64509,7 +64573,7 @@
         <v>0.35652131667585779</v>
       </c>
     </row>
-    <row r="379" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>26</v>
       </c>
@@ -64592,7 +64656,7 @@
         <v>0.17599845361741759</v>
       </c>
     </row>
-    <row r="380" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>27</v>
       </c>
@@ -64675,7 +64739,7 @@
         <v>0.17351496840262656</v>
       </c>
     </row>
-    <row r="381" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>28</v>
       </c>
@@ -64758,7 +64822,7 @@
         <v>-5.3810493598558315E-2</v>
       </c>
     </row>
-    <row r="382" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>29</v>
       </c>
@@ -64841,7 +64905,7 @@
         <v>-0.22489861421211996</v>
       </c>
     </row>
-    <row r="383" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>30</v>
       </c>
@@ -64924,7 +64988,7 @@
         <v>-0.27287552780237123</v>
       </c>
     </row>
-    <row r="384" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>31</v>
       </c>
@@ -65007,7 +65071,7 @@
         <v>-0.15444732521633295</v>
       </c>
     </row>
-    <row r="385" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>32</v>
       </c>
@@ -65098,9 +65162,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FC7B88F-64DB-4C68-8FFC-305A2A41AB55}">
   <dimension ref="A1:AA25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -65183,7 +65247,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -65266,7 +65330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -65349,7 +65413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -65432,7 +65496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -65515,7 +65579,7 @@
         <v>0.5335206744279406</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -65598,7 +65662,7 @@
         <v>0.49739060618225611</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -65681,7 +65745,7 @@
         <v>0.40405459654757125</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -65764,7 +65828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -65847,7 +65911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -65930,7 +65994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -66013,7 +66077,7 @@
         <v>0.36852669610598154</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -66096,7 +66160,7 @@
         <v>0.23966278602970695</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -66179,7 +66243,7 @@
         <v>0.30931352870333201</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -66262,7 +66326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -66345,7 +66409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -66428,7 +66492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -66511,7 +66575,7 @@
         <v>0.4676836611802489</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -66594,7 +66658,7 @@
         <v>0.17442794058611</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -66677,7 +66741,7 @@
         <v>0.34263348052990766</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -66760,7 +66824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -66843,7 +66907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -66926,7 +66990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -67009,7 +67073,7 @@
         <v>0.44439983942191891</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -67092,7 +67156,7 @@
         <v>0.50040144520272978</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -67183,9 +67247,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CBBB125-439E-474E-9960-563C78F44B33}">
   <dimension ref="A1:AA25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -67268,7 +67332,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -67351,7 +67415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -67434,7 +67498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -67517,7 +67581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -67600,7 +67664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -67683,7 +67747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -67766,7 +67830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -67849,7 +67913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -67932,7 +67996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -68015,7 +68079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -68098,7 +68162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -68181,7 +68245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -68264,7 +68328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -68347,7 +68411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -68430,7 +68494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -68513,7 +68577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -68596,7 +68660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -68679,7 +68743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -68762,7 +68826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>14</v>
       </c>
@@ -68845,7 +68909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -68928,7 +68992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -69011,7 +69075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>15</v>
       </c>
@@ -69094,7 +69158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>15</v>
       </c>
@@ -69177,7 +69241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>15</v>
       </c>
@@ -69268,13 +69332,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8D12B52-98C9-449E-BF4A-23F7CAD72921}">
   <dimension ref="A1:AA37"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.88671875" customWidth="1"/>
+    <col min="1" max="1" width="27.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -69357,7 +69421,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>16</v>
       </c>
@@ -69440,7 +69504,7 @@
         <v>4.5052000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -69523,7 +69587,7 @@
         <v>-9.797600000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -69606,7 +69670,7 @@
         <v>9.4448000000000025</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -69689,7 +69753,7 @@
         <v>4.5052000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -69772,7 +69836,7 @@
         <v>-9.4056960000000007</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -69855,7 +69919,7 @@
         <v>9.4448000000000025</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -69938,7 +70002,7 @@
         <v>4.3249919999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -70021,7 +70085,7 @@
         <v>-9.8759808000000007</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -70104,7 +70168,7 @@
         <v>9.9170400000000036</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -70187,7 +70251,7 @@
         <v>4.2799399999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>17</v>
       </c>
@@ -70270,7 +70334,7 @@
         <v>-9.6784611839999997</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -70353,7 +70417,7 @@
         <v>10.115380800000004</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -70436,7 +70500,7 @@
         <v>4.1943412000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -70519,7 +70583,7 @@
         <v>-10.06559963136</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -70602,7 +70666,7 @@
         <v>9.7107655680000047</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -70685,7 +70749,7 @@
         <v>4.1104543759999999</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -70768,7 +70832,7 @@
         <v>-10.06559963136</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -70851,7 +70915,7 @@
         <v>9.4194426009600036</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>16</v>
       </c>
@@ -70934,7 +70998,7 @@
         <v>4.7079339999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>17</v>
       </c>
@@ -71017,7 +71081,7 @@
         <v>-10.367567620300798</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -71100,7 +71164,7 @@
         <v>9.5136370269696027</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -71183,7 +71247,7 @@
         <v>4.8020926800000003</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>17</v>
       </c>
@@ -71266,7 +71330,7 @@
         <v>-10.263891944097791</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -71349,7 +71413,7 @@
         <v>9.7990461377786904</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>16</v>
       </c>
@@ -71432,7 +71496,7 @@
         <v>4.9461554604</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>17</v>
       </c>
@@ -71515,7 +71579,7 @@
         <v>-10.469169782979748</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -71598,7 +71662,7 @@
         <v>9.5050747536453297</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>16</v>
       </c>
@@ -71681,7 +71745,7 @@
         <v>4.4725372999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>17</v>
       </c>
@@ -71764,7 +71828,7 @@
         <v>-10.992628272128735</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -71847,7 +71911,7 @@
         <v>9.6001255011817825</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>16</v>
       </c>
@@ -71930,7 +71994,7 @@
         <v>4.4725372999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>17</v>
       </c>
@@ -72013,7 +72077,7 @@
         <v>-10.552923141243587</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -72096,7 +72160,7 @@
         <v>9.888129266217236</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>16</v>
       </c>
@@ -72179,7 +72243,7 @@
         <v>4.4278119270000005</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>17</v>
       </c>
@@ -72262,7 +72326,7 @@
         <v>-10.341864678418714</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>18</v>
       </c>

--- a/data/OP1/case33_1/case33_1_operational_data.xlsx
+++ b/data/OP1/case33_1/case33_1_operational_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS7/case33_1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP1/case33_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C614731-E163-634C-8926-8FFCC4133114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6621C4B1-9D88-0743-A32D-CDB2A0571E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52180" yWindow="1260" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3780" yWindow="1800" windowWidth="29400" windowHeight="19120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -473,12 +473,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*3.5</f>
-        <v>14</v>
+        <f>E2*2</f>
+        <v>8</v>
       </c>
       <c r="C2" s="1">
-        <f>F2*3.5</f>
-        <v>8.4</v>
+        <f>F2*2</f>
+        <v>4.8</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -495,12 +495,12 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B33" si="0">E3*3.5</f>
-        <v>12.599999999999998</v>
+        <f t="shared" ref="B3:B33" si="0">E3*2</f>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C33" si="1">F3*3.5</f>
-        <v>5.6000000000000005</v>
+        <f t="shared" ref="C3:C33" si="1">F3*2</f>
+        <v>3.2</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -518,11 +518,11 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" si="0"/>
-        <v>16.8</v>
+        <v>9.6</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="1"/>
-        <v>11.200000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -540,11 +540,11 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="1"/>
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -562,11 +562,11 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="1"/>
-        <v>2.8000000000000003</v>
+        <v>1.6</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -584,11 +584,11 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -606,11 +606,11 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -628,11 +628,11 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="1"/>
-        <v>2.8000000000000003</v>
+        <v>1.6</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="1"/>
-        <v>2.8000000000000003</v>
+        <v>1.6</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -672,11 +672,11 @@
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
-        <v>6.2999999999999989</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="1"/>
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -694,11 +694,11 @@
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="1"/>
-        <v>4.9000000000000004</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -716,11 +716,11 @@
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="1"/>
-        <v>4.9000000000000004</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -738,20 +738,20 @@
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
-        <v>16.8</v>
+        <v>4.8</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="1"/>
-        <v>11.200000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
       <c r="E14" s="4">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="F14" s="4">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -760,20 +760,20 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="1"/>
-        <v>1.4000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E15" s="4">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="F15" s="4">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -782,20 +782,20 @@
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="1"/>
-        <v>2.8000000000000003</v>
+        <v>0.8</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E16" s="4">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="F16" s="4">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -804,20 +804,20 @@
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="1"/>
-        <v>2.8000000000000003</v>
+        <v>0.8</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E17" s="4">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="F17" s="4">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -826,20 +826,20 @@
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
-        <v>12.599999999999998</v>
+        <v>3.6</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
+        <v>1.6</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
       <c r="E18" s="4">
-        <v>3.5999999999999996</v>
+        <v>1.8</v>
       </c>
       <c r="F18" s="4">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -848,17 +848,17 @@
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
-        <v>12.599999999999998</v>
+        <v>3.6</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
+        <v>3.2</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
       <c r="E19" s="4">
-        <v>3.5999999999999996</v>
+        <v>1.8</v>
       </c>
       <c r="F19" s="4">
         <v>1.6</v>
@@ -870,11 +870,11 @@
       </c>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
-        <v>12.599999999999998</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
+        <v>3.2</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -892,11 +892,11 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
-        <v>12.599999999999998</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
+        <v>3.2</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -914,11 +914,11 @@
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
-        <v>12.599999999999998</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C22" s="1">
         <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
+        <v>3.2</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -936,11 +936,11 @@
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
-        <v>12.599999999999998</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" si="1"/>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -958,11 +958,11 @@
       </c>
       <c r="B24" s="1">
         <f t="shared" si="0"/>
-        <v>58.800000000000004</v>
+        <v>33.6</v>
       </c>
       <c r="C24" s="1">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -980,11 +980,11 @@
       </c>
       <c r="B25" s="1">
         <f t="shared" si="0"/>
-        <v>58.800000000000004</v>
+        <v>33.6</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -1002,11 +1002,11 @@
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="C26" s="1">
         <f t="shared" si="1"/>
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1024,11 +1024,11 @@
       </c>
       <c r="B27" s="1">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="C27" s="1">
         <f t="shared" si="1"/>
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1046,11 +1046,11 @@
       </c>
       <c r="B28" s="1">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" si="1"/>
-        <v>2.8000000000000003</v>
+        <v>1.6</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B29" s="1">
         <f t="shared" si="0"/>
-        <v>16.8</v>
+        <v>9.6</v>
       </c>
       <c r="C29" s="1">
         <f t="shared" si="1"/>
-        <v>9.8000000000000007</v>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1090,11 +1090,11 @@
       </c>
       <c r="B30" s="1">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C30" s="1">
         <f t="shared" si="1"/>
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1112,11 +1112,11 @@
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" si="1"/>
-        <v>9.8000000000000007</v>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1134,11 +1134,11 @@
       </c>
       <c r="B32" s="1">
         <f t="shared" si="0"/>
-        <v>29.400000000000002</v>
+        <v>16.8</v>
       </c>
       <c r="C32" s="1">
         <f t="shared" si="1"/>
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1156,11 +1156,11 @@
       </c>
       <c r="B33" s="1">
         <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="C33" s="1">
         <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
+        <v>3.2</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
@@ -69432,76 +69432,76 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>4.9164000000000012</v>
+        <v>12.536820000000002</v>
       </c>
       <c r="E2" s="1">
-        <v>5.0804000000000009</v>
+        <v>12.955020000000003</v>
       </c>
       <c r="F2" s="1">
-        <v>4.5491999999999999</v>
+        <v>11.60046</v>
       </c>
       <c r="G2" s="1">
-        <v>4.3119999999999994</v>
+        <v>10.995599999999998</v>
       </c>
       <c r="H2" s="1">
-        <v>3.5328000000000004</v>
+        <v>9.0086400000000015</v>
       </c>
       <c r="I2" s="1">
-        <v>2.9984000000000006</v>
+        <v>7.645920000000002</v>
       </c>
       <c r="J2" s="1">
-        <v>3.6668000000000003</v>
+        <v>9.350340000000001</v>
       </c>
       <c r="K2" s="1">
-        <v>0.63680000000000003</v>
+        <v>1.62384</v>
       </c>
       <c r="L2" s="1">
-        <v>0.56000000000000005</v>
+        <v>1.4280000000000002</v>
       </c>
       <c r="M2" s="1">
-        <v>0.8163999999999999</v>
+        <v>2.08182</v>
       </c>
       <c r="N2" s="1">
-        <v>0.48080000000000006</v>
+        <v>1.22604</v>
       </c>
       <c r="O2" s="1">
-        <v>0.6008</v>
+        <v>1.5320400000000001</v>
       </c>
       <c r="P2" s="1">
-        <v>0.95720000000000027</v>
+        <v>2.4408600000000007</v>
       </c>
       <c r="Q2" s="1">
-        <v>1.7636000000000003</v>
+        <v>4.4971800000000002</v>
       </c>
       <c r="R2" s="1">
-        <v>1.8815999999999999</v>
+        <v>4.7980799999999997</v>
       </c>
       <c r="S2" s="1">
-        <v>1.8503999999999998</v>
+        <v>4.7185199999999998</v>
       </c>
       <c r="T2" s="1">
-        <v>1.038</v>
+        <v>2.6469</v>
       </c>
       <c r="U2" s="1">
-        <v>2.1143999999999998</v>
+        <v>5.3917199999999994</v>
       </c>
       <c r="V2" s="1">
-        <v>1.2408000000000001</v>
+        <v>3.1640400000000004</v>
       </c>
       <c r="W2" s="1">
-        <v>0.87239999999999984</v>
+        <v>2.2246199999999994</v>
       </c>
       <c r="X2" s="1">
-        <v>1.3248000000000002</v>
+        <v>3.3782400000000004</v>
       </c>
       <c r="Y2" s="1">
-        <v>0.81880000000000008</v>
+        <v>2.0879400000000001</v>
       </c>
       <c r="Z2" s="1">
-        <v>3.7372000000000005</v>
+        <v>9.5298600000000011</v>
       </c>
       <c r="AA2" s="1">
-        <v>4.5052000000000003</v>
+        <v>11.48826</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -69515,76 +69515,76 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>-11.100000000000001</v>
+        <v>-28.305000000000003</v>
       </c>
       <c r="E3" s="1">
-        <v>-11.8696</v>
+        <v>-30.267480000000003</v>
       </c>
       <c r="F3" s="1">
-        <v>-13.349600000000002</v>
+        <v>-34.041480000000007</v>
       </c>
       <c r="G3" s="1">
-        <v>-14.400400000000001</v>
+        <v>-36.721019999999996</v>
       </c>
       <c r="H3" s="1">
-        <v>-15.392000000000001</v>
+        <v>-39.249600000000001</v>
       </c>
       <c r="I3" s="1">
-        <v>-16.798000000000002</v>
+        <v>-42.834900000000005</v>
       </c>
       <c r="J3" s="1">
-        <v>-16.028400000000001</v>
+        <v>-40.872419999999998</v>
       </c>
       <c r="K3" s="1">
-        <v>-17.979759999999999</v>
+        <v>-45.848387999999993</v>
       </c>
       <c r="L3" s="1">
-        <v>-16.307359999999996</v>
+        <v>-41.583767999999985</v>
       </c>
       <c r="M3" s="1">
-        <v>-23.952839999999998</v>
+        <v>-61.079741999999996</v>
       </c>
       <c r="N3" s="1">
-        <v>-23.707360000000005</v>
+        <v>-60.453768000000011</v>
       </c>
       <c r="O3" s="1">
-        <v>-21.672160000000002</v>
+        <v>-55.264007999999997</v>
       </c>
       <c r="P3" s="1">
-        <v>-20.774560000000001</v>
+        <v>-52.975127999999998</v>
       </c>
       <c r="Q3" s="1">
-        <v>-20.057480000000002</v>
+        <v>-51.146574000000008</v>
       </c>
       <c r="R3" s="1">
-        <v>-18.905680000000004</v>
+        <v>-48.20948400000001</v>
       </c>
       <c r="S3" s="1">
-        <v>-17.204239999999999</v>
+        <v>-43.870811999999994</v>
       </c>
       <c r="T3" s="1">
-        <v>-16.086960000000001</v>
+        <v>-41.021748000000002</v>
       </c>
       <c r="U3" s="1">
-        <v>-14.396240000000002</v>
+        <v>-36.710412000000005</v>
       </c>
       <c r="V3" s="1">
-        <v>-9.1377199999999998</v>
+        <v>-23.301185999999998</v>
       </c>
       <c r="W3" s="1">
-        <v>-10.226479999999999</v>
+        <v>-26.077523999999997</v>
       </c>
       <c r="X3" s="1">
-        <v>-10.809839999999999</v>
+        <v>-27.565091999999996</v>
       </c>
       <c r="Y3" s="1">
-        <v>-11.605399999999999</v>
+        <v>-29.593769999999996</v>
       </c>
       <c r="Z3" s="1">
-        <v>-9.2204000000000015</v>
+        <v>-23.512020000000003</v>
       </c>
       <c r="AA3" s="1">
-        <v>-9.797600000000001</v>
+        <v>-24.983879999999999</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -69598,76 +69598,76 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>10.69356</v>
+        <v>27.268578000000002</v>
       </c>
       <c r="E4" s="1">
-        <v>11.440319999999996</v>
+        <v>29.172815999999987</v>
       </c>
       <c r="F4" s="1">
-        <v>12.82724</v>
+        <v>32.709461999999995</v>
       </c>
       <c r="G4" s="1">
-        <v>13.802440000000002</v>
+        <v>35.196222000000006</v>
       </c>
       <c r="H4" s="1">
-        <v>14.691399999999998</v>
+        <v>37.463069999999988</v>
       </c>
       <c r="I4" s="1">
-        <v>16.042000000000002</v>
+        <v>40.9071</v>
       </c>
       <c r="J4" s="1">
-        <v>15.293999999999999</v>
+        <v>38.999699999999997</v>
       </c>
       <c r="K4" s="1">
-        <v>17.259160000000001</v>
+        <v>44.010857999999999</v>
       </c>
       <c r="L4" s="1">
-        <v>15.809160000000002</v>
+        <v>40.313358000000001</v>
       </c>
       <c r="M4" s="1">
-        <v>18.039439999999999</v>
+        <v>46.000571999999998</v>
       </c>
       <c r="N4" s="1">
-        <v>18.181480000000001</v>
+        <v>46.362774000000002</v>
       </c>
       <c r="O4" s="1">
-        <v>17.019639999999999</v>
+        <v>43.400081999999998</v>
       </c>
       <c r="P4" s="1">
-        <v>16.446000000000002</v>
+        <v>41.937300000000008</v>
       </c>
       <c r="Q4" s="1">
-        <v>16.02328</v>
+        <v>40.859363999999999</v>
       </c>
       <c r="R4" s="1">
-        <v>15.016320000000004</v>
+        <v>38.291616000000005</v>
       </c>
       <c r="S4" s="1">
-        <v>13.671480000000003</v>
+        <v>34.862274000000006</v>
       </c>
       <c r="T4" s="1">
-        <v>12.736039999999997</v>
+        <v>32.476901999999995</v>
       </c>
       <c r="U4" s="1">
-        <v>11.38288</v>
+        <v>29.026343999999998</v>
       </c>
       <c r="V4" s="1">
-        <v>8.9093599999999995</v>
+        <v>22.718867999999997</v>
       </c>
       <c r="W4" s="1">
-        <v>9.9721600000000006</v>
+        <v>25.429008</v>
       </c>
       <c r="X4" s="1">
-        <v>10.596560000000002</v>
+        <v>27.021228000000004</v>
       </c>
       <c r="Y4" s="1">
-        <v>11.414560000000002</v>
+        <v>29.107128000000003</v>
       </c>
       <c r="Z4" s="1">
-        <v>8.8819999999999997</v>
+        <v>22.649100000000001</v>
       </c>
       <c r="AA4" s="1">
-        <v>9.4448000000000025</v>
+        <v>24.084240000000008</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -69681,76 +69681,76 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>4.8672360000000019</v>
+        <v>12.411451800000005</v>
       </c>
       <c r="E5" s="1">
-        <v>5.0804000000000009</v>
+        <v>12.955020000000003</v>
       </c>
       <c r="F5" s="1">
-        <v>4.7311680000000003</v>
+        <v>12.0644784</v>
       </c>
       <c r="G5" s="1">
-        <v>4.3982399999999995</v>
+        <v>11.215511999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>3.4621440000000003</v>
+        <v>8.8284672000000004</v>
       </c>
       <c r="I5" s="1">
-        <v>2.8784640000000006</v>
+        <v>7.3400832000000005</v>
       </c>
       <c r="J5" s="1">
-        <v>3.7034680000000004</v>
+        <v>9.4438434000000004</v>
       </c>
       <c r="K5" s="1">
-        <v>0.62406400000000006</v>
+        <v>1.5913632</v>
       </c>
       <c r="L5" s="1">
-        <v>0.58240000000000014</v>
+        <v>1.4851200000000002</v>
       </c>
       <c r="M5" s="1">
-        <v>0.85721999999999998</v>
+        <v>2.1859109999999999</v>
       </c>
       <c r="N5" s="1">
-        <v>0.4711840000000001</v>
+        <v>1.2015192000000003</v>
       </c>
       <c r="O5" s="1">
-        <v>0.60680800000000001</v>
+        <v>1.5473604000000001</v>
       </c>
       <c r="P5" s="1">
-        <v>0.95720000000000027</v>
+        <v>2.4408600000000007</v>
       </c>
       <c r="Q5" s="1">
-        <v>1.8517800000000002</v>
+        <v>4.7220390000000005</v>
       </c>
       <c r="R5" s="1">
-        <v>1.8815999999999999</v>
+        <v>4.7980799999999997</v>
       </c>
       <c r="S5" s="1">
-        <v>1.8874079999999998</v>
+        <v>4.8128903999999997</v>
       </c>
       <c r="T5" s="1">
-        <v>0.98609999999999998</v>
+        <v>2.5145550000000001</v>
       </c>
       <c r="U5" s="1">
-        <v>2.2201199999999996</v>
+        <v>5.6613059999999988</v>
       </c>
       <c r="V5" s="1">
-        <v>1.2532080000000001</v>
+        <v>3.1956804000000005</v>
       </c>
       <c r="W5" s="1">
-        <v>0.89857199999999982</v>
+        <v>2.2913585999999997</v>
       </c>
       <c r="X5" s="1">
-        <v>1.3380480000000003</v>
+        <v>3.4120224000000006</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.77786</v>
+        <v>1.9835429999999998</v>
       </c>
       <c r="Z5" s="1">
-        <v>3.8119440000000004</v>
+        <v>9.7204572000000002</v>
       </c>
       <c r="AA5" s="1">
-        <v>4.5052000000000003</v>
+        <v>11.48826</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -69764,76 +69764,76 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>-11.100000000000001</v>
+        <v>-28.305000000000003</v>
       </c>
       <c r="E6" s="1">
-        <v>-11.750904</v>
+        <v>-29.964805200000001</v>
       </c>
       <c r="F6" s="1">
-        <v>-13.349600000000002</v>
+        <v>-34.041480000000007</v>
       </c>
       <c r="G6" s="1">
-        <v>-13.68038</v>
+        <v>-34.884968999999998</v>
       </c>
       <c r="H6" s="1">
-        <v>-14.930240000000001</v>
+        <v>-38.072112000000004</v>
       </c>
       <c r="I6" s="1">
-        <v>-16.126080000000002</v>
+        <v>-41.121504000000002</v>
       </c>
       <c r="J6" s="1">
-        <v>-16.188684000000002</v>
+        <v>-41.281144200000007</v>
       </c>
       <c r="K6" s="1">
-        <v>-17.979759999999999</v>
+        <v>-45.848387999999993</v>
       </c>
       <c r="L6" s="1">
-        <v>-16.307359999999996</v>
+        <v>-41.583767999999985</v>
       </c>
       <c r="M6" s="1">
-        <v>-23.713311599999997</v>
+        <v>-60.468944579999992</v>
       </c>
       <c r="N6" s="1">
-        <v>-24.181507200000006</v>
+        <v>-61.662843360000018</v>
       </c>
       <c r="O6" s="1">
-        <v>-21.238716800000002</v>
+        <v>-54.158727840000005</v>
       </c>
       <c r="P6" s="1">
-        <v>-21.605542400000001</v>
+        <v>-55.094133119999995</v>
       </c>
       <c r="Q6" s="1">
-        <v>-19.8569052</v>
+        <v>-50.635108259999996</v>
       </c>
       <c r="R6" s="1">
-        <v>-19.661907200000005</v>
+        <v>-50.137863360000019</v>
       </c>
       <c r="S6" s="1">
-        <v>-17.204239999999999</v>
+        <v>-43.870811999999994</v>
       </c>
       <c r="T6" s="1">
-        <v>-15.765220800000002</v>
+        <v>-40.201313040000002</v>
       </c>
       <c r="U6" s="1">
-        <v>-13.820390400000001</v>
+        <v>-35.241995520000003</v>
       </c>
       <c r="V6" s="1">
-        <v>-9.1377199999999998</v>
+        <v>-23.301185999999998</v>
       </c>
       <c r="W6" s="1">
-        <v>-10.124215199999998</v>
+        <v>-25.816748759999996</v>
       </c>
       <c r="X6" s="1">
-        <v>-10.593643199999999</v>
+        <v>-27.013790159999996</v>
       </c>
       <c r="Y6" s="1">
-        <v>-11.257237999999999</v>
+        <v>-28.705956899999997</v>
       </c>
       <c r="Z6" s="1">
-        <v>-9.5892160000000004</v>
+        <v>-24.452500799999999</v>
       </c>
       <c r="AA6" s="1">
-        <v>-9.4056960000000007</v>
+        <v>-23.984524800000003</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
@@ -69847,76 +69847,76 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>10.158882</v>
+        <v>25.905149100000003</v>
       </c>
       <c r="E7" s="1">
-        <v>11.783529599999998</v>
+        <v>30.048000479999995</v>
       </c>
       <c r="F7" s="1">
-        <v>12.314150399999999</v>
+        <v>31.401083519999993</v>
       </c>
       <c r="G7" s="1">
-        <v>13.112318000000002</v>
+        <v>33.436410900000006</v>
       </c>
       <c r="H7" s="1">
-        <v>14.250657999999998</v>
+        <v>36.339177899999989</v>
       </c>
       <c r="I7" s="1">
-        <v>16.523260000000004</v>
+        <v>42.134313000000006</v>
       </c>
       <c r="J7" s="1">
-        <v>14.68224</v>
+        <v>37.439712</v>
       </c>
       <c r="K7" s="1">
-        <v>16.568793600000003</v>
+        <v>42.250423680000004</v>
       </c>
       <c r="L7" s="1">
-        <v>15.967251600000003</v>
+        <v>40.716491580000003</v>
       </c>
       <c r="M7" s="1">
-        <v>17.4982568</v>
+        <v>44.620554839999997</v>
       </c>
       <c r="N7" s="1">
-        <v>18.181480000000001</v>
+        <v>46.362774000000002</v>
       </c>
       <c r="O7" s="1">
-        <v>17.360032799999999</v>
+        <v>44.268083639999993</v>
       </c>
       <c r="P7" s="1">
-        <v>15.788160000000003</v>
+        <v>40.259808000000007</v>
       </c>
       <c r="Q7" s="1">
-        <v>16.343745599999998</v>
+        <v>41.676551279999991</v>
       </c>
       <c r="R7" s="1">
-        <v>15.767136000000004</v>
+        <v>40.206196800000008</v>
       </c>
       <c r="S7" s="1">
-        <v>14.081624400000003</v>
+        <v>35.908142220000009</v>
       </c>
       <c r="T7" s="1">
-        <v>12.353958799999997</v>
+        <v>31.502594939999991</v>
       </c>
       <c r="U7" s="1">
-        <v>11.838195199999999</v>
+        <v>30.187397759999996</v>
       </c>
       <c r="V7" s="1">
-        <v>9.3548279999999995</v>
+        <v>23.854811399999999</v>
       </c>
       <c r="W7" s="1">
-        <v>9.9721600000000006</v>
+        <v>25.429008</v>
       </c>
       <c r="X7" s="1">
-        <v>10.066732000000002</v>
+        <v>25.670166600000005</v>
       </c>
       <c r="Y7" s="1">
-        <v>11.985288000000002</v>
+        <v>30.562484400000002</v>
       </c>
       <c r="Z7" s="1">
-        <v>8.7931799999999996</v>
+        <v>22.422608999999998</v>
       </c>
       <c r="AA7" s="1">
-        <v>9.4448000000000025</v>
+        <v>24.084240000000008</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
@@ -69930,76 +69930,76 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>4.7698912800000013</v>
+        <v>12.163222764000002</v>
       </c>
       <c r="E8" s="1">
-        <v>5.1820080000000006</v>
+        <v>13.214120400000002</v>
       </c>
       <c r="F8" s="1">
-        <v>4.7784796800000002</v>
+        <v>12.185123184</v>
       </c>
       <c r="G8" s="1">
-        <v>4.2223103999999996</v>
+        <v>10.766891519999998</v>
       </c>
       <c r="H8" s="1">
-        <v>3.2890367999999999</v>
+        <v>8.3870438399999987</v>
       </c>
       <c r="I8" s="1">
-        <v>2.9072486400000006</v>
+        <v>7.4134840320000013</v>
       </c>
       <c r="J8" s="1">
-        <v>3.6664333200000003</v>
+        <v>9.3494049660000016</v>
       </c>
       <c r="K8" s="1">
-        <v>0.64902656000000003</v>
+        <v>1.655017728</v>
       </c>
       <c r="L8" s="1">
-        <v>0.58240000000000014</v>
+        <v>1.4851200000000002</v>
       </c>
       <c r="M8" s="1">
-        <v>0.81435900000000006</v>
+        <v>2.0766154500000003</v>
       </c>
       <c r="N8" s="1">
-        <v>0.47589584000000007</v>
+        <v>1.2135343920000001</v>
       </c>
       <c r="O8" s="1">
-        <v>0.60680800000000001</v>
+        <v>1.5473604000000001</v>
       </c>
       <c r="P8" s="1">
-        <v>0.94762800000000025</v>
+        <v>2.4164514000000006</v>
       </c>
       <c r="Q8" s="1">
-        <v>1.7591910000000002</v>
+        <v>4.4859370500000004</v>
       </c>
       <c r="R8" s="1">
-        <v>1.8251519999999999</v>
+        <v>4.6541375999999994</v>
       </c>
       <c r="S8" s="1">
-        <v>1.8307857599999997</v>
+        <v>4.6685036879999995</v>
       </c>
       <c r="T8" s="1">
-        <v>0.98609999999999998</v>
+        <v>2.5145550000000001</v>
       </c>
       <c r="U8" s="1">
-        <v>2.1535163999999996</v>
+        <v>5.4914668199999994</v>
       </c>
       <c r="V8" s="1">
-        <v>1.22814384</v>
+        <v>3.1317667920000001</v>
       </c>
       <c r="W8" s="1">
-        <v>0.9435005999999998</v>
+        <v>2.4059265299999995</v>
       </c>
       <c r="X8" s="1">
-        <v>1.3380480000000003</v>
+        <v>3.4120224000000006</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.80897439999999998</v>
+        <v>2.06288472</v>
       </c>
       <c r="Z8" s="1">
-        <v>3.7357051200000004</v>
+        <v>9.5260480560000005</v>
       </c>
       <c r="AA8" s="1">
-        <v>4.3249919999999999</v>
+        <v>11.0287296</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
@@ -70013,76 +70013,76 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>-10.545000000000002</v>
+        <v>-26.889750000000003</v>
       </c>
       <c r="E9" s="1">
-        <v>-11.750904</v>
+        <v>-29.964805200000001</v>
       </c>
       <c r="F9" s="1">
-        <v>-12.682120000000003</v>
+        <v>-32.339406000000004</v>
       </c>
       <c r="G9" s="1">
-        <v>-13.68038</v>
+        <v>-34.884968999999998</v>
       </c>
       <c r="H9" s="1">
-        <v>-15.527449600000002</v>
+        <v>-39.594996480000006</v>
       </c>
       <c r="I9" s="1">
-        <v>-15.803558400000002</v>
+        <v>-40.299073920000005</v>
       </c>
       <c r="J9" s="1">
-        <v>-16.674344520000002</v>
+        <v>-42.519578526000004</v>
       </c>
       <c r="K9" s="1">
-        <v>-17.620164799999998</v>
+        <v>-44.931420239999994</v>
       </c>
       <c r="L9" s="1">
-        <v>-17.122727999999995</v>
+        <v>-43.662956399999985</v>
       </c>
       <c r="M9" s="1">
-        <v>-23.950444715999996</v>
+        <v>-61.07363402579999</v>
       </c>
       <c r="N9" s="1">
-        <v>-23.456061984000009</v>
+        <v>-59.812958059200028</v>
       </c>
       <c r="O9" s="1">
-        <v>-21.875878304000004</v>
+        <v>-55.783489675200016</v>
       </c>
       <c r="P9" s="1">
-        <v>-21.389486976000004</v>
+        <v>-54.543191788800009</v>
       </c>
       <c r="Q9" s="1">
-        <v>-20.849750459999999</v>
+        <v>-53.166863673000002</v>
       </c>
       <c r="R9" s="1">
-        <v>-19.465288128000005</v>
+        <v>-49.636484726400013</v>
       </c>
       <c r="S9" s="1">
-        <v>-17.204239999999999</v>
+        <v>-43.870811999999994</v>
       </c>
       <c r="T9" s="1">
-        <v>-15.607568592000002</v>
+        <v>-39.799299909600002</v>
       </c>
       <c r="U9" s="1">
-        <v>-14.373206016000001</v>
+        <v>-36.651675340800004</v>
       </c>
       <c r="V9" s="1">
-        <v>-9.4118516000000003</v>
+        <v>-24.000221580000002</v>
       </c>
       <c r="W9" s="1">
-        <v>-10.022973047999997</v>
+        <v>-25.558581272399991</v>
       </c>
       <c r="X9" s="1">
-        <v>-10.593643199999999</v>
+        <v>-27.013790159999996</v>
       </c>
       <c r="Y9" s="1">
-        <v>-10.694376099999999</v>
+        <v>-27.270659054999999</v>
       </c>
       <c r="Z9" s="1">
-        <v>-9.4933238400000004</v>
+        <v>-24.207975791999999</v>
       </c>
       <c r="AA9" s="1">
-        <v>-9.8759808000000007</v>
+        <v>-25.183751040000001</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
@@ -70096,76 +70096,76 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>10.36205964</v>
+        <v>26.423252082000001</v>
       </c>
       <c r="E10" s="1">
-        <v>11.194353119999999</v>
+        <v>28.545600455999992</v>
       </c>
       <c r="F10" s="1">
-        <v>12.314150399999999</v>
+        <v>31.401083519999993</v>
       </c>
       <c r="G10" s="1">
-        <v>12.718948460000002</v>
+        <v>32.433318573000008</v>
       </c>
       <c r="H10" s="1">
-        <v>13.538125099999997</v>
+        <v>34.52221900499999</v>
       </c>
       <c r="I10" s="1">
-        <v>15.697097000000003</v>
+        <v>40.027597350000008</v>
       </c>
       <c r="J10" s="1">
-        <v>13.948127999999999</v>
+        <v>35.567726399999998</v>
       </c>
       <c r="K10" s="1">
-        <v>15.740353920000002</v>
+        <v>40.137902496000002</v>
       </c>
       <c r="L10" s="1">
-        <v>15.647906568000003</v>
+        <v>39.902161748400005</v>
       </c>
       <c r="M10" s="1">
-        <v>17.848221936000002</v>
+        <v>45.512965936800001</v>
       </c>
       <c r="N10" s="1">
-        <v>18.5451096</v>
+        <v>47.290029479999994</v>
       </c>
       <c r="O10" s="1">
-        <v>16.49203116</v>
+        <v>42.054679458000003</v>
       </c>
       <c r="P10" s="1">
-        <v>16.419686400000003</v>
+        <v>41.870200320000009</v>
       </c>
       <c r="Q10" s="1">
-        <v>16.507183055999999</v>
+        <v>42.093316792799996</v>
       </c>
       <c r="R10" s="1">
-        <v>16.082478720000005</v>
+        <v>41.010320736000011</v>
       </c>
       <c r="S10" s="1">
-        <v>13.518359424000003</v>
+        <v>34.471816531200005</v>
       </c>
       <c r="T10" s="1">
-        <v>12.848117151999997</v>
+        <v>32.76269873759999</v>
       </c>
       <c r="U10" s="1">
-        <v>11.364667391999999</v>
+        <v>28.979901849599997</v>
       </c>
       <c r="V10" s="1">
-        <v>9.822569399999999</v>
+        <v>25.047551969999997</v>
       </c>
       <c r="W10" s="1">
-        <v>10.071881600000001</v>
+        <v>25.683298080000004</v>
       </c>
       <c r="X10" s="1">
-        <v>10.469401280000001</v>
+        <v>26.696973264000004</v>
       </c>
       <c r="Y10" s="1">
-        <v>12.344846640000004</v>
+        <v>31.479358932000011</v>
       </c>
       <c r="Z10" s="1">
-        <v>8.8811117999999993</v>
+        <v>22.646835089999996</v>
       </c>
       <c r="AA10" s="1">
-        <v>9.9170400000000036</v>
+        <v>25.28845200000001</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
@@ -70179,76 +70179,76 @@
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>4.6705800000000011</v>
+        <v>11.909979000000002</v>
       </c>
       <c r="E11" s="1">
-        <v>4.8263800000000003</v>
+        <v>12.307269</v>
       </c>
       <c r="F11" s="1">
-        <v>4.3217400000000001</v>
+        <v>11.020436999999999</v>
       </c>
       <c r="G11" s="1">
-        <v>4.0963999999999992</v>
+        <v>10.445819999999998</v>
       </c>
       <c r="H11" s="1">
-        <v>3.35616</v>
+        <v>8.5582080000000005</v>
       </c>
       <c r="I11" s="1">
-        <v>2.8484800000000003</v>
+        <v>7.263624000000001</v>
       </c>
       <c r="J11" s="1">
-        <v>3.48346</v>
+        <v>8.8828229999999984</v>
       </c>
       <c r="K11" s="1">
-        <v>0.60496000000000005</v>
+        <v>1.542648</v>
       </c>
       <c r="L11" s="1">
-        <v>0.53200000000000003</v>
+        <v>1.3566</v>
       </c>
       <c r="M11" s="1">
-        <v>0.77557999999999983</v>
+        <v>1.9777289999999996</v>
       </c>
       <c r="N11" s="1">
-        <v>0.45676000000000005</v>
+        <v>1.1647380000000001</v>
       </c>
       <c r="O11" s="1">
-        <v>0.57075999999999993</v>
+        <v>1.4554379999999998</v>
       </c>
       <c r="P11" s="1">
-        <v>0.90934000000000026</v>
+        <v>2.3188170000000006</v>
       </c>
       <c r="Q11" s="1">
-        <v>1.6754200000000001</v>
+        <v>4.2723210000000007</v>
       </c>
       <c r="R11" s="1">
-        <v>1.7875199999999998</v>
+        <v>4.5581759999999996</v>
       </c>
       <c r="S11" s="1">
-        <v>1.7578799999999997</v>
+        <v>4.4825939999999989</v>
       </c>
       <c r="T11" s="1">
-        <v>0.98609999999999998</v>
+        <v>2.5145550000000001</v>
       </c>
       <c r="U11" s="1">
-        <v>2.0086799999999996</v>
+        <v>5.1221339999999982</v>
       </c>
       <c r="V11" s="1">
-        <v>1.17876</v>
+        <v>3.0058379999999998</v>
       </c>
       <c r="W11" s="1">
-        <v>0.82877999999999985</v>
+        <v>2.1133889999999993</v>
       </c>
       <c r="X11" s="1">
-        <v>1.2585600000000001</v>
+        <v>3.2093280000000002</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.77786</v>
+        <v>1.9835429999999998</v>
       </c>
       <c r="Z11" s="1">
-        <v>3.5503400000000003</v>
+        <v>9.0533669999999997</v>
       </c>
       <c r="AA11" s="1">
-        <v>4.2799399999999999</v>
+        <v>10.913846999999999</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
@@ -70262,76 +70262,76 @@
         <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>-10.966800000000003</v>
+        <v>-27.965340000000005</v>
       </c>
       <c r="E12" s="1">
-        <v>-11.750904</v>
+        <v>-29.964805200000001</v>
       </c>
       <c r="F12" s="1">
-        <v>-12.048014000000002</v>
+        <v>-30.722435700000005</v>
       </c>
       <c r="G12" s="1">
-        <v>-13.68038</v>
+        <v>-34.884968999999998</v>
       </c>
       <c r="H12" s="1">
-        <v>-15.372175104000002</v>
+        <v>-39.199046515200003</v>
       </c>
       <c r="I12" s="1">
-        <v>-16.435700736000001</v>
+        <v>-41.911036876800004</v>
       </c>
       <c r="J12" s="1">
-        <v>-16.174114184400004</v>
+        <v>-41.243991170220006</v>
       </c>
       <c r="K12" s="1">
-        <v>-17.443963151999995</v>
+        <v>-44.482106037599983</v>
       </c>
       <c r="L12" s="1">
-        <v>-17.465182559999995</v>
+        <v>-44.536215527999985</v>
       </c>
       <c r="M12" s="1">
-        <v>-22.992426927359997</v>
+        <v>-58.630688664767987</v>
       </c>
       <c r="N12" s="1">
-        <v>-23.690622603840012</v>
+        <v>-60.411087639792029</v>
       </c>
       <c r="O12" s="1">
-        <v>-22.532154653120006</v>
+        <v>-57.456994365456019</v>
       </c>
       <c r="P12" s="1">
-        <v>-20.747802366720002</v>
+        <v>-52.906896035136</v>
       </c>
       <c r="Q12" s="1">
-        <v>-19.807262936999997</v>
+        <v>-50.508520489349991</v>
       </c>
       <c r="R12" s="1">
-        <v>-19.270635246720005</v>
+        <v>-49.140119879136009</v>
       </c>
       <c r="S12" s="1">
-        <v>-17.204239999999999</v>
+        <v>-43.870811999999994</v>
       </c>
       <c r="T12" s="1">
-        <v>-16.231871335680001</v>
+        <v>-41.391271905984006</v>
       </c>
       <c r="U12" s="1">
-        <v>-14.08574189568</v>
+        <v>-35.918641833983997</v>
       </c>
       <c r="V12" s="1">
-        <v>-9.0353775360000004</v>
+        <v>-23.040212716800003</v>
       </c>
       <c r="W12" s="1">
-        <v>-10.123202778479998</v>
+        <v>-25.814167085123991</v>
       </c>
       <c r="X12" s="1">
-        <v>-11.123325359999999</v>
+        <v>-28.364479668000001</v>
       </c>
       <c r="Y12" s="1">
-        <v>-10.694376099999999</v>
+        <v>-27.270659054999999</v>
       </c>
       <c r="Z12" s="1">
-        <v>-9.2085241248000003</v>
+        <v>-23.481736518240002</v>
       </c>
       <c r="AA12" s="1">
-        <v>-9.6784611839999997</v>
+        <v>-24.680076019199998</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
@@ -70345,76 +70345,76 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>9.8439566579999997</v>
+        <v>25.102089477899998</v>
       </c>
       <c r="E13" s="1">
-        <v>10.8585225264</v>
+        <v>27.689232442319998</v>
       </c>
       <c r="F13" s="1">
-        <v>12.437291903999999</v>
+        <v>31.715094355199994</v>
       </c>
       <c r="G13" s="1">
-        <v>12.464569490800002</v>
+        <v>31.784652201540005</v>
       </c>
       <c r="H13" s="1">
-        <v>13.402743848999997</v>
+        <v>34.176996814949987</v>
       </c>
       <c r="I13" s="1">
-        <v>15.854067970000003</v>
+        <v>40.427873323500009</v>
       </c>
       <c r="J13" s="1">
-        <v>13.948127999999999</v>
+        <v>35.567726399999998</v>
       </c>
       <c r="K13" s="1">
-        <v>15.897757459200001</v>
+        <v>40.539281520960003</v>
       </c>
       <c r="L13" s="1">
-        <v>15.647906568000003</v>
+        <v>39.902161748400005</v>
       </c>
       <c r="M13" s="1">
-        <v>18.383668594080003</v>
+        <v>46.878354914904001</v>
       </c>
       <c r="N13" s="1">
-        <v>17.617854120000001</v>
+        <v>44.925528006</v>
       </c>
       <c r="O13" s="1">
-        <v>15.667429602</v>
+        <v>39.951945485100005</v>
       </c>
       <c r="P13" s="1">
-        <v>16.912276992000002</v>
+        <v>43.126306329600006</v>
       </c>
       <c r="Q13" s="1">
-        <v>16.34211122544</v>
+        <v>41.672383624871998</v>
       </c>
       <c r="R13" s="1">
-        <v>15.760829145600006</v>
+        <v>40.190114321280014</v>
       </c>
       <c r="S13" s="1">
-        <v>12.842441452800003</v>
+        <v>32.748225704640006</v>
       </c>
       <c r="T13" s="1">
-        <v>13.490523009599997</v>
+        <v>34.400833674479991</v>
       </c>
       <c r="U13" s="1">
-        <v>11.819254087679999</v>
+        <v>30.139097923583996</v>
       </c>
       <c r="V13" s="1">
-        <v>9.9207950939999989</v>
+        <v>25.298027489699997</v>
       </c>
       <c r="W13" s="1">
-        <v>10.374038048000003</v>
+        <v>26.453797022400007</v>
       </c>
       <c r="X13" s="1">
-        <v>10.364707267200002</v>
+        <v>26.430003531360004</v>
       </c>
       <c r="Y13" s="1">
-        <v>12.838640505600004</v>
+        <v>32.738533289280014</v>
       </c>
       <c r="Z13" s="1">
-        <v>8.8811117999999993</v>
+        <v>22.646835089999996</v>
       </c>
       <c r="AA13" s="1">
-        <v>10.115380800000004</v>
+        <v>25.794221040000011</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -70428,76 +70428,76 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>4.8574032000000011</v>
+        <v>12.386378160000003</v>
       </c>
       <c r="E14" s="1">
-        <v>4.8746438000000003</v>
+        <v>12.430341690000001</v>
       </c>
       <c r="F14" s="1">
-        <v>4.3217400000000001</v>
+        <v>11.020436999999999</v>
       </c>
       <c r="G14" s="1">
-        <v>4.1783279999999987</v>
+        <v>10.654736399999996</v>
       </c>
       <c r="H14" s="1">
-        <v>3.3897216000000001</v>
+        <v>8.6437900800000005</v>
       </c>
       <c r="I14" s="1">
-        <v>2.7630256000000002</v>
+        <v>7.0457152799999996</v>
       </c>
       <c r="J14" s="1">
-        <v>3.6227983999999998</v>
+        <v>9.2381359199999977</v>
       </c>
       <c r="K14" s="1">
-        <v>0.59891040000000006</v>
+        <v>1.5272215200000001</v>
       </c>
       <c r="L14" s="1">
-        <v>0.54796000000000011</v>
+        <v>1.3972980000000002</v>
       </c>
       <c r="M14" s="1">
-        <v>0.76782419999999985</v>
+        <v>1.9579517099999997</v>
       </c>
       <c r="N14" s="1">
-        <v>0.47046280000000001</v>
+        <v>1.1996801400000001</v>
       </c>
       <c r="O14" s="1">
-        <v>0.54222199999999998</v>
+        <v>1.3826661</v>
       </c>
       <c r="P14" s="1">
-        <v>0.90934000000000026</v>
+        <v>2.3188170000000006</v>
       </c>
       <c r="Q14" s="1">
-        <v>1.7256826000000001</v>
+        <v>4.4004906300000002</v>
       </c>
       <c r="R14" s="1">
-        <v>1.7517695999999998</v>
+        <v>4.4670124800000002</v>
       </c>
       <c r="S14" s="1">
-        <v>1.7930375999999995</v>
+        <v>4.5722458799999979</v>
       </c>
       <c r="T14" s="1">
-        <v>0.94665599999999994</v>
+        <v>2.4139727999999998</v>
       </c>
       <c r="U14" s="1">
-        <v>1.9283327999999995</v>
+        <v>4.9172486399999986</v>
       </c>
       <c r="V14" s="1">
-        <v>1.1316096</v>
+        <v>2.88560448</v>
       </c>
       <c r="W14" s="1">
-        <v>0.87021899999999985</v>
+        <v>2.2190584499999999</v>
       </c>
       <c r="X14" s="1">
-        <v>1.2208032000000002</v>
+        <v>3.1130481600000004</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.80119580000000001</v>
+        <v>2.0430492899999999</v>
       </c>
       <c r="Z14" s="1">
-        <v>3.5858434000000003</v>
+        <v>9.1439006700000007</v>
       </c>
       <c r="AA14" s="1">
-        <v>4.1943412000000002</v>
+        <v>10.69557006</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -70511,76 +70511,76 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>-11.076468000000002</v>
+        <v>-28.244993400000002</v>
       </c>
       <c r="E15" s="1">
-        <v>-11.515885920000001</v>
+        <v>-29.365509096</v>
       </c>
       <c r="F15" s="1">
-        <v>-11.566093440000001</v>
+        <v>-29.493538272000002</v>
       </c>
       <c r="G15" s="1">
-        <v>-13.133164799999999</v>
+        <v>-33.489570239999992</v>
       </c>
       <c r="H15" s="1">
-        <v>-15.987062108160004</v>
+        <v>-40.767008375808011</v>
       </c>
       <c r="I15" s="1">
-        <v>-16.106986721279998</v>
+        <v>-41.072816139263999</v>
       </c>
       <c r="J15" s="1">
-        <v>-15.850631900712003</v>
+        <v>-40.419111346815605</v>
       </c>
       <c r="K15" s="1">
-        <v>-16.746204625919994</v>
+        <v>-42.702821796095982</v>
       </c>
       <c r="L15" s="1">
-        <v>-17.639834385599997</v>
+        <v>-44.981577683279994</v>
       </c>
       <c r="M15" s="1">
-        <v>-22.762502658086397</v>
+        <v>-58.044381778120318</v>
       </c>
       <c r="N15" s="1">
-        <v>-24.638247507993611</v>
+        <v>-62.827531145383709</v>
       </c>
       <c r="O15" s="1">
-        <v>-22.081511560057606</v>
+        <v>-56.307854478146893</v>
       </c>
       <c r="P15" s="1">
-        <v>-20.540324343052802</v>
+        <v>-52.377827074784648</v>
       </c>
       <c r="Q15" s="1">
-        <v>-19.014972419519996</v>
+        <v>-48.488179669775988</v>
       </c>
       <c r="R15" s="1">
-        <v>-18.885222541785605</v>
+        <v>-48.157317481553292</v>
       </c>
       <c r="S15" s="1">
-        <v>-16.344027999999998</v>
+        <v>-41.677271399999995</v>
       </c>
       <c r="T15" s="1">
-        <v>-16.231871335680001</v>
+        <v>-41.391271905984006</v>
       </c>
       <c r="U15" s="1">
-        <v>-13.9448844767232</v>
+        <v>-35.559455415644152</v>
       </c>
       <c r="V15" s="1">
-        <v>-9.0353775360000004</v>
+        <v>-23.040212716800003</v>
       </c>
       <c r="W15" s="1">
-        <v>-10.325666834049597</v>
+        <v>-26.33045042682647</v>
       </c>
       <c r="X15" s="1">
-        <v>-11.234558613599999</v>
+        <v>-28.648124464679995</v>
       </c>
       <c r="Y15" s="1">
-        <v>-10.801319861</v>
+        <v>-27.543365645550001</v>
       </c>
       <c r="Z15" s="1">
-        <v>-8.8401831598079994</v>
+        <v>-22.542467057510397</v>
       </c>
       <c r="AA15" s="1">
-        <v>-10.06559963136</v>
+        <v>-25.667279059967996</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
@@ -70594,76 +70594,76 @@
         <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>9.3517588250999992</v>
+        <v>23.846985004004999</v>
       </c>
       <c r="E16" s="1">
-        <v>10.424181625344</v>
+        <v>26.5816631446272</v>
       </c>
       <c r="F16" s="1">
-        <v>13.059156499199998</v>
+        <v>33.300849072959991</v>
       </c>
       <c r="G16" s="1">
-        <v>11.965986711168002</v>
+        <v>30.513266113478405</v>
       </c>
       <c r="H16" s="1">
-        <v>14.072881041449996</v>
+        <v>35.885846655697492</v>
       </c>
       <c r="I16" s="1">
-        <v>15.219905251200002</v>
+        <v>38.810758390560004</v>
       </c>
       <c r="J16" s="1">
-        <v>14.087609279999999</v>
+        <v>35.923403663999999</v>
       </c>
       <c r="K16" s="1">
-        <v>15.897757459200001</v>
+        <v>40.539281520960003</v>
       </c>
       <c r="L16" s="1">
-        <v>14.865511239600004</v>
+        <v>37.907053660980012</v>
       </c>
       <c r="M16" s="1">
-        <v>18.751341965961604</v>
+        <v>47.815922013202091</v>
       </c>
       <c r="N16" s="1">
-        <v>17.265497037599999</v>
+        <v>44.027017445879999</v>
       </c>
       <c r="O16" s="1">
-        <v>16.29412678608</v>
+        <v>41.550023304503995</v>
       </c>
       <c r="P16" s="1">
-        <v>16.235785912320001</v>
+        <v>41.401254076416002</v>
       </c>
       <c r="Q16" s="1">
-        <v>16.832374562203199</v>
+        <v>42.922555133618154</v>
       </c>
       <c r="R16" s="1">
-        <v>16.076045728512007</v>
+        <v>40.993916607705614</v>
       </c>
       <c r="S16" s="1">
-        <v>12.970865867328003</v>
+        <v>33.075707961686412</v>
       </c>
       <c r="T16" s="1">
-        <v>13.760333469791997</v>
+        <v>35.08885034796959</v>
       </c>
       <c r="U16" s="1">
-        <v>11.582869005926399</v>
+        <v>29.536315965112319</v>
       </c>
       <c r="V16" s="1">
-        <v>10.020003044939999</v>
+        <v>25.551007764596999</v>
       </c>
       <c r="W16" s="1">
-        <v>10.374038048000003</v>
+        <v>26.453797022400007</v>
       </c>
       <c r="X16" s="1">
-        <v>10.779295557888002</v>
+        <v>27.487203672614402</v>
       </c>
       <c r="Y16" s="1">
-        <v>13.095413315712005</v>
+        <v>33.393303955065605</v>
       </c>
       <c r="Z16" s="1">
-        <v>8.969922918</v>
+        <v>22.873303440899999</v>
       </c>
       <c r="AA16" s="1">
-        <v>9.7107655680000047</v>
+        <v>24.762452198400009</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
@@ -70677,76 +70677,76 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>4.6145330400000013</v>
+        <v>11.767059252000003</v>
       </c>
       <c r="E17" s="1">
-        <v>5.0696295520000003</v>
+        <v>12.927555357600001</v>
       </c>
       <c r="F17" s="1">
-        <v>4.2785225999999996</v>
+        <v>10.910232629999999</v>
       </c>
       <c r="G17" s="1">
-        <v>4.3872443999999984</v>
+        <v>11.187473219999996</v>
       </c>
       <c r="H17" s="1">
-        <v>3.4236188159999998</v>
+        <v>8.7302279808000005</v>
       </c>
       <c r="I17" s="1">
-        <v>2.7353953440000005</v>
+        <v>6.9752581272000009</v>
       </c>
       <c r="J17" s="1">
-        <v>3.5141144479999995</v>
+        <v>8.9609918423999986</v>
       </c>
       <c r="K17" s="1">
-        <v>0.60489950400000003</v>
+        <v>1.5424937352000001</v>
       </c>
       <c r="L17" s="1">
-        <v>0.54796000000000011</v>
+        <v>1.3972980000000002</v>
       </c>
       <c r="M17" s="1">
-        <v>0.74478947399999984</v>
+        <v>1.8992131586999994</v>
       </c>
       <c r="N17" s="1">
-        <v>0.46575817200000003</v>
+        <v>1.1876833385999999</v>
       </c>
       <c r="O17" s="1">
-        <v>0.53679977999999995</v>
+        <v>1.3688394389999998</v>
       </c>
       <c r="P17" s="1">
-        <v>0.90934000000000026</v>
+        <v>2.3188170000000006</v>
       </c>
       <c r="Q17" s="1">
-        <v>1.7429394260000002</v>
+        <v>4.4444955362999998</v>
       </c>
       <c r="R17" s="1">
-        <v>1.8393580799999998</v>
+        <v>4.6903631039999993</v>
       </c>
       <c r="S17" s="1">
-        <v>1.7033857199999993</v>
+        <v>4.3436335859999984</v>
       </c>
       <c r="T17" s="1">
-        <v>0.91825632000000001</v>
+        <v>2.3415536159999997</v>
       </c>
       <c r="U17" s="1">
-        <v>1.9090494719999995</v>
+        <v>4.8680761535999988</v>
       </c>
       <c r="V17" s="1">
-        <v>1.1542417919999999</v>
+        <v>2.9433165695999999</v>
       </c>
       <c r="W17" s="1">
-        <v>0.87021899999999985</v>
+        <v>2.2190584499999999</v>
       </c>
       <c r="X17" s="1">
-        <v>1.1963871360000002</v>
+        <v>3.0507871968000004</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.80119580000000001</v>
+        <v>2.0430492899999999</v>
       </c>
       <c r="Z17" s="1">
-        <v>3.4424096640000004</v>
+        <v>8.778144643200001</v>
       </c>
       <c r="AA17" s="1">
-        <v>4.1104543759999999</v>
+        <v>10.481658658799999</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -70760,76 +70760,76 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>-10.965703320000003</v>
+        <v>-27.962543466000007</v>
       </c>
       <c r="E18" s="1">
-        <v>-11.976521356800001</v>
+        <v>-30.540129459840003</v>
       </c>
       <c r="F18" s="1">
-        <v>-10.987788768</v>
+        <v>-28.018861358399995</v>
       </c>
       <c r="G18" s="1">
-        <v>-13.264496447999999</v>
+        <v>-33.824465942399996</v>
       </c>
       <c r="H18" s="1">
-        <v>-16.466673971404802</v>
+        <v>-41.990018627082243</v>
       </c>
       <c r="I18" s="1">
-        <v>-16.268056588492797</v>
+        <v>-41.483544300656632</v>
       </c>
       <c r="J18" s="1">
-        <v>-15.216606624683523</v>
+        <v>-38.802346892942985</v>
       </c>
       <c r="K18" s="1">
-        <v>-17.081128718438393</v>
+        <v>-43.556878232017901</v>
       </c>
       <c r="L18" s="1">
-        <v>-17.816232729455997</v>
+        <v>-45.431393460112794</v>
       </c>
       <c r="M18" s="1">
-        <v>-21.852002551762943</v>
+        <v>-55.722606506995497</v>
       </c>
       <c r="N18" s="1">
-        <v>-25.131012458153482</v>
+        <v>-64.084081768291384</v>
       </c>
       <c r="O18" s="1">
-        <v>-21.86069644445703</v>
+        <v>-55.744775933365425</v>
       </c>
       <c r="P18" s="1">
-        <v>-21.156534073344389</v>
+        <v>-53.94916188702819</v>
       </c>
       <c r="Q18" s="1">
-        <v>-19.585421592105593</v>
+        <v>-49.942825059869264</v>
       </c>
       <c r="R18" s="1">
-        <v>-19.829483668874886</v>
+        <v>-50.565183355630957</v>
       </c>
       <c r="S18" s="1">
-        <v>-16.997789119999997</v>
+        <v>-43.344362255999997</v>
       </c>
       <c r="T18" s="1">
-        <v>-15.7449151956096</v>
+        <v>-40.14953374880448</v>
       </c>
       <c r="U18" s="1">
-        <v>-14.363231011024896</v>
+        <v>-36.626239078113485</v>
       </c>
       <c r="V18" s="1">
-        <v>-8.5836086592000012</v>
+        <v>-21.888202080959999</v>
       </c>
       <c r="W18" s="1">
-        <v>-10.119153497368606</v>
+        <v>-25.803841418289942</v>
       </c>
       <c r="X18" s="1">
-        <v>-11.122213027463999</v>
+        <v>-28.361643220033198</v>
       </c>
       <c r="Y18" s="1">
-        <v>-10.47728026517</v>
+        <v>-26.717064676183497</v>
       </c>
       <c r="Z18" s="1">
-        <v>-8.6633794966118405</v>
+        <v>-22.091617716360194</v>
       </c>
       <c r="AA18" s="1">
-        <v>-10.06559963136</v>
+        <v>-25.667279059967996</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
@@ -70843,76 +70843,76 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>8.884170883845</v>
+        <v>22.654635753804747</v>
       </c>
       <c r="E19" s="1">
-        <v>10.63266525785088</v>
+        <v>27.113296407519741</v>
       </c>
       <c r="F19" s="1">
-        <v>13.581522759167999</v>
+        <v>34.6328830358784</v>
       </c>
       <c r="G19" s="1">
-        <v>12.564286046726401</v>
+        <v>32.038929419152325</v>
       </c>
       <c r="H19" s="1">
-        <v>14.635796283107995</v>
+        <v>37.321280521925388</v>
       </c>
       <c r="I19" s="1">
-        <v>14.763308093664001</v>
+        <v>37.646435638843201</v>
       </c>
       <c r="J19" s="1">
-        <v>14.791989743999999</v>
+        <v>37.719573847199996</v>
       </c>
       <c r="K19" s="1">
-        <v>16.692645332160001</v>
+        <v>42.566245597008006</v>
       </c>
       <c r="L19" s="1">
-        <v>14.419545902412004</v>
+        <v>36.769842051150611</v>
       </c>
       <c r="M19" s="1">
-        <v>18.751341965961604</v>
+        <v>47.815922013202091</v>
       </c>
       <c r="N19" s="1">
-        <v>17.438152007976001</v>
+        <v>44.467287620338801</v>
       </c>
       <c r="O19" s="1">
-        <v>15.968244250358401</v>
+        <v>40.71902283841392</v>
       </c>
       <c r="P19" s="1">
-        <v>17.047575207936003</v>
+        <v>43.471316780236805</v>
       </c>
       <c r="Q19" s="1">
-        <v>16.327403325337105</v>
+        <v>41.634878479609618</v>
       </c>
       <c r="R19" s="1">
-        <v>15.272243442086406</v>
+        <v>38.944220777320332</v>
       </c>
       <c r="S19" s="1">
-        <v>12.841157208654723</v>
+        <v>32.744950882069546</v>
       </c>
       <c r="T19" s="1">
-        <v>13.760333469791997</v>
+        <v>35.08885034796959</v>
       </c>
       <c r="U19" s="1">
-        <v>11.814526386044927</v>
+        <v>30.127042284414564</v>
       </c>
       <c r="V19" s="1">
-        <v>10.420803166737599</v>
+        <v>26.573048075180878</v>
       </c>
       <c r="W19" s="1">
-        <v>10.685259189440004</v>
+        <v>27.247410933072008</v>
       </c>
       <c r="X19" s="1">
-        <v>10.779295557888002</v>
+        <v>27.487203672614402</v>
       </c>
       <c r="Y19" s="1">
-        <v>12.833505049397765</v>
+        <v>32.725437875964296</v>
       </c>
       <c r="Z19" s="1">
-        <v>8.6111260012799988</v>
+        <v>21.958371303263995</v>
       </c>
       <c r="AA19" s="1">
-        <v>9.4194426009600036</v>
+        <v>24.01957863244801</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
@@ -70926,76 +70926,76 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>5.1376380000000017</v>
+        <v>13.100976900000003</v>
       </c>
       <c r="E20" s="1">
-        <v>5.3090180000000009</v>
+        <v>13.537995900000002</v>
       </c>
       <c r="F20" s="1">
-        <v>4.7539140000000009</v>
+        <v>12.122480700000001</v>
       </c>
       <c r="G20" s="1">
-        <v>4.5060399999999996</v>
+        <v>11.490402</v>
       </c>
       <c r="H20" s="1">
-        <v>3.6917760000000004</v>
+        <v>9.4140288000000005</v>
       </c>
       <c r="I20" s="1">
-        <v>3.1333280000000006</v>
+        <v>7.9899864000000012</v>
       </c>
       <c r="J20" s="1">
-        <v>3.8318060000000003</v>
+        <v>9.7711053000000003</v>
       </c>
       <c r="K20" s="1">
-        <v>0.66545600000000016</v>
+        <v>1.6969128000000002</v>
       </c>
       <c r="L20" s="1">
-        <v>0.58520000000000005</v>
+        <v>1.4922600000000001</v>
       </c>
       <c r="M20" s="1">
-        <v>0.85313799999999984</v>
+        <v>2.1755018999999995</v>
       </c>
       <c r="N20" s="1">
-        <v>0.5024360000000001</v>
+        <v>1.2812118000000001</v>
       </c>
       <c r="O20" s="1">
-        <v>0.62783599999999995</v>
+        <v>1.6009818</v>
       </c>
       <c r="P20" s="1">
-        <v>1.0002740000000003</v>
+        <v>2.5506987000000008</v>
       </c>
       <c r="Q20" s="1">
-        <v>1.8429620000000002</v>
+        <v>4.699553100000001</v>
       </c>
       <c r="R20" s="1">
-        <v>1.966272</v>
+        <v>5.0139936000000001</v>
       </c>
       <c r="S20" s="1">
-        <v>1.9336679999999997</v>
+        <v>4.9308533999999993</v>
       </c>
       <c r="T20" s="1">
-        <v>1.0847100000000001</v>
+        <v>2.7660104999999997</v>
       </c>
       <c r="U20" s="1">
-        <v>2.2095479999999998</v>
+        <v>5.6343473999999993</v>
       </c>
       <c r="V20" s="1">
-        <v>1.2966360000000001</v>
+        <v>3.3064217999999999</v>
       </c>
       <c r="W20" s="1">
-        <v>0.91165799999999986</v>
+        <v>2.3247278999999992</v>
       </c>
       <c r="X20" s="1">
-        <v>1.3844160000000003</v>
+        <v>3.5302608000000011</v>
       </c>
       <c r="Y20" s="1">
-        <v>0.85564600000000002</v>
+        <v>2.1818972999999997</v>
       </c>
       <c r="Z20" s="1">
-        <v>3.9053740000000006</v>
+        <v>9.9587037000000009</v>
       </c>
       <c r="AA20" s="1">
-        <v>4.7079339999999998</v>
+        <v>12.0052317</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
@@ -71009,76 +71009,76 @@
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>-10.636732220400004</v>
+        <v>-27.123667162020009</v>
       </c>
       <c r="E21" s="1">
-        <v>-12.575347424640002</v>
+        <v>-32.067135932832009</v>
       </c>
       <c r="F21" s="1">
-        <v>-10.658155104959999</v>
+        <v>-27.178295517647996</v>
       </c>
       <c r="G21" s="1">
-        <v>-13.529786376959999</v>
+        <v>-34.500955261247995</v>
       </c>
       <c r="H21" s="1">
-        <v>-17.125340930260997</v>
+        <v>-43.669619372165542</v>
       </c>
       <c r="I21" s="1">
-        <v>-16.268056588492797</v>
+        <v>-41.483544300656632</v>
       </c>
       <c r="J21" s="1">
-        <v>-15.36877269093036</v>
+        <v>-39.190370361872418</v>
       </c>
       <c r="K21" s="1">
-        <v>-16.910317431254008</v>
+        <v>-43.121309449697719</v>
       </c>
       <c r="L21" s="1">
-        <v>-17.994395056750555</v>
+        <v>-45.885707394713911</v>
       </c>
       <c r="M21" s="1">
-        <v>-21.852002551762943</v>
+        <v>-55.722606506995497</v>
       </c>
       <c r="N21" s="1">
-        <v>-24.879702333571945</v>
+        <v>-63.443240950608462</v>
       </c>
       <c r="O21" s="1">
-        <v>-22.735124302235313</v>
+        <v>-57.974566970700053</v>
       </c>
       <c r="P21" s="1">
-        <v>-21.156534073344389</v>
+        <v>-53.94916188702819</v>
       </c>
       <c r="Q21" s="1">
-        <v>-20.172984239868761</v>
+        <v>-51.441109811665342</v>
       </c>
       <c r="R21" s="1">
-        <v>-19.234599158808638</v>
+        <v>-49.048227854962029</v>
       </c>
       <c r="S21" s="1">
-        <v>-16.657833337599996</v>
+        <v>-42.477475010879992</v>
       </c>
       <c r="T21" s="1">
-        <v>-14.957669435829121</v>
+        <v>-38.142057061364262</v>
       </c>
       <c r="U21" s="1">
-        <v>-14.363231011024896</v>
+        <v>-36.626239078113485</v>
       </c>
       <c r="V21" s="1">
-        <v>-8.7552808323840008</v>
+        <v>-22.325966122579199</v>
       </c>
       <c r="W21" s="1">
-        <v>-10.422728102289664</v>
+        <v>-26.577956660838641</v>
       </c>
       <c r="X21" s="1">
-        <v>-11.56710154856256</v>
+        <v>-29.496108948834525</v>
       </c>
       <c r="Y21" s="1">
-        <v>-10.267734659866601</v>
+        <v>-26.182723382659834</v>
       </c>
       <c r="Z21" s="1">
-        <v>-8.6633794966118405</v>
+        <v>-22.091617716360194</v>
       </c>
       <c r="AA21" s="1">
-        <v>-10.367567620300798</v>
+        <v>-26.437297431767036</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
@@ -71092,76 +71092,76 @@
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>8.4399623396527499</v>
+        <v>21.521903966114511</v>
       </c>
       <c r="E22" s="1">
-        <v>10.845318563007897</v>
+        <v>27.65556233567014</v>
       </c>
       <c r="F22" s="1">
-        <v>13.988968441943038</v>
+        <v>35.671869526954751</v>
       </c>
       <c r="G22" s="1">
-        <v>12.313000325791872</v>
+        <v>31.398150830769271</v>
       </c>
       <c r="H22" s="1">
-        <v>14.928512208770155</v>
+        <v>38.067706132363888</v>
       </c>
       <c r="I22" s="1">
-        <v>14.61567501272736</v>
+        <v>37.269971282454769</v>
       </c>
       <c r="J22" s="1">
-        <v>14.348230051679998</v>
+        <v>36.587986631783991</v>
       </c>
       <c r="K22" s="1">
-        <v>17.1934246921248</v>
+        <v>43.843232964918236</v>
       </c>
       <c r="L22" s="1">
-        <v>15.140523197532605</v>
+        <v>38.608334153708142</v>
       </c>
       <c r="M22" s="1">
-        <v>19.313882224940453</v>
+        <v>49.250399673598153</v>
       </c>
       <c r="N22" s="1">
-        <v>17.089388967816479</v>
+        <v>43.577941867932026</v>
       </c>
       <c r="O22" s="1">
-        <v>16.287609135365571</v>
+        <v>41.533403295182204</v>
       </c>
       <c r="P22" s="1">
-        <v>17.72947821625344</v>
+        <v>45.210169451446269</v>
       </c>
       <c r="Q22" s="1">
-        <v>16.817225425097217</v>
+        <v>42.883924833997895</v>
       </c>
       <c r="R22" s="1">
-        <v>14.814076138823815</v>
+        <v>37.775894154000724</v>
       </c>
       <c r="S22" s="1">
-        <v>12.712745636568174</v>
+        <v>32.417501373248847</v>
       </c>
       <c r="T22" s="1">
-        <v>14.035540139187836</v>
+        <v>35.790627354928979</v>
       </c>
       <c r="U22" s="1">
-        <v>11.46009059446358</v>
+        <v>29.223231015882128</v>
       </c>
       <c r="V22" s="1">
-        <v>10.733427261739727</v>
+        <v>27.370239517436303</v>
       </c>
       <c r="W22" s="1">
-        <v>11.112669557017602</v>
+        <v>28.337307370394882</v>
       </c>
       <c r="X22" s="1">
-        <v>10.671502602309122</v>
+        <v>27.212331635888262</v>
       </c>
       <c r="Y22" s="1">
-        <v>12.705169998903786</v>
+        <v>32.398183497204656</v>
       </c>
       <c r="Z22" s="1">
-        <v>8.783348521305598</v>
+        <v>22.397538729329273</v>
       </c>
       <c r="AA22" s="1">
-        <v>9.5136370269696027</v>
+        <v>24.259774418772484</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
@@ -71175,76 +71175,76 @@
         <v>2</v>
       </c>
       <c r="D23" s="1">
-        <v>5.3945199000000015</v>
+        <v>13.756025745000002</v>
       </c>
       <c r="E23" s="1">
-        <v>5.5744689000000003</v>
+        <v>14.214895695000001</v>
       </c>
       <c r="F23" s="1">
-        <v>4.5637574400000007</v>
+        <v>11.637581472000003</v>
       </c>
       <c r="G23" s="1">
-        <v>4.3708587999999997</v>
+        <v>11.145689939999999</v>
       </c>
       <c r="H23" s="1">
-        <v>3.6548582400000003</v>
+        <v>9.3198885120000003</v>
       </c>
       <c r="I23" s="1">
-        <v>3.0706614400000007</v>
+        <v>7.8301866720000017</v>
       </c>
       <c r="J23" s="1">
-        <v>3.7934879399999999</v>
+        <v>9.6733942469999992</v>
       </c>
       <c r="K23" s="1">
-        <v>0.67211056000000013</v>
+        <v>1.7138819280000004</v>
       </c>
       <c r="L23" s="1">
-        <v>0.57349600000000001</v>
+        <v>1.4624147999999999</v>
       </c>
       <c r="M23" s="1">
-        <v>0.86166937999999993</v>
+        <v>2.197256919</v>
       </c>
       <c r="N23" s="1">
-        <v>0.52253344000000013</v>
+        <v>1.3324602720000003</v>
       </c>
       <c r="O23" s="1">
-        <v>0.65294943999999999</v>
+        <v>1.665021072</v>
       </c>
       <c r="P23" s="1">
-        <v>0.98026852000000031</v>
+        <v>2.4996847260000008</v>
       </c>
       <c r="Q23" s="1">
-        <v>1.9166804800000004</v>
+        <v>4.8875352240000014</v>
       </c>
       <c r="R23" s="1">
-        <v>2.0645856</v>
+        <v>5.2646932799999995</v>
       </c>
       <c r="S23" s="1">
-        <v>1.8369845999999999</v>
+        <v>4.6843107299999991</v>
       </c>
       <c r="T23" s="1">
-        <v>1.1172513000000002</v>
+        <v>2.8489908150000001</v>
       </c>
       <c r="U23" s="1">
-        <v>2.2979299199999996</v>
+        <v>5.8597212959999991</v>
       </c>
       <c r="V23" s="1">
-        <v>1.2707032800000002</v>
+        <v>3.2402933640000007</v>
       </c>
       <c r="W23" s="1">
-        <v>0.90254141999999993</v>
+        <v>2.3014806209999996</v>
       </c>
       <c r="X23" s="1">
-        <v>1.3844160000000003</v>
+        <v>3.5302608000000011</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.88131538000000009</v>
+        <v>2.247354219</v>
       </c>
       <c r="Z23" s="1">
-        <v>4.1006427000000008</v>
+        <v>10.456638885</v>
       </c>
       <c r="AA23" s="1">
-        <v>4.8020926800000003</v>
+        <v>12.245336333999999</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
@@ -71258,76 +71258,76 @@
         <v>2</v>
       </c>
       <c r="D24" s="1">
-        <v>-10.743099542604005</v>
+        <v>-27.39490383364021</v>
       </c>
       <c r="E24" s="1">
-        <v>-12.952607847379202</v>
+        <v>-33.02915001081697</v>
       </c>
       <c r="F24" s="1">
-        <v>-10.444992002860799</v>
+        <v>-26.634729607295036</v>
       </c>
       <c r="G24" s="1">
-        <v>-13.259190649420798</v>
+        <v>-33.810936156023033</v>
       </c>
       <c r="H24" s="1">
-        <v>-17.296594339563608</v>
+        <v>-44.106315565887193</v>
       </c>
       <c r="I24" s="1">
-        <v>-15.780014890838013</v>
+        <v>-40.239037971636932</v>
       </c>
       <c r="J24" s="1">
-        <v>-15.061397237111754</v>
+        <v>-38.406562954634971</v>
       </c>
       <c r="K24" s="1">
-        <v>-17.248523779879086</v>
+        <v>-43.98373563869167</v>
       </c>
       <c r="L24" s="1">
-        <v>-18.714170859020577</v>
+        <v>-47.721135690502472</v>
       </c>
       <c r="M24" s="1">
-        <v>-22.507562628315831</v>
+        <v>-57.394284702205361</v>
       </c>
       <c r="N24" s="1">
-        <v>-23.88451424022907</v>
+        <v>-60.905511312584132</v>
       </c>
       <c r="O24" s="1">
-        <v>-23.417178031302374</v>
+        <v>-59.713803979821051</v>
       </c>
       <c r="P24" s="1">
-        <v>-20.521838051144059</v>
+        <v>-52.330687030417351</v>
       </c>
       <c r="Q24" s="1">
-        <v>-19.769524555071385</v>
+        <v>-50.412287615432028</v>
       </c>
       <c r="R24" s="1">
-        <v>-19.234599158808638</v>
+        <v>-49.048227854962029</v>
       </c>
       <c r="S24" s="1">
-        <v>-15.991520004095996</v>
+        <v>-40.778376010444788</v>
       </c>
       <c r="T24" s="1">
-        <v>-15.107246130187413</v>
+        <v>-38.523477631977904</v>
       </c>
       <c r="U24" s="1">
-        <v>-13.645069460473652</v>
+        <v>-34.79492712420781</v>
       </c>
       <c r="V24" s="1">
-        <v>-8.405069599088641</v>
+        <v>-21.432927477676035</v>
       </c>
       <c r="W24" s="1">
-        <v>-10.422728102289664</v>
+        <v>-26.577956660838641</v>
       </c>
       <c r="X24" s="1">
-        <v>-12.029785610505062</v>
+        <v>-30.67595330678791</v>
       </c>
       <c r="Y24" s="1">
-        <v>-9.9597026200706029</v>
+        <v>-25.397241681180038</v>
       </c>
       <c r="Z24" s="1">
-        <v>-8.8366470865440778</v>
+        <v>-22.533450070687401</v>
       </c>
       <c r="AA24" s="1">
-        <v>-10.263891944097791</v>
+        <v>-26.172924457449366</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
@@ -71341,76 +71341,76 @@
         <v>2</v>
       </c>
       <c r="D25" s="1">
-        <v>8.3555627162562232</v>
+        <v>21.306684926453368</v>
       </c>
       <c r="E25" s="1">
-        <v>10.845318563007897</v>
+        <v>27.65556233567014</v>
       </c>
       <c r="F25" s="1">
-        <v>13.289520019845886</v>
+        <v>33.888276050607004</v>
       </c>
       <c r="G25" s="1">
-        <v>12.55926033230771</v>
+        <v>32.026113847384664</v>
       </c>
       <c r="H25" s="1">
-        <v>15.227082452945558</v>
+        <v>38.829060255011171</v>
       </c>
       <c r="I25" s="1">
-        <v>15.054145263109181</v>
+        <v>38.388070420928415</v>
       </c>
       <c r="J25" s="1">
-        <v>14.491712352196798</v>
+        <v>36.953866498101831</v>
       </c>
       <c r="K25" s="1">
-        <v>17.1934246921248</v>
+        <v>43.843232964918236</v>
       </c>
       <c r="L25" s="1">
-        <v>14.383497037655975</v>
+        <v>36.67791744602274</v>
       </c>
       <c r="M25" s="1">
-        <v>20.086437513938073</v>
+        <v>51.220415660542081</v>
       </c>
       <c r="N25" s="1">
-        <v>17.602070636850975</v>
+        <v>44.885280123969984</v>
       </c>
       <c r="O25" s="1">
-        <v>16.450485226719227</v>
+        <v>41.94873732813403</v>
       </c>
       <c r="P25" s="1">
-        <v>17.72947821625344</v>
+        <v>45.210169451446269</v>
       </c>
       <c r="Q25" s="1">
-        <v>16.649053170846244</v>
+        <v>42.455085585657919</v>
       </c>
       <c r="R25" s="1">
-        <v>14.073372331882624</v>
+        <v>35.887099446300688</v>
       </c>
       <c r="S25" s="1">
-        <v>12.077108354739764</v>
+        <v>30.796626304586397</v>
       </c>
       <c r="T25" s="1">
-        <v>13.614473935012199</v>
+        <v>34.71690853428111</v>
       </c>
       <c r="U25" s="1">
-        <v>11.23088878257431</v>
+        <v>28.638766395564488</v>
       </c>
       <c r="V25" s="1">
-        <v>10.733427261739727</v>
+        <v>27.370239517436303</v>
       </c>
       <c r="W25" s="1">
-        <v>11.446049643728131</v>
+        <v>29.187426591506732</v>
       </c>
       <c r="X25" s="1">
-        <v>10.137927472193665</v>
+        <v>25.851715054093845</v>
       </c>
       <c r="Y25" s="1">
-        <v>13.340428498848976</v>
+        <v>34.018092672064881</v>
       </c>
       <c r="Z25" s="1">
-        <v>8.6076815508794855</v>
+        <v>21.94958795474269</v>
       </c>
       <c r="AA25" s="1">
-        <v>9.7990461377786904</v>
+        <v>24.987567651335663</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
@@ -71424,76 +71424,76 @@
         <v>3</v>
       </c>
       <c r="D26" s="1">
-        <v>5.556355497000002</v>
+        <v>14.168706517350005</v>
       </c>
       <c r="E26" s="1">
-        <v>5.6302135890000002</v>
+        <v>14.35704465195</v>
       </c>
       <c r="F26" s="1">
-        <v>4.518119865600001</v>
+        <v>11.521205657280003</v>
       </c>
       <c r="G26" s="1">
-        <v>4.5894017399999996</v>
+        <v>11.702974436999998</v>
       </c>
       <c r="H26" s="1">
-        <v>3.6914068224000003</v>
+        <v>9.41308739712</v>
       </c>
       <c r="I26" s="1">
-        <v>3.0706614400000007</v>
+        <v>7.8301866720000017</v>
       </c>
       <c r="J26" s="1">
-        <v>3.6038135429999998</v>
+        <v>9.1897245346499989</v>
       </c>
       <c r="K26" s="1">
-        <v>0.63850503200000008</v>
+        <v>1.6281878316000002</v>
       </c>
       <c r="L26" s="1">
-        <v>0.54482120000000001</v>
+        <v>1.3892940600000001</v>
       </c>
       <c r="M26" s="1">
-        <v>0.83581929859999993</v>
+        <v>2.1313392114299998</v>
       </c>
       <c r="N26" s="1">
-        <v>0.51730810560000007</v>
+        <v>1.31913566928</v>
       </c>
       <c r="O26" s="1">
-        <v>0.6660084288</v>
+        <v>1.6983214934399999</v>
       </c>
       <c r="P26" s="1">
-        <v>0.96066314960000032</v>
+        <v>2.4496910314800009</v>
       </c>
       <c r="Q26" s="1">
-        <v>2.0125145040000003</v>
+        <v>5.1319119852000004</v>
       </c>
       <c r="R26" s="1">
-        <v>2.1678148799999999</v>
+        <v>5.527927944</v>
       </c>
       <c r="S26" s="1">
-        <v>1.9288338299999999</v>
+        <v>4.9185262664999989</v>
       </c>
       <c r="T26" s="1">
-        <v>1.1284238130000002</v>
+        <v>2.8774807231500001</v>
       </c>
       <c r="U26" s="1">
-        <v>2.2979299199999996</v>
+        <v>5.8597212959999991</v>
       </c>
       <c r="V26" s="1">
-        <v>1.2707032800000002</v>
+        <v>3.2402933640000007</v>
       </c>
       <c r="W26" s="1">
-        <v>0.86643976319999993</v>
+        <v>2.2094213961599998</v>
       </c>
       <c r="X26" s="1">
-        <v>1.3428835200000002</v>
+        <v>3.4243529760000007</v>
       </c>
       <c r="Y26" s="1">
-        <v>0.89012853380000012</v>
+        <v>2.2698277611900002</v>
       </c>
       <c r="Z26" s="1">
-        <v>3.9776234190000008</v>
+        <v>10.142939718450002</v>
       </c>
       <c r="AA26" s="1">
-        <v>4.9461554604</v>
+        <v>12.612696424019999</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
@@ -71507,76 +71507,76 @@
         <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>-11.280254519734205</v>
+        <v>-28.764649025322221</v>
       </c>
       <c r="E27" s="1">
-        <v>-12.823081768905411</v>
+        <v>-32.698858510708796</v>
       </c>
       <c r="F27" s="1">
-        <v>-10.340542082832192</v>
+        <v>-26.368382311222089</v>
       </c>
       <c r="G27" s="1">
-        <v>-12.861414929938173</v>
+        <v>-32.796608071342341</v>
       </c>
       <c r="H27" s="1">
-        <v>-17.123628396167973</v>
+        <v>-43.665252410228334</v>
       </c>
       <c r="I27" s="1">
-        <v>-16.253415337563155</v>
+        <v>-41.446209110786043</v>
       </c>
       <c r="J27" s="1">
-        <v>-14.308327375256164</v>
+        <v>-36.486234806903219</v>
       </c>
       <c r="K27" s="1">
-        <v>-17.076038542080298</v>
+        <v>-43.54389828230476</v>
       </c>
       <c r="L27" s="1">
-        <v>-18.152745733249962</v>
+        <v>-46.289501619787401</v>
       </c>
       <c r="M27" s="1">
-        <v>-23.182789507165307</v>
+        <v>-59.116113243271528</v>
       </c>
       <c r="N27" s="1">
-        <v>-23.88451424022907</v>
+        <v>-60.905511312584132</v>
       </c>
       <c r="O27" s="1">
-        <v>-23.417178031302374</v>
+        <v>-59.713803979821051</v>
       </c>
       <c r="P27" s="1">
-        <v>-20.111401290121179</v>
+        <v>-51.284073289809008</v>
       </c>
       <c r="Q27" s="1">
-        <v>-19.769524555071385</v>
+        <v>-50.412287615432028</v>
       </c>
       <c r="R27" s="1">
-        <v>-19.61929114198481</v>
+        <v>-50.029192412061263</v>
       </c>
       <c r="S27" s="1">
-        <v>-16.311350404177915</v>
+        <v>-41.593943530653682</v>
       </c>
       <c r="T27" s="1">
-        <v>-15.560463514093035</v>
+        <v>-39.679181960937235</v>
       </c>
       <c r="U27" s="1">
-        <v>-13.645069460473652</v>
+        <v>-34.79492712420781</v>
       </c>
       <c r="V27" s="1">
-        <v>-8.5731709910704144</v>
+        <v>-21.861586027229556</v>
       </c>
       <c r="W27" s="1">
-        <v>-10.839637226381251</v>
+        <v>-27.641074927272193</v>
       </c>
       <c r="X27" s="1">
-        <v>-11.66889204218991</v>
+        <v>-29.755674707584269</v>
       </c>
       <c r="Y27" s="1">
-        <v>-10.059299646271308</v>
+        <v>-25.651214097991836</v>
       </c>
       <c r="Z27" s="1">
-        <v>-8.394814732216874</v>
+        <v>-21.406777567153028</v>
       </c>
       <c r="AA27" s="1">
-        <v>-10.469169782979748</v>
+        <v>-26.696382946598355</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
@@ -71590,76 +71590,76 @@
         <v>3</v>
       </c>
       <c r="D28" s="1">
-        <v>8.104895834768536</v>
+        <v>20.667484378659768</v>
       </c>
       <c r="E28" s="1">
-        <v>10.519959006117661</v>
+        <v>26.825895465600038</v>
       </c>
       <c r="F28" s="1">
-        <v>13.289520019845886</v>
+        <v>33.888276050607004</v>
       </c>
       <c r="G28" s="1">
-        <v>12.93603814227694</v>
+        <v>32.986897262806195</v>
       </c>
       <c r="H28" s="1">
-        <v>15.988436575592836</v>
+        <v>40.770513267761729</v>
       </c>
       <c r="I28" s="1">
-        <v>14.903603810478089</v>
+        <v>38.004189716719125</v>
       </c>
       <c r="J28" s="1">
-        <v>15.216297969806638</v>
+        <v>38.801559823006926</v>
       </c>
       <c r="K28" s="1">
-        <v>16.849556198282304</v>
+        <v>42.966368305619881</v>
       </c>
       <c r="L28" s="1">
-        <v>14.239662067279415</v>
+        <v>36.311138271562513</v>
       </c>
       <c r="M28" s="1">
-        <v>21.090759389634979</v>
+        <v>53.781436443569191</v>
       </c>
       <c r="N28" s="1">
-        <v>18.306153462325014</v>
+        <v>46.680691328928788</v>
       </c>
       <c r="O28" s="1">
-        <v>15.95697066991765</v>
+        <v>40.690275208290004</v>
       </c>
       <c r="P28" s="1">
-        <v>17.72947821625344</v>
+        <v>45.210169451446269</v>
       </c>
       <c r="Q28" s="1">
-        <v>17.315015297680091</v>
+        <v>44.153289009084233</v>
       </c>
       <c r="R28" s="1">
-        <v>14.073372331882624</v>
+        <v>35.887099446300688</v>
       </c>
       <c r="S28" s="1">
-        <v>11.835566187644968</v>
+        <v>30.180693778494664</v>
       </c>
       <c r="T28" s="1">
-        <v>13.206039716961834</v>
+        <v>33.675401278252679</v>
       </c>
       <c r="U28" s="1">
-        <v>11.792433221703025</v>
+        <v>30.070704715342714</v>
       </c>
       <c r="V28" s="1">
-        <v>10.733427261739727</v>
+        <v>27.370239517436303</v>
       </c>
       <c r="W28" s="1">
-        <v>11.331589147290849</v>
+        <v>28.895552325591662</v>
       </c>
       <c r="X28" s="1">
-        <v>10.543444571081411</v>
+        <v>26.885783656257598</v>
       </c>
       <c r="Y28" s="1">
-        <v>12.940215643883507</v>
+        <v>32.997549891902942</v>
       </c>
       <c r="Z28" s="1">
-        <v>8.8659119974058704</v>
+        <v>22.608075593384967</v>
       </c>
       <c r="AA28" s="1">
-        <v>9.5050747536453297</v>
+        <v>24.237940621795588</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -71673,76 +71673,76 @@
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>4.880756100000001</v>
+        <v>12.445928055000003</v>
       </c>
       <c r="E29" s="1">
-        <v>5.0435671000000006</v>
+        <v>12.861096105000001</v>
       </c>
       <c r="F29" s="1">
-        <v>4.5162183000000002</v>
+        <v>11.516356665</v>
       </c>
       <c r="G29" s="1">
-        <v>4.2807379999999995</v>
+        <v>10.915881899999999</v>
       </c>
       <c r="H29" s="1">
-        <v>3.5071872000000002</v>
+        <v>8.9433273599999996</v>
       </c>
       <c r="I29" s="1">
-        <v>2.9766616000000004</v>
+        <v>7.5904870800000008</v>
       </c>
       <c r="J29" s="1">
-        <v>3.6402157000000002</v>
+        <v>9.2825500349999999</v>
       </c>
       <c r="K29" s="1">
-        <v>0.63218320000000017</v>
+        <v>1.6120671600000005</v>
       </c>
       <c r="L29" s="1">
-        <v>0.55593999999999999</v>
+        <v>1.4176469999999999</v>
       </c>
       <c r="M29" s="1">
-        <v>0.81048109999999984</v>
+        <v>2.0667268049999996</v>
       </c>
       <c r="N29" s="1">
-        <v>0.47731420000000008</v>
+        <v>1.2171512100000001</v>
       </c>
       <c r="O29" s="1">
-        <v>0.59644419999999987</v>
+        <v>1.5209327099999996</v>
       </c>
       <c r="P29" s="1">
-        <v>0.95026030000000028</v>
+        <v>2.4231637650000009</v>
       </c>
       <c r="Q29" s="1">
-        <v>1.7508139</v>
+        <v>4.4645754450000004</v>
       </c>
       <c r="R29" s="1">
-        <v>1.8679584</v>
+        <v>4.7632939199999997</v>
       </c>
       <c r="S29" s="1">
-        <v>1.8369845999999996</v>
+        <v>4.6843107299999991</v>
       </c>
       <c r="T29" s="1">
-        <v>1.0304745</v>
+        <v>2.6277099749999997</v>
       </c>
       <c r="U29" s="1">
-        <v>2.0990705999999997</v>
+        <v>5.3526300299999994</v>
       </c>
       <c r="V29" s="1">
-        <v>1.2318042</v>
+        <v>3.1411007099999999</v>
       </c>
       <c r="W29" s="1">
-        <v>0.86607509999999988</v>
+        <v>2.2084915049999996</v>
       </c>
       <c r="X29" s="1">
-        <v>1.3151952000000002</v>
+        <v>3.3537477600000005</v>
       </c>
       <c r="Y29" s="1">
-        <v>0.81286369999999997</v>
+        <v>2.0728024349999998</v>
       </c>
       <c r="Z29" s="1">
-        <v>3.7101053000000004</v>
+        <v>9.4607685150000016</v>
       </c>
       <c r="AA29" s="1">
-        <v>4.4725372999999999</v>
+        <v>11.404970115000001</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -71756,76 +71756,76 @@
         <v>1</v>
       </c>
       <c r="D30" s="1">
-        <v>-11.167451974536863</v>
+        <v>-28.477002535069005</v>
       </c>
       <c r="E30" s="1">
-        <v>-12.823081768905411</v>
+        <v>-32.698858510708796</v>
       </c>
       <c r="F30" s="1">
-        <v>-10.030325820347226</v>
+        <v>-25.577330841885427</v>
       </c>
       <c r="G30" s="1">
-        <v>-13.3758715271357</v>
+        <v>-34.108472394196035</v>
       </c>
       <c r="H30" s="1">
-        <v>-17.808573532014695</v>
+        <v>-45.411862506637476</v>
       </c>
       <c r="I30" s="1">
-        <v>-16.90355195106568</v>
+        <v>-43.104057475217481</v>
       </c>
       <c r="J30" s="1">
-        <v>-15.023743744018972</v>
+        <v>-38.310546547248379</v>
       </c>
       <c r="K30" s="1">
-        <v>-17.759080083763511</v>
+        <v>-45.285654213596956</v>
       </c>
       <c r="L30" s="1">
-        <v>-18.697328105247461</v>
+        <v>-47.678186668381024</v>
       </c>
       <c r="M30" s="1">
-        <v>-23.646445297308613</v>
+        <v>-60.298435508136961</v>
       </c>
       <c r="N30" s="1">
-        <v>-24.12335938263136</v>
+        <v>-61.514566425709965</v>
       </c>
       <c r="O30" s="1">
-        <v>-23.651349811615397</v>
+        <v>-60.310942019619254</v>
       </c>
       <c r="P30" s="1">
-        <v>-19.306945238516331</v>
+        <v>-49.232710358216643</v>
       </c>
       <c r="Q30" s="1">
-        <v>-18.978743572868531</v>
+        <v>-48.39579611081475</v>
       </c>
       <c r="R30" s="1">
-        <v>-20.011676964824506</v>
+        <v>-51.029776260302491</v>
       </c>
       <c r="S30" s="1">
-        <v>-16.474463908219697</v>
+        <v>-42.009882965960223</v>
       </c>
       <c r="T30" s="1">
-        <v>-15.716068149233966</v>
+        <v>-40.075973780546612</v>
       </c>
       <c r="U30" s="1">
-        <v>-14.054421544287861</v>
+        <v>-35.838774937934041</v>
       </c>
       <c r="V30" s="1">
-        <v>-8.144512441516893</v>
+        <v>-20.768506725868075</v>
       </c>
       <c r="W30" s="1">
-        <v>-10.948033598645063</v>
+        <v>-27.91748567654491</v>
       </c>
       <c r="X30" s="1">
-        <v>-11.202136360502314</v>
+        <v>-28.565447719280897</v>
       </c>
       <c r="Y30" s="1">
-        <v>-10.361078635659446</v>
+        <v>-26.420750520931588</v>
       </c>
       <c r="Z30" s="1">
-        <v>-8.5627110268612121</v>
+        <v>-21.83491311849609</v>
       </c>
       <c r="AA30" s="1">
-        <v>-10.992628272128735</v>
+        <v>-28.031202093928275</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
@@ -71839,76 +71839,76 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>8.4290916681592769</v>
+        <v>21.494183753806155</v>
       </c>
       <c r="E31" s="1">
-        <v>10.625158596178837</v>
+        <v>27.094154420256036</v>
       </c>
       <c r="F31" s="1">
-        <v>13.821100820639721</v>
+        <v>35.243807092631286</v>
       </c>
       <c r="G31" s="1">
-        <v>13.194758905122479</v>
+        <v>33.646635208062321</v>
       </c>
       <c r="H31" s="1">
-        <v>16.468089672860621</v>
+        <v>41.993628665794581</v>
       </c>
       <c r="I31" s="1">
-        <v>14.605531734268528</v>
+        <v>37.244105922384747</v>
       </c>
       <c r="J31" s="1">
-        <v>14.455483071316305</v>
+        <v>36.861481831856572</v>
       </c>
       <c r="K31" s="1">
-        <v>16.849556198282304</v>
+        <v>42.966368305619881</v>
       </c>
       <c r="L31" s="1">
-        <v>14.524455308625004</v>
+        <v>37.037361036993758</v>
       </c>
       <c r="M31" s="1">
-        <v>22.145297359116725</v>
+        <v>56.470508265747647</v>
       </c>
       <c r="N31" s="1">
-        <v>17.940030393078516</v>
+        <v>45.747077502350216</v>
       </c>
       <c r="O31" s="1">
-        <v>15.95697066991765</v>
+        <v>40.690275208290004</v>
       </c>
       <c r="P31" s="1">
-        <v>18.438657344903575</v>
+        <v>47.018576229504113</v>
       </c>
       <c r="Q31" s="1">
-        <v>16.449264532796086</v>
+        <v>41.945624558630016</v>
       </c>
       <c r="R31" s="1">
-        <v>14.073372331882624</v>
+        <v>35.887099446300688</v>
       </c>
       <c r="S31" s="1">
-        <v>12.427344497027216</v>
+        <v>31.6897284674194</v>
       </c>
       <c r="T31" s="1">
-        <v>13.073979319792215</v>
+        <v>33.338647265470151</v>
       </c>
       <c r="U31" s="1">
-        <v>11.556584557268964</v>
+        <v>29.46929062103586</v>
       </c>
       <c r="V31" s="1">
-        <v>10.948095806974523</v>
+        <v>27.917644307785036</v>
       </c>
       <c r="W31" s="1">
-        <v>11.671536821709573</v>
+        <v>29.76241889535941</v>
       </c>
       <c r="X31" s="1">
-        <v>10.75431346250304</v>
+        <v>27.42349932938275</v>
       </c>
       <c r="Y31" s="1">
-        <v>12.552009174567001</v>
+        <v>32.007623395145849</v>
       </c>
       <c r="Z31" s="1">
-        <v>8.9545711173799294</v>
+        <v>22.834156349318821</v>
       </c>
       <c r="AA31" s="1">
-        <v>9.6001255011817825</v>
+        <v>24.480320028013544</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
@@ -71922,76 +71922,76 @@
         <v>2</v>
       </c>
       <c r="D32" s="1">
-        <v>4.8319485390000008</v>
+        <v>12.321468774450002</v>
       </c>
       <c r="E32" s="1">
-        <v>5.2957454550000014</v>
+        <v>13.504150910250003</v>
       </c>
       <c r="F32" s="1">
-        <v>4.5162183000000002</v>
+        <v>11.516356665</v>
       </c>
       <c r="G32" s="1">
-        <v>4.0667010999999995</v>
+        <v>10.370087804999999</v>
       </c>
       <c r="H32" s="1">
-        <v>3.4721153280000006</v>
+        <v>8.8538940864000004</v>
       </c>
       <c r="I32" s="1">
-        <v>2.8278285200000006</v>
+        <v>7.2109627260000018</v>
       </c>
       <c r="J32" s="1">
-        <v>3.494607072</v>
+        <v>8.9112480335999997</v>
       </c>
       <c r="K32" s="1">
-        <v>0.65114869600000025</v>
+        <v>1.6604291748000004</v>
       </c>
       <c r="L32" s="1">
-        <v>0.55593999999999999</v>
+        <v>1.4176469999999999</v>
       </c>
       <c r="M32" s="1">
-        <v>0.79427147799999986</v>
+        <v>2.0253922688999997</v>
       </c>
       <c r="N32" s="1">
-        <v>0.47254105800000007</v>
+        <v>1.2049796979000003</v>
       </c>
       <c r="O32" s="1">
-        <v>0.60240864199999988</v>
+        <v>1.5361420370999996</v>
       </c>
       <c r="P32" s="1">
-        <v>0.94075769700000023</v>
+        <v>2.3989321273500002</v>
       </c>
       <c r="Q32" s="1">
-        <v>1.733305761</v>
+        <v>4.4199296905499992</v>
       </c>
       <c r="R32" s="1">
-        <v>1.8866379839999998</v>
+        <v>4.8109268591999994</v>
       </c>
       <c r="S32" s="1">
-        <v>1.7635052159999998</v>
+        <v>4.4969383007999992</v>
       </c>
       <c r="T32" s="1">
-        <v>1.0304745</v>
+        <v>2.6277099749999997</v>
       </c>
       <c r="U32" s="1">
-        <v>2.2040241299999996</v>
+        <v>5.6202615314999989</v>
       </c>
       <c r="V32" s="1">
-        <v>1.1825320320000001</v>
+        <v>3.0154566816000004</v>
       </c>
       <c r="W32" s="1">
-        <v>0.88339660199999981</v>
+        <v>2.2526613350999996</v>
       </c>
       <c r="X32" s="1">
-        <v>1.2625873920000001</v>
+        <v>3.2195978496</v>
       </c>
       <c r="Y32" s="1">
-        <v>0.78034915199999999</v>
+        <v>1.9898903376000001</v>
       </c>
       <c r="Z32" s="1">
-        <v>3.6730042470000006</v>
+        <v>9.366160829850001</v>
       </c>
       <c r="AA32" s="1">
-        <v>4.4725372999999999</v>
+        <v>11.404970115000001</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
@@ -72005,76 +72005,76 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>-10.944102935046125</v>
+        <v>-27.907462484367617</v>
       </c>
       <c r="E33" s="1">
-        <v>-12.566620133527303</v>
+        <v>-32.044881340494626</v>
       </c>
       <c r="F33" s="1">
-        <v>-9.8297193039402817</v>
+        <v>-25.065784225047718</v>
       </c>
       <c r="G33" s="1">
-        <v>-12.974595381321627</v>
+        <v>-33.085218222370152</v>
       </c>
       <c r="H33" s="1">
-        <v>-18.699002208615429</v>
+        <v>-47.682455631969347</v>
       </c>
       <c r="I33" s="1">
-        <v>-16.39644539253371</v>
+        <v>-41.810935750960965</v>
       </c>
       <c r="J33" s="1">
-        <v>-15.324218618899351</v>
+        <v>-39.076757478193343</v>
       </c>
       <c r="K33" s="1">
-        <v>-17.581489282925876</v>
+        <v>-44.832797671460987</v>
       </c>
       <c r="L33" s="1">
-        <v>-18.136408262090036</v>
+        <v>-46.247841068329592</v>
       </c>
       <c r="M33" s="1">
-        <v>-22.937051938389356</v>
+        <v>-58.48948244289285</v>
       </c>
       <c r="N33" s="1">
-        <v>-22.91719141349979</v>
+        <v>-58.438838104424462</v>
       </c>
       <c r="O33" s="1">
-        <v>-24.83391730219617</v>
+        <v>-63.326489120600229</v>
       </c>
       <c r="P33" s="1">
-        <v>-19.886153595671821</v>
+        <v>-50.709691668963146</v>
       </c>
       <c r="Q33" s="1">
-        <v>-19.358318444325899</v>
+        <v>-49.363712033031042</v>
       </c>
       <c r="R33" s="1">
-        <v>-20.81214404341749</v>
+        <v>-53.0709673107146</v>
       </c>
       <c r="S33" s="1">
-        <v>-17.133442464548484</v>
+        <v>-43.690278284598634</v>
       </c>
       <c r="T33" s="1">
-        <v>-15.558907467741626</v>
+        <v>-39.675214042741146</v>
       </c>
       <c r="U33" s="1">
-        <v>-13.913877328844983</v>
+        <v>-35.480387188554708</v>
       </c>
       <c r="V33" s="1">
-        <v>-8.2259575659320614</v>
+        <v>-20.976191793126755</v>
       </c>
       <c r="W33" s="1">
-        <v>-10.948033598645063</v>
+        <v>-27.91748567654491</v>
       </c>
       <c r="X33" s="1">
-        <v>-11.426179087712359</v>
+        <v>-29.136756673666518</v>
       </c>
       <c r="Y33" s="1">
-        <v>-10.879132567442419</v>
+        <v>-27.741788046978165</v>
       </c>
       <c r="Z33" s="1">
-        <v>-8.9908465782042732</v>
+        <v>-22.926658774420897</v>
       </c>
       <c r="AA33" s="1">
-        <v>-10.552923141243587</v>
+        <v>-26.909954010171145</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
@@ -72088,76 +72088,76 @@
         <v>2</v>
       </c>
       <c r="D34" s="1">
-        <v>8.0076370847513143</v>
+        <v>20.419474566115849</v>
       </c>
       <c r="E34" s="1">
-        <v>10.943913354064202</v>
+        <v>27.906979052863715</v>
       </c>
       <c r="F34" s="1">
-        <v>13.130045779607736</v>
+        <v>33.48161673799973</v>
       </c>
       <c r="G34" s="1">
-        <v>12.666968548917581</v>
+        <v>32.300769799739832</v>
       </c>
       <c r="H34" s="1">
-        <v>15.644685189217592</v>
+        <v>39.893947232504857</v>
       </c>
       <c r="I34" s="1">
-        <v>15.043697686296584</v>
+        <v>38.361429100056291</v>
       </c>
       <c r="J34" s="1">
-        <v>13.877263748463651</v>
+        <v>35.387022558582309</v>
       </c>
       <c r="K34" s="1">
-        <v>16.007078388368189</v>
+        <v>40.818049890338884</v>
       </c>
       <c r="L34" s="1">
-        <v>15.105433520970005</v>
+        <v>38.518855478473512</v>
       </c>
       <c r="M34" s="1">
-        <v>21.038032491160887</v>
+        <v>53.646982852460262</v>
       </c>
       <c r="N34" s="1">
-        <v>17.043028873424589</v>
+        <v>43.459723627232698</v>
       </c>
       <c r="O34" s="1">
-        <v>16.754819203413533</v>
+        <v>42.724788968704509</v>
       </c>
       <c r="P34" s="1">
-        <v>18.807430491801647</v>
+        <v>47.958947754094197</v>
       </c>
       <c r="Q34" s="1">
-        <v>16.778249823452008</v>
+        <v>42.784537049802616</v>
       </c>
       <c r="R34" s="1">
-        <v>14.354839778520278</v>
+        <v>36.604841435226703</v>
       </c>
       <c r="S34" s="1">
-        <v>12.427344497027216</v>
+        <v>31.6897284674194</v>
       </c>
       <c r="T34" s="1">
-        <v>13.204719112990137</v>
+        <v>33.672033738124853</v>
       </c>
       <c r="U34" s="1">
-        <v>11.209887020550896</v>
+        <v>28.585211902404787</v>
       </c>
       <c r="V34" s="1">
-        <v>11.276538681183759</v>
+        <v>28.755173637018583</v>
       </c>
       <c r="W34" s="1">
-        <v>11.904967558143765</v>
+        <v>30.3576672732666</v>
       </c>
       <c r="X34" s="1">
-        <v>10.216597789377888</v>
+        <v>26.052324362913616</v>
       </c>
       <c r="Y34" s="1">
-        <v>12.42648908282133</v>
+        <v>31.687547161194388</v>
       </c>
       <c r="Z34" s="1">
-        <v>8.5068425615109327</v>
+        <v>21.692448531852879</v>
       </c>
       <c r="AA34" s="1">
-        <v>9.888129266217236</v>
+        <v>25.214729628853952</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
@@ -72171,76 +72171,76 @@
         <v>3</v>
       </c>
       <c r="D35" s="1">
-        <v>4.8319485390000008</v>
+        <v>12.321468774450002</v>
       </c>
       <c r="E35" s="1">
-        <v>5.5075752732000014</v>
+        <v>14.044316946660004</v>
       </c>
       <c r="F35" s="1">
-        <v>4.5162183000000002</v>
+        <v>11.516356665</v>
       </c>
       <c r="G35" s="1">
-        <v>3.9853670779999995</v>
+        <v>10.162686048899998</v>
       </c>
       <c r="H35" s="1">
-        <v>3.2985095616000009</v>
+        <v>8.4111993820800013</v>
       </c>
       <c r="I35" s="1">
-        <v>2.7712719496000005</v>
+        <v>7.0667434714800006</v>
       </c>
       <c r="J35" s="1">
-        <v>3.3198767184000002</v>
+        <v>8.4656856319200013</v>
       </c>
       <c r="K35" s="1">
-        <v>0.63812572208000029</v>
+        <v>1.6272205913040008</v>
       </c>
       <c r="L35" s="1">
-        <v>0.55593999999999999</v>
+        <v>1.4176469999999999</v>
       </c>
       <c r="M35" s="1">
-        <v>0.80221419277999984</v>
+        <v>2.0456461915889994</v>
       </c>
       <c r="N35" s="1">
-        <v>0.49616811090000007</v>
+        <v>1.2652286827950001</v>
       </c>
       <c r="O35" s="1">
-        <v>0.59638455557999992</v>
+        <v>1.5207806167289999</v>
       </c>
       <c r="P35" s="1">
-        <v>0.98779558185000027</v>
+        <v>2.5188787337175005</v>
       </c>
       <c r="Q35" s="1">
-        <v>1.7679718762199998</v>
+        <v>4.5083282843609993</v>
       </c>
       <c r="R35" s="1">
-        <v>1.9243707436799997</v>
+        <v>4.9071453963839993</v>
       </c>
       <c r="S35" s="1">
-        <v>1.7106000595199999</v>
+        <v>4.3620301517759996</v>
       </c>
       <c r="T35" s="1">
-        <v>1.061388735</v>
+        <v>2.7065412742499997</v>
       </c>
       <c r="U35" s="1">
-        <v>2.1379034060999995</v>
+        <v>5.4516536855549989</v>
       </c>
       <c r="V35" s="1">
-        <v>1.2298333132800001</v>
+        <v>3.1360749488640001</v>
       </c>
       <c r="W35" s="1">
-        <v>0.85689470393999978</v>
+        <v>2.1850814950469997</v>
       </c>
       <c r="X35" s="1">
-        <v>1.1994580224000002</v>
+        <v>3.0586179571200005</v>
       </c>
       <c r="Y35" s="1">
-        <v>0.77254566048000006</v>
+        <v>1.9699914342240001</v>
       </c>
       <c r="Z35" s="1">
-        <v>3.7464643319400004</v>
+        <v>9.5534840464470001</v>
       </c>
       <c r="AA35" s="1">
-        <v>4.4278119270000005</v>
+        <v>11.290920413850001</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
@@ -72254,76 +72254,76 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>-11.491308081798431</v>
+        <v>-29.302835608586001</v>
       </c>
       <c r="E36" s="1">
-        <v>-13.194951140203669</v>
+        <v>-33.647125407519354</v>
       </c>
       <c r="F36" s="1">
-        <v>-10.124610883058489</v>
+        <v>-25.817757751799149</v>
       </c>
       <c r="G36" s="1">
-        <v>-13.234087288948061</v>
+        <v>-33.746922586817554</v>
       </c>
       <c r="H36" s="1">
-        <v>-19.072982252787739</v>
+        <v>-48.63610474460873</v>
       </c>
       <c r="I36" s="1">
-        <v>-17.216267662160398</v>
+        <v>-43.901482538509015</v>
       </c>
       <c r="J36" s="1">
-        <v>-14.86449206033237</v>
+        <v>-37.904454753847546</v>
       </c>
       <c r="K36" s="1">
-        <v>-17.933119068584393</v>
+        <v>-45.729453624890205</v>
       </c>
       <c r="L36" s="1">
-        <v>-17.955044179469137</v>
+        <v>-45.785362657646296</v>
       </c>
       <c r="M36" s="1">
-        <v>-22.248940380237677</v>
+        <v>-56.73479796960607</v>
       </c>
       <c r="N36" s="1">
-        <v>-21.771331842824804</v>
+        <v>-55.516896199203245</v>
       </c>
       <c r="O36" s="1">
-        <v>-24.337238956152245</v>
+        <v>-62.059959338188222</v>
       </c>
       <c r="P36" s="1">
-        <v>-18.891845915888229</v>
+        <v>-48.174207085514986</v>
       </c>
       <c r="Q36" s="1">
-        <v>-19.16473525988264</v>
+        <v>-48.87007491270073</v>
       </c>
       <c r="R36" s="1">
-        <v>-21.852751245588365</v>
+        <v>-55.724515676250327</v>
       </c>
       <c r="S36" s="1">
-        <v>-17.64744573848494</v>
+        <v>-45.000986633136598</v>
       </c>
       <c r="T36" s="1">
-        <v>-14.780962094354544</v>
+        <v>-37.691453340604092</v>
       </c>
       <c r="U36" s="1">
-        <v>-14.609571195287231</v>
+        <v>-37.254406547982434</v>
       </c>
       <c r="V36" s="1">
-        <v>-8.3082171415913812</v>
+        <v>-21.185953711058023</v>
       </c>
       <c r="W36" s="1">
-        <v>-11.166994270617963</v>
+        <v>-28.475835390075805</v>
       </c>
       <c r="X36" s="1">
-        <v>-11.083393715080987</v>
+        <v>-28.262653973456516</v>
       </c>
       <c r="Y36" s="1">
-        <v>-10.443967264744721</v>
+        <v>-26.63211652509904</v>
       </c>
       <c r="Z36" s="1">
-        <v>-9.3504804413324436</v>
+        <v>-23.843725125397732</v>
       </c>
       <c r="AA36" s="1">
-        <v>-10.341864678418714</v>
+        <v>-26.371754929967718</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
@@ -72337,76 +72337,76 @@
         <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>8.0076370847513143</v>
+        <v>20.419474566115849</v>
       </c>
       <c r="E37" s="1">
-        <v>10.725035086982919</v>
+        <v>27.348839471806439</v>
       </c>
       <c r="F37" s="1">
-        <v>13.130045779607736</v>
+        <v>33.48161673799973</v>
       </c>
       <c r="G37" s="1">
-        <v>12.033620121471701</v>
+        <v>30.685731309752839</v>
       </c>
       <c r="H37" s="1">
-        <v>16.114025744894121</v>
+        <v>41.090765649480005</v>
       </c>
       <c r="I37" s="1">
-        <v>15.795882570611413</v>
+        <v>40.279500555059101</v>
       </c>
       <c r="J37" s="1">
-        <v>14.432354298402197</v>
+        <v>36.802503460925607</v>
       </c>
       <c r="K37" s="1">
-        <v>16.327219956135551</v>
+        <v>41.634410888145652</v>
       </c>
       <c r="L37" s="1">
-        <v>15.105433520970005</v>
+        <v>38.518855478473512</v>
       </c>
       <c r="M37" s="1">
-        <v>21.458793140984103</v>
+        <v>54.719922509509466</v>
       </c>
       <c r="N37" s="1">
-        <v>17.724750028361573</v>
+        <v>45.19811257232201</v>
       </c>
       <c r="O37" s="1">
-        <v>17.257463779515938</v>
+        <v>44.006532637765638</v>
       </c>
       <c r="P37" s="1">
-        <v>17.867058967211566</v>
+        <v>45.561000366389493</v>
       </c>
       <c r="Q37" s="1">
-        <v>15.939337332279408</v>
+        <v>40.64531019731249</v>
       </c>
       <c r="R37" s="1">
-        <v>14.641936574090682</v>
+        <v>37.336938263931238</v>
       </c>
       <c r="S37" s="1">
-        <v>12.178797607086672</v>
+        <v>31.055933898071011</v>
       </c>
       <c r="T37" s="1">
-        <v>13.46881349524994</v>
+        <v>34.345474412887349</v>
       </c>
       <c r="U37" s="1">
-        <v>10.873590409934371</v>
+        <v>27.727655545332645</v>
       </c>
       <c r="V37" s="1">
-        <v>11.727600228431108</v>
+        <v>29.905380582499323</v>
       </c>
       <c r="W37" s="1">
-        <v>11.666868206980888</v>
+        <v>29.750513927801265</v>
       </c>
       <c r="X37" s="1">
-        <v>10.114431811484108</v>
+        <v>25.791801119284475</v>
       </c>
       <c r="Y37" s="1">
-        <v>12.42648908282133</v>
+        <v>31.687547161194388</v>
       </c>
       <c r="Z37" s="1">
-        <v>8.1665688590504946</v>
+        <v>20.824750590578763</v>
       </c>
       <c r="AA37" s="1">
-        <v>9.888129266217236</v>
+        <v>25.214729628853952</v>
       </c>
     </row>
   </sheetData>

--- a/data/OP1/case33_1/case33_1_operational_data.xlsx
+++ b/data/OP1/case33_1/case33_1_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP1/case33_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6621C4B1-9D88-0743-A32D-CDB2A0571E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A950BA-2080-8640-9E6B-43259F433EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="1800" windowWidth="29400" windowHeight="19120" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3780" yWindow="1800" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -473,21 +473,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*2</f>
-        <v>8</v>
+        <f>E2*5</f>
+        <v>30</v>
       </c>
       <c r="C2" s="1">
-        <f>F2*2</f>
-        <v>4.8</v>
+        <f>F2*5</f>
+        <v>18</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
       </c>
       <c r="E2" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" s="4">
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -495,21 +495,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B33" si="0">E3*2</f>
-        <v>7.1999999999999993</v>
+        <f t="shared" ref="B3:B33" si="0">E3*5</f>
+        <v>26.999999999999996</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C33" si="1">F3*2</f>
-        <v>3.2</v>
+        <f t="shared" ref="C3:C33" si="1">F3*5</f>
+        <v>12.000000000000002</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
       <c r="E3" s="4">
-        <v>3.5999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="F3" s="4">
-        <v>1.6</v>
+        <v>2.4000000000000004</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -518,20 +518,20 @@
       </c>
       <c r="B4" s="1">
         <f t="shared" si="0"/>
-        <v>9.6</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1">
         <f t="shared" si="1"/>
-        <v>6.4</v>
+        <v>24.000000000000004</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
       <c r="E4" s="4">
-        <v>4.8</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="F4" s="4">
-        <v>3.2</v>
+        <v>4.8000000000000007</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -540,20 +540,20 @@
       </c>
       <c r="B5" s="1">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1">
         <f t="shared" si="1"/>
-        <v>2.4</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E5" s="4">
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="F5" s="4">
-        <v>1.2</v>
+        <v>1.7999999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -562,20 +562,20 @@
       </c>
       <c r="B6" s="1">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>6.0000000000000009</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E6" s="4">
-        <v>2.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="F6" s="4">
-        <v>0.8</v>
+        <v>1.2000000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -584,20 +584,20 @@
       </c>
       <c r="B7" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
       <c r="E7" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -606,20 +606,20 @@
       </c>
       <c r="B8" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C8" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
       <c r="E8" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -628,20 +628,20 @@
       </c>
       <c r="B9" s="1">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="1">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>3.0000000000000004</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E9" s="4">
-        <v>2.4</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="F9" s="4">
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -650,20 +650,20 @@
       </c>
       <c r="B10" s="1">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>3.0000000000000004</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E10" s="4">
-        <v>2.4</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="F10" s="4">
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -672,20 +672,20 @@
       </c>
       <c r="B11" s="1">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>6.7499999999999991</v>
       </c>
       <c r="C11" s="1">
         <f t="shared" si="1"/>
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
       </c>
       <c r="E11" s="4">
-        <v>1.7999999999999998</v>
+        <v>1.3499999999999999</v>
       </c>
       <c r="F11" s="4">
-        <v>1.2</v>
+        <v>0.89999999999999991</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -694,20 +694,20 @@
       </c>
       <c r="B12" s="1">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="1">
         <f t="shared" si="1"/>
-        <v>2.8000000000000003</v>
+        <v>5.25</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E12" s="4">
-        <v>2.4</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="F12" s="4">
-        <v>1.4000000000000001</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -716,20 +716,20 @@
       </c>
       <c r="B13" s="1">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1">
         <f t="shared" si="1"/>
-        <v>2.8000000000000003</v>
+        <v>5.25</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E13" s="4">
-        <v>2.4</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="F13" s="4">
-        <v>1.4000000000000001</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -738,20 +738,20 @@
       </c>
       <c r="B14" s="1">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="1">
         <f t="shared" si="1"/>
-        <v>3.2</v>
+        <v>6.0000000000000009</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
       <c r="E14" s="4">
-        <v>2.4</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="F14" s="4">
-        <v>1.6</v>
+        <v>1.2000000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -760,20 +760,20 @@
       </c>
       <c r="B15" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="C15" s="1">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.75000000000000011</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E15" s="4">
-        <v>1.2</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="F15" s="4">
-        <v>0.2</v>
+        <v>0.15000000000000002</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -782,20 +782,20 @@
       </c>
       <c r="B16" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="C16" s="1">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>1.5000000000000002</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E16" s="4">
-        <v>1.2</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="F16" s="4">
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -804,20 +804,20 @@
       </c>
       <c r="B17" s="1">
         <f t="shared" si="0"/>
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="C17" s="1">
         <f t="shared" si="1"/>
-        <v>0.8</v>
+        <v>1.5000000000000002</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E17" s="4">
-        <v>1.2</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="F17" s="4">
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -826,20 +826,20 @@
       </c>
       <c r="B18" s="1">
         <f t="shared" si="0"/>
-        <v>3.6</v>
+        <v>6.75</v>
       </c>
       <c r="C18" s="1">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>3.0000000000000004</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
       <c r="E18" s="4">
-        <v>1.8</v>
+        <v>1.35</v>
       </c>
       <c r="F18" s="4">
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -848,20 +848,20 @@
       </c>
       <c r="B19" s="1">
         <f t="shared" si="0"/>
-        <v>3.6</v>
+        <v>13.5</v>
       </c>
       <c r="C19" s="1">
         <f t="shared" si="1"/>
-        <v>3.2</v>
+        <v>12.000000000000002</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
       <c r="E19" s="4">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="F19" s="4">
-        <v>1.6</v>
+        <v>2.4000000000000004</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -870,20 +870,20 @@
       </c>
       <c r="B20" s="1">
         <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>26.999999999999996</v>
       </c>
       <c r="C20" s="1">
         <f t="shared" si="1"/>
-        <v>3.2</v>
+        <v>12.000000000000002</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
       <c r="E20" s="4">
-        <v>3.5999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="F20" s="4">
-        <v>1.6</v>
+        <v>2.4000000000000004</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -892,11 +892,11 @@
       </c>
       <c r="B21" s="1">
         <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>18</v>
       </c>
       <c r="C21" s="1">
         <f t="shared" si="1"/>
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -914,11 +914,11 @@
       </c>
       <c r="B22" s="1">
         <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>18</v>
       </c>
       <c r="C22" s="1">
         <f t="shared" si="1"/>
-        <v>3.2</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -936,11 +936,11 @@
       </c>
       <c r="B23" s="1">
         <f t="shared" si="0"/>
-        <v>7.1999999999999993</v>
+        <v>18</v>
       </c>
       <c r="C23" s="1">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -958,11 +958,11 @@
       </c>
       <c r="B24" s="1">
         <f t="shared" si="0"/>
-        <v>33.6</v>
+        <v>84</v>
       </c>
       <c r="C24" s="1">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -980,11 +980,11 @@
       </c>
       <c r="B25" s="1">
         <f t="shared" si="0"/>
-        <v>33.6</v>
+        <v>84</v>
       </c>
       <c r="C25" s="1">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -1002,11 +1002,11 @@
       </c>
       <c r="B26" s="1">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="C26" s="1">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1024,11 +1024,11 @@
       </c>
       <c r="B27" s="1">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="C27" s="1">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1046,11 +1046,11 @@
       </c>
       <c r="B28" s="1">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="C28" s="1">
         <f t="shared" si="1"/>
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B29" s="1">
         <f t="shared" si="0"/>
-        <v>9.6</v>
+        <v>24</v>
       </c>
       <c r="C29" s="1">
         <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
+        <v>14.000000000000002</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1090,11 +1090,11 @@
       </c>
       <c r="B30" s="1">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C30" s="1">
         <f t="shared" si="1"/>
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1103,7 +1103,7 @@
         <v>8</v>
       </c>
       <c r="F30" s="4">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -1112,20 +1112,20 @@
       </c>
       <c r="B31" s="1">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C31" s="1">
         <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
+        <v>7.0000000000000009</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
       </c>
       <c r="E31" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F31" s="4">
-        <v>2.8000000000000003</v>
+        <v>1.4000000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -1134,20 +1134,20 @@
       </c>
       <c r="B32" s="1">
         <f t="shared" si="0"/>
-        <v>16.8</v>
+        <v>21</v>
       </c>
       <c r="C32" s="1">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
       </c>
       <c r="E32" s="4">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="F32" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -1156,20 +1156,20 @@
       </c>
       <c r="B33" s="1">
         <f t="shared" si="0"/>
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="C33" s="1">
         <f t="shared" si="1"/>
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E33" s="4">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="F33" s="4">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">

--- a/data/OP1/case33_1/case33_1_operational_data.xlsx
+++ b/data/OP1/case33_1/case33_1_operational_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP1/case33_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A950BA-2080-8640-9E6B-43259F433EE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609E8FAB-4DDC-FC45-AFE4-6A67F6D42EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3780" yWindow="1800" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -473,12 +473,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*5</f>
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1">
-        <f>F2*5</f>
-        <v>18</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -495,12 +493,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B33" si="0">E3*5</f>
-        <v>26.999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C33" si="1">F3*5</f>
-        <v>12.000000000000002</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -517,12 +513,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <f t="shared" si="0"/>
-        <v>36</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" si="1"/>
-        <v>24.000000000000004</v>
+        <v>4.8000000000000007</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -539,12 +533,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C5" s="1">
-        <f t="shared" si="1"/>
-        <v>9</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -561,12 +553,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C6" s="1">
-        <f t="shared" si="1"/>
-        <v>6.0000000000000009</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -583,12 +573,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <f t="shared" si="0"/>
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -605,12 +593,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <f t="shared" si="0"/>
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1">
-        <f t="shared" si="1"/>
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -627,12 +613,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C9" s="1">
-        <f t="shared" si="1"/>
-        <v>3.0000000000000004</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -649,12 +633,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C10" s="1">
-        <f t="shared" si="1"/>
-        <v>3.0000000000000004</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -671,12 +653,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <f t="shared" si="0"/>
-        <v>6.7499999999999991</v>
+        <v>1.3499999999999999</v>
       </c>
       <c r="C11" s="1">
-        <f t="shared" si="1"/>
-        <v>4.5</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -693,12 +673,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C12" s="1">
-        <f t="shared" si="1"/>
-        <v>5.25</v>
+        <v>1.05</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -715,12 +693,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C13" s="1">
-        <f t="shared" si="1"/>
-        <v>5.25</v>
+        <v>1.05</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -737,12 +713,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="C14" s="1">
-        <f t="shared" si="1"/>
-        <v>6.0000000000000009</v>
+        <v>1.2000000000000002</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -759,12 +733,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="C15" s="1">
-        <f t="shared" si="1"/>
-        <v>0.75000000000000011</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -781,12 +753,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="C16" s="1">
-        <f t="shared" si="1"/>
-        <v>1.5000000000000002</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -803,12 +773,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <f t="shared" si="0"/>
-        <v>4.5</v>
+        <v>0.89999999999999991</v>
       </c>
       <c r="C17" s="1">
-        <f t="shared" si="1"/>
-        <v>1.5000000000000002</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -825,12 +793,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <f t="shared" si="0"/>
-        <v>6.75</v>
+        <v>1.35</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" si="1"/>
-        <v>3.0000000000000004</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -847,12 +813,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <f t="shared" si="0"/>
-        <v>13.5</v>
+        <v>2.7</v>
       </c>
       <c r="C19" s="1">
-        <f t="shared" si="1"/>
-        <v>12.000000000000002</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -869,12 +833,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <f t="shared" si="0"/>
-        <v>26.999999999999996</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C20" s="1">
-        <f t="shared" si="1"/>
-        <v>12.000000000000002</v>
+        <v>2.4000000000000004</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -891,12 +853,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C21" s="1">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -913,12 +873,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C22" s="1">
-        <f t="shared" si="1"/>
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -935,12 +893,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C23" s="1">
-        <f t="shared" si="1"/>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -957,12 +913,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <f t="shared" si="0"/>
-        <v>84</v>
+        <v>16.8</v>
       </c>
       <c r="C24" s="1">
-        <f t="shared" si="1"/>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -979,12 +933,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <f t="shared" si="0"/>
-        <v>84</v>
+        <v>16.8</v>
       </c>
       <c r="C25" s="1">
-        <f t="shared" si="1"/>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -1001,12 +953,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <v>2.4</v>
       </c>
       <c r="C26" s="1">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1023,12 +973,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <v>2.4</v>
       </c>
       <c r="C27" s="1">
-        <f t="shared" si="1"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1045,12 +993,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <f t="shared" si="0"/>
-        <v>12</v>
+        <v>2.4</v>
       </c>
       <c r="C28" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1067,12 +1013,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <f t="shared" si="0"/>
-        <v>24</v>
+        <v>4.8</v>
       </c>
       <c r="C29" s="1">
-        <f t="shared" si="1"/>
-        <v>14.000000000000002</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1089,12 +1033,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <f t="shared" si="0"/>
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C30" s="1">
-        <f t="shared" si="1"/>
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1111,12 +1053,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C31" s="1">
-        <f t="shared" si="1"/>
-        <v>7.0000000000000009</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1133,12 +1073,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <f t="shared" si="0"/>
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="C32" s="1">
-        <f t="shared" si="1"/>
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1155,12 +1093,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <f t="shared" si="0"/>
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="C33" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>

--- a/data/OP1/case33_1/case33_1_operational_data.xlsx
+++ b/data/OP1/case33_1/case33_1_operational_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP1/case33_1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS7/case33_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{609E8FAB-4DDC-FC45-AFE4-6A67F6D42EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C614731-E163-634C-8926-8FFCC4133114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="1800" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="52180" yWindow="1260" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -473,19 +473,21 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>6</v>
+        <f>E2*3.5</f>
+        <v>14</v>
       </c>
       <c r="C2" s="1">
-        <v>3.5999999999999996</v>
+        <f>F2*3.5</f>
+        <v>8.4</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
       </c>
       <c r="E2" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" s="4">
-        <v>3.5999999999999996</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -493,19 +495,21 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>5.3999999999999995</v>
+        <f t="shared" ref="B3:B33" si="0">E3*3.5</f>
+        <v>12.599999999999998</v>
       </c>
       <c r="C3" s="1">
-        <v>2.4000000000000004</v>
+        <f t="shared" ref="C3:C33" si="1">F3*3.5</f>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
       <c r="E3" s="4">
-        <v>5.3999999999999995</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="F3" s="4">
-        <v>2.4000000000000004</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -513,19 +517,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>7.1999999999999993</v>
+        <f t="shared" si="0"/>
+        <v>16.8</v>
       </c>
       <c r="C4" s="1">
-        <v>4.8000000000000007</v>
+        <f t="shared" si="1"/>
+        <v>11.200000000000001</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
       <c r="E4" s="4">
-        <v>7.1999999999999993</v>
+        <v>4.8</v>
       </c>
       <c r="F4" s="4">
-        <v>4.8000000000000007</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -533,19 +539,21 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C5" s="1">
-        <v>1.7999999999999998</v>
+        <f t="shared" si="1"/>
+        <v>4.2</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E5" s="4">
-        <v>3.5999999999999996</v>
+        <v>2.4</v>
       </c>
       <c r="F5" s="4">
-        <v>1.7999999999999998</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -553,19 +561,21 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C6" s="1">
-        <v>1.2000000000000002</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E6" s="4">
-        <v>3.5999999999999996</v>
+        <v>2.4</v>
       </c>
       <c r="F6" s="4">
-        <v>1.2000000000000002</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -573,19 +583,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="C7" s="1">
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
       <c r="E7" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -593,19 +605,21 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <v>6</v>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="C8" s="1">
-        <v>3</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
       </c>
       <c r="E8" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F8" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -613,19 +627,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <v>1.7999999999999998</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C9" s="1">
-        <v>0.60000000000000009</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E9" s="4">
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="F9" s="4">
-        <v>0.60000000000000009</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -633,19 +649,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <v>1.7999999999999998</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C10" s="1">
-        <v>0.60000000000000009</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E10" s="4">
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="F10" s="4">
-        <v>0.60000000000000009</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -653,19 +671,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <v>1.3499999999999999</v>
+        <f t="shared" si="0"/>
+        <v>6.2999999999999989</v>
       </c>
       <c r="C11" s="1">
-        <v>0.89999999999999991</v>
+        <f t="shared" si="1"/>
+        <v>4.2</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
       </c>
       <c r="E11" s="4">
-        <v>1.3499999999999999</v>
+        <v>1.7999999999999998</v>
       </c>
       <c r="F11" s="4">
-        <v>0.89999999999999991</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -673,19 +693,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <v>1.7999999999999998</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C12" s="1">
-        <v>1.05</v>
+        <f t="shared" si="1"/>
+        <v>4.9000000000000004</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E12" s="4">
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="F12" s="4">
-        <v>1.05</v>
+        <v>1.4000000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -693,19 +715,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <v>1.7999999999999998</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C13" s="1">
-        <v>1.05</v>
+        <f t="shared" si="1"/>
+        <v>4.9000000000000004</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E13" s="4">
-        <v>1.7999999999999998</v>
+        <v>2.4</v>
       </c>
       <c r="F13" s="4">
-        <v>1.05</v>
+        <v>1.4000000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -713,19 +737,21 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>1.7999999999999998</v>
+        <f t="shared" si="0"/>
+        <v>16.8</v>
       </c>
       <c r="C14" s="1">
-        <v>1.2000000000000002</v>
+        <f t="shared" si="1"/>
+        <v>11.200000000000001</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
       </c>
       <c r="E14" s="4">
-        <v>1.7999999999999998</v>
+        <v>4.8</v>
       </c>
       <c r="F14" s="4">
-        <v>1.2000000000000002</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -733,19 +759,21 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>0.89999999999999991</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C15" s="1">
-        <v>0.15000000000000002</v>
+        <f t="shared" si="1"/>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E15" s="4">
-        <v>0.89999999999999991</v>
+        <v>2.4</v>
       </c>
       <c r="F15" s="4">
-        <v>0.15000000000000002</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -753,19 +781,21 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>0.89999999999999991</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C16" s="1">
-        <v>0.30000000000000004</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E16" s="4">
-        <v>0.89999999999999991</v>
+        <v>2.4</v>
       </c>
       <c r="F16" s="4">
-        <v>0.30000000000000004</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -773,19 +803,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <v>0.89999999999999991</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C17" s="1">
-        <v>0.30000000000000004</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E17" s="4">
-        <v>0.89999999999999991</v>
+        <v>2.4</v>
       </c>
       <c r="F17" s="4">
-        <v>0.30000000000000004</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -793,19 +825,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <v>1.35</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C18" s="1">
-        <v>0.60000000000000009</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
       <c r="E18" s="4">
-        <v>1.35</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="F18" s="4">
-        <v>0.60000000000000009</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -813,19 +847,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <v>2.7</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C19" s="1">
-        <v>2.4000000000000004</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
       <c r="E19" s="4">
-        <v>2.7</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="F19" s="4">
-        <v>2.4000000000000004</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -833,19 +869,21 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <v>5.3999999999999995</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C20" s="1">
-        <v>2.4000000000000004</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
       </c>
       <c r="E20" s="4">
-        <v>5.3999999999999995</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="F20" s="4">
-        <v>2.4000000000000004</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -853,10 +891,12 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C21" s="1">
-        <v>1.6</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -873,10 +913,12 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C22" s="1">
-        <v>1.6</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -893,10 +935,12 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <v>3.5999999999999996</v>
+        <f t="shared" si="0"/>
+        <v>12.599999999999998</v>
       </c>
       <c r="C23" s="1">
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>7</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -913,10 +957,12 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <v>16.8</v>
+        <f t="shared" si="0"/>
+        <v>58.800000000000004</v>
       </c>
       <c r="C24" s="1">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -933,10 +979,12 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <v>16.8</v>
+        <f t="shared" si="0"/>
+        <v>58.800000000000004</v>
       </c>
       <c r="C25" s="1">
-        <v>8</v>
+        <f t="shared" si="1"/>
+        <v>28</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -953,10 +1001,12 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C26" s="1">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>3.5</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -973,10 +1023,12 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C27" s="1">
-        <v>1</v>
+        <f t="shared" si="1"/>
+        <v>3.5</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -993,10 +1045,12 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <v>2.4</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C28" s="1">
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1013,10 +1067,12 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <v>4.8</v>
+        <f t="shared" si="0"/>
+        <v>16.8</v>
       </c>
       <c r="C29" s="1">
-        <v>2.8000000000000003</v>
+        <f t="shared" si="1"/>
+        <v>9.8000000000000007</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1033,10 +1089,12 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <v>8</v>
+        <f t="shared" si="0"/>
+        <v>28</v>
       </c>
       <c r="C30" s="1">
-        <v>12</v>
+        <f t="shared" si="1"/>
+        <v>84</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1045,7 +1103,7 @@
         <v>8</v>
       </c>
       <c r="F30" s="4">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -1053,19 +1111,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <v>3</v>
+        <f t="shared" si="0"/>
+        <v>21</v>
       </c>
       <c r="C31" s="1">
-        <v>1.4000000000000001</v>
+        <f t="shared" si="1"/>
+        <v>9.8000000000000007</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
       </c>
       <c r="E31" s="4">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F31" s="4">
-        <v>1.4000000000000001</v>
+        <v>2.8000000000000003</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -1073,19 +1133,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <v>4.2</v>
+        <f t="shared" si="0"/>
+        <v>29.400000000000002</v>
       </c>
       <c r="C32" s="1">
-        <v>2</v>
+        <f t="shared" si="1"/>
+        <v>14</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
       </c>
       <c r="E32" s="4">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="F32" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -1093,19 +1155,21 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <v>1.2</v>
+        <f t="shared" si="0"/>
+        <v>8.4</v>
       </c>
       <c r="C33" s="1">
-        <v>0.8</v>
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>
       </c>
       <c r="E33" s="4">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="F33" s="4">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -69368,76 +69432,76 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>12.536820000000002</v>
+        <v>4.9164000000000012</v>
       </c>
       <c r="E2" s="1">
-        <v>12.955020000000003</v>
+        <v>5.0804000000000009</v>
       </c>
       <c r="F2" s="1">
-        <v>11.60046</v>
+        <v>4.5491999999999999</v>
       </c>
       <c r="G2" s="1">
-        <v>10.995599999999998</v>
+        <v>4.3119999999999994</v>
       </c>
       <c r="H2" s="1">
-        <v>9.0086400000000015</v>
+        <v>3.5328000000000004</v>
       </c>
       <c r="I2" s="1">
-        <v>7.645920000000002</v>
+        <v>2.9984000000000006</v>
       </c>
       <c r="J2" s="1">
-        <v>9.350340000000001</v>
+        <v>3.6668000000000003</v>
       </c>
       <c r="K2" s="1">
-        <v>1.62384</v>
+        <v>0.63680000000000003</v>
       </c>
       <c r="L2" s="1">
-        <v>1.4280000000000002</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="M2" s="1">
-        <v>2.08182</v>
+        <v>0.8163999999999999</v>
       </c>
       <c r="N2" s="1">
-        <v>1.22604</v>
+        <v>0.48080000000000006</v>
       </c>
       <c r="O2" s="1">
-        <v>1.5320400000000001</v>
+        <v>0.6008</v>
       </c>
       <c r="P2" s="1">
-        <v>2.4408600000000007</v>
+        <v>0.95720000000000027</v>
       </c>
       <c r="Q2" s="1">
-        <v>4.4971800000000002</v>
+        <v>1.7636000000000003</v>
       </c>
       <c r="R2" s="1">
-        <v>4.7980799999999997</v>
+        <v>1.8815999999999999</v>
       </c>
       <c r="S2" s="1">
-        <v>4.7185199999999998</v>
+        <v>1.8503999999999998</v>
       </c>
       <c r="T2" s="1">
-        <v>2.6469</v>
+        <v>1.038</v>
       </c>
       <c r="U2" s="1">
-        <v>5.3917199999999994</v>
+        <v>2.1143999999999998</v>
       </c>
       <c r="V2" s="1">
-        <v>3.1640400000000004</v>
+        <v>1.2408000000000001</v>
       </c>
       <c r="W2" s="1">
-        <v>2.2246199999999994</v>
+        <v>0.87239999999999984</v>
       </c>
       <c r="X2" s="1">
-        <v>3.3782400000000004</v>
+        <v>1.3248000000000002</v>
       </c>
       <c r="Y2" s="1">
-        <v>2.0879400000000001</v>
+        <v>0.81880000000000008</v>
       </c>
       <c r="Z2" s="1">
-        <v>9.5298600000000011</v>
+        <v>3.7372000000000005</v>
       </c>
       <c r="AA2" s="1">
-        <v>11.48826</v>
+        <v>4.5052000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -69451,76 +69515,76 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>-28.305000000000003</v>
+        <v>-11.100000000000001</v>
       </c>
       <c r="E3" s="1">
-        <v>-30.267480000000003</v>
+        <v>-11.8696</v>
       </c>
       <c r="F3" s="1">
-        <v>-34.041480000000007</v>
+        <v>-13.349600000000002</v>
       </c>
       <c r="G3" s="1">
-        <v>-36.721019999999996</v>
+        <v>-14.400400000000001</v>
       </c>
       <c r="H3" s="1">
-        <v>-39.249600000000001</v>
+        <v>-15.392000000000001</v>
       </c>
       <c r="I3" s="1">
-        <v>-42.834900000000005</v>
+        <v>-16.798000000000002</v>
       </c>
       <c r="J3" s="1">
-        <v>-40.872419999999998</v>
+        <v>-16.028400000000001</v>
       </c>
       <c r="K3" s="1">
-        <v>-45.848387999999993</v>
+        <v>-17.979759999999999</v>
       </c>
       <c r="L3" s="1">
-        <v>-41.583767999999985</v>
+        <v>-16.307359999999996</v>
       </c>
       <c r="M3" s="1">
-        <v>-61.079741999999996</v>
+        <v>-23.952839999999998</v>
       </c>
       <c r="N3" s="1">
-        <v>-60.453768000000011</v>
+        <v>-23.707360000000005</v>
       </c>
       <c r="O3" s="1">
-        <v>-55.264007999999997</v>
+        <v>-21.672160000000002</v>
       </c>
       <c r="P3" s="1">
-        <v>-52.975127999999998</v>
+        <v>-20.774560000000001</v>
       </c>
       <c r="Q3" s="1">
-        <v>-51.146574000000008</v>
+        <v>-20.057480000000002</v>
       </c>
       <c r="R3" s="1">
-        <v>-48.20948400000001</v>
+        <v>-18.905680000000004</v>
       </c>
       <c r="S3" s="1">
-        <v>-43.870811999999994</v>
+        <v>-17.204239999999999</v>
       </c>
       <c r="T3" s="1">
-        <v>-41.021748000000002</v>
+        <v>-16.086960000000001</v>
       </c>
       <c r="U3" s="1">
-        <v>-36.710412000000005</v>
+        <v>-14.396240000000002</v>
       </c>
       <c r="V3" s="1">
-        <v>-23.301185999999998</v>
+        <v>-9.1377199999999998</v>
       </c>
       <c r="W3" s="1">
-        <v>-26.077523999999997</v>
+        <v>-10.226479999999999</v>
       </c>
       <c r="X3" s="1">
-        <v>-27.565091999999996</v>
+        <v>-10.809839999999999</v>
       </c>
       <c r="Y3" s="1">
-        <v>-29.593769999999996</v>
+        <v>-11.605399999999999</v>
       </c>
       <c r="Z3" s="1">
-        <v>-23.512020000000003</v>
+        <v>-9.2204000000000015</v>
       </c>
       <c r="AA3" s="1">
-        <v>-24.983879999999999</v>
+        <v>-9.797600000000001</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -69534,76 +69598,76 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>27.268578000000002</v>
+        <v>10.69356</v>
       </c>
       <c r="E4" s="1">
-        <v>29.172815999999987</v>
+        <v>11.440319999999996</v>
       </c>
       <c r="F4" s="1">
-        <v>32.709461999999995</v>
+        <v>12.82724</v>
       </c>
       <c r="G4" s="1">
-        <v>35.196222000000006</v>
+        <v>13.802440000000002</v>
       </c>
       <c r="H4" s="1">
-        <v>37.463069999999988</v>
+        <v>14.691399999999998</v>
       </c>
       <c r="I4" s="1">
-        <v>40.9071</v>
+        <v>16.042000000000002</v>
       </c>
       <c r="J4" s="1">
-        <v>38.999699999999997</v>
+        <v>15.293999999999999</v>
       </c>
       <c r="K4" s="1">
-        <v>44.010857999999999</v>
+        <v>17.259160000000001</v>
       </c>
       <c r="L4" s="1">
-        <v>40.313358000000001</v>
+        <v>15.809160000000002</v>
       </c>
       <c r="M4" s="1">
-        <v>46.000571999999998</v>
+        <v>18.039439999999999</v>
       </c>
       <c r="N4" s="1">
-        <v>46.362774000000002</v>
+        <v>18.181480000000001</v>
       </c>
       <c r="O4" s="1">
-        <v>43.400081999999998</v>
+        <v>17.019639999999999</v>
       </c>
       <c r="P4" s="1">
-        <v>41.937300000000008</v>
+        <v>16.446000000000002</v>
       </c>
       <c r="Q4" s="1">
-        <v>40.859363999999999</v>
+        <v>16.02328</v>
       </c>
       <c r="R4" s="1">
-        <v>38.291616000000005</v>
+        <v>15.016320000000004</v>
       </c>
       <c r="S4" s="1">
-        <v>34.862274000000006</v>
+        <v>13.671480000000003</v>
       </c>
       <c r="T4" s="1">
-        <v>32.476901999999995</v>
+        <v>12.736039999999997</v>
       </c>
       <c r="U4" s="1">
-        <v>29.026343999999998</v>
+        <v>11.38288</v>
       </c>
       <c r="V4" s="1">
-        <v>22.718867999999997</v>
+        <v>8.9093599999999995</v>
       </c>
       <c r="W4" s="1">
-        <v>25.429008</v>
+        <v>9.9721600000000006</v>
       </c>
       <c r="X4" s="1">
-        <v>27.021228000000004</v>
+        <v>10.596560000000002</v>
       </c>
       <c r="Y4" s="1">
-        <v>29.107128000000003</v>
+        <v>11.414560000000002</v>
       </c>
       <c r="Z4" s="1">
-        <v>22.649100000000001</v>
+        <v>8.8819999999999997</v>
       </c>
       <c r="AA4" s="1">
-        <v>24.084240000000008</v>
+        <v>9.4448000000000025</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -69617,76 +69681,76 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>12.411451800000005</v>
+        <v>4.8672360000000019</v>
       </c>
       <c r="E5" s="1">
-        <v>12.955020000000003</v>
+        <v>5.0804000000000009</v>
       </c>
       <c r="F5" s="1">
-        <v>12.0644784</v>
+        <v>4.7311680000000003</v>
       </c>
       <c r="G5" s="1">
-        <v>11.215511999999999</v>
+        <v>4.3982399999999995</v>
       </c>
       <c r="H5" s="1">
-        <v>8.8284672000000004</v>
+        <v>3.4621440000000003</v>
       </c>
       <c r="I5" s="1">
-        <v>7.3400832000000005</v>
+        <v>2.8784640000000006</v>
       </c>
       <c r="J5" s="1">
-        <v>9.4438434000000004</v>
+        <v>3.7034680000000004</v>
       </c>
       <c r="K5" s="1">
-        <v>1.5913632</v>
+        <v>0.62406400000000006</v>
       </c>
       <c r="L5" s="1">
-        <v>1.4851200000000002</v>
+        <v>0.58240000000000014</v>
       </c>
       <c r="M5" s="1">
-        <v>2.1859109999999999</v>
+        <v>0.85721999999999998</v>
       </c>
       <c r="N5" s="1">
-        <v>1.2015192000000003</v>
+        <v>0.4711840000000001</v>
       </c>
       <c r="O5" s="1">
-        <v>1.5473604000000001</v>
+        <v>0.60680800000000001</v>
       </c>
       <c r="P5" s="1">
-        <v>2.4408600000000007</v>
+        <v>0.95720000000000027</v>
       </c>
       <c r="Q5" s="1">
-        <v>4.7220390000000005</v>
+        <v>1.8517800000000002</v>
       </c>
       <c r="R5" s="1">
-        <v>4.7980799999999997</v>
+        <v>1.8815999999999999</v>
       </c>
       <c r="S5" s="1">
-        <v>4.8128903999999997</v>
+        <v>1.8874079999999998</v>
       </c>
       <c r="T5" s="1">
-        <v>2.5145550000000001</v>
+        <v>0.98609999999999998</v>
       </c>
       <c r="U5" s="1">
-        <v>5.6613059999999988</v>
+        <v>2.2201199999999996</v>
       </c>
       <c r="V5" s="1">
-        <v>3.1956804000000005</v>
+        <v>1.2532080000000001</v>
       </c>
       <c r="W5" s="1">
-        <v>2.2913585999999997</v>
+        <v>0.89857199999999982</v>
       </c>
       <c r="X5" s="1">
-        <v>3.4120224000000006</v>
+        <v>1.3380480000000003</v>
       </c>
       <c r="Y5" s="1">
-        <v>1.9835429999999998</v>
+        <v>0.77786</v>
       </c>
       <c r="Z5" s="1">
-        <v>9.7204572000000002</v>
+        <v>3.8119440000000004</v>
       </c>
       <c r="AA5" s="1">
-        <v>11.48826</v>
+        <v>4.5052000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -69700,76 +69764,76 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>-28.305000000000003</v>
+        <v>-11.100000000000001</v>
       </c>
       <c r="E6" s="1">
-        <v>-29.964805200000001</v>
+        <v>-11.750904</v>
       </c>
       <c r="F6" s="1">
-        <v>-34.041480000000007</v>
+        <v>-13.349600000000002</v>
       </c>
       <c r="G6" s="1">
-        <v>-34.884968999999998</v>
+        <v>-13.68038</v>
       </c>
       <c r="H6" s="1">
-        <v>-38.072112000000004</v>
+        <v>-14.930240000000001</v>
       </c>
       <c r="I6" s="1">
-        <v>-41.121504000000002</v>
+        <v>-16.126080000000002</v>
       </c>
       <c r="J6" s="1">
-        <v>-41.281144200000007</v>
+        <v>-16.188684000000002</v>
       </c>
       <c r="K6" s="1">
-        <v>-45.848387999999993</v>
+        <v>-17.979759999999999</v>
       </c>
       <c r="L6" s="1">
-        <v>-41.583767999999985</v>
+        <v>-16.307359999999996</v>
       </c>
       <c r="M6" s="1">
-        <v>-60.468944579999992</v>
+        <v>-23.713311599999997</v>
       </c>
       <c r="N6" s="1">
-        <v>-61.662843360000018</v>
+        <v>-24.181507200000006</v>
       </c>
       <c r="O6" s="1">
-        <v>-54.158727840000005</v>
+        <v>-21.238716800000002</v>
       </c>
       <c r="P6" s="1">
-        <v>-55.094133119999995</v>
+        <v>-21.605542400000001</v>
       </c>
       <c r="Q6" s="1">
-        <v>-50.635108259999996</v>
+        <v>-19.8569052</v>
       </c>
       <c r="R6" s="1">
-        <v>-50.137863360000019</v>
+        <v>-19.661907200000005</v>
       </c>
       <c r="S6" s="1">
-        <v>-43.870811999999994</v>
+        <v>-17.204239999999999</v>
       </c>
       <c r="T6" s="1">
-        <v>-40.201313040000002</v>
+        <v>-15.765220800000002</v>
       </c>
       <c r="U6" s="1">
-        <v>-35.241995520000003</v>
+        <v>-13.820390400000001</v>
       </c>
       <c r="V6" s="1">
-        <v>-23.301185999999998</v>
+        <v>-9.1377199999999998</v>
       </c>
       <c r="W6" s="1">
-        <v>-25.816748759999996</v>
+        <v>-10.124215199999998</v>
       </c>
       <c r="X6" s="1">
-        <v>-27.013790159999996</v>
+        <v>-10.593643199999999</v>
       </c>
       <c r="Y6" s="1">
-        <v>-28.705956899999997</v>
+        <v>-11.257237999999999</v>
       </c>
       <c r="Z6" s="1">
-        <v>-24.452500799999999</v>
+        <v>-9.5892160000000004</v>
       </c>
       <c r="AA6" s="1">
-        <v>-23.984524800000003</v>
+        <v>-9.4056960000000007</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
@@ -69783,76 +69847,76 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>25.905149100000003</v>
+        <v>10.158882</v>
       </c>
       <c r="E7" s="1">
-        <v>30.048000479999995</v>
+        <v>11.783529599999998</v>
       </c>
       <c r="F7" s="1">
-        <v>31.401083519999993</v>
+        <v>12.314150399999999</v>
       </c>
       <c r="G7" s="1">
-        <v>33.436410900000006</v>
+        <v>13.112318000000002</v>
       </c>
       <c r="H7" s="1">
-        <v>36.339177899999989</v>
+        <v>14.250657999999998</v>
       </c>
       <c r="I7" s="1">
-        <v>42.134313000000006</v>
+        <v>16.523260000000004</v>
       </c>
       <c r="J7" s="1">
-        <v>37.439712</v>
+        <v>14.68224</v>
       </c>
       <c r="K7" s="1">
-        <v>42.250423680000004</v>
+        <v>16.568793600000003</v>
       </c>
       <c r="L7" s="1">
-        <v>40.716491580000003</v>
+        <v>15.967251600000003</v>
       </c>
       <c r="M7" s="1">
-        <v>44.620554839999997</v>
+        <v>17.4982568</v>
       </c>
       <c r="N7" s="1">
-        <v>46.362774000000002</v>
+        <v>18.181480000000001</v>
       </c>
       <c r="O7" s="1">
-        <v>44.268083639999993</v>
+        <v>17.360032799999999</v>
       </c>
       <c r="P7" s="1">
-        <v>40.259808000000007</v>
+        <v>15.788160000000003</v>
       </c>
       <c r="Q7" s="1">
-        <v>41.676551279999991</v>
+        <v>16.343745599999998</v>
       </c>
       <c r="R7" s="1">
-        <v>40.206196800000008</v>
+        <v>15.767136000000004</v>
       </c>
       <c r="S7" s="1">
-        <v>35.908142220000009</v>
+        <v>14.081624400000003</v>
       </c>
       <c r="T7" s="1">
-        <v>31.502594939999991</v>
+        <v>12.353958799999997</v>
       </c>
       <c r="U7" s="1">
-        <v>30.187397759999996</v>
+        <v>11.838195199999999</v>
       </c>
       <c r="V7" s="1">
-        <v>23.854811399999999</v>
+        <v>9.3548279999999995</v>
       </c>
       <c r="W7" s="1">
-        <v>25.429008</v>
+        <v>9.9721600000000006</v>
       </c>
       <c r="X7" s="1">
-        <v>25.670166600000005</v>
+        <v>10.066732000000002</v>
       </c>
       <c r="Y7" s="1">
-        <v>30.562484400000002</v>
+        <v>11.985288000000002</v>
       </c>
       <c r="Z7" s="1">
-        <v>22.422608999999998</v>
+        <v>8.7931799999999996</v>
       </c>
       <c r="AA7" s="1">
-        <v>24.084240000000008</v>
+        <v>9.4448000000000025</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
@@ -69866,76 +69930,76 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>12.163222764000002</v>
+        <v>4.7698912800000013</v>
       </c>
       <c r="E8" s="1">
-        <v>13.214120400000002</v>
+        <v>5.1820080000000006</v>
       </c>
       <c r="F8" s="1">
-        <v>12.185123184</v>
+        <v>4.7784796800000002</v>
       </c>
       <c r="G8" s="1">
-        <v>10.766891519999998</v>
+        <v>4.2223103999999996</v>
       </c>
       <c r="H8" s="1">
-        <v>8.3870438399999987</v>
+        <v>3.2890367999999999</v>
       </c>
       <c r="I8" s="1">
-        <v>7.4134840320000013</v>
+        <v>2.9072486400000006</v>
       </c>
       <c r="J8" s="1">
-        <v>9.3494049660000016</v>
+        <v>3.6664333200000003</v>
       </c>
       <c r="K8" s="1">
-        <v>1.655017728</v>
+        <v>0.64902656000000003</v>
       </c>
       <c r="L8" s="1">
-        <v>1.4851200000000002</v>
+        <v>0.58240000000000014</v>
       </c>
       <c r="M8" s="1">
-        <v>2.0766154500000003</v>
+        <v>0.81435900000000006</v>
       </c>
       <c r="N8" s="1">
-        <v>1.2135343920000001</v>
+        <v>0.47589584000000007</v>
       </c>
       <c r="O8" s="1">
-        <v>1.5473604000000001</v>
+        <v>0.60680800000000001</v>
       </c>
       <c r="P8" s="1">
-        <v>2.4164514000000006</v>
+        <v>0.94762800000000025</v>
       </c>
       <c r="Q8" s="1">
-        <v>4.4859370500000004</v>
+        <v>1.7591910000000002</v>
       </c>
       <c r="R8" s="1">
-        <v>4.6541375999999994</v>
+        <v>1.8251519999999999</v>
       </c>
       <c r="S8" s="1">
-        <v>4.6685036879999995</v>
+        <v>1.8307857599999997</v>
       </c>
       <c r="T8" s="1">
-        <v>2.5145550000000001</v>
+        <v>0.98609999999999998</v>
       </c>
       <c r="U8" s="1">
-        <v>5.4914668199999994</v>
+        <v>2.1535163999999996</v>
       </c>
       <c r="V8" s="1">
-        <v>3.1317667920000001</v>
+        <v>1.22814384</v>
       </c>
       <c r="W8" s="1">
-        <v>2.4059265299999995</v>
+        <v>0.9435005999999998</v>
       </c>
       <c r="X8" s="1">
-        <v>3.4120224000000006</v>
+        <v>1.3380480000000003</v>
       </c>
       <c r="Y8" s="1">
-        <v>2.06288472</v>
+        <v>0.80897439999999998</v>
       </c>
       <c r="Z8" s="1">
-        <v>9.5260480560000005</v>
+        <v>3.7357051200000004</v>
       </c>
       <c r="AA8" s="1">
-        <v>11.0287296</v>
+        <v>4.3249919999999999</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
@@ -69949,76 +70013,76 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>-26.889750000000003</v>
+        <v>-10.545000000000002</v>
       </c>
       <c r="E9" s="1">
-        <v>-29.964805200000001</v>
+        <v>-11.750904</v>
       </c>
       <c r="F9" s="1">
-        <v>-32.339406000000004</v>
+        <v>-12.682120000000003</v>
       </c>
       <c r="G9" s="1">
-        <v>-34.884968999999998</v>
+        <v>-13.68038</v>
       </c>
       <c r="H9" s="1">
-        <v>-39.594996480000006</v>
+        <v>-15.527449600000002</v>
       </c>
       <c r="I9" s="1">
-        <v>-40.299073920000005</v>
+        <v>-15.803558400000002</v>
       </c>
       <c r="J9" s="1">
-        <v>-42.519578526000004</v>
+        <v>-16.674344520000002</v>
       </c>
       <c r="K9" s="1">
-        <v>-44.931420239999994</v>
+        <v>-17.620164799999998</v>
       </c>
       <c r="L9" s="1">
-        <v>-43.662956399999985</v>
+        <v>-17.122727999999995</v>
       </c>
       <c r="M9" s="1">
-        <v>-61.07363402579999</v>
+        <v>-23.950444715999996</v>
       </c>
       <c r="N9" s="1">
-        <v>-59.812958059200028</v>
+        <v>-23.456061984000009</v>
       </c>
       <c r="O9" s="1">
-        <v>-55.783489675200016</v>
+        <v>-21.875878304000004</v>
       </c>
       <c r="P9" s="1">
-        <v>-54.543191788800009</v>
+        <v>-21.389486976000004</v>
       </c>
       <c r="Q9" s="1">
-        <v>-53.166863673000002</v>
+        <v>-20.849750459999999</v>
       </c>
       <c r="R9" s="1">
-        <v>-49.636484726400013</v>
+        <v>-19.465288128000005</v>
       </c>
       <c r="S9" s="1">
-        <v>-43.870811999999994</v>
+        <v>-17.204239999999999</v>
       </c>
       <c r="T9" s="1">
-        <v>-39.799299909600002</v>
+        <v>-15.607568592000002</v>
       </c>
       <c r="U9" s="1">
-        <v>-36.651675340800004</v>
+        <v>-14.373206016000001</v>
       </c>
       <c r="V9" s="1">
-        <v>-24.000221580000002</v>
+        <v>-9.4118516000000003</v>
       </c>
       <c r="W9" s="1">
-        <v>-25.558581272399991</v>
+        <v>-10.022973047999997</v>
       </c>
       <c r="X9" s="1">
-        <v>-27.013790159999996</v>
+        <v>-10.593643199999999</v>
       </c>
       <c r="Y9" s="1">
-        <v>-27.270659054999999</v>
+        <v>-10.694376099999999</v>
       </c>
       <c r="Z9" s="1">
-        <v>-24.207975791999999</v>
+        <v>-9.4933238400000004</v>
       </c>
       <c r="AA9" s="1">
-        <v>-25.183751040000001</v>
+        <v>-9.8759808000000007</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
@@ -70032,76 +70096,76 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>26.423252082000001</v>
+        <v>10.36205964</v>
       </c>
       <c r="E10" s="1">
-        <v>28.545600455999992</v>
+        <v>11.194353119999999</v>
       </c>
       <c r="F10" s="1">
-        <v>31.401083519999993</v>
+        <v>12.314150399999999</v>
       </c>
       <c r="G10" s="1">
-        <v>32.433318573000008</v>
+        <v>12.718948460000002</v>
       </c>
       <c r="H10" s="1">
-        <v>34.52221900499999</v>
+        <v>13.538125099999997</v>
       </c>
       <c r="I10" s="1">
-        <v>40.027597350000008</v>
+        <v>15.697097000000003</v>
       </c>
       <c r="J10" s="1">
-        <v>35.567726399999998</v>
+        <v>13.948127999999999</v>
       </c>
       <c r="K10" s="1">
-        <v>40.137902496000002</v>
+        <v>15.740353920000002</v>
       </c>
       <c r="L10" s="1">
-        <v>39.902161748400005</v>
+        <v>15.647906568000003</v>
       </c>
       <c r="M10" s="1">
-        <v>45.512965936800001</v>
+        <v>17.848221936000002</v>
       </c>
       <c r="N10" s="1">
-        <v>47.290029479999994</v>
+        <v>18.5451096</v>
       </c>
       <c r="O10" s="1">
-        <v>42.054679458000003</v>
+        <v>16.49203116</v>
       </c>
       <c r="P10" s="1">
-        <v>41.870200320000009</v>
+        <v>16.419686400000003</v>
       </c>
       <c r="Q10" s="1">
-        <v>42.093316792799996</v>
+        <v>16.507183055999999</v>
       </c>
       <c r="R10" s="1">
-        <v>41.010320736000011</v>
+        <v>16.082478720000005</v>
       </c>
       <c r="S10" s="1">
-        <v>34.471816531200005</v>
+        <v>13.518359424000003</v>
       </c>
       <c r="T10" s="1">
-        <v>32.76269873759999</v>
+        <v>12.848117151999997</v>
       </c>
       <c r="U10" s="1">
-        <v>28.979901849599997</v>
+        <v>11.364667391999999</v>
       </c>
       <c r="V10" s="1">
-        <v>25.047551969999997</v>
+        <v>9.822569399999999</v>
       </c>
       <c r="W10" s="1">
-        <v>25.683298080000004</v>
+        <v>10.071881600000001</v>
       </c>
       <c r="X10" s="1">
-        <v>26.696973264000004</v>
+        <v>10.469401280000001</v>
       </c>
       <c r="Y10" s="1">
-        <v>31.479358932000011</v>
+        <v>12.344846640000004</v>
       </c>
       <c r="Z10" s="1">
-        <v>22.646835089999996</v>
+        <v>8.8811117999999993</v>
       </c>
       <c r="AA10" s="1">
-        <v>25.28845200000001</v>
+        <v>9.9170400000000036</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
@@ -70115,76 +70179,76 @@
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>11.909979000000002</v>
+        <v>4.6705800000000011</v>
       </c>
       <c r="E11" s="1">
-        <v>12.307269</v>
+        <v>4.8263800000000003</v>
       </c>
       <c r="F11" s="1">
-        <v>11.020436999999999</v>
+        <v>4.3217400000000001</v>
       </c>
       <c r="G11" s="1">
-        <v>10.445819999999998</v>
+        <v>4.0963999999999992</v>
       </c>
       <c r="H11" s="1">
-        <v>8.5582080000000005</v>
+        <v>3.35616</v>
       </c>
       <c r="I11" s="1">
-        <v>7.263624000000001</v>
+        <v>2.8484800000000003</v>
       </c>
       <c r="J11" s="1">
-        <v>8.8828229999999984</v>
+        <v>3.48346</v>
       </c>
       <c r="K11" s="1">
-        <v>1.542648</v>
+        <v>0.60496000000000005</v>
       </c>
       <c r="L11" s="1">
-        <v>1.3566</v>
+        <v>0.53200000000000003</v>
       </c>
       <c r="M11" s="1">
-        <v>1.9777289999999996</v>
+        <v>0.77557999999999983</v>
       </c>
       <c r="N11" s="1">
-        <v>1.1647380000000001</v>
+        <v>0.45676000000000005</v>
       </c>
       <c r="O11" s="1">
-        <v>1.4554379999999998</v>
+        <v>0.57075999999999993</v>
       </c>
       <c r="P11" s="1">
-        <v>2.3188170000000006</v>
+        <v>0.90934000000000026</v>
       </c>
       <c r="Q11" s="1">
-        <v>4.2723210000000007</v>
+        <v>1.6754200000000001</v>
       </c>
       <c r="R11" s="1">
-        <v>4.5581759999999996</v>
+        <v>1.7875199999999998</v>
       </c>
       <c r="S11" s="1">
-        <v>4.4825939999999989</v>
+        <v>1.7578799999999997</v>
       </c>
       <c r="T11" s="1">
-        <v>2.5145550000000001</v>
+        <v>0.98609999999999998</v>
       </c>
       <c r="U11" s="1">
-        <v>5.1221339999999982</v>
+        <v>2.0086799999999996</v>
       </c>
       <c r="V11" s="1">
-        <v>3.0058379999999998</v>
+        <v>1.17876</v>
       </c>
       <c r="W11" s="1">
-        <v>2.1133889999999993</v>
+        <v>0.82877999999999985</v>
       </c>
       <c r="X11" s="1">
-        <v>3.2093280000000002</v>
+        <v>1.2585600000000001</v>
       </c>
       <c r="Y11" s="1">
-        <v>1.9835429999999998</v>
+        <v>0.77786</v>
       </c>
       <c r="Z11" s="1">
-        <v>9.0533669999999997</v>
+        <v>3.5503400000000003</v>
       </c>
       <c r="AA11" s="1">
-        <v>10.913846999999999</v>
+        <v>4.2799399999999999</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
@@ -70198,76 +70262,76 @@
         <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>-27.965340000000005</v>
+        <v>-10.966800000000003</v>
       </c>
       <c r="E12" s="1">
-        <v>-29.964805200000001</v>
+        <v>-11.750904</v>
       </c>
       <c r="F12" s="1">
-        <v>-30.722435700000005</v>
+        <v>-12.048014000000002</v>
       </c>
       <c r="G12" s="1">
-        <v>-34.884968999999998</v>
+        <v>-13.68038</v>
       </c>
       <c r="H12" s="1">
-        <v>-39.199046515200003</v>
+        <v>-15.372175104000002</v>
       </c>
       <c r="I12" s="1">
-        <v>-41.911036876800004</v>
+        <v>-16.435700736000001</v>
       </c>
       <c r="J12" s="1">
-        <v>-41.243991170220006</v>
+        <v>-16.174114184400004</v>
       </c>
       <c r="K12" s="1">
-        <v>-44.482106037599983</v>
+        <v>-17.443963151999995</v>
       </c>
       <c r="L12" s="1">
-        <v>-44.536215527999985</v>
+        <v>-17.465182559999995</v>
       </c>
       <c r="M12" s="1">
-        <v>-58.630688664767987</v>
+        <v>-22.992426927359997</v>
       </c>
       <c r="N12" s="1">
-        <v>-60.411087639792029</v>
+        <v>-23.690622603840012</v>
       </c>
       <c r="O12" s="1">
-        <v>-57.456994365456019</v>
+        <v>-22.532154653120006</v>
       </c>
       <c r="P12" s="1">
-        <v>-52.906896035136</v>
+        <v>-20.747802366720002</v>
       </c>
       <c r="Q12" s="1">
-        <v>-50.508520489349991</v>
+        <v>-19.807262936999997</v>
       </c>
       <c r="R12" s="1">
-        <v>-49.140119879136009</v>
+        <v>-19.270635246720005</v>
       </c>
       <c r="S12" s="1">
-        <v>-43.870811999999994</v>
+        <v>-17.204239999999999</v>
       </c>
       <c r="T12" s="1">
-        <v>-41.391271905984006</v>
+        <v>-16.231871335680001</v>
       </c>
       <c r="U12" s="1">
-        <v>-35.918641833983997</v>
+        <v>-14.08574189568</v>
       </c>
       <c r="V12" s="1">
-        <v>-23.040212716800003</v>
+        <v>-9.0353775360000004</v>
       </c>
       <c r="W12" s="1">
-        <v>-25.814167085123991</v>
+        <v>-10.123202778479998</v>
       </c>
       <c r="X12" s="1">
-        <v>-28.364479668000001</v>
+        <v>-11.123325359999999</v>
       </c>
       <c r="Y12" s="1">
-        <v>-27.270659054999999</v>
+        <v>-10.694376099999999</v>
       </c>
       <c r="Z12" s="1">
-        <v>-23.481736518240002</v>
+        <v>-9.2085241248000003</v>
       </c>
       <c r="AA12" s="1">
-        <v>-24.680076019199998</v>
+        <v>-9.6784611839999997</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
@@ -70281,76 +70345,76 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>25.102089477899998</v>
+        <v>9.8439566579999997</v>
       </c>
       <c r="E13" s="1">
-        <v>27.689232442319998</v>
+        <v>10.8585225264</v>
       </c>
       <c r="F13" s="1">
-        <v>31.715094355199994</v>
+        <v>12.437291903999999</v>
       </c>
       <c r="G13" s="1">
-        <v>31.784652201540005</v>
+        <v>12.464569490800002</v>
       </c>
       <c r="H13" s="1">
-        <v>34.176996814949987</v>
+        <v>13.402743848999997</v>
       </c>
       <c r="I13" s="1">
-        <v>40.427873323500009</v>
+        <v>15.854067970000003</v>
       </c>
       <c r="J13" s="1">
-        <v>35.567726399999998</v>
+        <v>13.948127999999999</v>
       </c>
       <c r="K13" s="1">
-        <v>40.539281520960003</v>
+        <v>15.897757459200001</v>
       </c>
       <c r="L13" s="1">
-        <v>39.902161748400005</v>
+        <v>15.647906568000003</v>
       </c>
       <c r="M13" s="1">
-        <v>46.878354914904001</v>
+        <v>18.383668594080003</v>
       </c>
       <c r="N13" s="1">
-        <v>44.925528006</v>
+        <v>17.617854120000001</v>
       </c>
       <c r="O13" s="1">
-        <v>39.951945485100005</v>
+        <v>15.667429602</v>
       </c>
       <c r="P13" s="1">
-        <v>43.126306329600006</v>
+        <v>16.912276992000002</v>
       </c>
       <c r="Q13" s="1">
-        <v>41.672383624871998</v>
+        <v>16.34211122544</v>
       </c>
       <c r="R13" s="1">
-        <v>40.190114321280014</v>
+        <v>15.760829145600006</v>
       </c>
       <c r="S13" s="1">
-        <v>32.748225704640006</v>
+        <v>12.842441452800003</v>
       </c>
       <c r="T13" s="1">
-        <v>34.400833674479991</v>
+        <v>13.490523009599997</v>
       </c>
       <c r="U13" s="1">
-        <v>30.139097923583996</v>
+        <v>11.819254087679999</v>
       </c>
       <c r="V13" s="1">
-        <v>25.298027489699997</v>
+        <v>9.9207950939999989</v>
       </c>
       <c r="W13" s="1">
-        <v>26.453797022400007</v>
+        <v>10.374038048000003</v>
       </c>
       <c r="X13" s="1">
-        <v>26.430003531360004</v>
+        <v>10.364707267200002</v>
       </c>
       <c r="Y13" s="1">
-        <v>32.738533289280014</v>
+        <v>12.838640505600004</v>
       </c>
       <c r="Z13" s="1">
-        <v>22.646835089999996</v>
+        <v>8.8811117999999993</v>
       </c>
       <c r="AA13" s="1">
-        <v>25.794221040000011</v>
+        <v>10.115380800000004</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -70364,76 +70428,76 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>12.386378160000003</v>
+        <v>4.8574032000000011</v>
       </c>
       <c r="E14" s="1">
-        <v>12.430341690000001</v>
+        <v>4.8746438000000003</v>
       </c>
       <c r="F14" s="1">
-        <v>11.020436999999999</v>
+        <v>4.3217400000000001</v>
       </c>
       <c r="G14" s="1">
-        <v>10.654736399999996</v>
+        <v>4.1783279999999987</v>
       </c>
       <c r="H14" s="1">
-        <v>8.6437900800000005</v>
+        <v>3.3897216000000001</v>
       </c>
       <c r="I14" s="1">
-        <v>7.0457152799999996</v>
+        <v>2.7630256000000002</v>
       </c>
       <c r="J14" s="1">
-        <v>9.2381359199999977</v>
+        <v>3.6227983999999998</v>
       </c>
       <c r="K14" s="1">
-        <v>1.5272215200000001</v>
+        <v>0.59891040000000006</v>
       </c>
       <c r="L14" s="1">
-        <v>1.3972980000000002</v>
+        <v>0.54796000000000011</v>
       </c>
       <c r="M14" s="1">
-        <v>1.9579517099999997</v>
+        <v>0.76782419999999985</v>
       </c>
       <c r="N14" s="1">
-        <v>1.1996801400000001</v>
+        <v>0.47046280000000001</v>
       </c>
       <c r="O14" s="1">
-        <v>1.3826661</v>
+        <v>0.54222199999999998</v>
       </c>
       <c r="P14" s="1">
-        <v>2.3188170000000006</v>
+        <v>0.90934000000000026</v>
       </c>
       <c r="Q14" s="1">
-        <v>4.4004906300000002</v>
+        <v>1.7256826000000001</v>
       </c>
       <c r="R14" s="1">
-        <v>4.4670124800000002</v>
+        <v>1.7517695999999998</v>
       </c>
       <c r="S14" s="1">
-        <v>4.5722458799999979</v>
+        <v>1.7930375999999995</v>
       </c>
       <c r="T14" s="1">
-        <v>2.4139727999999998</v>
+        <v>0.94665599999999994</v>
       </c>
       <c r="U14" s="1">
-        <v>4.9172486399999986</v>
+        <v>1.9283327999999995</v>
       </c>
       <c r="V14" s="1">
-        <v>2.88560448</v>
+        <v>1.1316096</v>
       </c>
       <c r="W14" s="1">
-        <v>2.2190584499999999</v>
+        <v>0.87021899999999985</v>
       </c>
       <c r="X14" s="1">
-        <v>3.1130481600000004</v>
+        <v>1.2208032000000002</v>
       </c>
       <c r="Y14" s="1">
-        <v>2.0430492899999999</v>
+        <v>0.80119580000000001</v>
       </c>
       <c r="Z14" s="1">
-        <v>9.1439006700000007</v>
+        <v>3.5858434000000003</v>
       </c>
       <c r="AA14" s="1">
-        <v>10.69557006</v>
+        <v>4.1943412000000002</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -70447,76 +70511,76 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>-28.244993400000002</v>
+        <v>-11.076468000000002</v>
       </c>
       <c r="E15" s="1">
-        <v>-29.365509096</v>
+        <v>-11.515885920000001</v>
       </c>
       <c r="F15" s="1">
-        <v>-29.493538272000002</v>
+        <v>-11.566093440000001</v>
       </c>
       <c r="G15" s="1">
-        <v>-33.489570239999992</v>
+        <v>-13.133164799999999</v>
       </c>
       <c r="H15" s="1">
-        <v>-40.767008375808011</v>
+        <v>-15.987062108160004</v>
       </c>
       <c r="I15" s="1">
-        <v>-41.072816139263999</v>
+        <v>-16.106986721279998</v>
       </c>
       <c r="J15" s="1">
-        <v>-40.419111346815605</v>
+        <v>-15.850631900712003</v>
       </c>
       <c r="K15" s="1">
-        <v>-42.702821796095982</v>
+        <v>-16.746204625919994</v>
       </c>
       <c r="L15" s="1">
-        <v>-44.981577683279994</v>
+        <v>-17.639834385599997</v>
       </c>
       <c r="M15" s="1">
-        <v>-58.044381778120318</v>
+        <v>-22.762502658086397</v>
       </c>
       <c r="N15" s="1">
-        <v>-62.827531145383709</v>
+        <v>-24.638247507993611</v>
       </c>
       <c r="O15" s="1">
-        <v>-56.307854478146893</v>
+        <v>-22.081511560057606</v>
       </c>
       <c r="P15" s="1">
-        <v>-52.377827074784648</v>
+        <v>-20.540324343052802</v>
       </c>
       <c r="Q15" s="1">
-        <v>-48.488179669775988</v>
+        <v>-19.014972419519996</v>
       </c>
       <c r="R15" s="1">
-        <v>-48.157317481553292</v>
+        <v>-18.885222541785605</v>
       </c>
       <c r="S15" s="1">
-        <v>-41.677271399999995</v>
+        <v>-16.344027999999998</v>
       </c>
       <c r="T15" s="1">
-        <v>-41.391271905984006</v>
+        <v>-16.231871335680001</v>
       </c>
       <c r="U15" s="1">
-        <v>-35.559455415644152</v>
+        <v>-13.9448844767232</v>
       </c>
       <c r="V15" s="1">
-        <v>-23.040212716800003</v>
+        <v>-9.0353775360000004</v>
       </c>
       <c r="W15" s="1">
-        <v>-26.33045042682647</v>
+        <v>-10.325666834049597</v>
       </c>
       <c r="X15" s="1">
-        <v>-28.648124464679995</v>
+        <v>-11.234558613599999</v>
       </c>
       <c r="Y15" s="1">
-        <v>-27.543365645550001</v>
+        <v>-10.801319861</v>
       </c>
       <c r="Z15" s="1">
-        <v>-22.542467057510397</v>
+        <v>-8.8401831598079994</v>
       </c>
       <c r="AA15" s="1">
-        <v>-25.667279059967996</v>
+        <v>-10.06559963136</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
@@ -70530,76 +70594,76 @@
         <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>23.846985004004999</v>
+        <v>9.3517588250999992</v>
       </c>
       <c r="E16" s="1">
-        <v>26.5816631446272</v>
+        <v>10.424181625344</v>
       </c>
       <c r="F16" s="1">
-        <v>33.300849072959991</v>
+        <v>13.059156499199998</v>
       </c>
       <c r="G16" s="1">
-        <v>30.513266113478405</v>
+        <v>11.965986711168002</v>
       </c>
       <c r="H16" s="1">
-        <v>35.885846655697492</v>
+        <v>14.072881041449996</v>
       </c>
       <c r="I16" s="1">
-        <v>38.810758390560004</v>
+        <v>15.219905251200002</v>
       </c>
       <c r="J16" s="1">
-        <v>35.923403663999999</v>
+        <v>14.087609279999999</v>
       </c>
       <c r="K16" s="1">
-        <v>40.539281520960003</v>
+        <v>15.897757459200001</v>
       </c>
       <c r="L16" s="1">
-        <v>37.907053660980012</v>
+        <v>14.865511239600004</v>
       </c>
       <c r="M16" s="1">
-        <v>47.815922013202091</v>
+        <v>18.751341965961604</v>
       </c>
       <c r="N16" s="1">
-        <v>44.027017445879999</v>
+        <v>17.265497037599999</v>
       </c>
       <c r="O16" s="1">
-        <v>41.550023304503995</v>
+        <v>16.29412678608</v>
       </c>
       <c r="P16" s="1">
-        <v>41.401254076416002</v>
+        <v>16.235785912320001</v>
       </c>
       <c r="Q16" s="1">
-        <v>42.922555133618154</v>
+        <v>16.832374562203199</v>
       </c>
       <c r="R16" s="1">
-        <v>40.993916607705614</v>
+        <v>16.076045728512007</v>
       </c>
       <c r="S16" s="1">
-        <v>33.075707961686412</v>
+        <v>12.970865867328003</v>
       </c>
       <c r="T16" s="1">
-        <v>35.08885034796959</v>
+        <v>13.760333469791997</v>
       </c>
       <c r="U16" s="1">
-        <v>29.536315965112319</v>
+        <v>11.582869005926399</v>
       </c>
       <c r="V16" s="1">
-        <v>25.551007764596999</v>
+        <v>10.020003044939999</v>
       </c>
       <c r="W16" s="1">
-        <v>26.453797022400007</v>
+        <v>10.374038048000003</v>
       </c>
       <c r="X16" s="1">
-        <v>27.487203672614402</v>
+        <v>10.779295557888002</v>
       </c>
       <c r="Y16" s="1">
-        <v>33.393303955065605</v>
+        <v>13.095413315712005</v>
       </c>
       <c r="Z16" s="1">
-        <v>22.873303440899999</v>
+        <v>8.969922918</v>
       </c>
       <c r="AA16" s="1">
-        <v>24.762452198400009</v>
+        <v>9.7107655680000047</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
@@ -70613,76 +70677,76 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>11.767059252000003</v>
+        <v>4.6145330400000013</v>
       </c>
       <c r="E17" s="1">
-        <v>12.927555357600001</v>
+        <v>5.0696295520000003</v>
       </c>
       <c r="F17" s="1">
-        <v>10.910232629999999</v>
+        <v>4.2785225999999996</v>
       </c>
       <c r="G17" s="1">
-        <v>11.187473219999996</v>
+        <v>4.3872443999999984</v>
       </c>
       <c r="H17" s="1">
-        <v>8.7302279808000005</v>
+        <v>3.4236188159999998</v>
       </c>
       <c r="I17" s="1">
-        <v>6.9752581272000009</v>
+        <v>2.7353953440000005</v>
       </c>
       <c r="J17" s="1">
-        <v>8.9609918423999986</v>
+        <v>3.5141144479999995</v>
       </c>
       <c r="K17" s="1">
-        <v>1.5424937352000001</v>
+        <v>0.60489950400000003</v>
       </c>
       <c r="L17" s="1">
-        <v>1.3972980000000002</v>
+        <v>0.54796000000000011</v>
       </c>
       <c r="M17" s="1">
-        <v>1.8992131586999994</v>
+        <v>0.74478947399999984</v>
       </c>
       <c r="N17" s="1">
-        <v>1.1876833385999999</v>
+        <v>0.46575817200000003</v>
       </c>
       <c r="O17" s="1">
-        <v>1.3688394389999998</v>
+        <v>0.53679977999999995</v>
       </c>
       <c r="P17" s="1">
-        <v>2.3188170000000006</v>
+        <v>0.90934000000000026</v>
       </c>
       <c r="Q17" s="1">
-        <v>4.4444955362999998</v>
+        <v>1.7429394260000002</v>
       </c>
       <c r="R17" s="1">
-        <v>4.6903631039999993</v>
+        <v>1.8393580799999998</v>
       </c>
       <c r="S17" s="1">
-        <v>4.3436335859999984</v>
+        <v>1.7033857199999993</v>
       </c>
       <c r="T17" s="1">
-        <v>2.3415536159999997</v>
+        <v>0.91825632000000001</v>
       </c>
       <c r="U17" s="1">
-        <v>4.8680761535999988</v>
+        <v>1.9090494719999995</v>
       </c>
       <c r="V17" s="1">
-        <v>2.9433165695999999</v>
+        <v>1.1542417919999999</v>
       </c>
       <c r="W17" s="1">
-        <v>2.2190584499999999</v>
+        <v>0.87021899999999985</v>
       </c>
       <c r="X17" s="1">
-        <v>3.0507871968000004</v>
+        <v>1.1963871360000002</v>
       </c>
       <c r="Y17" s="1">
-        <v>2.0430492899999999</v>
+        <v>0.80119580000000001</v>
       </c>
       <c r="Z17" s="1">
-        <v>8.778144643200001</v>
+        <v>3.4424096640000004</v>
       </c>
       <c r="AA17" s="1">
-        <v>10.481658658799999</v>
+        <v>4.1104543759999999</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -70696,76 +70760,76 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>-27.962543466000007</v>
+        <v>-10.965703320000003</v>
       </c>
       <c r="E18" s="1">
-        <v>-30.540129459840003</v>
+        <v>-11.976521356800001</v>
       </c>
       <c r="F18" s="1">
-        <v>-28.018861358399995</v>
+        <v>-10.987788768</v>
       </c>
       <c r="G18" s="1">
-        <v>-33.824465942399996</v>
+        <v>-13.264496447999999</v>
       </c>
       <c r="H18" s="1">
-        <v>-41.990018627082243</v>
+        <v>-16.466673971404802</v>
       </c>
       <c r="I18" s="1">
-        <v>-41.483544300656632</v>
+        <v>-16.268056588492797</v>
       </c>
       <c r="J18" s="1">
-        <v>-38.802346892942985</v>
+        <v>-15.216606624683523</v>
       </c>
       <c r="K18" s="1">
-        <v>-43.556878232017901</v>
+        <v>-17.081128718438393</v>
       </c>
       <c r="L18" s="1">
-        <v>-45.431393460112794</v>
+        <v>-17.816232729455997</v>
       </c>
       <c r="M18" s="1">
-        <v>-55.722606506995497</v>
+        <v>-21.852002551762943</v>
       </c>
       <c r="N18" s="1">
-        <v>-64.084081768291384</v>
+        <v>-25.131012458153482</v>
       </c>
       <c r="O18" s="1">
-        <v>-55.744775933365425</v>
+        <v>-21.86069644445703</v>
       </c>
       <c r="P18" s="1">
-        <v>-53.94916188702819</v>
+        <v>-21.156534073344389</v>
       </c>
       <c r="Q18" s="1">
-        <v>-49.942825059869264</v>
+        <v>-19.585421592105593</v>
       </c>
       <c r="R18" s="1">
-        <v>-50.565183355630957</v>
+        <v>-19.829483668874886</v>
       </c>
       <c r="S18" s="1">
-        <v>-43.344362255999997</v>
+        <v>-16.997789119999997</v>
       </c>
       <c r="T18" s="1">
-        <v>-40.14953374880448</v>
+        <v>-15.7449151956096</v>
       </c>
       <c r="U18" s="1">
-        <v>-36.626239078113485</v>
+        <v>-14.363231011024896</v>
       </c>
       <c r="V18" s="1">
-        <v>-21.888202080959999</v>
+        <v>-8.5836086592000012</v>
       </c>
       <c r="W18" s="1">
-        <v>-25.803841418289942</v>
+        <v>-10.119153497368606</v>
       </c>
       <c r="X18" s="1">
-        <v>-28.361643220033198</v>
+        <v>-11.122213027463999</v>
       </c>
       <c r="Y18" s="1">
-        <v>-26.717064676183497</v>
+        <v>-10.47728026517</v>
       </c>
       <c r="Z18" s="1">
-        <v>-22.091617716360194</v>
+        <v>-8.6633794966118405</v>
       </c>
       <c r="AA18" s="1">
-        <v>-25.667279059967996</v>
+        <v>-10.06559963136</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
@@ -70779,76 +70843,76 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>22.654635753804747</v>
+        <v>8.884170883845</v>
       </c>
       <c r="E19" s="1">
-        <v>27.113296407519741</v>
+        <v>10.63266525785088</v>
       </c>
       <c r="F19" s="1">
-        <v>34.6328830358784</v>
+        <v>13.581522759167999</v>
       </c>
       <c r="G19" s="1">
-        <v>32.038929419152325</v>
+        <v>12.564286046726401</v>
       </c>
       <c r="H19" s="1">
-        <v>37.321280521925388</v>
+        <v>14.635796283107995</v>
       </c>
       <c r="I19" s="1">
-        <v>37.646435638843201</v>
+        <v>14.763308093664001</v>
       </c>
       <c r="J19" s="1">
-        <v>37.719573847199996</v>
+        <v>14.791989743999999</v>
       </c>
       <c r="K19" s="1">
-        <v>42.566245597008006</v>
+        <v>16.692645332160001</v>
       </c>
       <c r="L19" s="1">
-        <v>36.769842051150611</v>
+        <v>14.419545902412004</v>
       </c>
       <c r="M19" s="1">
-        <v>47.815922013202091</v>
+        <v>18.751341965961604</v>
       </c>
       <c r="N19" s="1">
-        <v>44.467287620338801</v>
+        <v>17.438152007976001</v>
       </c>
       <c r="O19" s="1">
-        <v>40.71902283841392</v>
+        <v>15.968244250358401</v>
       </c>
       <c r="P19" s="1">
-        <v>43.471316780236805</v>
+        <v>17.047575207936003</v>
       </c>
       <c r="Q19" s="1">
-        <v>41.634878479609618</v>
+        <v>16.327403325337105</v>
       </c>
       <c r="R19" s="1">
-        <v>38.944220777320332</v>
+        <v>15.272243442086406</v>
       </c>
       <c r="S19" s="1">
-        <v>32.744950882069546</v>
+        <v>12.841157208654723</v>
       </c>
       <c r="T19" s="1">
-        <v>35.08885034796959</v>
+        <v>13.760333469791997</v>
       </c>
       <c r="U19" s="1">
-        <v>30.127042284414564</v>
+        <v>11.814526386044927</v>
       </c>
       <c r="V19" s="1">
-        <v>26.573048075180878</v>
+        <v>10.420803166737599</v>
       </c>
       <c r="W19" s="1">
-        <v>27.247410933072008</v>
+        <v>10.685259189440004</v>
       </c>
       <c r="X19" s="1">
-        <v>27.487203672614402</v>
+        <v>10.779295557888002</v>
       </c>
       <c r="Y19" s="1">
-        <v>32.725437875964296</v>
+        <v>12.833505049397765</v>
       </c>
       <c r="Z19" s="1">
-        <v>21.958371303263995</v>
+        <v>8.6111260012799988</v>
       </c>
       <c r="AA19" s="1">
-        <v>24.01957863244801</v>
+        <v>9.4194426009600036</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
@@ -70862,76 +70926,76 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>13.100976900000003</v>
+        <v>5.1376380000000017</v>
       </c>
       <c r="E20" s="1">
-        <v>13.537995900000002</v>
+        <v>5.3090180000000009</v>
       </c>
       <c r="F20" s="1">
-        <v>12.122480700000001</v>
+        <v>4.7539140000000009</v>
       </c>
       <c r="G20" s="1">
-        <v>11.490402</v>
+        <v>4.5060399999999996</v>
       </c>
       <c r="H20" s="1">
-        <v>9.4140288000000005</v>
+        <v>3.6917760000000004</v>
       </c>
       <c r="I20" s="1">
-        <v>7.9899864000000012</v>
+        <v>3.1333280000000006</v>
       </c>
       <c r="J20" s="1">
-        <v>9.7711053000000003</v>
+        <v>3.8318060000000003</v>
       </c>
       <c r="K20" s="1">
-        <v>1.6969128000000002</v>
+        <v>0.66545600000000016</v>
       </c>
       <c r="L20" s="1">
-        <v>1.4922600000000001</v>
+        <v>0.58520000000000005</v>
       </c>
       <c r="M20" s="1">
-        <v>2.1755018999999995</v>
+        <v>0.85313799999999984</v>
       </c>
       <c r="N20" s="1">
-        <v>1.2812118000000001</v>
+        <v>0.5024360000000001</v>
       </c>
       <c r="O20" s="1">
-        <v>1.6009818</v>
+        <v>0.62783599999999995</v>
       </c>
       <c r="P20" s="1">
-        <v>2.5506987000000008</v>
+        <v>1.0002740000000003</v>
       </c>
       <c r="Q20" s="1">
-        <v>4.699553100000001</v>
+        <v>1.8429620000000002</v>
       </c>
       <c r="R20" s="1">
-        <v>5.0139936000000001</v>
+        <v>1.966272</v>
       </c>
       <c r="S20" s="1">
-        <v>4.9308533999999993</v>
+        <v>1.9336679999999997</v>
       </c>
       <c r="T20" s="1">
-        <v>2.7660104999999997</v>
+        <v>1.0847100000000001</v>
       </c>
       <c r="U20" s="1">
-        <v>5.6343473999999993</v>
+        <v>2.2095479999999998</v>
       </c>
       <c r="V20" s="1">
-        <v>3.3064217999999999</v>
+        <v>1.2966360000000001</v>
       </c>
       <c r="W20" s="1">
-        <v>2.3247278999999992</v>
+        <v>0.91165799999999986</v>
       </c>
       <c r="X20" s="1">
-        <v>3.5302608000000011</v>
+        <v>1.3844160000000003</v>
       </c>
       <c r="Y20" s="1">
-        <v>2.1818972999999997</v>
+        <v>0.85564600000000002</v>
       </c>
       <c r="Z20" s="1">
-        <v>9.9587037000000009</v>
+        <v>3.9053740000000006</v>
       </c>
       <c r="AA20" s="1">
-        <v>12.0052317</v>
+        <v>4.7079339999999998</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
@@ -70945,76 +71009,76 @@
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>-27.123667162020009</v>
+        <v>-10.636732220400004</v>
       </c>
       <c r="E21" s="1">
-        <v>-32.067135932832009</v>
+        <v>-12.575347424640002</v>
       </c>
       <c r="F21" s="1">
-        <v>-27.178295517647996</v>
+        <v>-10.658155104959999</v>
       </c>
       <c r="G21" s="1">
-        <v>-34.500955261247995</v>
+        <v>-13.529786376959999</v>
       </c>
       <c r="H21" s="1">
-        <v>-43.669619372165542</v>
+        <v>-17.125340930260997</v>
       </c>
       <c r="I21" s="1">
-        <v>-41.483544300656632</v>
+        <v>-16.268056588492797</v>
       </c>
       <c r="J21" s="1">
-        <v>-39.190370361872418</v>
+        <v>-15.36877269093036</v>
       </c>
       <c r="K21" s="1">
-        <v>-43.121309449697719</v>
+        <v>-16.910317431254008</v>
       </c>
       <c r="L21" s="1">
-        <v>-45.885707394713911</v>
+        <v>-17.994395056750555</v>
       </c>
       <c r="M21" s="1">
-        <v>-55.722606506995497</v>
+        <v>-21.852002551762943</v>
       </c>
       <c r="N21" s="1">
-        <v>-63.443240950608462</v>
+        <v>-24.879702333571945</v>
       </c>
       <c r="O21" s="1">
-        <v>-57.974566970700053</v>
+        <v>-22.735124302235313</v>
       </c>
       <c r="P21" s="1">
-        <v>-53.94916188702819</v>
+        <v>-21.156534073344389</v>
       </c>
       <c r="Q21" s="1">
-        <v>-51.441109811665342</v>
+        <v>-20.172984239868761</v>
       </c>
       <c r="R21" s="1">
-        <v>-49.048227854962029</v>
+        <v>-19.234599158808638</v>
       </c>
       <c r="S21" s="1">
-        <v>-42.477475010879992</v>
+        <v>-16.657833337599996</v>
       </c>
       <c r="T21" s="1">
-        <v>-38.142057061364262</v>
+        <v>-14.957669435829121</v>
       </c>
       <c r="U21" s="1">
-        <v>-36.626239078113485</v>
+        <v>-14.363231011024896</v>
       </c>
       <c r="V21" s="1">
-        <v>-22.325966122579199</v>
+        <v>-8.7552808323840008</v>
       </c>
       <c r="W21" s="1">
-        <v>-26.577956660838641</v>
+        <v>-10.422728102289664</v>
       </c>
       <c r="X21" s="1">
-        <v>-29.496108948834525</v>
+        <v>-11.56710154856256</v>
       </c>
       <c r="Y21" s="1">
-        <v>-26.182723382659834</v>
+        <v>-10.267734659866601</v>
       </c>
       <c r="Z21" s="1">
-        <v>-22.091617716360194</v>
+        <v>-8.6633794966118405</v>
       </c>
       <c r="AA21" s="1">
-        <v>-26.437297431767036</v>
+        <v>-10.367567620300798</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
@@ -71028,76 +71092,76 @@
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>21.521903966114511</v>
+        <v>8.4399623396527499</v>
       </c>
       <c r="E22" s="1">
-        <v>27.65556233567014</v>
+        <v>10.845318563007897</v>
       </c>
       <c r="F22" s="1">
-        <v>35.671869526954751</v>
+        <v>13.988968441943038</v>
       </c>
       <c r="G22" s="1">
-        <v>31.398150830769271</v>
+        <v>12.313000325791872</v>
       </c>
       <c r="H22" s="1">
-        <v>38.067706132363888</v>
+        <v>14.928512208770155</v>
       </c>
       <c r="I22" s="1">
-        <v>37.269971282454769</v>
+        <v>14.61567501272736</v>
       </c>
       <c r="J22" s="1">
-        <v>36.587986631783991</v>
+        <v>14.348230051679998</v>
       </c>
       <c r="K22" s="1">
-        <v>43.843232964918236</v>
+        <v>17.1934246921248</v>
       </c>
       <c r="L22" s="1">
-        <v>38.608334153708142</v>
+        <v>15.140523197532605</v>
       </c>
       <c r="M22" s="1">
-        <v>49.250399673598153</v>
+        <v>19.313882224940453</v>
       </c>
       <c r="N22" s="1">
-        <v>43.577941867932026</v>
+        <v>17.089388967816479</v>
       </c>
       <c r="O22" s="1">
-        <v>41.533403295182204</v>
+        <v>16.287609135365571</v>
       </c>
       <c r="P22" s="1">
-        <v>45.210169451446269</v>
+        <v>17.72947821625344</v>
       </c>
       <c r="Q22" s="1">
-        <v>42.883924833997895</v>
+        <v>16.817225425097217</v>
       </c>
       <c r="R22" s="1">
-        <v>37.775894154000724</v>
+        <v>14.814076138823815</v>
       </c>
       <c r="S22" s="1">
-        <v>32.417501373248847</v>
+        <v>12.712745636568174</v>
       </c>
       <c r="T22" s="1">
-        <v>35.790627354928979</v>
+        <v>14.035540139187836</v>
       </c>
       <c r="U22" s="1">
-        <v>29.223231015882128</v>
+        <v>11.46009059446358</v>
       </c>
       <c r="V22" s="1">
-        <v>27.370239517436303</v>
+        <v>10.733427261739727</v>
       </c>
       <c r="W22" s="1">
-        <v>28.337307370394882</v>
+        <v>11.112669557017602</v>
       </c>
       <c r="X22" s="1">
-        <v>27.212331635888262</v>
+        <v>10.671502602309122</v>
       </c>
       <c r="Y22" s="1">
-        <v>32.398183497204656</v>
+        <v>12.705169998903786</v>
       </c>
       <c r="Z22" s="1">
-        <v>22.397538729329273</v>
+        <v>8.783348521305598</v>
       </c>
       <c r="AA22" s="1">
-        <v>24.259774418772484</v>
+        <v>9.5136370269696027</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
@@ -71111,76 +71175,76 @@
         <v>2</v>
       </c>
       <c r="D23" s="1">
-        <v>13.756025745000002</v>
+        <v>5.3945199000000015</v>
       </c>
       <c r="E23" s="1">
-        <v>14.214895695000001</v>
+        <v>5.5744689000000003</v>
       </c>
       <c r="F23" s="1">
-        <v>11.637581472000003</v>
+        <v>4.5637574400000007</v>
       </c>
       <c r="G23" s="1">
-        <v>11.145689939999999</v>
+        <v>4.3708587999999997</v>
       </c>
       <c r="H23" s="1">
-        <v>9.3198885120000003</v>
+        <v>3.6548582400000003</v>
       </c>
       <c r="I23" s="1">
-        <v>7.8301866720000017</v>
+        <v>3.0706614400000007</v>
       </c>
       <c r="J23" s="1">
-        <v>9.6733942469999992</v>
+        <v>3.7934879399999999</v>
       </c>
       <c r="K23" s="1">
-        <v>1.7138819280000004</v>
+        <v>0.67211056000000013</v>
       </c>
       <c r="L23" s="1">
-        <v>1.4624147999999999</v>
+        <v>0.57349600000000001</v>
       </c>
       <c r="M23" s="1">
-        <v>2.197256919</v>
+        <v>0.86166937999999993</v>
       </c>
       <c r="N23" s="1">
-        <v>1.3324602720000003</v>
+        <v>0.52253344000000013</v>
       </c>
       <c r="O23" s="1">
-        <v>1.665021072</v>
+        <v>0.65294943999999999</v>
       </c>
       <c r="P23" s="1">
-        <v>2.4996847260000008</v>
+        <v>0.98026852000000031</v>
       </c>
       <c r="Q23" s="1">
-        <v>4.8875352240000014</v>
+        <v>1.9166804800000004</v>
       </c>
       <c r="R23" s="1">
-        <v>5.2646932799999995</v>
+        <v>2.0645856</v>
       </c>
       <c r="S23" s="1">
-        <v>4.6843107299999991</v>
+        <v>1.8369845999999999</v>
       </c>
       <c r="T23" s="1">
-        <v>2.8489908150000001</v>
+        <v>1.1172513000000002</v>
       </c>
       <c r="U23" s="1">
-        <v>5.8597212959999991</v>
+        <v>2.2979299199999996</v>
       </c>
       <c r="V23" s="1">
-        <v>3.2402933640000007</v>
+        <v>1.2707032800000002</v>
       </c>
       <c r="W23" s="1">
-        <v>2.3014806209999996</v>
+        <v>0.90254141999999993</v>
       </c>
       <c r="X23" s="1">
-        <v>3.5302608000000011</v>
+        <v>1.3844160000000003</v>
       </c>
       <c r="Y23" s="1">
-        <v>2.247354219</v>
+        <v>0.88131538000000009</v>
       </c>
       <c r="Z23" s="1">
-        <v>10.456638885</v>
+        <v>4.1006427000000008</v>
       </c>
       <c r="AA23" s="1">
-        <v>12.245336333999999</v>
+        <v>4.8020926800000003</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
@@ -71194,76 +71258,76 @@
         <v>2</v>
       </c>
       <c r="D24" s="1">
-        <v>-27.39490383364021</v>
+        <v>-10.743099542604005</v>
       </c>
       <c r="E24" s="1">
-        <v>-33.02915001081697</v>
+        <v>-12.952607847379202</v>
       </c>
       <c r="F24" s="1">
-        <v>-26.634729607295036</v>
+        <v>-10.444992002860799</v>
       </c>
       <c r="G24" s="1">
-        <v>-33.810936156023033</v>
+        <v>-13.259190649420798</v>
       </c>
       <c r="H24" s="1">
-        <v>-44.106315565887193</v>
+        <v>-17.296594339563608</v>
       </c>
       <c r="I24" s="1">
-        <v>-40.239037971636932</v>
+        <v>-15.780014890838013</v>
       </c>
       <c r="J24" s="1">
-        <v>-38.406562954634971</v>
+        <v>-15.061397237111754</v>
       </c>
       <c r="K24" s="1">
-        <v>-43.98373563869167</v>
+        <v>-17.248523779879086</v>
       </c>
       <c r="L24" s="1">
-        <v>-47.721135690502472</v>
+        <v>-18.714170859020577</v>
       </c>
       <c r="M24" s="1">
-        <v>-57.394284702205361</v>
+        <v>-22.507562628315831</v>
       </c>
       <c r="N24" s="1">
-        <v>-60.905511312584132</v>
+        <v>-23.88451424022907</v>
       </c>
       <c r="O24" s="1">
-        <v>-59.713803979821051</v>
+        <v>-23.417178031302374</v>
       </c>
       <c r="P24" s="1">
-        <v>-52.330687030417351</v>
+        <v>-20.521838051144059</v>
       </c>
       <c r="Q24" s="1">
-        <v>-50.412287615432028</v>
+        <v>-19.769524555071385</v>
       </c>
       <c r="R24" s="1">
-        <v>-49.048227854962029</v>
+        <v>-19.234599158808638</v>
       </c>
       <c r="S24" s="1">
-        <v>-40.778376010444788</v>
+        <v>-15.991520004095996</v>
       </c>
       <c r="T24" s="1">
-        <v>-38.523477631977904</v>
+        <v>-15.107246130187413</v>
       </c>
       <c r="U24" s="1">
-        <v>-34.79492712420781</v>
+        <v>-13.645069460473652</v>
       </c>
       <c r="V24" s="1">
-        <v>-21.432927477676035</v>
+        <v>-8.405069599088641</v>
       </c>
       <c r="W24" s="1">
-        <v>-26.577956660838641</v>
+        <v>-10.422728102289664</v>
       </c>
       <c r="X24" s="1">
-        <v>-30.67595330678791</v>
+        <v>-12.029785610505062</v>
       </c>
       <c r="Y24" s="1">
-        <v>-25.397241681180038</v>
+        <v>-9.9597026200706029</v>
       </c>
       <c r="Z24" s="1">
-        <v>-22.533450070687401</v>
+        <v>-8.8366470865440778</v>
       </c>
       <c r="AA24" s="1">
-        <v>-26.172924457449366</v>
+        <v>-10.263891944097791</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
@@ -71277,76 +71341,76 @@
         <v>2</v>
       </c>
       <c r="D25" s="1">
-        <v>21.306684926453368</v>
+        <v>8.3555627162562232</v>
       </c>
       <c r="E25" s="1">
-        <v>27.65556233567014</v>
+        <v>10.845318563007897</v>
       </c>
       <c r="F25" s="1">
-        <v>33.888276050607004</v>
+        <v>13.289520019845886</v>
       </c>
       <c r="G25" s="1">
-        <v>32.026113847384664</v>
+        <v>12.55926033230771</v>
       </c>
       <c r="H25" s="1">
-        <v>38.829060255011171</v>
+        <v>15.227082452945558</v>
       </c>
       <c r="I25" s="1">
-        <v>38.388070420928415</v>
+        <v>15.054145263109181</v>
       </c>
       <c r="J25" s="1">
-        <v>36.953866498101831</v>
+        <v>14.491712352196798</v>
       </c>
       <c r="K25" s="1">
-        <v>43.843232964918236</v>
+        <v>17.1934246921248</v>
       </c>
       <c r="L25" s="1">
-        <v>36.67791744602274</v>
+        <v>14.383497037655975</v>
       </c>
       <c r="M25" s="1">
-        <v>51.220415660542081</v>
+        <v>20.086437513938073</v>
       </c>
       <c r="N25" s="1">
-        <v>44.885280123969984</v>
+        <v>17.602070636850975</v>
       </c>
       <c r="O25" s="1">
-        <v>41.94873732813403</v>
+        <v>16.450485226719227</v>
       </c>
       <c r="P25" s="1">
-        <v>45.210169451446269</v>
+        <v>17.72947821625344</v>
       </c>
       <c r="Q25" s="1">
-        <v>42.455085585657919</v>
+        <v>16.649053170846244</v>
       </c>
       <c r="R25" s="1">
-        <v>35.887099446300688</v>
+        <v>14.073372331882624</v>
       </c>
       <c r="S25" s="1">
-        <v>30.796626304586397</v>
+        <v>12.077108354739764</v>
       </c>
       <c r="T25" s="1">
-        <v>34.71690853428111</v>
+        <v>13.614473935012199</v>
       </c>
       <c r="U25" s="1">
-        <v>28.638766395564488</v>
+        <v>11.23088878257431</v>
       </c>
       <c r="V25" s="1">
-        <v>27.370239517436303</v>
+        <v>10.733427261739727</v>
       </c>
       <c r="W25" s="1">
-        <v>29.187426591506732</v>
+        <v>11.446049643728131</v>
       </c>
       <c r="X25" s="1">
-        <v>25.851715054093845</v>
+        <v>10.137927472193665</v>
       </c>
       <c r="Y25" s="1">
-        <v>34.018092672064881</v>
+        <v>13.340428498848976</v>
       </c>
       <c r="Z25" s="1">
-        <v>21.94958795474269</v>
+        <v>8.6076815508794855</v>
       </c>
       <c r="AA25" s="1">
-        <v>24.987567651335663</v>
+        <v>9.7990461377786904</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
@@ -71360,76 +71424,76 @@
         <v>3</v>
       </c>
       <c r="D26" s="1">
-        <v>14.168706517350005</v>
+        <v>5.556355497000002</v>
       </c>
       <c r="E26" s="1">
-        <v>14.35704465195</v>
+        <v>5.6302135890000002</v>
       </c>
       <c r="F26" s="1">
-        <v>11.521205657280003</v>
+        <v>4.518119865600001</v>
       </c>
       <c r="G26" s="1">
-        <v>11.702974436999998</v>
+        <v>4.5894017399999996</v>
       </c>
       <c r="H26" s="1">
-        <v>9.41308739712</v>
+        <v>3.6914068224000003</v>
       </c>
       <c r="I26" s="1">
-        <v>7.8301866720000017</v>
+        <v>3.0706614400000007</v>
       </c>
       <c r="J26" s="1">
-        <v>9.1897245346499989</v>
+        <v>3.6038135429999998</v>
       </c>
       <c r="K26" s="1">
-        <v>1.6281878316000002</v>
+        <v>0.63850503200000008</v>
       </c>
       <c r="L26" s="1">
-        <v>1.3892940600000001</v>
+        <v>0.54482120000000001</v>
       </c>
       <c r="M26" s="1">
-        <v>2.1313392114299998</v>
+        <v>0.83581929859999993</v>
       </c>
       <c r="N26" s="1">
-        <v>1.31913566928</v>
+        <v>0.51730810560000007</v>
       </c>
       <c r="O26" s="1">
-        <v>1.6983214934399999</v>
+        <v>0.6660084288</v>
       </c>
       <c r="P26" s="1">
-        <v>2.4496910314800009</v>
+        <v>0.96066314960000032</v>
       </c>
       <c r="Q26" s="1">
-        <v>5.1319119852000004</v>
+        <v>2.0125145040000003</v>
       </c>
       <c r="R26" s="1">
-        <v>5.527927944</v>
+        <v>2.1678148799999999</v>
       </c>
       <c r="S26" s="1">
-        <v>4.9185262664999989</v>
+        <v>1.9288338299999999</v>
       </c>
       <c r="T26" s="1">
-        <v>2.8774807231500001</v>
+        <v>1.1284238130000002</v>
       </c>
       <c r="U26" s="1">
-        <v>5.8597212959999991</v>
+        <v>2.2979299199999996</v>
       </c>
       <c r="V26" s="1">
-        <v>3.2402933640000007</v>
+        <v>1.2707032800000002</v>
       </c>
       <c r="W26" s="1">
-        <v>2.2094213961599998</v>
+        <v>0.86643976319999993</v>
       </c>
       <c r="X26" s="1">
-        <v>3.4243529760000007</v>
+        <v>1.3428835200000002</v>
       </c>
       <c r="Y26" s="1">
-        <v>2.2698277611900002</v>
+        <v>0.89012853380000012</v>
       </c>
       <c r="Z26" s="1">
-        <v>10.142939718450002</v>
+        <v>3.9776234190000008</v>
       </c>
       <c r="AA26" s="1">
-        <v>12.612696424019999</v>
+        <v>4.9461554604</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
@@ -71443,76 +71507,76 @@
         <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>-28.764649025322221</v>
+        <v>-11.280254519734205</v>
       </c>
       <c r="E27" s="1">
-        <v>-32.698858510708796</v>
+        <v>-12.823081768905411</v>
       </c>
       <c r="F27" s="1">
-        <v>-26.368382311222089</v>
+        <v>-10.340542082832192</v>
       </c>
       <c r="G27" s="1">
-        <v>-32.796608071342341</v>
+        <v>-12.861414929938173</v>
       </c>
       <c r="H27" s="1">
-        <v>-43.665252410228334</v>
+        <v>-17.123628396167973</v>
       </c>
       <c r="I27" s="1">
-        <v>-41.446209110786043</v>
+        <v>-16.253415337563155</v>
       </c>
       <c r="J27" s="1">
-        <v>-36.486234806903219</v>
+        <v>-14.308327375256164</v>
       </c>
       <c r="K27" s="1">
-        <v>-43.54389828230476</v>
+        <v>-17.076038542080298</v>
       </c>
       <c r="L27" s="1">
-        <v>-46.289501619787401</v>
+        <v>-18.152745733249962</v>
       </c>
       <c r="M27" s="1">
-        <v>-59.116113243271528</v>
+        <v>-23.182789507165307</v>
       </c>
       <c r="N27" s="1">
-        <v>-60.905511312584132</v>
+        <v>-23.88451424022907</v>
       </c>
       <c r="O27" s="1">
-        <v>-59.713803979821051</v>
+        <v>-23.417178031302374</v>
       </c>
       <c r="P27" s="1">
-        <v>-51.284073289809008</v>
+        <v>-20.111401290121179</v>
       </c>
       <c r="Q27" s="1">
-        <v>-50.412287615432028</v>
+        <v>-19.769524555071385</v>
       </c>
       <c r="R27" s="1">
-        <v>-50.029192412061263</v>
+        <v>-19.61929114198481</v>
       </c>
       <c r="S27" s="1">
-        <v>-41.593943530653682</v>
+        <v>-16.311350404177915</v>
       </c>
       <c r="T27" s="1">
-        <v>-39.679181960937235</v>
+        <v>-15.560463514093035</v>
       </c>
       <c r="U27" s="1">
-        <v>-34.79492712420781</v>
+        <v>-13.645069460473652</v>
       </c>
       <c r="V27" s="1">
-        <v>-21.861586027229556</v>
+        <v>-8.5731709910704144</v>
       </c>
       <c r="W27" s="1">
-        <v>-27.641074927272193</v>
+        <v>-10.839637226381251</v>
       </c>
       <c r="X27" s="1">
-        <v>-29.755674707584269</v>
+        <v>-11.66889204218991</v>
       </c>
       <c r="Y27" s="1">
-        <v>-25.651214097991836</v>
+        <v>-10.059299646271308</v>
       </c>
       <c r="Z27" s="1">
-        <v>-21.406777567153028</v>
+        <v>-8.394814732216874</v>
       </c>
       <c r="AA27" s="1">
-        <v>-26.696382946598355</v>
+        <v>-10.469169782979748</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
@@ -71526,76 +71590,76 @@
         <v>3</v>
       </c>
       <c r="D28" s="1">
-        <v>20.667484378659768</v>
+        <v>8.104895834768536</v>
       </c>
       <c r="E28" s="1">
-        <v>26.825895465600038</v>
+        <v>10.519959006117661</v>
       </c>
       <c r="F28" s="1">
-        <v>33.888276050607004</v>
+        <v>13.289520019845886</v>
       </c>
       <c r="G28" s="1">
-        <v>32.986897262806195</v>
+        <v>12.93603814227694</v>
       </c>
       <c r="H28" s="1">
-        <v>40.770513267761729</v>
+        <v>15.988436575592836</v>
       </c>
       <c r="I28" s="1">
-        <v>38.004189716719125</v>
+        <v>14.903603810478089</v>
       </c>
       <c r="J28" s="1">
-        <v>38.801559823006926</v>
+        <v>15.216297969806638</v>
       </c>
       <c r="K28" s="1">
-        <v>42.966368305619881</v>
+        <v>16.849556198282304</v>
       </c>
       <c r="L28" s="1">
-        <v>36.311138271562513</v>
+        <v>14.239662067279415</v>
       </c>
       <c r="M28" s="1">
-        <v>53.781436443569191</v>
+        <v>21.090759389634979</v>
       </c>
       <c r="N28" s="1">
-        <v>46.680691328928788</v>
+        <v>18.306153462325014</v>
       </c>
       <c r="O28" s="1">
-        <v>40.690275208290004</v>
+        <v>15.95697066991765</v>
       </c>
       <c r="P28" s="1">
-        <v>45.210169451446269</v>
+        <v>17.72947821625344</v>
       </c>
       <c r="Q28" s="1">
-        <v>44.153289009084233</v>
+        <v>17.315015297680091</v>
       </c>
       <c r="R28" s="1">
-        <v>35.887099446300688</v>
+        <v>14.073372331882624</v>
       </c>
       <c r="S28" s="1">
-        <v>30.180693778494664</v>
+        <v>11.835566187644968</v>
       </c>
       <c r="T28" s="1">
-        <v>33.675401278252679</v>
+        <v>13.206039716961834</v>
       </c>
       <c r="U28" s="1">
-        <v>30.070704715342714</v>
+        <v>11.792433221703025</v>
       </c>
       <c r="V28" s="1">
-        <v>27.370239517436303</v>
+        <v>10.733427261739727</v>
       </c>
       <c r="W28" s="1">
-        <v>28.895552325591662</v>
+        <v>11.331589147290849</v>
       </c>
       <c r="X28" s="1">
-        <v>26.885783656257598</v>
+        <v>10.543444571081411</v>
       </c>
       <c r="Y28" s="1">
-        <v>32.997549891902942</v>
+        <v>12.940215643883507</v>
       </c>
       <c r="Z28" s="1">
-        <v>22.608075593384967</v>
+        <v>8.8659119974058704</v>
       </c>
       <c r="AA28" s="1">
-        <v>24.237940621795588</v>
+        <v>9.5050747536453297</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -71609,76 +71673,76 @@
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>12.445928055000003</v>
+        <v>4.880756100000001</v>
       </c>
       <c r="E29" s="1">
-        <v>12.861096105000001</v>
+        <v>5.0435671000000006</v>
       </c>
       <c r="F29" s="1">
-        <v>11.516356665</v>
+        <v>4.5162183000000002</v>
       </c>
       <c r="G29" s="1">
-        <v>10.915881899999999</v>
+        <v>4.2807379999999995</v>
       </c>
       <c r="H29" s="1">
-        <v>8.9433273599999996</v>
+        <v>3.5071872000000002</v>
       </c>
       <c r="I29" s="1">
-        <v>7.5904870800000008</v>
+        <v>2.9766616000000004</v>
       </c>
       <c r="J29" s="1">
-        <v>9.2825500349999999</v>
+        <v>3.6402157000000002</v>
       </c>
       <c r="K29" s="1">
-        <v>1.6120671600000005</v>
+        <v>0.63218320000000017</v>
       </c>
       <c r="L29" s="1">
-        <v>1.4176469999999999</v>
+        <v>0.55593999999999999</v>
       </c>
       <c r="M29" s="1">
-        <v>2.0667268049999996</v>
+        <v>0.81048109999999984</v>
       </c>
       <c r="N29" s="1">
-        <v>1.2171512100000001</v>
+        <v>0.47731420000000008</v>
       </c>
       <c r="O29" s="1">
-        <v>1.5209327099999996</v>
+        <v>0.59644419999999987</v>
       </c>
       <c r="P29" s="1">
-        <v>2.4231637650000009</v>
+        <v>0.95026030000000028</v>
       </c>
       <c r="Q29" s="1">
-        <v>4.4645754450000004</v>
+        <v>1.7508139</v>
       </c>
       <c r="R29" s="1">
-        <v>4.7632939199999997</v>
+        <v>1.8679584</v>
       </c>
       <c r="S29" s="1">
-        <v>4.6843107299999991</v>
+        <v>1.8369845999999996</v>
       </c>
       <c r="T29" s="1">
-        <v>2.6277099749999997</v>
+        <v>1.0304745</v>
       </c>
       <c r="U29" s="1">
-        <v>5.3526300299999994</v>
+        <v>2.0990705999999997</v>
       </c>
       <c r="V29" s="1">
-        <v>3.1411007099999999</v>
+        <v>1.2318042</v>
       </c>
       <c r="W29" s="1">
-        <v>2.2084915049999996</v>
+        <v>0.86607509999999988</v>
       </c>
       <c r="X29" s="1">
-        <v>3.3537477600000005</v>
+        <v>1.3151952000000002</v>
       </c>
       <c r="Y29" s="1">
-        <v>2.0728024349999998</v>
+        <v>0.81286369999999997</v>
       </c>
       <c r="Z29" s="1">
-        <v>9.4607685150000016</v>
+        <v>3.7101053000000004</v>
       </c>
       <c r="AA29" s="1">
-        <v>11.404970115000001</v>
+        <v>4.4725372999999999</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -71692,76 +71756,76 @@
         <v>1</v>
       </c>
       <c r="D30" s="1">
-        <v>-28.477002535069005</v>
+        <v>-11.167451974536863</v>
       </c>
       <c r="E30" s="1">
-        <v>-32.698858510708796</v>
+        <v>-12.823081768905411</v>
       </c>
       <c r="F30" s="1">
-        <v>-25.577330841885427</v>
+        <v>-10.030325820347226</v>
       </c>
       <c r="G30" s="1">
-        <v>-34.108472394196035</v>
+        <v>-13.3758715271357</v>
       </c>
       <c r="H30" s="1">
-        <v>-45.411862506637476</v>
+        <v>-17.808573532014695</v>
       </c>
       <c r="I30" s="1">
-        <v>-43.104057475217481</v>
+        <v>-16.90355195106568</v>
       </c>
       <c r="J30" s="1">
-        <v>-38.310546547248379</v>
+        <v>-15.023743744018972</v>
       </c>
       <c r="K30" s="1">
-        <v>-45.285654213596956</v>
+        <v>-17.759080083763511</v>
       </c>
       <c r="L30" s="1">
-        <v>-47.678186668381024</v>
+        <v>-18.697328105247461</v>
       </c>
       <c r="M30" s="1">
-        <v>-60.298435508136961</v>
+        <v>-23.646445297308613</v>
       </c>
       <c r="N30" s="1">
-        <v>-61.514566425709965</v>
+        <v>-24.12335938263136</v>
       </c>
       <c r="O30" s="1">
-        <v>-60.310942019619254</v>
+        <v>-23.651349811615397</v>
       </c>
       <c r="P30" s="1">
-        <v>-49.232710358216643</v>
+        <v>-19.306945238516331</v>
       </c>
       <c r="Q30" s="1">
-        <v>-48.39579611081475</v>
+        <v>-18.978743572868531</v>
       </c>
       <c r="R30" s="1">
-        <v>-51.029776260302491</v>
+        <v>-20.011676964824506</v>
       </c>
       <c r="S30" s="1">
-        <v>-42.009882965960223</v>
+        <v>-16.474463908219697</v>
       </c>
       <c r="T30" s="1">
-        <v>-40.075973780546612</v>
+        <v>-15.716068149233966</v>
       </c>
       <c r="U30" s="1">
-        <v>-35.838774937934041</v>
+        <v>-14.054421544287861</v>
       </c>
       <c r="V30" s="1">
-        <v>-20.768506725868075</v>
+        <v>-8.144512441516893</v>
       </c>
       <c r="W30" s="1">
-        <v>-27.91748567654491</v>
+        <v>-10.948033598645063</v>
       </c>
       <c r="X30" s="1">
-        <v>-28.565447719280897</v>
+        <v>-11.202136360502314</v>
       </c>
       <c r="Y30" s="1">
-        <v>-26.420750520931588</v>
+        <v>-10.361078635659446</v>
       </c>
       <c r="Z30" s="1">
-        <v>-21.83491311849609</v>
+        <v>-8.5627110268612121</v>
       </c>
       <c r="AA30" s="1">
-        <v>-28.031202093928275</v>
+        <v>-10.992628272128735</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
@@ -71775,76 +71839,76 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>21.494183753806155</v>
+        <v>8.4290916681592769</v>
       </c>
       <c r="E31" s="1">
-        <v>27.094154420256036</v>
+        <v>10.625158596178837</v>
       </c>
       <c r="F31" s="1">
-        <v>35.243807092631286</v>
+        <v>13.821100820639721</v>
       </c>
       <c r="G31" s="1">
-        <v>33.646635208062321</v>
+        <v>13.194758905122479</v>
       </c>
       <c r="H31" s="1">
-        <v>41.993628665794581</v>
+        <v>16.468089672860621</v>
       </c>
       <c r="I31" s="1">
-        <v>37.244105922384747</v>
+        <v>14.605531734268528</v>
       </c>
       <c r="J31" s="1">
-        <v>36.861481831856572</v>
+        <v>14.455483071316305</v>
       </c>
       <c r="K31" s="1">
-        <v>42.966368305619881</v>
+        <v>16.849556198282304</v>
       </c>
       <c r="L31" s="1">
-        <v>37.037361036993758</v>
+        <v>14.524455308625004</v>
       </c>
       <c r="M31" s="1">
-        <v>56.470508265747647</v>
+        <v>22.145297359116725</v>
       </c>
       <c r="N31" s="1">
-        <v>45.747077502350216</v>
+        <v>17.940030393078516</v>
       </c>
       <c r="O31" s="1">
-        <v>40.690275208290004</v>
+        <v>15.95697066991765</v>
       </c>
       <c r="P31" s="1">
-        <v>47.018576229504113</v>
+        <v>18.438657344903575</v>
       </c>
       <c r="Q31" s="1">
-        <v>41.945624558630016</v>
+        <v>16.449264532796086</v>
       </c>
       <c r="R31" s="1">
-        <v>35.887099446300688</v>
+        <v>14.073372331882624</v>
       </c>
       <c r="S31" s="1">
-        <v>31.6897284674194</v>
+        <v>12.427344497027216</v>
       </c>
       <c r="T31" s="1">
-        <v>33.338647265470151</v>
+        <v>13.073979319792215</v>
       </c>
       <c r="U31" s="1">
-        <v>29.46929062103586</v>
+        <v>11.556584557268964</v>
       </c>
       <c r="V31" s="1">
-        <v>27.917644307785036</v>
+        <v>10.948095806974523</v>
       </c>
       <c r="W31" s="1">
-        <v>29.76241889535941</v>
+        <v>11.671536821709573</v>
       </c>
       <c r="X31" s="1">
-        <v>27.42349932938275</v>
+        <v>10.75431346250304</v>
       </c>
       <c r="Y31" s="1">
-        <v>32.007623395145849</v>
+        <v>12.552009174567001</v>
       </c>
       <c r="Z31" s="1">
-        <v>22.834156349318821</v>
+        <v>8.9545711173799294</v>
       </c>
       <c r="AA31" s="1">
-        <v>24.480320028013544</v>
+        <v>9.6001255011817825</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
@@ -71858,76 +71922,76 @@
         <v>2</v>
       </c>
       <c r="D32" s="1">
-        <v>12.321468774450002</v>
+        <v>4.8319485390000008</v>
       </c>
       <c r="E32" s="1">
-        <v>13.504150910250003</v>
+        <v>5.2957454550000014</v>
       </c>
       <c r="F32" s="1">
-        <v>11.516356665</v>
+        <v>4.5162183000000002</v>
       </c>
       <c r="G32" s="1">
-        <v>10.370087804999999</v>
+        <v>4.0667010999999995</v>
       </c>
       <c r="H32" s="1">
-        <v>8.8538940864000004</v>
+        <v>3.4721153280000006</v>
       </c>
       <c r="I32" s="1">
-        <v>7.2109627260000018</v>
+        <v>2.8278285200000006</v>
       </c>
       <c r="J32" s="1">
-        <v>8.9112480335999997</v>
+        <v>3.494607072</v>
       </c>
       <c r="K32" s="1">
-        <v>1.6604291748000004</v>
+        <v>0.65114869600000025</v>
       </c>
       <c r="L32" s="1">
-        <v>1.4176469999999999</v>
+        <v>0.55593999999999999</v>
       </c>
       <c r="M32" s="1">
-        <v>2.0253922688999997</v>
+        <v>0.79427147799999986</v>
       </c>
       <c r="N32" s="1">
-        <v>1.2049796979000003</v>
+        <v>0.47254105800000007</v>
       </c>
       <c r="O32" s="1">
-        <v>1.5361420370999996</v>
+        <v>0.60240864199999988</v>
       </c>
       <c r="P32" s="1">
-        <v>2.3989321273500002</v>
+        <v>0.94075769700000023</v>
       </c>
       <c r="Q32" s="1">
-        <v>4.4199296905499992</v>
+        <v>1.733305761</v>
       </c>
       <c r="R32" s="1">
-        <v>4.8109268591999994</v>
+        <v>1.8866379839999998</v>
       </c>
       <c r="S32" s="1">
-        <v>4.4969383007999992</v>
+        <v>1.7635052159999998</v>
       </c>
       <c r="T32" s="1">
-        <v>2.6277099749999997</v>
+        <v>1.0304745</v>
       </c>
       <c r="U32" s="1">
-        <v>5.6202615314999989</v>
+        <v>2.2040241299999996</v>
       </c>
       <c r="V32" s="1">
-        <v>3.0154566816000004</v>
+        <v>1.1825320320000001</v>
       </c>
       <c r="W32" s="1">
-        <v>2.2526613350999996</v>
+        <v>0.88339660199999981</v>
       </c>
       <c r="X32" s="1">
-        <v>3.2195978496</v>
+        <v>1.2625873920000001</v>
       </c>
       <c r="Y32" s="1">
-        <v>1.9898903376000001</v>
+        <v>0.78034915199999999</v>
       </c>
       <c r="Z32" s="1">
-        <v>9.366160829850001</v>
+        <v>3.6730042470000006</v>
       </c>
       <c r="AA32" s="1">
-        <v>11.404970115000001</v>
+        <v>4.4725372999999999</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
@@ -71941,76 +72005,76 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>-27.907462484367617</v>
+        <v>-10.944102935046125</v>
       </c>
       <c r="E33" s="1">
-        <v>-32.044881340494626</v>
+        <v>-12.566620133527303</v>
       </c>
       <c r="F33" s="1">
-        <v>-25.065784225047718</v>
+        <v>-9.8297193039402817</v>
       </c>
       <c r="G33" s="1">
-        <v>-33.085218222370152</v>
+        <v>-12.974595381321627</v>
       </c>
       <c r="H33" s="1">
-        <v>-47.682455631969347</v>
+        <v>-18.699002208615429</v>
       </c>
       <c r="I33" s="1">
-        <v>-41.810935750960965</v>
+        <v>-16.39644539253371</v>
       </c>
       <c r="J33" s="1">
-        <v>-39.076757478193343</v>
+        <v>-15.324218618899351</v>
       </c>
       <c r="K33" s="1">
-        <v>-44.832797671460987</v>
+        <v>-17.581489282925876</v>
       </c>
       <c r="L33" s="1">
-        <v>-46.247841068329592</v>
+        <v>-18.136408262090036</v>
       </c>
       <c r="M33" s="1">
-        <v>-58.48948244289285</v>
+        <v>-22.937051938389356</v>
       </c>
       <c r="N33" s="1">
-        <v>-58.438838104424462</v>
+        <v>-22.91719141349979</v>
       </c>
       <c r="O33" s="1">
-        <v>-63.326489120600229</v>
+        <v>-24.83391730219617</v>
       </c>
       <c r="P33" s="1">
-        <v>-50.709691668963146</v>
+        <v>-19.886153595671821</v>
       </c>
       <c r="Q33" s="1">
-        <v>-49.363712033031042</v>
+        <v>-19.358318444325899</v>
       </c>
       <c r="R33" s="1">
-        <v>-53.0709673107146</v>
+        <v>-20.81214404341749</v>
       </c>
       <c r="S33" s="1">
-        <v>-43.690278284598634</v>
+        <v>-17.133442464548484</v>
       </c>
       <c r="T33" s="1">
-        <v>-39.675214042741146</v>
+        <v>-15.558907467741626</v>
       </c>
       <c r="U33" s="1">
-        <v>-35.480387188554708</v>
+        <v>-13.913877328844983</v>
       </c>
       <c r="V33" s="1">
-        <v>-20.976191793126755</v>
+        <v>-8.2259575659320614</v>
       </c>
       <c r="W33" s="1">
-        <v>-27.91748567654491</v>
+        <v>-10.948033598645063</v>
       </c>
       <c r="X33" s="1">
-        <v>-29.136756673666518</v>
+        <v>-11.426179087712359</v>
       </c>
       <c r="Y33" s="1">
-        <v>-27.741788046978165</v>
+        <v>-10.879132567442419</v>
       </c>
       <c r="Z33" s="1">
-        <v>-22.926658774420897</v>
+        <v>-8.9908465782042732</v>
       </c>
       <c r="AA33" s="1">
-        <v>-26.909954010171145</v>
+        <v>-10.552923141243587</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
@@ -72024,76 +72088,76 @@
         <v>2</v>
       </c>
       <c r="D34" s="1">
-        <v>20.419474566115849</v>
+        <v>8.0076370847513143</v>
       </c>
       <c r="E34" s="1">
-        <v>27.906979052863715</v>
+        <v>10.943913354064202</v>
       </c>
       <c r="F34" s="1">
-        <v>33.48161673799973</v>
+        <v>13.130045779607736</v>
       </c>
       <c r="G34" s="1">
-        <v>32.300769799739832</v>
+        <v>12.666968548917581</v>
       </c>
       <c r="H34" s="1">
-        <v>39.893947232504857</v>
+        <v>15.644685189217592</v>
       </c>
       <c r="I34" s="1">
-        <v>38.361429100056291</v>
+        <v>15.043697686296584</v>
       </c>
       <c r="J34" s="1">
-        <v>35.387022558582309</v>
+        <v>13.877263748463651</v>
       </c>
       <c r="K34" s="1">
-        <v>40.818049890338884</v>
+        <v>16.007078388368189</v>
       </c>
       <c r="L34" s="1">
-        <v>38.518855478473512</v>
+        <v>15.105433520970005</v>
       </c>
       <c r="M34" s="1">
-        <v>53.646982852460262</v>
+        <v>21.038032491160887</v>
       </c>
       <c r="N34" s="1">
-        <v>43.459723627232698</v>
+        <v>17.043028873424589</v>
       </c>
       <c r="O34" s="1">
-        <v>42.724788968704509</v>
+        <v>16.754819203413533</v>
       </c>
       <c r="P34" s="1">
-        <v>47.958947754094197</v>
+        <v>18.807430491801647</v>
       </c>
       <c r="Q34" s="1">
-        <v>42.784537049802616</v>
+        <v>16.778249823452008</v>
       </c>
       <c r="R34" s="1">
-        <v>36.604841435226703</v>
+        <v>14.354839778520278</v>
       </c>
       <c r="S34" s="1">
-        <v>31.6897284674194</v>
+        <v>12.427344497027216</v>
       </c>
       <c r="T34" s="1">
-        <v>33.672033738124853</v>
+        <v>13.204719112990137</v>
       </c>
       <c r="U34" s="1">
-        <v>28.585211902404787</v>
+        <v>11.209887020550896</v>
       </c>
       <c r="V34" s="1">
-        <v>28.755173637018583</v>
+        <v>11.276538681183759</v>
       </c>
       <c r="W34" s="1">
-        <v>30.3576672732666</v>
+        <v>11.904967558143765</v>
       </c>
       <c r="X34" s="1">
-        <v>26.052324362913616</v>
+        <v>10.216597789377888</v>
       </c>
       <c r="Y34" s="1">
-        <v>31.687547161194388</v>
+        <v>12.42648908282133</v>
       </c>
       <c r="Z34" s="1">
-        <v>21.692448531852879</v>
+        <v>8.5068425615109327</v>
       </c>
       <c r="AA34" s="1">
-        <v>25.214729628853952</v>
+        <v>9.888129266217236</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
@@ -72107,76 +72171,76 @@
         <v>3</v>
       </c>
       <c r="D35" s="1">
-        <v>12.321468774450002</v>
+        <v>4.8319485390000008</v>
       </c>
       <c r="E35" s="1">
-        <v>14.044316946660004</v>
+        <v>5.5075752732000014</v>
       </c>
       <c r="F35" s="1">
-        <v>11.516356665</v>
+        <v>4.5162183000000002</v>
       </c>
       <c r="G35" s="1">
-        <v>10.162686048899998</v>
+        <v>3.9853670779999995</v>
       </c>
       <c r="H35" s="1">
-        <v>8.4111993820800013</v>
+        <v>3.2985095616000009</v>
       </c>
       <c r="I35" s="1">
-        <v>7.0667434714800006</v>
+        <v>2.7712719496000005</v>
       </c>
       <c r="J35" s="1">
-        <v>8.4656856319200013</v>
+        <v>3.3198767184000002</v>
       </c>
       <c r="K35" s="1">
-        <v>1.6272205913040008</v>
+        <v>0.63812572208000029</v>
       </c>
       <c r="L35" s="1">
-        <v>1.4176469999999999</v>
+        <v>0.55593999999999999</v>
       </c>
       <c r="M35" s="1">
-        <v>2.0456461915889994</v>
+        <v>0.80221419277999984</v>
       </c>
       <c r="N35" s="1">
-        <v>1.2652286827950001</v>
+        <v>0.49616811090000007</v>
       </c>
       <c r="O35" s="1">
-        <v>1.5207806167289999</v>
+        <v>0.59638455557999992</v>
       </c>
       <c r="P35" s="1">
-        <v>2.5188787337175005</v>
+        <v>0.98779558185000027</v>
       </c>
       <c r="Q35" s="1">
-        <v>4.5083282843609993</v>
+        <v>1.7679718762199998</v>
       </c>
       <c r="R35" s="1">
-        <v>4.9071453963839993</v>
+        <v>1.9243707436799997</v>
       </c>
       <c r="S35" s="1">
-        <v>4.3620301517759996</v>
+        <v>1.7106000595199999</v>
       </c>
       <c r="T35" s="1">
-        <v>2.7065412742499997</v>
+        <v>1.061388735</v>
       </c>
       <c r="U35" s="1">
-        <v>5.4516536855549989</v>
+        <v>2.1379034060999995</v>
       </c>
       <c r="V35" s="1">
-        <v>3.1360749488640001</v>
+        <v>1.2298333132800001</v>
       </c>
       <c r="W35" s="1">
-        <v>2.1850814950469997</v>
+        <v>0.85689470393999978</v>
       </c>
       <c r="X35" s="1">
-        <v>3.0586179571200005</v>
+        <v>1.1994580224000002</v>
       </c>
       <c r="Y35" s="1">
-        <v>1.9699914342240001</v>
+        <v>0.77254566048000006</v>
       </c>
       <c r="Z35" s="1">
-        <v>9.5534840464470001</v>
+        <v>3.7464643319400004</v>
       </c>
       <c r="AA35" s="1">
-        <v>11.290920413850001</v>
+        <v>4.4278119270000005</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
@@ -72190,76 +72254,76 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>-29.302835608586001</v>
+        <v>-11.491308081798431</v>
       </c>
       <c r="E36" s="1">
-        <v>-33.647125407519354</v>
+        <v>-13.194951140203669</v>
       </c>
       <c r="F36" s="1">
-        <v>-25.817757751799149</v>
+        <v>-10.124610883058489</v>
       </c>
       <c r="G36" s="1">
-        <v>-33.746922586817554</v>
+        <v>-13.234087288948061</v>
       </c>
       <c r="H36" s="1">
-        <v>-48.63610474460873</v>
+        <v>-19.072982252787739</v>
       </c>
       <c r="I36" s="1">
-        <v>-43.901482538509015</v>
+        <v>-17.216267662160398</v>
       </c>
       <c r="J36" s="1">
-        <v>-37.904454753847546</v>
+        <v>-14.86449206033237</v>
       </c>
       <c r="K36" s="1">
-        <v>-45.729453624890205</v>
+        <v>-17.933119068584393</v>
       </c>
       <c r="L36" s="1">
-        <v>-45.785362657646296</v>
+        <v>-17.955044179469137</v>
       </c>
       <c r="M36" s="1">
-        <v>-56.73479796960607</v>
+        <v>-22.248940380237677</v>
       </c>
       <c r="N36" s="1">
-        <v>-55.516896199203245</v>
+        <v>-21.771331842824804</v>
       </c>
       <c r="O36" s="1">
-        <v>-62.059959338188222</v>
+        <v>-24.337238956152245</v>
       </c>
       <c r="P36" s="1">
-        <v>-48.174207085514986</v>
+        <v>-18.891845915888229</v>
       </c>
       <c r="Q36" s="1">
-        <v>-48.87007491270073</v>
+        <v>-19.16473525988264</v>
       </c>
       <c r="R36" s="1">
-        <v>-55.724515676250327</v>
+        <v>-21.852751245588365</v>
       </c>
       <c r="S36" s="1">
-        <v>-45.000986633136598</v>
+        <v>-17.64744573848494</v>
       </c>
       <c r="T36" s="1">
-        <v>-37.691453340604092</v>
+        <v>-14.780962094354544</v>
       </c>
       <c r="U36" s="1">
-        <v>-37.254406547982434</v>
+        <v>-14.609571195287231</v>
       </c>
       <c r="V36" s="1">
-        <v>-21.185953711058023</v>
+        <v>-8.3082171415913812</v>
       </c>
       <c r="W36" s="1">
-        <v>-28.475835390075805</v>
+        <v>-11.166994270617963</v>
       </c>
       <c r="X36" s="1">
-        <v>-28.262653973456516</v>
+        <v>-11.083393715080987</v>
       </c>
       <c r="Y36" s="1">
-        <v>-26.63211652509904</v>
+        <v>-10.443967264744721</v>
       </c>
       <c r="Z36" s="1">
-        <v>-23.843725125397732</v>
+        <v>-9.3504804413324436</v>
       </c>
       <c r="AA36" s="1">
-        <v>-26.371754929967718</v>
+        <v>-10.341864678418714</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
@@ -72273,76 +72337,76 @@
         <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>20.419474566115849</v>
+        <v>8.0076370847513143</v>
       </c>
       <c r="E37" s="1">
-        <v>27.348839471806439</v>
+        <v>10.725035086982919</v>
       </c>
       <c r="F37" s="1">
-        <v>33.48161673799973</v>
+        <v>13.130045779607736</v>
       </c>
       <c r="G37" s="1">
-        <v>30.685731309752839</v>
+        <v>12.033620121471701</v>
       </c>
       <c r="H37" s="1">
-        <v>41.090765649480005</v>
+        <v>16.114025744894121</v>
       </c>
       <c r="I37" s="1">
-        <v>40.279500555059101</v>
+        <v>15.795882570611413</v>
       </c>
       <c r="J37" s="1">
-        <v>36.802503460925607</v>
+        <v>14.432354298402197</v>
       </c>
       <c r="K37" s="1">
-        <v>41.634410888145652</v>
+        <v>16.327219956135551</v>
       </c>
       <c r="L37" s="1">
-        <v>38.518855478473512</v>
+        <v>15.105433520970005</v>
       </c>
       <c r="M37" s="1">
-        <v>54.719922509509466</v>
+        <v>21.458793140984103</v>
       </c>
       <c r="N37" s="1">
-        <v>45.19811257232201</v>
+        <v>17.724750028361573</v>
       </c>
       <c r="O37" s="1">
-        <v>44.006532637765638</v>
+        <v>17.257463779515938</v>
       </c>
       <c r="P37" s="1">
-        <v>45.561000366389493</v>
+        <v>17.867058967211566</v>
       </c>
       <c r="Q37" s="1">
-        <v>40.64531019731249</v>
+        <v>15.939337332279408</v>
       </c>
       <c r="R37" s="1">
-        <v>37.336938263931238</v>
+        <v>14.641936574090682</v>
       </c>
       <c r="S37" s="1">
-        <v>31.055933898071011</v>
+        <v>12.178797607086672</v>
       </c>
       <c r="T37" s="1">
-        <v>34.345474412887349</v>
+        <v>13.46881349524994</v>
       </c>
       <c r="U37" s="1">
-        <v>27.727655545332645</v>
+        <v>10.873590409934371</v>
       </c>
       <c r="V37" s="1">
-        <v>29.905380582499323</v>
+        <v>11.727600228431108</v>
       </c>
       <c r="W37" s="1">
-        <v>29.750513927801265</v>
+        <v>11.666868206980888</v>
       </c>
       <c r="X37" s="1">
-        <v>25.791801119284475</v>
+        <v>10.114431811484108</v>
       </c>
       <c r="Y37" s="1">
-        <v>31.687547161194388</v>
+        <v>12.42648908282133</v>
       </c>
       <c r="Z37" s="1">
-        <v>20.824750590578763</v>
+        <v>8.1665688590504946</v>
       </c>
       <c r="AA37" s="1">
-        <v>25.214729628853952</v>
+        <v>9.888129266217236</v>
       </c>
     </row>
   </sheetData>

--- a/data/OP1/case33_1/case33_1_operational_data.xlsx
+++ b/data/OP1/case33_1/case33_1_operational_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/CS7/case33_1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP1/case33_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C614731-E163-634C-8926-8FFCC4133114}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6554AEFC-BFD6-6141-8CFA-ED4DBDBB377D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="52180" yWindow="1260" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10540" yWindow="3620" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -473,12 +473,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>E2*3.5</f>
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1">
-        <f>F2*3.5</f>
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="D2" s="2">
         <v>2.6917900403768499E-2</v>
@@ -495,12 +493,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <f t="shared" ref="B3:B33" si="0">E3*3.5</f>
-        <v>12.599999999999998</v>
+        <v>5.3999999999999995</v>
       </c>
       <c r="C3" s="1">
-        <f t="shared" ref="C3:C33" si="1">F3*3.5</f>
-        <v>5.6000000000000005</v>
+        <v>1.6</v>
       </c>
       <c r="D3" s="2">
         <v>2.4226110363391645E-2</v>
@@ -517,12 +513,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <f t="shared" si="0"/>
-        <v>16.8</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" si="1"/>
-        <v>11.200000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="D4" s="2">
         <v>3.2301480484522194E-2</v>
@@ -539,12 +533,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C5" s="1">
-        <f t="shared" si="1"/>
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="D5" s="2">
         <v>1.6150740242261097E-2</v>
@@ -561,12 +553,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C6" s="1">
-        <f t="shared" si="1"/>
-        <v>2.8000000000000003</v>
+        <v>0.8</v>
       </c>
       <c r="D6" s="2">
         <v>1.6150740242261097E-2</v>
@@ -583,12 +573,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1">
-        <f t="shared" si="0"/>
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2">
         <v>5.3835800807536999E-2</v>
@@ -605,12 +593,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1">
-        <f t="shared" si="0"/>
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D8" s="2">
         <v>5.3835800807536999E-2</v>
@@ -627,12 +613,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="1">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C9" s="1">
-        <f t="shared" si="1"/>
-        <v>2.8000000000000003</v>
+        <v>0.8</v>
       </c>
       <c r="D9" s="2">
         <v>1.6150740242261097E-2</v>
@@ -649,12 +633,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="1">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C10" s="1">
-        <f t="shared" si="1"/>
-        <v>2.8000000000000003</v>
+        <v>0.8</v>
       </c>
       <c r="D10" s="2">
         <v>1.6150740242261097E-2</v>
@@ -671,12 +653,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1">
-        <f t="shared" si="0"/>
-        <v>6.2999999999999989</v>
+        <v>2.6999999999999997</v>
       </c>
       <c r="C11" s="1">
-        <f t="shared" si="1"/>
-        <v>4.2</v>
+        <v>1.2</v>
       </c>
       <c r="D11" s="2">
         <v>1.2113055181695823E-2</v>
@@ -693,12 +673,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="1">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C12" s="1">
-        <f t="shared" si="1"/>
-        <v>4.9000000000000004</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D12" s="2">
         <v>1.6150740242261097E-2</v>
@@ -715,12 +693,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="1">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C13" s="1">
-        <f t="shared" si="1"/>
-        <v>4.9000000000000004</v>
+        <v>1.4000000000000001</v>
       </c>
       <c r="D13" s="2">
         <v>1.6150740242261097E-2</v>
@@ -737,12 +713,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <f t="shared" si="0"/>
-        <v>16.8</v>
+        <v>7.1999999999999993</v>
       </c>
       <c r="C14" s="1">
-        <f t="shared" si="1"/>
-        <v>11.200000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="D14" s="2">
         <v>3.2301480484522194E-2</v>
@@ -759,12 +733,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C15" s="1">
-        <f t="shared" si="1"/>
-        <v>1.4000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="D15" s="2">
         <v>1.6150740242261097E-2</v>
@@ -781,12 +753,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C16" s="1">
-        <f t="shared" si="1"/>
-        <v>2.8000000000000003</v>
+        <v>0.8</v>
       </c>
       <c r="D16" s="2">
         <v>1.6150740242261097E-2</v>
@@ -803,12 +773,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="1">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C17" s="1">
-        <f t="shared" si="1"/>
-        <v>2.8000000000000003</v>
+        <v>0.8</v>
       </c>
       <c r="D17" s="2">
         <v>1.6150740242261097E-2</v>
@@ -825,12 +793,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1">
-        <f t="shared" si="0"/>
-        <v>12.599999999999998</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C18" s="1">
-        <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
+        <v>1.6</v>
       </c>
       <c r="D18" s="2">
         <v>2.4226110363391645E-2</v>
@@ -847,12 +813,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="1">
-        <f t="shared" si="0"/>
-        <v>12.599999999999998</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C19" s="1">
-        <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
+        <v>1.6</v>
       </c>
       <c r="D19" s="2">
         <v>2.4226110363391645E-2</v>
@@ -869,12 +833,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1">
-        <f t="shared" si="0"/>
-        <v>12.599999999999998</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C20" s="1">
-        <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
+        <v>1.6</v>
       </c>
       <c r="D20" s="2">
         <v>2.4226110363391645E-2</v>
@@ -891,12 +853,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1">
-        <f t="shared" si="0"/>
-        <v>12.599999999999998</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C21" s="1">
-        <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
+        <v>1.6</v>
       </c>
       <c r="D21" s="2">
         <v>2.4226110363391645E-2</v>
@@ -913,12 +873,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="1">
-        <f t="shared" si="0"/>
-        <v>12.599999999999998</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C22" s="1">
-        <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
+        <v>1.6</v>
       </c>
       <c r="D22" s="2">
         <v>2.4226110363391645E-2</v>
@@ -935,12 +893,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="1">
-        <f t="shared" si="0"/>
-        <v>12.599999999999998</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="C23" s="1">
-        <f t="shared" si="1"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D23" s="2">
         <v>2.4226110363391645E-2</v>
@@ -957,12 +913,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="1">
-        <f t="shared" si="0"/>
-        <v>58.800000000000004</v>
+        <v>16.8</v>
       </c>
       <c r="C24" s="1">
-        <f t="shared" si="1"/>
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2">
         <v>0.11305518169582769</v>
@@ -979,12 +933,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1">
-        <f t="shared" si="0"/>
-        <v>58.800000000000004</v>
+        <v>16.8</v>
       </c>
       <c r="C25" s="1">
-        <f t="shared" si="1"/>
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2">
         <v>0.11305518169582769</v>
@@ -1001,12 +953,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="1">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="C26" s="1">
-        <f t="shared" si="1"/>
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="D26" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1023,12 +973,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="1">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="C27" s="1">
-        <f t="shared" si="1"/>
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="D27" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1045,12 +993,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="1">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="C28" s="1">
-        <f t="shared" si="1"/>
-        <v>2.8000000000000003</v>
+        <v>0.8</v>
       </c>
       <c r="D28" s="2">
         <v>1.6150740242261097E-2</v>
@@ -1067,12 +1013,10 @@
         <v>28</v>
       </c>
       <c r="B29" s="1">
-        <f t="shared" si="0"/>
-        <v>16.8</v>
+        <v>4.8</v>
       </c>
       <c r="C29" s="1">
-        <f t="shared" si="1"/>
-        <v>9.8000000000000007</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D29" s="2">
         <v>3.2301480484522194E-2</v>
@@ -1089,12 +1033,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="1">
-        <f t="shared" si="0"/>
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="C30" s="1">
-        <f t="shared" si="1"/>
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="D30" s="2">
         <v>5.3835800807536999E-2</v>
@@ -1111,12 +1053,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1">
-        <f t="shared" si="0"/>
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C31" s="1">
-        <f t="shared" si="1"/>
-        <v>9.8000000000000007</v>
+        <v>2.8000000000000003</v>
       </c>
       <c r="D31" s="2">
         <v>4.0376850605652742E-2</v>
@@ -1133,12 +1073,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="1">
-        <f t="shared" si="0"/>
-        <v>29.400000000000002</v>
+        <v>8.4</v>
       </c>
       <c r="C32" s="1">
-        <f t="shared" si="1"/>
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D32" s="2">
         <v>5.6527590847913846E-2</v>
@@ -1155,12 +1093,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="1">
-        <f t="shared" si="0"/>
-        <v>8.4</v>
+        <v>2.4</v>
       </c>
       <c r="C33" s="1">
-        <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
+        <v>1.6</v>
       </c>
       <c r="D33" s="2">
         <v>1.6150740242261097E-2</v>

--- a/data/OP1/case33_1/case33_1_operational_data.xlsx
+++ b/data/OP1/case33_1/case33_1_operational_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/micaelsimoes/PycharmProjects/shared-resources-planning/data/OP1/case33_1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6554AEFC-BFD6-6141-8CFA-ED4DBDBB377D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE3DF0D-3A27-2E40-AB39-167DC1D29ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10540" yWindow="3620" windowWidth="29400" windowHeight="19120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1120" yWindow="620" windowWidth="50080" windowHeight="28180" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Characterization" sheetId="2" r:id="rId1"/>
@@ -69368,76 +69368,76 @@
         <v>1</v>
       </c>
       <c r="D2" s="1">
-        <v>4.9164000000000012</v>
+        <v>14.749200000000004</v>
       </c>
       <c r="E2" s="1">
-        <v>5.0804000000000009</v>
+        <v>15.241200000000003</v>
       </c>
       <c r="F2" s="1">
-        <v>4.5491999999999999</v>
+        <v>13.647600000000001</v>
       </c>
       <c r="G2" s="1">
-        <v>4.3119999999999994</v>
+        <v>12.935999999999998</v>
       </c>
       <c r="H2" s="1">
-        <v>3.5328000000000004</v>
+        <v>10.598400000000002</v>
       </c>
       <c r="I2" s="1">
-        <v>2.9984000000000006</v>
+        <v>8.9952000000000023</v>
       </c>
       <c r="J2" s="1">
-        <v>3.6668000000000003</v>
+        <v>11.000400000000001</v>
       </c>
       <c r="K2" s="1">
-        <v>0.63680000000000003</v>
+        <v>1.9104000000000001</v>
       </c>
       <c r="L2" s="1">
-        <v>0.56000000000000005</v>
+        <v>1.6800000000000002</v>
       </c>
       <c r="M2" s="1">
-        <v>0.8163999999999999</v>
+        <v>2.4491999999999998</v>
       </c>
       <c r="N2" s="1">
-        <v>0.48080000000000006</v>
+        <v>1.4424000000000001</v>
       </c>
       <c r="O2" s="1">
-        <v>0.6008</v>
+        <v>1.8024</v>
       </c>
       <c r="P2" s="1">
-        <v>0.95720000000000027</v>
+        <v>2.8716000000000008</v>
       </c>
       <c r="Q2" s="1">
-        <v>1.7636000000000003</v>
+        <v>5.2908000000000008</v>
       </c>
       <c r="R2" s="1">
-        <v>1.8815999999999999</v>
+        <v>5.6448</v>
       </c>
       <c r="S2" s="1">
-        <v>1.8503999999999998</v>
+        <v>5.5511999999999997</v>
       </c>
       <c r="T2" s="1">
-        <v>1.038</v>
+        <v>3.1139999999999999</v>
       </c>
       <c r="U2" s="1">
-        <v>2.1143999999999998</v>
+        <v>6.3431999999999995</v>
       </c>
       <c r="V2" s="1">
-        <v>1.2408000000000001</v>
+        <v>3.7224000000000004</v>
       </c>
       <c r="W2" s="1">
-        <v>0.87239999999999984</v>
+        <v>2.6171999999999995</v>
       </c>
       <c r="X2" s="1">
-        <v>1.3248000000000002</v>
+        <v>3.9744000000000006</v>
       </c>
       <c r="Y2" s="1">
-        <v>0.81880000000000008</v>
+        <v>2.4564000000000004</v>
       </c>
       <c r="Z2" s="1">
-        <v>3.7372000000000005</v>
+        <v>11.211600000000001</v>
       </c>
       <c r="AA2" s="1">
-        <v>4.5052000000000003</v>
+        <v>13.515600000000001</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -69451,76 +69451,76 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>-11.100000000000001</v>
+        <v>-33.300000000000004</v>
       </c>
       <c r="E3" s="1">
-        <v>-11.8696</v>
+        <v>-35.608800000000002</v>
       </c>
       <c r="F3" s="1">
-        <v>-13.349600000000002</v>
+        <v>-40.048800000000007</v>
       </c>
       <c r="G3" s="1">
-        <v>-14.400400000000001</v>
+        <v>-43.2012</v>
       </c>
       <c r="H3" s="1">
-        <v>-15.392000000000001</v>
+        <v>-46.176000000000002</v>
       </c>
       <c r="I3" s="1">
-        <v>-16.798000000000002</v>
+        <v>-50.394000000000005</v>
       </c>
       <c r="J3" s="1">
-        <v>-16.028400000000001</v>
+        <v>-48.0852</v>
       </c>
       <c r="K3" s="1">
-        <v>-17.979759999999999</v>
+        <v>-53.939279999999997</v>
       </c>
       <c r="L3" s="1">
-        <v>-16.307359999999996</v>
+        <v>-48.922079999999987</v>
       </c>
       <c r="M3" s="1">
-        <v>-23.952839999999998</v>
+        <v>-71.858519999999999</v>
       </c>
       <c r="N3" s="1">
-        <v>-23.707360000000005</v>
+        <v>-71.122080000000011</v>
       </c>
       <c r="O3" s="1">
-        <v>-21.672160000000002</v>
+        <v>-65.016480000000001</v>
       </c>
       <c r="P3" s="1">
-        <v>-20.774560000000001</v>
+        <v>-62.323680000000003</v>
       </c>
       <c r="Q3" s="1">
-        <v>-20.057480000000002</v>
+        <v>-60.172440000000009</v>
       </c>
       <c r="R3" s="1">
-        <v>-18.905680000000004</v>
+        <v>-56.717040000000011</v>
       </c>
       <c r="S3" s="1">
-        <v>-17.204239999999999</v>
+        <v>-51.612719999999996</v>
       </c>
       <c r="T3" s="1">
-        <v>-16.086960000000001</v>
+        <v>-48.26088</v>
       </c>
       <c r="U3" s="1">
-        <v>-14.396240000000002</v>
+        <v>-43.188720000000004</v>
       </c>
       <c r="V3" s="1">
-        <v>-9.1377199999999998</v>
+        <v>-27.413159999999998</v>
       </c>
       <c r="W3" s="1">
-        <v>-10.226479999999999</v>
+        <v>-30.679439999999996</v>
       </c>
       <c r="X3" s="1">
-        <v>-10.809839999999999</v>
+        <v>-32.429519999999997</v>
       </c>
       <c r="Y3" s="1">
-        <v>-11.605399999999999</v>
+        <v>-34.816199999999995</v>
       </c>
       <c r="Z3" s="1">
-        <v>-9.2204000000000015</v>
+        <v>-27.661200000000004</v>
       </c>
       <c r="AA3" s="1">
-        <v>-9.797600000000001</v>
+        <v>-29.392800000000001</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -69534,76 +69534,76 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>10.69356</v>
+        <v>32.080680000000001</v>
       </c>
       <c r="E4" s="1">
-        <v>11.440319999999996</v>
+        <v>34.320959999999985</v>
       </c>
       <c r="F4" s="1">
-        <v>12.82724</v>
+        <v>38.481719999999996</v>
       </c>
       <c r="G4" s="1">
-        <v>13.802440000000002</v>
+        <v>41.407320000000006</v>
       </c>
       <c r="H4" s="1">
-        <v>14.691399999999998</v>
+        <v>44.07419999999999</v>
       </c>
       <c r="I4" s="1">
-        <v>16.042000000000002</v>
+        <v>48.126000000000005</v>
       </c>
       <c r="J4" s="1">
-        <v>15.293999999999999</v>
+        <v>45.881999999999998</v>
       </c>
       <c r="K4" s="1">
-        <v>17.259160000000001</v>
+        <v>51.777480000000004</v>
       </c>
       <c r="L4" s="1">
-        <v>15.809160000000002</v>
+        <v>47.427480000000003</v>
       </c>
       <c r="M4" s="1">
-        <v>18.039439999999999</v>
+        <v>54.118319999999997</v>
       </c>
       <c r="N4" s="1">
-        <v>18.181480000000001</v>
+        <v>54.544440000000002</v>
       </c>
       <c r="O4" s="1">
-        <v>17.019639999999999</v>
+        <v>51.058920000000001</v>
       </c>
       <c r="P4" s="1">
-        <v>16.446000000000002</v>
+        <v>49.338000000000008</v>
       </c>
       <c r="Q4" s="1">
-        <v>16.02328</v>
+        <v>48.069839999999999</v>
       </c>
       <c r="R4" s="1">
-        <v>15.016320000000004</v>
+        <v>45.048960000000008</v>
       </c>
       <c r="S4" s="1">
-        <v>13.671480000000003</v>
+        <v>41.014440000000008</v>
       </c>
       <c r="T4" s="1">
-        <v>12.736039999999997</v>
+        <v>38.208119999999994</v>
       </c>
       <c r="U4" s="1">
-        <v>11.38288</v>
+        <v>34.14864</v>
       </c>
       <c r="V4" s="1">
-        <v>8.9093599999999995</v>
+        <v>26.728079999999999</v>
       </c>
       <c r="W4" s="1">
-        <v>9.9721600000000006</v>
+        <v>29.91648</v>
       </c>
       <c r="X4" s="1">
-        <v>10.596560000000002</v>
+        <v>31.789680000000004</v>
       </c>
       <c r="Y4" s="1">
-        <v>11.414560000000002</v>
+        <v>34.243680000000005</v>
       </c>
       <c r="Z4" s="1">
-        <v>8.8819999999999997</v>
+        <v>26.646000000000001</v>
       </c>
       <c r="AA4" s="1">
-        <v>9.4448000000000025</v>
+        <v>28.334400000000009</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
@@ -69617,76 +69617,76 @@
         <v>2</v>
       </c>
       <c r="D5" s="1">
-        <v>4.8672360000000019</v>
+        <v>14.601708000000006</v>
       </c>
       <c r="E5" s="1">
-        <v>5.0804000000000009</v>
+        <v>15.241200000000003</v>
       </c>
       <c r="F5" s="1">
-        <v>4.7311680000000003</v>
+        <v>14.193504000000001</v>
       </c>
       <c r="G5" s="1">
-        <v>4.3982399999999995</v>
+        <v>13.194719999999998</v>
       </c>
       <c r="H5" s="1">
-        <v>3.4621440000000003</v>
+        <v>10.386432000000001</v>
       </c>
       <c r="I5" s="1">
-        <v>2.8784640000000006</v>
+        <v>8.6353920000000013</v>
       </c>
       <c r="J5" s="1">
-        <v>3.7034680000000004</v>
+        <v>11.110404000000001</v>
       </c>
       <c r="K5" s="1">
-        <v>0.62406400000000006</v>
+        <v>1.8721920000000001</v>
       </c>
       <c r="L5" s="1">
-        <v>0.58240000000000014</v>
+        <v>1.7472000000000003</v>
       </c>
       <c r="M5" s="1">
-        <v>0.85721999999999998</v>
+        <v>2.5716600000000001</v>
       </c>
       <c r="N5" s="1">
-        <v>0.4711840000000001</v>
+        <v>1.4135520000000004</v>
       </c>
       <c r="O5" s="1">
-        <v>0.60680800000000001</v>
+        <v>1.820424</v>
       </c>
       <c r="P5" s="1">
-        <v>0.95720000000000027</v>
+        <v>2.8716000000000008</v>
       </c>
       <c r="Q5" s="1">
-        <v>1.8517800000000002</v>
+        <v>5.5553400000000011</v>
       </c>
       <c r="R5" s="1">
-        <v>1.8815999999999999</v>
+        <v>5.6448</v>
       </c>
       <c r="S5" s="1">
-        <v>1.8874079999999998</v>
+        <v>5.6622239999999993</v>
       </c>
       <c r="T5" s="1">
-        <v>0.98609999999999998</v>
+        <v>2.9582999999999999</v>
       </c>
       <c r="U5" s="1">
-        <v>2.2201199999999996</v>
+        <v>6.6603599999999989</v>
       </c>
       <c r="V5" s="1">
-        <v>1.2532080000000001</v>
+        <v>3.7596240000000005</v>
       </c>
       <c r="W5" s="1">
-        <v>0.89857199999999982</v>
+        <v>2.6957159999999996</v>
       </c>
       <c r="X5" s="1">
-        <v>1.3380480000000003</v>
+        <v>4.0141440000000008</v>
       </c>
       <c r="Y5" s="1">
-        <v>0.77786</v>
+        <v>2.33358</v>
       </c>
       <c r="Z5" s="1">
-        <v>3.8119440000000004</v>
+        <v>11.435832000000001</v>
       </c>
       <c r="AA5" s="1">
-        <v>4.5052000000000003</v>
+        <v>13.515600000000001</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
@@ -69700,76 +69700,76 @@
         <v>2</v>
       </c>
       <c r="D6" s="1">
-        <v>-11.100000000000001</v>
+        <v>-33.300000000000004</v>
       </c>
       <c r="E6" s="1">
-        <v>-11.750904</v>
+        <v>-35.252712000000002</v>
       </c>
       <c r="F6" s="1">
-        <v>-13.349600000000002</v>
+        <v>-40.048800000000007</v>
       </c>
       <c r="G6" s="1">
-        <v>-13.68038</v>
+        <v>-41.041139999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>-14.930240000000001</v>
+        <v>-44.790720000000007</v>
       </c>
       <c r="I6" s="1">
-        <v>-16.126080000000002</v>
+        <v>-48.378240000000005</v>
       </c>
       <c r="J6" s="1">
-        <v>-16.188684000000002</v>
+        <v>-48.566052000000006</v>
       </c>
       <c r="K6" s="1">
-        <v>-17.979759999999999</v>
+        <v>-53.939279999999997</v>
       </c>
       <c r="L6" s="1">
-        <v>-16.307359999999996</v>
+        <v>-48.922079999999987</v>
       </c>
       <c r="M6" s="1">
-        <v>-23.713311599999997</v>
+        <v>-71.139934799999992</v>
       </c>
       <c r="N6" s="1">
-        <v>-24.181507200000006</v>
+        <v>-72.544521600000024</v>
       </c>
       <c r="O6" s="1">
-        <v>-21.238716800000002</v>
+        <v>-63.716150400000004</v>
       </c>
       <c r="P6" s="1">
-        <v>-21.605542400000001</v>
+        <v>-64.816627199999999</v>
       </c>
       <c r="Q6" s="1">
-        <v>-19.8569052</v>
+        <v>-59.5707156</v>
       </c>
       <c r="R6" s="1">
-        <v>-19.661907200000005</v>
+        <v>-58.985721600000019</v>
       </c>
       <c r="S6" s="1">
-        <v>-17.204239999999999</v>
+        <v>-51.612719999999996</v>
       </c>
       <c r="T6" s="1">
-        <v>-15.765220800000002</v>
+        <v>-47.295662400000005</v>
       </c>
       <c r="U6" s="1">
-        <v>-13.820390400000001</v>
+        <v>-41.461171200000003</v>
       </c>
       <c r="V6" s="1">
-        <v>-9.1377199999999998</v>
+        <v>-27.413159999999998</v>
       </c>
       <c r="W6" s="1">
-        <v>-10.124215199999998</v>
+        <v>-30.372645599999995</v>
       </c>
       <c r="X6" s="1">
-        <v>-10.593643199999999</v>
+        <v>-31.780929599999997</v>
       </c>
       <c r="Y6" s="1">
-        <v>-11.257237999999999</v>
+        <v>-33.771713999999996</v>
       </c>
       <c r="Z6" s="1">
-        <v>-9.5892160000000004</v>
+        <v>-28.767648000000001</v>
       </c>
       <c r="AA6" s="1">
-        <v>-9.4056960000000007</v>
+        <v>-28.217088000000004</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.2">
@@ -69783,76 +69783,76 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>10.158882</v>
+        <v>30.476646000000002</v>
       </c>
       <c r="E7" s="1">
-        <v>11.783529599999998</v>
+        <v>35.350588799999997</v>
       </c>
       <c r="F7" s="1">
-        <v>12.314150399999999</v>
+        <v>36.942451199999994</v>
       </c>
       <c r="G7" s="1">
-        <v>13.112318000000002</v>
+        <v>39.336954000000006</v>
       </c>
       <c r="H7" s="1">
-        <v>14.250657999999998</v>
+        <v>42.75197399999999</v>
       </c>
       <c r="I7" s="1">
-        <v>16.523260000000004</v>
+        <v>49.569780000000009</v>
       </c>
       <c r="J7" s="1">
-        <v>14.68224</v>
+        <v>44.046720000000001</v>
       </c>
       <c r="K7" s="1">
-        <v>16.568793600000003</v>
+        <v>49.706380800000005</v>
       </c>
       <c r="L7" s="1">
-        <v>15.967251600000003</v>
+        <v>47.901754800000006</v>
       </c>
       <c r="M7" s="1">
-        <v>17.4982568</v>
+        <v>52.4947704</v>
       </c>
       <c r="N7" s="1">
-        <v>18.181480000000001</v>
+        <v>54.544440000000002</v>
       </c>
       <c r="O7" s="1">
-        <v>17.360032799999999</v>
+        <v>52.080098399999997</v>
       </c>
       <c r="P7" s="1">
-        <v>15.788160000000003</v>
+        <v>47.364480000000007</v>
       </c>
       <c r="Q7" s="1">
-        <v>16.343745599999998</v>
+        <v>49.031236799999995</v>
       </c>
       <c r="R7" s="1">
-        <v>15.767136000000004</v>
+        <v>47.301408000000009</v>
       </c>
       <c r="S7" s="1">
-        <v>14.081624400000003</v>
+        <v>42.244873200000008</v>
       </c>
       <c r="T7" s="1">
-        <v>12.353958799999997</v>
+        <v>37.061876399999989</v>
       </c>
       <c r="U7" s="1">
-        <v>11.838195199999999</v>
+        <v>35.514585599999997</v>
       </c>
       <c r="V7" s="1">
-        <v>9.3548279999999995</v>
+        <v>28.064484</v>
       </c>
       <c r="W7" s="1">
-        <v>9.9721600000000006</v>
+        <v>29.91648</v>
       </c>
       <c r="X7" s="1">
-        <v>10.066732000000002</v>
+        <v>30.200196000000005</v>
       </c>
       <c r="Y7" s="1">
-        <v>11.985288000000002</v>
+        <v>35.955864000000005</v>
       </c>
       <c r="Z7" s="1">
-        <v>8.7931799999999996</v>
+        <v>26.379539999999999</v>
       </c>
       <c r="AA7" s="1">
-        <v>9.4448000000000025</v>
+        <v>28.334400000000009</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.2">
@@ -69866,76 +69866,76 @@
         <v>3</v>
       </c>
       <c r="D8" s="1">
-        <v>4.7698912800000013</v>
+        <v>14.309673840000004</v>
       </c>
       <c r="E8" s="1">
-        <v>5.1820080000000006</v>
+        <v>15.546024000000003</v>
       </c>
       <c r="F8" s="1">
-        <v>4.7784796800000002</v>
+        <v>14.335439040000001</v>
       </c>
       <c r="G8" s="1">
-        <v>4.2223103999999996</v>
+        <v>12.666931199999999</v>
       </c>
       <c r="H8" s="1">
-        <v>3.2890367999999999</v>
+        <v>9.8671103999999996</v>
       </c>
       <c r="I8" s="1">
-        <v>2.9072486400000006</v>
+        <v>8.7217459200000018</v>
       </c>
       <c r="J8" s="1">
-        <v>3.6664333200000003</v>
+        <v>10.999299960000002</v>
       </c>
       <c r="K8" s="1">
-        <v>0.64902656000000003</v>
+        <v>1.9470796800000001</v>
       </c>
       <c r="L8" s="1">
-        <v>0.58240000000000014</v>
+        <v>1.7472000000000003</v>
       </c>
       <c r="M8" s="1">
-        <v>0.81435900000000006</v>
+        <v>2.4430770000000002</v>
       </c>
       <c r="N8" s="1">
-        <v>0.47589584000000007</v>
+        <v>1.4276875200000001</v>
       </c>
       <c r="O8" s="1">
-        <v>0.60680800000000001</v>
+        <v>1.820424</v>
       </c>
       <c r="P8" s="1">
-        <v>0.94762800000000025</v>
+        <v>2.8428840000000006</v>
       </c>
       <c r="Q8" s="1">
-        <v>1.7591910000000002</v>
+        <v>5.2775730000000003</v>
       </c>
       <c r="R8" s="1">
-        <v>1.8251519999999999</v>
+        <v>5.4754559999999994</v>
       </c>
       <c r="S8" s="1">
-        <v>1.8307857599999997</v>
+        <v>5.4923572799999993</v>
       </c>
       <c r="T8" s="1">
-        <v>0.98609999999999998</v>
+        <v>2.9582999999999999</v>
       </c>
       <c r="U8" s="1">
-        <v>2.1535163999999996</v>
+        <v>6.4605491999999991</v>
       </c>
       <c r="V8" s="1">
-        <v>1.22814384</v>
+        <v>3.68443152</v>
       </c>
       <c r="W8" s="1">
-        <v>0.9435005999999998</v>
+        <v>2.8305017999999995</v>
       </c>
       <c r="X8" s="1">
-        <v>1.3380480000000003</v>
+        <v>4.0141440000000008</v>
       </c>
       <c r="Y8" s="1">
-        <v>0.80897439999999998</v>
+        <v>2.4269232000000001</v>
       </c>
       <c r="Z8" s="1">
-        <v>3.7357051200000004</v>
+        <v>11.207115360000001</v>
       </c>
       <c r="AA8" s="1">
-        <v>4.3249919999999999</v>
+        <v>12.974976</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.2">
@@ -69949,76 +69949,76 @@
         <v>3</v>
       </c>
       <c r="D9" s="1">
-        <v>-10.545000000000002</v>
+        <v>-31.635000000000005</v>
       </c>
       <c r="E9" s="1">
-        <v>-11.750904</v>
+        <v>-35.252712000000002</v>
       </c>
       <c r="F9" s="1">
-        <v>-12.682120000000003</v>
+        <v>-38.046360000000007</v>
       </c>
       <c r="G9" s="1">
-        <v>-13.68038</v>
+        <v>-41.041139999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>-15.527449600000002</v>
+        <v>-46.582348800000005</v>
       </c>
       <c r="I9" s="1">
-        <v>-15.803558400000002</v>
+        <v>-47.410675200000007</v>
       </c>
       <c r="J9" s="1">
-        <v>-16.674344520000002</v>
+        <v>-50.023033560000002</v>
       </c>
       <c r="K9" s="1">
-        <v>-17.620164799999998</v>
+        <v>-52.860494399999993</v>
       </c>
       <c r="L9" s="1">
-        <v>-17.122727999999995</v>
+        <v>-51.368183999999985</v>
       </c>
       <c r="M9" s="1">
-        <v>-23.950444715999996</v>
+        <v>-71.851334147999992</v>
       </c>
       <c r="N9" s="1">
-        <v>-23.456061984000009</v>
+        <v>-70.368185952000033</v>
       </c>
       <c r="O9" s="1">
-        <v>-21.875878304000004</v>
+        <v>-65.627634912000019</v>
       </c>
       <c r="P9" s="1">
-        <v>-21.389486976000004</v>
+        <v>-64.168460928000016</v>
       </c>
       <c r="Q9" s="1">
-        <v>-20.849750459999999</v>
+        <v>-62.549251380000001</v>
       </c>
       <c r="R9" s="1">
-        <v>-19.465288128000005</v>
+        <v>-58.395864384000014</v>
       </c>
       <c r="S9" s="1">
-        <v>-17.204239999999999</v>
+        <v>-51.612719999999996</v>
       </c>
       <c r="T9" s="1">
-        <v>-15.607568592000002</v>
+        <v>-46.822705776000006</v>
       </c>
       <c r="U9" s="1">
-        <v>-14.373206016000001</v>
+        <v>-43.119618048000007</v>
       </c>
       <c r="V9" s="1">
-        <v>-9.4118516000000003</v>
+        <v>-28.235554800000003</v>
       </c>
       <c r="W9" s="1">
-        <v>-10.022973047999997</v>
+        <v>-30.068919143999992</v>
       </c>
       <c r="X9" s="1">
-        <v>-10.593643199999999</v>
+        <v>-31.780929599999997</v>
       </c>
       <c r="Y9" s="1">
-        <v>-10.694376099999999</v>
+        <v>-32.083128299999998</v>
       </c>
       <c r="Z9" s="1">
-        <v>-9.4933238400000004</v>
+        <v>-28.479971519999999</v>
       </c>
       <c r="AA9" s="1">
-        <v>-9.8759808000000007</v>
+        <v>-29.627942400000002</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.2">
@@ -70032,76 +70032,76 @@
         <v>3</v>
       </c>
       <c r="D10" s="1">
-        <v>10.36205964</v>
+        <v>31.086178920000002</v>
       </c>
       <c r="E10" s="1">
-        <v>11.194353119999999</v>
+        <v>33.583059359999993</v>
       </c>
       <c r="F10" s="1">
-        <v>12.314150399999999</v>
+        <v>36.942451199999994</v>
       </c>
       <c r="G10" s="1">
-        <v>12.718948460000002</v>
+        <v>38.156845380000007</v>
       </c>
       <c r="H10" s="1">
-        <v>13.538125099999997</v>
+        <v>40.614375299999992</v>
       </c>
       <c r="I10" s="1">
-        <v>15.697097000000003</v>
+        <v>47.091291000000012</v>
       </c>
       <c r="J10" s="1">
-        <v>13.948127999999999</v>
+        <v>41.844383999999998</v>
       </c>
       <c r="K10" s="1">
-        <v>15.740353920000002</v>
+        <v>47.221061760000005</v>
       </c>
       <c r="L10" s="1">
-        <v>15.647906568000003</v>
+        <v>46.94371970400001</v>
       </c>
       <c r="M10" s="1">
-        <v>17.848221936000002</v>
+        <v>53.544665808000005</v>
       </c>
       <c r="N10" s="1">
-        <v>18.5451096</v>
+        <v>55.635328799999996</v>
       </c>
       <c r="O10" s="1">
-        <v>16.49203116</v>
+        <v>49.476093480000003</v>
       </c>
       <c r="P10" s="1">
-        <v>16.419686400000003</v>
+        <v>49.25905920000001</v>
       </c>
       <c r="Q10" s="1">
-        <v>16.507183055999999</v>
+        <v>49.521549167999993</v>
       </c>
       <c r="R10" s="1">
-        <v>16.082478720000005</v>
+        <v>48.247436160000014</v>
       </c>
       <c r="S10" s="1">
-        <v>13.518359424000003</v>
+        <v>40.55507827200001</v>
       </c>
       <c r="T10" s="1">
-        <v>12.848117151999997</v>
+        <v>38.544351455999987</v>
       </c>
       <c r="U10" s="1">
-        <v>11.364667391999999</v>
+        <v>34.094002175999996</v>
       </c>
       <c r="V10" s="1">
-        <v>9.822569399999999</v>
+        <v>29.467708199999997</v>
       </c>
       <c r="W10" s="1">
-        <v>10.071881600000001</v>
+        <v>30.215644800000003</v>
       </c>
       <c r="X10" s="1">
-        <v>10.469401280000001</v>
+        <v>31.408203840000006</v>
       </c>
       <c r="Y10" s="1">
-        <v>12.344846640000004</v>
+        <v>37.034539920000014</v>
       </c>
       <c r="Z10" s="1">
-        <v>8.8811117999999993</v>
+        <v>26.643335399999998</v>
       </c>
       <c r="AA10" s="1">
-        <v>9.9170400000000036</v>
+        <v>29.751120000000011</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.2">
@@ -70115,76 +70115,76 @@
         <v>1</v>
       </c>
       <c r="D11" s="1">
-        <v>4.6705800000000011</v>
+        <v>14.011740000000003</v>
       </c>
       <c r="E11" s="1">
-        <v>4.8263800000000003</v>
+        <v>14.479140000000001</v>
       </c>
       <c r="F11" s="1">
-        <v>4.3217400000000001</v>
+        <v>12.96522</v>
       </c>
       <c r="G11" s="1">
-        <v>4.0963999999999992</v>
+        <v>12.289199999999997</v>
       </c>
       <c r="H11" s="1">
-        <v>3.35616</v>
+        <v>10.068480000000001</v>
       </c>
       <c r="I11" s="1">
-        <v>2.8484800000000003</v>
+        <v>8.545440000000001</v>
       </c>
       <c r="J11" s="1">
-        <v>3.48346</v>
+        <v>10.450379999999999</v>
       </c>
       <c r="K11" s="1">
-        <v>0.60496000000000005</v>
+        <v>1.81488</v>
       </c>
       <c r="L11" s="1">
-        <v>0.53200000000000003</v>
+        <v>1.5960000000000001</v>
       </c>
       <c r="M11" s="1">
-        <v>0.77557999999999983</v>
+        <v>2.3267399999999996</v>
       </c>
       <c r="N11" s="1">
-        <v>0.45676000000000005</v>
+        <v>1.3702800000000002</v>
       </c>
       <c r="O11" s="1">
-        <v>0.57075999999999993</v>
+        <v>1.7122799999999998</v>
       </c>
       <c r="P11" s="1">
-        <v>0.90934000000000026</v>
+        <v>2.7280200000000008</v>
       </c>
       <c r="Q11" s="1">
-        <v>1.6754200000000001</v>
+        <v>5.0262600000000006</v>
       </c>
       <c r="R11" s="1">
-        <v>1.7875199999999998</v>
+        <v>5.3625599999999993</v>
       </c>
       <c r="S11" s="1">
-        <v>1.7578799999999997</v>
+        <v>5.2736399999999986</v>
       </c>
       <c r="T11" s="1">
-        <v>0.98609999999999998</v>
+        <v>2.9582999999999999</v>
       </c>
       <c r="U11" s="1">
-        <v>2.0086799999999996</v>
+        <v>6.0260399999999983</v>
       </c>
       <c r="V11" s="1">
-        <v>1.17876</v>
+        <v>3.5362800000000001</v>
       </c>
       <c r="W11" s="1">
-        <v>0.82877999999999985</v>
+        <v>2.4863399999999993</v>
       </c>
       <c r="X11" s="1">
-        <v>1.2585600000000001</v>
+        <v>3.7756800000000004</v>
       </c>
       <c r="Y11" s="1">
-        <v>0.77786</v>
+        <v>2.33358</v>
       </c>
       <c r="Z11" s="1">
-        <v>3.5503400000000003</v>
+        <v>10.651020000000001</v>
       </c>
       <c r="AA11" s="1">
-        <v>4.2799399999999999</v>
+        <v>12.83982</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.2">
@@ -70198,76 +70198,76 @@
         <v>1</v>
       </c>
       <c r="D12" s="1">
-        <v>-10.966800000000003</v>
+        <v>-32.900400000000005</v>
       </c>
       <c r="E12" s="1">
-        <v>-11.750904</v>
+        <v>-35.252712000000002</v>
       </c>
       <c r="F12" s="1">
-        <v>-12.048014000000002</v>
+        <v>-36.144042000000006</v>
       </c>
       <c r="G12" s="1">
-        <v>-13.68038</v>
+        <v>-41.041139999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>-15.372175104000002</v>
+        <v>-46.116525312000007</v>
       </c>
       <c r="I12" s="1">
-        <v>-16.435700736000001</v>
+        <v>-49.307102208000003</v>
       </c>
       <c r="J12" s="1">
-        <v>-16.174114184400004</v>
+        <v>-48.522342553200012</v>
       </c>
       <c r="K12" s="1">
-        <v>-17.443963151999995</v>
+        <v>-52.331889455999985</v>
       </c>
       <c r="L12" s="1">
-        <v>-17.465182559999995</v>
+        <v>-52.395547679999986</v>
       </c>
       <c r="M12" s="1">
-        <v>-22.992426927359997</v>
+        <v>-68.977280782079987</v>
       </c>
       <c r="N12" s="1">
-        <v>-23.690622603840012</v>
+        <v>-71.071867811520036</v>
       </c>
       <c r="O12" s="1">
-        <v>-22.532154653120006</v>
+        <v>-67.596463959360022</v>
       </c>
       <c r="P12" s="1">
-        <v>-20.747802366720002</v>
+        <v>-62.243407100160006</v>
       </c>
       <c r="Q12" s="1">
-        <v>-19.807262936999997</v>
+        <v>-59.421788810999992</v>
       </c>
       <c r="R12" s="1">
-        <v>-19.270635246720005</v>
+        <v>-57.811905740160014</v>
       </c>
       <c r="S12" s="1">
-        <v>-17.204239999999999</v>
+        <v>-51.612719999999996</v>
       </c>
       <c r="T12" s="1">
-        <v>-16.231871335680001</v>
+        <v>-48.695614007040007</v>
       </c>
       <c r="U12" s="1">
-        <v>-14.08574189568</v>
+        <v>-42.257225687039998</v>
       </c>
       <c r="V12" s="1">
-        <v>-9.0353775360000004</v>
+        <v>-27.106132608000003</v>
       </c>
       <c r="W12" s="1">
-        <v>-10.123202778479998</v>
+        <v>-30.369608335439992</v>
       </c>
       <c r="X12" s="1">
-        <v>-11.123325359999999</v>
+        <v>-33.369976080000001</v>
       </c>
       <c r="Y12" s="1">
-        <v>-10.694376099999999</v>
+        <v>-32.083128299999998</v>
       </c>
       <c r="Z12" s="1">
-        <v>-9.2085241248000003</v>
+        <v>-27.625572374400001</v>
       </c>
       <c r="AA12" s="1">
-        <v>-9.6784611839999997</v>
+        <v>-29.035383551999999</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.2">
@@ -70281,76 +70281,76 @@
         <v>1</v>
       </c>
       <c r="D13" s="1">
-        <v>9.8439566579999997</v>
+        <v>29.531869973999999</v>
       </c>
       <c r="E13" s="1">
-        <v>10.8585225264</v>
+        <v>32.575567579199998</v>
       </c>
       <c r="F13" s="1">
-        <v>12.437291903999999</v>
+        <v>37.311875711999996</v>
       </c>
       <c r="G13" s="1">
-        <v>12.464569490800002</v>
+        <v>37.393708472400007</v>
       </c>
       <c r="H13" s="1">
-        <v>13.402743848999997</v>
+        <v>40.20823154699999</v>
       </c>
       <c r="I13" s="1">
-        <v>15.854067970000003</v>
+        <v>47.562203910000008</v>
       </c>
       <c r="J13" s="1">
-        <v>13.948127999999999</v>
+        <v>41.844383999999998</v>
       </c>
       <c r="K13" s="1">
-        <v>15.897757459200001</v>
+        <v>47.693272377600003</v>
       </c>
       <c r="L13" s="1">
-        <v>15.647906568000003</v>
+        <v>46.94371970400001</v>
       </c>
       <c r="M13" s="1">
-        <v>18.383668594080003</v>
+        <v>55.151005782240006</v>
       </c>
       <c r="N13" s="1">
-        <v>17.617854120000001</v>
+        <v>52.853562359999998</v>
       </c>
       <c r="O13" s="1">
-        <v>15.667429602</v>
+        <v>47.002288806000003</v>
       </c>
       <c r="P13" s="1">
-        <v>16.912276992000002</v>
+        <v>50.736830976000007</v>
       </c>
       <c r="Q13" s="1">
-        <v>16.34211122544</v>
+        <v>49.02633367632</v>
       </c>
       <c r="R13" s="1">
-        <v>15.760829145600006</v>
+        <v>47.282487436800018</v>
       </c>
       <c r="S13" s="1">
-        <v>12.842441452800003</v>
+        <v>38.527324358400008</v>
       </c>
       <c r="T13" s="1">
-        <v>13.490523009599997</v>
+        <v>40.471569028799991</v>
       </c>
       <c r="U13" s="1">
-        <v>11.819254087679999</v>
+        <v>35.457762263039996</v>
       </c>
       <c r="V13" s="1">
-        <v>9.9207950939999989</v>
+        <v>29.762385281999997</v>
       </c>
       <c r="W13" s="1">
-        <v>10.374038048000003</v>
+        <v>31.122114144000008</v>
       </c>
       <c r="X13" s="1">
-        <v>10.364707267200002</v>
+        <v>31.094121801600004</v>
       </c>
       <c r="Y13" s="1">
-        <v>12.838640505600004</v>
+        <v>38.515921516800013</v>
       </c>
       <c r="Z13" s="1">
-        <v>8.8811117999999993</v>
+        <v>26.643335399999998</v>
       </c>
       <c r="AA13" s="1">
-        <v>10.115380800000004</v>
+        <v>30.346142400000012</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -70364,76 +70364,76 @@
         <v>2</v>
       </c>
       <c r="D14" s="1">
-        <v>4.8574032000000011</v>
+        <v>14.572209600000004</v>
       </c>
       <c r="E14" s="1">
-        <v>4.8746438000000003</v>
+        <v>14.6239314</v>
       </c>
       <c r="F14" s="1">
-        <v>4.3217400000000001</v>
+        <v>12.96522</v>
       </c>
       <c r="G14" s="1">
-        <v>4.1783279999999987</v>
+        <v>12.534983999999996</v>
       </c>
       <c r="H14" s="1">
-        <v>3.3897216000000001</v>
+        <v>10.169164800000001</v>
       </c>
       <c r="I14" s="1">
-        <v>2.7630256000000002</v>
+        <v>8.2890768000000001</v>
       </c>
       <c r="J14" s="1">
-        <v>3.6227983999999998</v>
+        <v>10.868395199999998</v>
       </c>
       <c r="K14" s="1">
-        <v>0.59891040000000006</v>
+        <v>1.7967312000000002</v>
       </c>
       <c r="L14" s="1">
-        <v>0.54796000000000011</v>
+        <v>1.6438800000000002</v>
       </c>
       <c r="M14" s="1">
-        <v>0.76782419999999985</v>
+        <v>2.3034725999999996</v>
       </c>
       <c r="N14" s="1">
-        <v>0.47046280000000001</v>
+        <v>1.4113884000000001</v>
       </c>
       <c r="O14" s="1">
-        <v>0.54222199999999998</v>
+        <v>1.6266659999999999</v>
       </c>
       <c r="P14" s="1">
-        <v>0.90934000000000026</v>
+        <v>2.7280200000000008</v>
       </c>
       <c r="Q14" s="1">
-        <v>1.7256826000000001</v>
+        <v>5.1770478000000004</v>
       </c>
       <c r="R14" s="1">
-        <v>1.7517695999999998</v>
+        <v>5.2553087999999999</v>
       </c>
       <c r="S14" s="1">
-        <v>1.7930375999999995</v>
+        <v>5.3791127999999979</v>
       </c>
       <c r="T14" s="1">
-        <v>0.94665599999999994</v>
+        <v>2.8399679999999998</v>
       </c>
       <c r="U14" s="1">
-        <v>1.9283327999999995</v>
+        <v>5.7849983999999983</v>
       </c>
       <c r="V14" s="1">
-        <v>1.1316096</v>
+        <v>3.3948288</v>
       </c>
       <c r="W14" s="1">
-        <v>0.87021899999999985</v>
+        <v>2.6106569999999998</v>
       </c>
       <c r="X14" s="1">
-        <v>1.2208032000000002</v>
+        <v>3.6624096000000006</v>
       </c>
       <c r="Y14" s="1">
-        <v>0.80119580000000001</v>
+        <v>2.4035874000000002</v>
       </c>
       <c r="Z14" s="1">
-        <v>3.5858434000000003</v>
+        <v>10.757530200000001</v>
       </c>
       <c r="AA14" s="1">
-        <v>4.1943412000000002</v>
+        <v>12.583023600000001</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -70447,76 +70447,76 @@
         <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>-11.076468000000002</v>
+        <v>-33.229404000000002</v>
       </c>
       <c r="E15" s="1">
-        <v>-11.515885920000001</v>
+        <v>-34.54765776</v>
       </c>
       <c r="F15" s="1">
-        <v>-11.566093440000001</v>
+        <v>-34.698280320000002</v>
       </c>
       <c r="G15" s="1">
-        <v>-13.133164799999999</v>
+        <v>-39.399494399999995</v>
       </c>
       <c r="H15" s="1">
-        <v>-15.987062108160004</v>
+        <v>-47.961186324480011</v>
       </c>
       <c r="I15" s="1">
-        <v>-16.106986721279998</v>
+        <v>-48.320960163839999</v>
       </c>
       <c r="J15" s="1">
-        <v>-15.850631900712003</v>
+        <v>-47.551895702136008</v>
       </c>
       <c r="K15" s="1">
-        <v>-16.746204625919994</v>
+        <v>-50.238613877759981</v>
       </c>
       <c r="L15" s="1">
-        <v>-17.639834385599997</v>
+        <v>-52.919503156799991</v>
       </c>
       <c r="M15" s="1">
-        <v>-22.762502658086397</v>
+        <v>-68.287507974259199</v>
       </c>
       <c r="N15" s="1">
-        <v>-24.638247507993611</v>
+        <v>-73.914742523980834</v>
       </c>
       <c r="O15" s="1">
-        <v>-22.081511560057606</v>
+        <v>-66.244534680172819</v>
       </c>
       <c r="P15" s="1">
-        <v>-20.540324343052802</v>
+        <v>-61.620973029158407</v>
       </c>
       <c r="Q15" s="1">
-        <v>-19.014972419519996</v>
+        <v>-57.044917258559991</v>
       </c>
       <c r="R15" s="1">
-        <v>-18.885222541785605</v>
+        <v>-56.655667625356813</v>
       </c>
       <c r="S15" s="1">
-        <v>-16.344027999999998</v>
+        <v>-49.032083999999998</v>
       </c>
       <c r="T15" s="1">
-        <v>-16.231871335680001</v>
+        <v>-48.695614007040007</v>
       </c>
       <c r="U15" s="1">
-        <v>-13.9448844767232</v>
+        <v>-41.834653430169595</v>
       </c>
       <c r="V15" s="1">
-        <v>-9.0353775360000004</v>
+        <v>-27.106132608000003</v>
       </c>
       <c r="W15" s="1">
-        <v>-10.325666834049597</v>
+        <v>-30.97700050214879</v>
       </c>
       <c r="X15" s="1">
-        <v>-11.234558613599999</v>
+        <v>-33.703675840799995</v>
       </c>
       <c r="Y15" s="1">
-        <v>-10.801319861</v>
+        <v>-32.403959583000002</v>
       </c>
       <c r="Z15" s="1">
-        <v>-8.8401831598079994</v>
+        <v>-26.520549479423998</v>
       </c>
       <c r="AA15" s="1">
-        <v>-10.06559963136</v>
+        <v>-30.196798894079997</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
@@ -70530,76 +70530,76 @@
         <v>2</v>
       </c>
       <c r="D16" s="1">
-        <v>9.3517588250999992</v>
+        <v>28.055276475299998</v>
       </c>
       <c r="E16" s="1">
-        <v>10.424181625344</v>
+        <v>31.272544876032001</v>
       </c>
       <c r="F16" s="1">
-        <v>13.059156499199998</v>
+        <v>39.177469497599994</v>
       </c>
       <c r="G16" s="1">
-        <v>11.965986711168002</v>
+        <v>35.897960133504007</v>
       </c>
       <c r="H16" s="1">
-        <v>14.072881041449996</v>
+        <v>42.218643124349988</v>
       </c>
       <c r="I16" s="1">
-        <v>15.219905251200002</v>
+        <v>45.659715753600004</v>
       </c>
       <c r="J16" s="1">
-        <v>14.087609279999999</v>
+        <v>42.26282784</v>
       </c>
       <c r="K16" s="1">
-        <v>15.897757459200001</v>
+        <v>47.693272377600003</v>
       </c>
       <c r="L16" s="1">
-        <v>14.865511239600004</v>
+        <v>44.596533718800011</v>
       </c>
       <c r="M16" s="1">
-        <v>18.751341965961604</v>
+        <v>56.254025897884816</v>
       </c>
       <c r="N16" s="1">
-        <v>17.265497037599999</v>
+        <v>51.796491112799998</v>
       </c>
       <c r="O16" s="1">
-        <v>16.29412678608</v>
+        <v>48.882380358239999</v>
       </c>
       <c r="P16" s="1">
-        <v>16.235785912320001</v>
+        <v>48.707357736960006</v>
       </c>
       <c r="Q16" s="1">
-        <v>16.832374562203199</v>
+        <v>50.497123686609598</v>
       </c>
       <c r="R16" s="1">
-        <v>16.076045728512007</v>
+        <v>48.228137185536021</v>
       </c>
       <c r="S16" s="1">
-        <v>12.970865867328003</v>
+        <v>38.912597601984011</v>
       </c>
       <c r="T16" s="1">
-        <v>13.760333469791997</v>
+        <v>41.281000409375991</v>
       </c>
       <c r="U16" s="1">
-        <v>11.582869005926399</v>
+        <v>34.7486070177792</v>
       </c>
       <c r="V16" s="1">
-        <v>10.020003044939999</v>
+        <v>30.06000913482</v>
       </c>
       <c r="W16" s="1">
-        <v>10.374038048000003</v>
+        <v>31.122114144000008</v>
       </c>
       <c r="X16" s="1">
-        <v>10.779295557888002</v>
+        <v>32.337886673664002</v>
       </c>
       <c r="Y16" s="1">
-        <v>13.095413315712005</v>
+        <v>39.286239947136011</v>
       </c>
       <c r="Z16" s="1">
-        <v>8.969922918</v>
+        <v>26.909768753999998</v>
       </c>
       <c r="AA16" s="1">
-        <v>9.7107655680000047</v>
+        <v>29.132296704000012</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.2">
@@ -70613,76 +70613,76 @@
         <v>3</v>
       </c>
       <c r="D17" s="1">
-        <v>4.6145330400000013</v>
+        <v>13.843599120000004</v>
       </c>
       <c r="E17" s="1">
-        <v>5.0696295520000003</v>
+        <v>15.208888656000001</v>
       </c>
       <c r="F17" s="1">
-        <v>4.2785225999999996</v>
+        <v>12.8355678</v>
       </c>
       <c r="G17" s="1">
-        <v>4.3872443999999984</v>
+        <v>13.161733199999995</v>
       </c>
       <c r="H17" s="1">
-        <v>3.4236188159999998</v>
+        <v>10.270856448</v>
       </c>
       <c r="I17" s="1">
-        <v>2.7353953440000005</v>
+        <v>8.2061860320000015</v>
       </c>
       <c r="J17" s="1">
-        <v>3.5141144479999995</v>
+        <v>10.542343343999999</v>
       </c>
       <c r="K17" s="1">
-        <v>0.60489950400000003</v>
+        <v>1.8146985120000001</v>
       </c>
       <c r="L17" s="1">
-        <v>0.54796000000000011</v>
+        <v>1.6438800000000002</v>
       </c>
       <c r="M17" s="1">
-        <v>0.74478947399999984</v>
+        <v>2.2343684219999993</v>
       </c>
       <c r="N17" s="1">
-        <v>0.46575817200000003</v>
+        <v>1.397274516</v>
       </c>
       <c r="O17" s="1">
-        <v>0.53679977999999995</v>
+        <v>1.6103993399999998</v>
       </c>
       <c r="P17" s="1">
-        <v>0.90934000000000026</v>
+        <v>2.7280200000000008</v>
       </c>
       <c r="Q17" s="1">
-        <v>1.7429394260000002</v>
+        <v>5.2288182780000003</v>
       </c>
       <c r="R17" s="1">
-        <v>1.8393580799999998</v>
+        <v>5.5180742399999989</v>
       </c>
       <c r="S17" s="1">
-        <v>1.7033857199999993</v>
+        <v>5.1101571599999982</v>
       </c>
       <c r="T17" s="1">
-        <v>0.91825632000000001</v>
+        <v>2.7547689599999998</v>
       </c>
       <c r="U17" s="1">
-        <v>1.9090494719999995</v>
+        <v>5.7271484159999986</v>
       </c>
       <c r="V17" s="1">
-        <v>1.1542417919999999</v>
+        <v>3.4627253759999999</v>
       </c>
       <c r="W17" s="1">
-        <v>0.87021899999999985</v>
+        <v>2.6106569999999998</v>
       </c>
       <c r="X17" s="1">
-        <v>1.1963871360000002</v>
+        <v>3.5891614080000007</v>
       </c>
       <c r="Y17" s="1">
-        <v>0.80119580000000001</v>
+        <v>2.4035874000000002</v>
       </c>
       <c r="Z17" s="1">
-        <v>3.4424096640000004</v>
+        <v>10.327228992000002</v>
       </c>
       <c r="AA17" s="1">
-        <v>4.1104543759999999</v>
+        <v>12.331363128</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -70696,76 +70696,76 @@
         <v>3</v>
       </c>
       <c r="D18" s="1">
-        <v>-10.965703320000003</v>
+        <v>-32.897109960000009</v>
       </c>
       <c r="E18" s="1">
-        <v>-11.976521356800001</v>
+        <v>-35.929564070400005</v>
       </c>
       <c r="F18" s="1">
-        <v>-10.987788768</v>
+        <v>-32.963366303999997</v>
       </c>
       <c r="G18" s="1">
-        <v>-13.264496447999999</v>
+        <v>-39.793489343999994</v>
       </c>
       <c r="H18" s="1">
-        <v>-16.466673971404802</v>
+        <v>-49.400021914214406</v>
       </c>
       <c r="I18" s="1">
-        <v>-16.268056588492797</v>
+        <v>-48.804169765478392</v>
       </c>
       <c r="J18" s="1">
-        <v>-15.216606624683523</v>
+        <v>-45.649819874050571</v>
       </c>
       <c r="K18" s="1">
-        <v>-17.081128718438393</v>
+        <v>-51.243386155315179</v>
       </c>
       <c r="L18" s="1">
-        <v>-17.816232729455997</v>
+        <v>-53.448698188367992</v>
       </c>
       <c r="M18" s="1">
-        <v>-21.852002551762943</v>
+        <v>-65.556007655288823</v>
       </c>
       <c r="N18" s="1">
-        <v>-25.131012458153482</v>
+        <v>-75.393037374460448</v>
       </c>
       <c r="O18" s="1">
-        <v>-21.86069644445703</v>
+        <v>-65.582089333371087</v>
       </c>
       <c r="P18" s="1">
-        <v>-21.156534073344389</v>
+        <v>-63.469602220033167</v>
       </c>
       <c r="Q18" s="1">
-        <v>-19.585421592105593</v>
+        <v>-58.756264776316783</v>
       </c>
       <c r="R18" s="1">
-        <v>-19.829483668874886</v>
+        <v>-59.488451006624658</v>
       </c>
       <c r="S18" s="1">
-        <v>-16.997789119999997</v>
+        <v>-50.993367359999993</v>
       </c>
       <c r="T18" s="1">
-        <v>-15.7449151956096</v>
+        <v>-47.234745586828801</v>
       </c>
       <c r="U18" s="1">
-        <v>-14.363231011024896</v>
+        <v>-43.089693033074688</v>
       </c>
       <c r="V18" s="1">
-        <v>-8.5836086592000012</v>
+        <v>-25.750825977600002</v>
       </c>
       <c r="W18" s="1">
-        <v>-10.119153497368606</v>
+        <v>-30.357460492105815</v>
       </c>
       <c r="X18" s="1">
-        <v>-11.122213027463999</v>
+        <v>-33.366639082391998</v>
       </c>
       <c r="Y18" s="1">
-        <v>-10.47728026517</v>
+        <v>-31.431840795509999</v>
       </c>
       <c r="Z18" s="1">
-        <v>-8.6633794966118405</v>
+        <v>-25.990138489835523</v>
       </c>
       <c r="AA18" s="1">
-        <v>-10.06559963136</v>
+        <v>-30.196798894079997</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.2">
@@ -70779,76 +70779,76 @@
         <v>3</v>
       </c>
       <c r="D19" s="1">
-        <v>8.884170883845</v>
+        <v>26.652512651534998</v>
       </c>
       <c r="E19" s="1">
-        <v>10.63266525785088</v>
+        <v>31.897995773552637</v>
       </c>
       <c r="F19" s="1">
-        <v>13.581522759167999</v>
+        <v>40.744568277504001</v>
       </c>
       <c r="G19" s="1">
-        <v>12.564286046726401</v>
+        <v>37.692858140179204</v>
       </c>
       <c r="H19" s="1">
-        <v>14.635796283107995</v>
+        <v>43.907388849323986</v>
       </c>
       <c r="I19" s="1">
-        <v>14.763308093664001</v>
+        <v>44.289924280992004</v>
       </c>
       <c r="J19" s="1">
-        <v>14.791989743999999</v>
+        <v>44.375969231999996</v>
       </c>
       <c r="K19" s="1">
-        <v>16.692645332160001</v>
+        <v>50.077935996480008</v>
       </c>
       <c r="L19" s="1">
-        <v>14.419545902412004</v>
+        <v>43.258637707236012</v>
       </c>
       <c r="M19" s="1">
-        <v>18.751341965961604</v>
+        <v>56.254025897884816</v>
       </c>
       <c r="N19" s="1">
-        <v>17.438152007976001</v>
+        <v>52.314456023928003</v>
       </c>
       <c r="O19" s="1">
-        <v>15.968244250358401</v>
+        <v>47.904732751075201</v>
       </c>
       <c r="P19" s="1">
-        <v>17.047575207936003</v>
+        <v>51.142725623808005</v>
       </c>
       <c r="Q19" s="1">
-        <v>16.327403325337105</v>
+        <v>48.982209976011319</v>
       </c>
       <c r="R19" s="1">
-        <v>15.272243442086406</v>
+        <v>45.816730326259218</v>
       </c>
       <c r="S19" s="1">
-        <v>12.841157208654723</v>
+        <v>38.52347162596417</v>
       </c>
       <c r="T19" s="1">
-        <v>13.760333469791997</v>
+        <v>41.281000409375991</v>
       </c>
       <c r="U19" s="1">
-        <v>11.814526386044927</v>
+        <v>35.443579158134781</v>
       </c>
       <c r="V19" s="1">
-        <v>10.420803166737599</v>
+        <v>31.262409500212797</v>
       </c>
       <c r="W19" s="1">
-        <v>10.685259189440004</v>
+        <v>32.055777568320011</v>
       </c>
       <c r="X19" s="1">
-        <v>10.779295557888002</v>
+        <v>32.337886673664002</v>
       </c>
       <c r="Y19" s="1">
-        <v>12.833505049397765</v>
+        <v>38.500515148193294</v>
       </c>
       <c r="Z19" s="1">
-        <v>8.6111260012799988</v>
+        <v>25.833378003839996</v>
       </c>
       <c r="AA19" s="1">
-        <v>9.4194426009600036</v>
+        <v>28.258327802880011</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.2">
@@ -70862,76 +70862,76 @@
         <v>1</v>
       </c>
       <c r="D20" s="1">
-        <v>5.1376380000000017</v>
+        <v>15.412914000000004</v>
       </c>
       <c r="E20" s="1">
-        <v>5.3090180000000009</v>
+        <v>15.927054000000002</v>
       </c>
       <c r="F20" s="1">
-        <v>4.7539140000000009</v>
+        <v>14.261742000000002</v>
       </c>
       <c r="G20" s="1">
-        <v>4.5060399999999996</v>
+        <v>13.51812</v>
       </c>
       <c r="H20" s="1">
-        <v>3.6917760000000004</v>
+        <v>11.075328000000001</v>
       </c>
       <c r="I20" s="1">
-        <v>3.1333280000000006</v>
+        <v>9.3999840000000017</v>
       </c>
       <c r="J20" s="1">
-        <v>3.8318060000000003</v>
+        <v>11.495418000000001</v>
       </c>
       <c r="K20" s="1">
-        <v>0.66545600000000016</v>
+        <v>1.9963680000000004</v>
       </c>
       <c r="L20" s="1">
-        <v>0.58520000000000005</v>
+        <v>1.7556000000000003</v>
       </c>
       <c r="M20" s="1">
-        <v>0.85313799999999984</v>
+        <v>2.5594139999999994</v>
       </c>
       <c r="N20" s="1">
-        <v>0.5024360000000001</v>
+        <v>1.5073080000000003</v>
       </c>
       <c r="O20" s="1">
-        <v>0.62783599999999995</v>
+        <v>1.883508</v>
       </c>
       <c r="P20" s="1">
-        <v>1.0002740000000003</v>
+        <v>3.0008220000000012</v>
       </c>
       <c r="Q20" s="1">
-        <v>1.8429620000000002</v>
+        <v>5.5288860000000009</v>
       </c>
       <c r="R20" s="1">
-        <v>1.966272</v>
+        <v>5.8988160000000001</v>
       </c>
       <c r="S20" s="1">
-        <v>1.9336679999999997</v>
+        <v>5.8010039999999989</v>
       </c>
       <c r="T20" s="1">
-        <v>1.0847100000000001</v>
+        <v>3.25413</v>
       </c>
       <c r="U20" s="1">
-        <v>2.2095479999999998</v>
+        <v>6.6286439999999995</v>
       </c>
       <c r="V20" s="1">
-        <v>1.2966360000000001</v>
+        <v>3.8899080000000001</v>
       </c>
       <c r="W20" s="1">
-        <v>0.91165799999999986</v>
+        <v>2.7349739999999994</v>
       </c>
       <c r="X20" s="1">
-        <v>1.3844160000000003</v>
+        <v>4.1532480000000014</v>
       </c>
       <c r="Y20" s="1">
-        <v>0.85564600000000002</v>
+        <v>2.5669379999999999</v>
       </c>
       <c r="Z20" s="1">
-        <v>3.9053740000000006</v>
+        <v>11.716122000000002</v>
       </c>
       <c r="AA20" s="1">
-        <v>4.7079339999999998</v>
+        <v>14.123802</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.2">
@@ -70945,76 +70945,76 @@
         <v>1</v>
       </c>
       <c r="D21" s="1">
-        <v>-10.636732220400004</v>
+        <v>-31.910196661200011</v>
       </c>
       <c r="E21" s="1">
-        <v>-12.575347424640002</v>
+        <v>-37.726042273920008</v>
       </c>
       <c r="F21" s="1">
-        <v>-10.658155104959999</v>
+        <v>-31.974465314879996</v>
       </c>
       <c r="G21" s="1">
-        <v>-13.529786376959999</v>
+        <v>-40.589359130879998</v>
       </c>
       <c r="H21" s="1">
-        <v>-17.125340930260997</v>
+        <v>-51.37602279078299</v>
       </c>
       <c r="I21" s="1">
-        <v>-16.268056588492797</v>
+        <v>-48.804169765478392</v>
       </c>
       <c r="J21" s="1">
-        <v>-15.36877269093036</v>
+        <v>-46.106318072791083</v>
       </c>
       <c r="K21" s="1">
-        <v>-16.910317431254008</v>
+        <v>-50.730952293762023</v>
       </c>
       <c r="L21" s="1">
-        <v>-17.994395056750555</v>
+        <v>-53.983185170251666</v>
       </c>
       <c r="M21" s="1">
-        <v>-21.852002551762943</v>
+        <v>-65.556007655288823</v>
       </c>
       <c r="N21" s="1">
-        <v>-24.879702333571945</v>
+        <v>-74.639107000715839</v>
       </c>
       <c r="O21" s="1">
-        <v>-22.735124302235313</v>
+        <v>-68.205372906705946</v>
       </c>
       <c r="P21" s="1">
-        <v>-21.156534073344389</v>
+        <v>-63.469602220033167</v>
       </c>
       <c r="Q21" s="1">
-        <v>-20.172984239868761</v>
+        <v>-60.518952719606283</v>
       </c>
       <c r="R21" s="1">
-        <v>-19.234599158808638</v>
+        <v>-57.703797476425919</v>
       </c>
       <c r="S21" s="1">
-        <v>-16.657833337599996</v>
+        <v>-49.973500012799988</v>
       </c>
       <c r="T21" s="1">
-        <v>-14.957669435829121</v>
+        <v>-44.873008307487368</v>
       </c>
       <c r="U21" s="1">
-        <v>-14.363231011024896</v>
+        <v>-43.089693033074688</v>
       </c>
       <c r="V21" s="1">
-        <v>-8.7552808323840008</v>
+        <v>-26.265842497152001</v>
       </c>
       <c r="W21" s="1">
-        <v>-10.422728102289664</v>
+        <v>-31.268184306868992</v>
       </c>
       <c r="X21" s="1">
-        <v>-11.56710154856256</v>
+        <v>-34.701304645687678</v>
       </c>
       <c r="Y21" s="1">
-        <v>-10.267734659866601</v>
+        <v>-30.803203979599804</v>
       </c>
       <c r="Z21" s="1">
-        <v>-8.6633794966118405</v>
+        <v>-25.990138489835523</v>
       </c>
       <c r="AA21" s="1">
-        <v>-10.367567620300798</v>
+        <v>-31.102702860902397</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.2">
@@ -71028,76 +71028,76 @@
         <v>1</v>
       </c>
       <c r="D22" s="1">
-        <v>8.4399623396527499</v>
+        <v>25.319887018958248</v>
       </c>
       <c r="E22" s="1">
-        <v>10.845318563007897</v>
+        <v>32.535955689023695</v>
       </c>
       <c r="F22" s="1">
-        <v>13.988968441943038</v>
+        <v>41.966905325829117</v>
       </c>
       <c r="G22" s="1">
-        <v>12.313000325791872</v>
+        <v>36.939000977375613</v>
       </c>
       <c r="H22" s="1">
-        <v>14.928512208770155</v>
+        <v>44.78553662631046</v>
       </c>
       <c r="I22" s="1">
-        <v>14.61567501272736</v>
+        <v>43.847025038182082</v>
       </c>
       <c r="J22" s="1">
-        <v>14.348230051679998</v>
+        <v>43.044690155039994</v>
       </c>
       <c r="K22" s="1">
-        <v>17.1934246921248</v>
+        <v>51.580274076374401</v>
       </c>
       <c r="L22" s="1">
-        <v>15.140523197532605</v>
+        <v>45.42156959259782</v>
       </c>
       <c r="M22" s="1">
-        <v>19.313882224940453</v>
+        <v>57.941646674821357</v>
       </c>
       <c r="N22" s="1">
-        <v>17.089388967816479</v>
+        <v>51.26816690344944</v>
       </c>
       <c r="O22" s="1">
-        <v>16.287609135365571</v>
+        <v>48.862827406096713</v>
       </c>
       <c r="P22" s="1">
-        <v>17.72947821625344</v>
+        <v>53.188434648760321</v>
       </c>
       <c r="Q22" s="1">
-        <v>16.817225425097217</v>
+        <v>50.451676275291646</v>
       </c>
       <c r="R22" s="1">
-        <v>14.814076138823815</v>
+        <v>44.442228416471444</v>
       </c>
       <c r="S22" s="1">
-        <v>12.712745636568174</v>
+        <v>38.138236909704524</v>
       </c>
       <c r="T22" s="1">
-        <v>14.035540139187836</v>
+        <v>42.106620417563505</v>
       </c>
       <c r="U22" s="1">
-        <v>11.46009059446358</v>
+        <v>34.380271783390739</v>
       </c>
       <c r="V22" s="1">
-        <v>10.733427261739727</v>
+        <v>32.200281785219182</v>
       </c>
       <c r="W22" s="1">
-        <v>11.112669557017602</v>
+        <v>33.338008671052805</v>
       </c>
       <c r="X22" s="1">
-        <v>10.671502602309122</v>
+        <v>32.014507806927369</v>
       </c>
       <c r="Y22" s="1">
-        <v>12.705169998903786</v>
+        <v>38.11550999671136</v>
       </c>
       <c r="Z22" s="1">
-        <v>8.783348521305598</v>
+        <v>26.350045563916794</v>
       </c>
       <c r="AA22" s="1">
-        <v>9.5136370269696027</v>
+        <v>28.540911080908806</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.2">
@@ -71111,76 +71111,76 @@
         <v>2</v>
       </c>
       <c r="D23" s="1">
-        <v>5.3945199000000015</v>
+        <v>16.183559700000004</v>
       </c>
       <c r="E23" s="1">
-        <v>5.5744689000000003</v>
+        <v>16.723406700000002</v>
       </c>
       <c r="F23" s="1">
-        <v>4.5637574400000007</v>
+        <v>13.691272320000003</v>
       </c>
       <c r="G23" s="1">
-        <v>4.3708587999999997</v>
+        <v>13.112576399999998</v>
       </c>
       <c r="H23" s="1">
-        <v>3.6548582400000003</v>
+        <v>10.964574720000002</v>
       </c>
       <c r="I23" s="1">
-        <v>3.0706614400000007</v>
+        <v>9.2119843200000027</v>
       </c>
       <c r="J23" s="1">
-        <v>3.7934879399999999</v>
+        <v>11.380463819999999</v>
       </c>
       <c r="K23" s="1">
-        <v>0.67211056000000013</v>
+        <v>2.0163316800000004</v>
       </c>
       <c r="L23" s="1">
-        <v>0.57349600000000001</v>
+        <v>1.720488</v>
       </c>
       <c r="M23" s="1">
-        <v>0.86166937999999993</v>
+        <v>2.5850081399999998</v>
       </c>
       <c r="N23" s="1">
-        <v>0.52253344000000013</v>
+        <v>1.5676003200000004</v>
       </c>
       <c r="O23" s="1">
-        <v>0.65294943999999999</v>
+        <v>1.95884832</v>
       </c>
       <c r="P23" s="1">
-        <v>0.98026852000000031</v>
+        <v>2.9408055600000012</v>
       </c>
       <c r="Q23" s="1">
-        <v>1.9166804800000004</v>
+        <v>5.7500414400000013</v>
       </c>
       <c r="R23" s="1">
-        <v>2.0645856</v>
+        <v>6.1937568000000001</v>
       </c>
       <c r="S23" s="1">
-        <v>1.8369845999999999</v>
+        <v>5.5109537999999993</v>
       </c>
       <c r="T23" s="1">
-        <v>1.1172513000000002</v>
+        <v>3.3517539000000003</v>
       </c>
       <c r="U23" s="1">
-        <v>2.2979299199999996</v>
+        <v>6.8937897599999989</v>
       </c>
       <c r="V23" s="1">
-        <v>1.2707032800000002</v>
+        <v>3.8121098400000006</v>
       </c>
       <c r="W23" s="1">
-        <v>0.90254141999999993</v>
+        <v>2.7076242599999998</v>
       </c>
       <c r="X23" s="1">
-        <v>1.3844160000000003</v>
+        <v>4.1532480000000014</v>
       </c>
       <c r="Y23" s="1">
-        <v>0.88131538000000009</v>
+        <v>2.6439461400000002</v>
       </c>
       <c r="Z23" s="1">
-        <v>4.1006427000000008</v>
+        <v>12.301928100000001</v>
       </c>
       <c r="AA23" s="1">
-        <v>4.8020926800000003</v>
+        <v>14.40627804</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.2">
@@ -71194,76 +71194,76 @@
         <v>2</v>
       </c>
       <c r="D24" s="1">
-        <v>-10.743099542604005</v>
+        <v>-32.229298627812014</v>
       </c>
       <c r="E24" s="1">
-        <v>-12.952607847379202</v>
+        <v>-38.857823542137609</v>
       </c>
       <c r="F24" s="1">
-        <v>-10.444992002860799</v>
+        <v>-31.334976008582395</v>
       </c>
       <c r="G24" s="1">
-        <v>-13.259190649420798</v>
+        <v>-39.777571948262391</v>
       </c>
       <c r="H24" s="1">
-        <v>-17.296594339563608</v>
+        <v>-51.889783018690821</v>
       </c>
       <c r="I24" s="1">
-        <v>-15.780014890838013</v>
+        <v>-47.34004467251404</v>
       </c>
       <c r="J24" s="1">
-        <v>-15.061397237111754</v>
+        <v>-45.184191711335259</v>
       </c>
       <c r="K24" s="1">
-        <v>-17.248523779879086</v>
+        <v>-51.745571339637259</v>
       </c>
       <c r="L24" s="1">
-        <v>-18.714170859020577</v>
+        <v>-56.14251257706173</v>
       </c>
       <c r="M24" s="1">
-        <v>-22.507562628315831</v>
+        <v>-67.522687884947487</v>
       </c>
       <c r="N24" s="1">
-        <v>-23.88451424022907</v>
+        <v>-71.653542720687213</v>
       </c>
       <c r="O24" s="1">
-        <v>-23.417178031302374</v>
+        <v>-70.251534093907125</v>
       </c>
       <c r="P24" s="1">
-        <v>-20.521838051144059</v>
+        <v>-61.565514153432176</v>
       </c>
       <c r="Q24" s="1">
-        <v>-19.769524555071385</v>
+        <v>-59.308573665214155</v>
       </c>
       <c r="R24" s="1">
-        <v>-19.234599158808638</v>
+        <v>-57.703797476425919</v>
       </c>
       <c r="S24" s="1">
-        <v>-15.991520004095996</v>
+        <v>-47.974560012287988</v>
       </c>
       <c r="T24" s="1">
-        <v>-15.107246130187413</v>
+        <v>-45.321738390562238</v>
       </c>
       <c r="U24" s="1">
-        <v>-13.645069460473652</v>
+        <v>-40.935208381420956</v>
       </c>
       <c r="V24" s="1">
-        <v>-8.405069599088641</v>
+        <v>-25.215208797265923</v>
       </c>
       <c r="W24" s="1">
-        <v>-10.422728102289664</v>
+        <v>-31.268184306868992</v>
       </c>
       <c r="X24" s="1">
-        <v>-12.029785610505062</v>
+        <v>-36.08935683151519</v>
       </c>
       <c r="Y24" s="1">
-        <v>-9.9597026200706029</v>
+        <v>-29.879107860211811</v>
       </c>
       <c r="Z24" s="1">
-        <v>-8.8366470865440778</v>
+        <v>-26.509941259632235</v>
       </c>
       <c r="AA24" s="1">
-        <v>-10.263891944097791</v>
+        <v>-30.791675832293372</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.2">
@@ -71277,76 +71277,76 @@
         <v>2</v>
       </c>
       <c r="D25" s="1">
-        <v>8.3555627162562232</v>
+        <v>25.066688148768669</v>
       </c>
       <c r="E25" s="1">
-        <v>10.845318563007897</v>
+        <v>32.535955689023695</v>
       </c>
       <c r="F25" s="1">
-        <v>13.289520019845886</v>
+        <v>39.868560059537657</v>
       </c>
       <c r="G25" s="1">
-        <v>12.55926033230771</v>
+        <v>37.677780996923133</v>
       </c>
       <c r="H25" s="1">
-        <v>15.227082452945558</v>
+        <v>45.681247358836671</v>
       </c>
       <c r="I25" s="1">
-        <v>15.054145263109181</v>
+        <v>45.162435789327546</v>
       </c>
       <c r="J25" s="1">
-        <v>14.491712352196798</v>
+        <v>43.475137056590391</v>
       </c>
       <c r="K25" s="1">
-        <v>17.1934246921248</v>
+        <v>51.580274076374401</v>
       </c>
       <c r="L25" s="1">
-        <v>14.383497037655975</v>
+        <v>43.150491112967927</v>
       </c>
       <c r="M25" s="1">
-        <v>20.086437513938073</v>
+        <v>60.259312541814218</v>
       </c>
       <c r="N25" s="1">
-        <v>17.602070636850975</v>
+        <v>52.806211910552925</v>
       </c>
       <c r="O25" s="1">
-        <v>16.450485226719227</v>
+        <v>49.351455680157684</v>
       </c>
       <c r="P25" s="1">
-        <v>17.72947821625344</v>
+        <v>53.188434648760321</v>
       </c>
       <c r="Q25" s="1">
-        <v>16.649053170846244</v>
+        <v>49.947159512538732</v>
       </c>
       <c r="R25" s="1">
-        <v>14.073372331882624</v>
+        <v>42.220116995647871</v>
       </c>
       <c r="S25" s="1">
-        <v>12.077108354739764</v>
+        <v>36.231325064219291</v>
       </c>
       <c r="T25" s="1">
-        <v>13.614473935012199</v>
+        <v>40.843421805036598</v>
       </c>
       <c r="U25" s="1">
-        <v>11.23088878257431</v>
+        <v>33.692666347722927</v>
       </c>
       <c r="V25" s="1">
-        <v>10.733427261739727</v>
+        <v>32.200281785219182</v>
       </c>
       <c r="W25" s="1">
-        <v>11.446049643728131</v>
+        <v>34.338148931184392</v>
       </c>
       <c r="X25" s="1">
-        <v>10.137927472193665</v>
+        <v>30.413782416580993</v>
       </c>
       <c r="Y25" s="1">
-        <v>13.340428498848976</v>
+        <v>40.021285496546923</v>
       </c>
       <c r="Z25" s="1">
-        <v>8.6076815508794855</v>
+        <v>25.823044652638458</v>
       </c>
       <c r="AA25" s="1">
-        <v>9.7990461377786904</v>
+        <v>29.397138413336073</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.2">
@@ -71360,76 +71360,76 @@
         <v>3</v>
       </c>
       <c r="D26" s="1">
-        <v>5.556355497000002</v>
+        <v>16.669066491000006</v>
       </c>
       <c r="E26" s="1">
-        <v>5.6302135890000002</v>
+        <v>16.890640767000001</v>
       </c>
       <c r="F26" s="1">
-        <v>4.518119865600001</v>
+        <v>13.554359596800003</v>
       </c>
       <c r="G26" s="1">
-        <v>4.5894017399999996</v>
+        <v>13.768205219999999</v>
       </c>
       <c r="H26" s="1">
-        <v>3.6914068224000003</v>
+        <v>11.0742204672</v>
       </c>
       <c r="I26" s="1">
-        <v>3.0706614400000007</v>
+        <v>9.2119843200000027</v>
       </c>
       <c r="J26" s="1">
-        <v>3.6038135429999998</v>
+        <v>10.811440629</v>
       </c>
       <c r="K26" s="1">
-        <v>0.63850503200000008</v>
+        <v>1.9155150960000003</v>
       </c>
       <c r="L26" s="1">
-        <v>0.54482120000000001</v>
+        <v>1.6344636000000001</v>
       </c>
       <c r="M26" s="1">
-        <v>0.83581929859999993</v>
+        <v>2.5074578958</v>
       </c>
       <c r="N26" s="1">
-        <v>0.51730810560000007</v>
+        <v>1.5519243168000001</v>
       </c>
       <c r="O26" s="1">
-        <v>0.6660084288</v>
+        <v>1.9980252863999999</v>
       </c>
       <c r="P26" s="1">
-        <v>0.96066314960000032</v>
+        <v>2.8819894488000011</v>
       </c>
       <c r="Q26" s="1">
-        <v>2.0125145040000003</v>
+        <v>6.0375435120000009</v>
       </c>
       <c r="R26" s="1">
-        <v>2.1678148799999999</v>
+        <v>6.5034446399999997</v>
       </c>
       <c r="S26" s="1">
-        <v>1.9288338299999999</v>
+        <v>5.7865014899999991</v>
       </c>
       <c r="T26" s="1">
-        <v>1.1284238130000002</v>
+        <v>3.3852714390000003</v>
       </c>
       <c r="U26" s="1">
-        <v>2.2979299199999996</v>
+        <v>6.8937897599999989</v>
       </c>
       <c r="V26" s="1">
-        <v>1.2707032800000002</v>
+        <v>3.8121098400000006</v>
       </c>
       <c r="W26" s="1">
-        <v>0.86643976319999993</v>
+        <v>2.5993192895999999</v>
       </c>
       <c r="X26" s="1">
-        <v>1.3428835200000002</v>
+        <v>4.0286505600000009</v>
       </c>
       <c r="Y26" s="1">
-        <v>0.89012853380000012</v>
+        <v>2.6703856014000005</v>
       </c>
       <c r="Z26" s="1">
-        <v>3.9776234190000008</v>
+        <v>11.932870257000003</v>
       </c>
       <c r="AA26" s="1">
-        <v>4.9461554604</v>
+        <v>14.8384663812</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.2">
@@ -71443,76 +71443,76 @@
         <v>3</v>
       </c>
       <c r="D27" s="1">
-        <v>-11.280254519734205</v>
+        <v>-33.840763559202614</v>
       </c>
       <c r="E27" s="1">
-        <v>-12.823081768905411</v>
+        <v>-38.469245306716232</v>
       </c>
       <c r="F27" s="1">
-        <v>-10.340542082832192</v>
+        <v>-31.021626248496574</v>
       </c>
       <c r="G27" s="1">
-        <v>-12.861414929938173</v>
+        <v>-38.58424478981452</v>
       </c>
       <c r="H27" s="1">
-        <v>-17.123628396167973</v>
+        <v>-51.370885188503919</v>
       </c>
       <c r="I27" s="1">
-        <v>-16.253415337563155</v>
+        <v>-48.760246012689464</v>
       </c>
       <c r="J27" s="1">
-        <v>-14.308327375256164</v>
+        <v>-42.924982125768494</v>
       </c>
       <c r="K27" s="1">
-        <v>-17.076038542080298</v>
+        <v>-51.228115626240893</v>
       </c>
       <c r="L27" s="1">
-        <v>-18.152745733249962</v>
+        <v>-54.458237199749888</v>
       </c>
       <c r="M27" s="1">
-        <v>-23.182789507165307</v>
+        <v>-69.548368521495917</v>
       </c>
       <c r="N27" s="1">
-        <v>-23.88451424022907</v>
+        <v>-71.653542720687213</v>
       </c>
       <c r="O27" s="1">
-        <v>-23.417178031302374</v>
+        <v>-70.251534093907125</v>
       </c>
       <c r="P27" s="1">
-        <v>-20.111401290121179</v>
+        <v>-60.334203870363538</v>
       </c>
       <c r="Q27" s="1">
-        <v>-19.769524555071385</v>
+        <v>-59.308573665214155</v>
       </c>
       <c r="R27" s="1">
-        <v>-19.61929114198481</v>
+        <v>-58.857873425954431</v>
       </c>
       <c r="S27" s="1">
-        <v>-16.311350404177915</v>
+        <v>-48.934051212533745</v>
       </c>
       <c r="T27" s="1">
-        <v>-15.560463514093035</v>
+        <v>-46.681390542279104</v>
       </c>
       <c r="U27" s="1">
-        <v>-13.645069460473652</v>
+        <v>-40.935208381420956</v>
       </c>
       <c r="V27" s="1">
-        <v>-8.5731709910704144</v>
+        <v>-25.719512973211245</v>
       </c>
       <c r="W27" s="1">
-        <v>-10.839637226381251</v>
+        <v>-32.518911679143756</v>
       </c>
       <c r="X27" s="1">
-        <v>-11.66889204218991</v>
+        <v>-35.006676126569729</v>
       </c>
       <c r="Y27" s="1">
-        <v>-10.059299646271308</v>
+        <v>-30.177898938813925</v>
       </c>
       <c r="Z27" s="1">
-        <v>-8.394814732216874</v>
+        <v>-25.184444196650624</v>
       </c>
       <c r="AA27" s="1">
-        <v>-10.469169782979748</v>
+        <v>-31.407509348939243</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.2">
@@ -71526,76 +71526,76 @@
         <v>3</v>
       </c>
       <c r="D28" s="1">
-        <v>8.104895834768536</v>
+        <v>24.31468750430561</v>
       </c>
       <c r="E28" s="1">
-        <v>10.519959006117661</v>
+        <v>31.559877018352985</v>
       </c>
       <c r="F28" s="1">
-        <v>13.289520019845886</v>
+        <v>39.868560059537657</v>
       </c>
       <c r="G28" s="1">
-        <v>12.93603814227694</v>
+        <v>38.808114426830819</v>
       </c>
       <c r="H28" s="1">
-        <v>15.988436575592836</v>
+        <v>47.965309726778507</v>
       </c>
       <c r="I28" s="1">
-        <v>14.903603810478089</v>
+        <v>44.710811431434266</v>
       </c>
       <c r="J28" s="1">
-        <v>15.216297969806638</v>
+        <v>45.648893909419911</v>
       </c>
       <c r="K28" s="1">
-        <v>16.849556198282304</v>
+        <v>50.548668594846916</v>
       </c>
       <c r="L28" s="1">
-        <v>14.239662067279415</v>
+        <v>42.718986201838248</v>
       </c>
       <c r="M28" s="1">
-        <v>21.090759389634979</v>
+        <v>63.272278168904933</v>
       </c>
       <c r="N28" s="1">
-        <v>18.306153462325014</v>
+        <v>54.918460386975042</v>
       </c>
       <c r="O28" s="1">
-        <v>15.95697066991765</v>
+        <v>47.870912009752949</v>
       </c>
       <c r="P28" s="1">
-        <v>17.72947821625344</v>
+        <v>53.188434648760321</v>
       </c>
       <c r="Q28" s="1">
-        <v>17.315015297680091</v>
+        <v>51.945045893040273</v>
       </c>
       <c r="R28" s="1">
-        <v>14.073372331882624</v>
+        <v>42.220116995647871</v>
       </c>
       <c r="S28" s="1">
-        <v>11.835566187644968</v>
+        <v>35.506698562934901</v>
       </c>
       <c r="T28" s="1">
-        <v>13.206039716961834</v>
+        <v>39.618119150885505</v>
       </c>
       <c r="U28" s="1">
-        <v>11.792433221703025</v>
+        <v>35.377299665109078</v>
       </c>
       <c r="V28" s="1">
-        <v>10.733427261739727</v>
+        <v>32.200281785219182</v>
       </c>
       <c r="W28" s="1">
-        <v>11.331589147290849</v>
+        <v>33.994767441872547</v>
       </c>
       <c r="X28" s="1">
-        <v>10.543444571081411</v>
+        <v>31.630333713244234</v>
       </c>
       <c r="Y28" s="1">
-        <v>12.940215643883507</v>
+        <v>38.820646931650522</v>
       </c>
       <c r="Z28" s="1">
-        <v>8.8659119974058704</v>
+        <v>26.597735992217611</v>
       </c>
       <c r="AA28" s="1">
-        <v>9.5050747536453297</v>
+        <v>28.515224260935987</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -71609,76 +71609,76 @@
         <v>1</v>
       </c>
       <c r="D29" s="1">
-        <v>4.880756100000001</v>
+        <v>14.642268300000003</v>
       </c>
       <c r="E29" s="1">
-        <v>5.0435671000000006</v>
+        <v>15.130701300000002</v>
       </c>
       <c r="F29" s="1">
-        <v>4.5162183000000002</v>
+        <v>13.548654900000001</v>
       </c>
       <c r="G29" s="1">
-        <v>4.2807379999999995</v>
+        <v>12.842213999999998</v>
       </c>
       <c r="H29" s="1">
-        <v>3.5071872000000002</v>
+        <v>10.5215616</v>
       </c>
       <c r="I29" s="1">
-        <v>2.9766616000000004</v>
+        <v>8.9299848000000015</v>
       </c>
       <c r="J29" s="1">
-        <v>3.6402157000000002</v>
+        <v>10.9206471</v>
       </c>
       <c r="K29" s="1">
-        <v>0.63218320000000017</v>
+        <v>1.8965496000000006</v>
       </c>
       <c r="L29" s="1">
-        <v>0.55593999999999999</v>
+        <v>1.6678199999999999</v>
       </c>
       <c r="M29" s="1">
-        <v>0.81048109999999984</v>
+        <v>2.4314432999999998</v>
       </c>
       <c r="N29" s="1">
-        <v>0.47731420000000008</v>
+        <v>1.4319426000000002</v>
       </c>
       <c r="O29" s="1">
-        <v>0.59644419999999987</v>
+        <v>1.7893325999999996</v>
       </c>
       <c r="P29" s="1">
-        <v>0.95026030000000028</v>
+        <v>2.8507809000000011</v>
       </c>
       <c r="Q29" s="1">
-        <v>1.7508139</v>
+        <v>5.2524417000000003</v>
       </c>
       <c r="R29" s="1">
-        <v>1.8679584</v>
+        <v>5.6038752000000001</v>
       </c>
       <c r="S29" s="1">
-        <v>1.8369845999999996</v>
+        <v>5.5109537999999993</v>
       </c>
       <c r="T29" s="1">
-        <v>1.0304745</v>
+        <v>3.0914234999999999</v>
       </c>
       <c r="U29" s="1">
-        <v>2.0990705999999997</v>
+        <v>6.2972117999999995</v>
       </c>
       <c r="V29" s="1">
-        <v>1.2318042</v>
+        <v>3.6954126</v>
       </c>
       <c r="W29" s="1">
-        <v>0.86607509999999988</v>
+        <v>2.5982252999999997</v>
       </c>
       <c r="X29" s="1">
-        <v>1.3151952000000002</v>
+        <v>3.9455856000000007</v>
       </c>
       <c r="Y29" s="1">
-        <v>0.81286369999999997</v>
+        <v>2.4385911</v>
       </c>
       <c r="Z29" s="1">
-        <v>3.7101053000000004</v>
+        <v>11.130315900000001</v>
       </c>
       <c r="AA29" s="1">
-        <v>4.4725372999999999</v>
+        <v>13.417611900000001</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -71692,76 +71692,76 @@
         <v>1</v>
       </c>
       <c r="D30" s="1">
-        <v>-11.167451974536863</v>
+        <v>-33.502355923610594</v>
       </c>
       <c r="E30" s="1">
-        <v>-12.823081768905411</v>
+        <v>-38.469245306716232</v>
       </c>
       <c r="F30" s="1">
-        <v>-10.030325820347226</v>
+        <v>-30.090977461041678</v>
       </c>
       <c r="G30" s="1">
-        <v>-13.3758715271357</v>
+        <v>-40.127614581407101</v>
       </c>
       <c r="H30" s="1">
-        <v>-17.808573532014695</v>
+        <v>-53.425720596044087</v>
       </c>
       <c r="I30" s="1">
-        <v>-16.90355195106568</v>
+        <v>-50.710655853197039</v>
       </c>
       <c r="J30" s="1">
-        <v>-15.023743744018972</v>
+        <v>-45.071231232056917</v>
       </c>
       <c r="K30" s="1">
-        <v>-17.759080083763511</v>
+        <v>-53.277240251290536</v>
       </c>
       <c r="L30" s="1">
-        <v>-18.697328105247461</v>
+        <v>-56.09198431574238</v>
       </c>
       <c r="M30" s="1">
-        <v>-23.646445297308613</v>
+        <v>-70.939335891925836</v>
       </c>
       <c r="N30" s="1">
-        <v>-24.12335938263136</v>
+        <v>-72.370078147894077</v>
       </c>
       <c r="O30" s="1">
-        <v>-23.651349811615397</v>
+        <v>-70.954049434846183</v>
       </c>
       <c r="P30" s="1">
-        <v>-19.306945238516331</v>
+        <v>-57.920835715548989</v>
       </c>
       <c r="Q30" s="1">
-        <v>-18.978743572868531</v>
+        <v>-56.936230718605593</v>
       </c>
       <c r="R30" s="1">
-        <v>-20.011676964824506</v>
+        <v>-60.035030894473522</v>
       </c>
       <c r="S30" s="1">
-        <v>-16.474463908219697</v>
+        <v>-49.423391724659091</v>
       </c>
       <c r="T30" s="1">
-        <v>-15.716068149233966</v>
+        <v>-47.1482044477019</v>
       </c>
       <c r="U30" s="1">
-        <v>-14.054421544287861</v>
+        <v>-42.16326463286358</v>
       </c>
       <c r="V30" s="1">
-        <v>-8.144512441516893</v>
+        <v>-24.433537324550677</v>
       </c>
       <c r="W30" s="1">
-        <v>-10.948033598645063</v>
+        <v>-32.844100795935191</v>
       </c>
       <c r="X30" s="1">
-        <v>-11.202136360502314</v>
+        <v>-33.606409081506939</v>
       </c>
       <c r="Y30" s="1">
-        <v>-10.361078635659446</v>
+        <v>-31.083235906978338</v>
       </c>
       <c r="Z30" s="1">
-        <v>-8.5627110268612121</v>
+        <v>-25.688133080583636</v>
       </c>
       <c r="AA30" s="1">
-        <v>-10.992628272128735</v>
+        <v>-32.977884816386208</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.2">
@@ -71775,76 +71775,76 @@
         <v>1</v>
       </c>
       <c r="D31" s="1">
-        <v>8.4290916681592769</v>
+        <v>25.287275004477831</v>
       </c>
       <c r="E31" s="1">
-        <v>10.625158596178837</v>
+        <v>31.875475788536512</v>
       </c>
       <c r="F31" s="1">
-        <v>13.821100820639721</v>
+        <v>41.463302461919163</v>
       </c>
       <c r="G31" s="1">
-        <v>13.194758905122479</v>
+        <v>39.584276715367437</v>
       </c>
       <c r="H31" s="1">
-        <v>16.468089672860621</v>
+        <v>49.404269018581864</v>
       </c>
       <c r="I31" s="1">
-        <v>14.605531734268528</v>
+        <v>43.816595202805587</v>
       </c>
       <c r="J31" s="1">
-        <v>14.455483071316305</v>
+        <v>43.366449213948911</v>
       </c>
       <c r="K31" s="1">
-        <v>16.849556198282304</v>
+        <v>50.548668594846916</v>
       </c>
       <c r="L31" s="1">
-        <v>14.524455308625004</v>
+        <v>43.573365925875009</v>
       </c>
       <c r="M31" s="1">
-        <v>22.145297359116725</v>
+        <v>66.435892077350175</v>
       </c>
       <c r="N31" s="1">
-        <v>17.940030393078516</v>
+        <v>53.820091179235547</v>
       </c>
       <c r="O31" s="1">
-        <v>15.95697066991765</v>
+        <v>47.870912009752949</v>
       </c>
       <c r="P31" s="1">
-        <v>18.438657344903575</v>
+        <v>55.315972034710725</v>
       </c>
       <c r="Q31" s="1">
-        <v>16.449264532796086</v>
+        <v>49.347793598388257</v>
       </c>
       <c r="R31" s="1">
-        <v>14.073372331882624</v>
+        <v>42.220116995647871</v>
       </c>
       <c r="S31" s="1">
-        <v>12.427344497027216</v>
+        <v>37.282033491081648</v>
       </c>
       <c r="T31" s="1">
-        <v>13.073979319792215</v>
+        <v>39.221937959376646</v>
       </c>
       <c r="U31" s="1">
-        <v>11.556584557268964</v>
+        <v>34.669753671806895</v>
       </c>
       <c r="V31" s="1">
-        <v>10.948095806974523</v>
+        <v>32.844287420923571</v>
       </c>
       <c r="W31" s="1">
-        <v>11.671536821709573</v>
+        <v>35.014610465128719</v>
       </c>
       <c r="X31" s="1">
-        <v>10.75431346250304</v>
+        <v>32.262940387509119</v>
       </c>
       <c r="Y31" s="1">
-        <v>12.552009174567001</v>
+        <v>37.656027523700999</v>
       </c>
       <c r="Z31" s="1">
-        <v>8.9545711173799294</v>
+        <v>26.86371335213979</v>
       </c>
       <c r="AA31" s="1">
-        <v>9.6001255011817825</v>
+        <v>28.800376503545348</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.2">
@@ -71858,76 +71858,76 @@
         <v>2</v>
       </c>
       <c r="D32" s="1">
-        <v>4.8319485390000008</v>
+        <v>14.495845617000002</v>
       </c>
       <c r="E32" s="1">
-        <v>5.2957454550000014</v>
+        <v>15.887236365000003</v>
       </c>
       <c r="F32" s="1">
-        <v>4.5162183000000002</v>
+        <v>13.548654900000001</v>
       </c>
       <c r="G32" s="1">
-        <v>4.0667010999999995</v>
+        <v>12.200103299999999</v>
       </c>
       <c r="H32" s="1">
-        <v>3.4721153280000006</v>
+        <v>10.416345984000001</v>
       </c>
       <c r="I32" s="1">
-        <v>2.8278285200000006</v>
+        <v>8.4834855600000019</v>
       </c>
       <c r="J32" s="1">
-        <v>3.494607072</v>
+        <v>10.483821215999999</v>
       </c>
       <c r="K32" s="1">
-        <v>0.65114869600000025</v>
+        <v>1.9534460880000006</v>
       </c>
       <c r="L32" s="1">
-        <v>0.55593999999999999</v>
+        <v>1.6678199999999999</v>
       </c>
       <c r="M32" s="1">
-        <v>0.79427147799999986</v>
+        <v>2.3828144339999997</v>
       </c>
       <c r="N32" s="1">
-        <v>0.47254105800000007</v>
+        <v>1.4176231740000003</v>
       </c>
       <c r="O32" s="1">
-        <v>0.60240864199999988</v>
+        <v>1.8072259259999996</v>
       </c>
       <c r="P32" s="1">
-        <v>0.94075769700000023</v>
+        <v>2.8222730910000005</v>
       </c>
       <c r="Q32" s="1">
-        <v>1.733305761</v>
+        <v>5.1999172829999996</v>
       </c>
       <c r="R32" s="1">
-        <v>1.8866379839999998</v>
+        <v>5.6599139519999992</v>
       </c>
       <c r="S32" s="1">
-        <v>1.7635052159999998</v>
+        <v>5.2905156479999995</v>
       </c>
       <c r="T32" s="1">
-        <v>1.0304745</v>
+        <v>3.0914234999999999</v>
       </c>
       <c r="U32" s="1">
-        <v>2.2040241299999996</v>
+        <v>6.6120723899999989</v>
       </c>
       <c r="V32" s="1">
-        <v>1.1825320320000001</v>
+        <v>3.5475960960000004</v>
       </c>
       <c r="W32" s="1">
-        <v>0.88339660199999981</v>
+        <v>2.6501898059999993</v>
       </c>
       <c r="X32" s="1">
-        <v>1.2625873920000001</v>
+        <v>3.7877621760000002</v>
       </c>
       <c r="Y32" s="1">
-        <v>0.78034915199999999</v>
+        <v>2.3410474560000001</v>
       </c>
       <c r="Z32" s="1">
-        <v>3.6730042470000006</v>
+        <v>11.019012741000001</v>
       </c>
       <c r="AA32" s="1">
-        <v>4.4725372999999999</v>
+        <v>13.417611900000001</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
@@ -71941,76 +71941,76 @@
         <v>2</v>
       </c>
       <c r="D33" s="1">
-        <v>-10.944102935046125</v>
+        <v>-32.832308805138375</v>
       </c>
       <c r="E33" s="1">
-        <v>-12.566620133527303</v>
+        <v>-37.699860400581912</v>
       </c>
       <c r="F33" s="1">
-        <v>-9.8297193039402817</v>
+        <v>-29.489157911820847</v>
       </c>
       <c r="G33" s="1">
-        <v>-12.974595381321627</v>
+        <v>-38.923786143964882</v>
       </c>
       <c r="H33" s="1">
-        <v>-18.699002208615429</v>
+        <v>-56.097006625846291</v>
       </c>
       <c r="I33" s="1">
-        <v>-16.39644539253371</v>
+        <v>-49.189336177601135</v>
       </c>
       <c r="J33" s="1">
-        <v>-15.324218618899351</v>
+        <v>-45.972655856698054</v>
       </c>
       <c r="K33" s="1">
-        <v>-17.581489282925876</v>
+        <v>-52.744467848777632</v>
       </c>
       <c r="L33" s="1">
-        <v>-18.136408262090036</v>
+        <v>-54.409224786270109</v>
       </c>
       <c r="M33" s="1">
-        <v>-22.937051938389356</v>
+        <v>-68.811155815168064</v>
       </c>
       <c r="N33" s="1">
-        <v>-22.91719141349979</v>
+        <v>-68.751574240499366</v>
       </c>
       <c r="O33" s="1">
-        <v>-24.83391730219617</v>
+        <v>-74.50175190658851</v>
       </c>
       <c r="P33" s="1">
-        <v>-19.886153595671821</v>
+        <v>-59.658460787015464</v>
       </c>
       <c r="Q33" s="1">
-        <v>-19.358318444325899</v>
+        <v>-58.074955332977694</v>
       </c>
       <c r="R33" s="1">
-        <v>-20.81214404341749</v>
+        <v>-62.43643213025247</v>
       </c>
       <c r="S33" s="1">
-        <v>-17.133442464548484</v>
+        <v>-51.400327393645455</v>
       </c>
       <c r="T33" s="1">
-        <v>-15.558907467741626</v>
+        <v>-46.676722403224879</v>
       </c>
       <c r="U33" s="1">
-        <v>-13.913877328844983</v>
+        <v>-41.741631986534948</v>
       </c>
       <c r="V33" s="1">
-        <v>-8.2259575659320614</v>
+        <v>-24.677872697796182</v>
       </c>
       <c r="W33" s="1">
-        <v>-10.948033598645063</v>
+        <v>-32.844100795935191</v>
       </c>
       <c r="X33" s="1">
-        <v>-11.426179087712359</v>
+        <v>-34.278537263137082</v>
       </c>
       <c r="Y33" s="1">
-        <v>-10.879132567442419</v>
+        <v>-32.637397702327256</v>
       </c>
       <c r="Z33" s="1">
-        <v>-8.9908465782042732</v>
+        <v>-26.97253973461282</v>
       </c>
       <c r="AA33" s="1">
-        <v>-10.552923141243587</v>
+        <v>-31.65876942373076</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.2">
@@ -72024,76 +72024,76 @@
         <v>2</v>
       </c>
       <c r="D34" s="1">
-        <v>8.0076370847513143</v>
+        <v>24.022911254253941</v>
       </c>
       <c r="E34" s="1">
-        <v>10.943913354064202</v>
+        <v>32.831740062192608</v>
       </c>
       <c r="F34" s="1">
-        <v>13.130045779607736</v>
+        <v>39.390137338823209</v>
       </c>
       <c r="G34" s="1">
-        <v>12.666968548917581</v>
+        <v>38.000905646752742</v>
       </c>
       <c r="H34" s="1">
-        <v>15.644685189217592</v>
+        <v>46.934055567652777</v>
       </c>
       <c r="I34" s="1">
-        <v>15.043697686296584</v>
+        <v>45.131093058889753</v>
       </c>
       <c r="J34" s="1">
-        <v>13.877263748463651</v>
+        <v>41.631791245390957</v>
       </c>
       <c r="K34" s="1">
-        <v>16.007078388368189</v>
+        <v>48.021235165104571</v>
       </c>
       <c r="L34" s="1">
-        <v>15.105433520970005</v>
+        <v>45.316300562910016</v>
       </c>
       <c r="M34" s="1">
-        <v>21.038032491160887</v>
+        <v>63.114097473482659</v>
       </c>
       <c r="N34" s="1">
-        <v>17.043028873424589</v>
+        <v>51.129086620273767</v>
       </c>
       <c r="O34" s="1">
-        <v>16.754819203413533</v>
+        <v>50.264457610240598</v>
       </c>
       <c r="P34" s="1">
-        <v>18.807430491801647</v>
+        <v>56.42229147540494</v>
       </c>
       <c r="Q34" s="1">
-        <v>16.778249823452008</v>
+        <v>50.334749470356023</v>
       </c>
       <c r="R34" s="1">
-        <v>14.354839778520278</v>
+        <v>43.064519335560831</v>
       </c>
       <c r="S34" s="1">
-        <v>12.427344497027216</v>
+        <v>37.282033491081648</v>
       </c>
       <c r="T34" s="1">
-        <v>13.204719112990137</v>
+        <v>39.614157338970415</v>
       </c>
       <c r="U34" s="1">
-        <v>11.209887020550896</v>
+        <v>33.629661061652691</v>
       </c>
       <c r="V34" s="1">
-        <v>11.276538681183759</v>
+        <v>33.829616043551276</v>
       </c>
       <c r="W34" s="1">
-        <v>11.904967558143765</v>
+        <v>35.714902674431293</v>
       </c>
       <c r="X34" s="1">
-        <v>10.216597789377888</v>
+        <v>30.649793368133665</v>
       </c>
       <c r="Y34" s="1">
-        <v>12.42648908282133</v>
+        <v>37.279467248463988</v>
       </c>
       <c r="Z34" s="1">
-        <v>8.5068425615109327</v>
+        <v>25.520527684532798</v>
       </c>
       <c r="AA34" s="1">
-        <v>9.888129266217236</v>
+        <v>29.66438779865171</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.2">
@@ -72107,76 +72107,76 @@
         <v>3</v>
       </c>
       <c r="D35" s="1">
-        <v>4.8319485390000008</v>
+        <v>14.495845617000002</v>
       </c>
       <c r="E35" s="1">
-        <v>5.5075752732000014</v>
+        <v>16.522725819600005</v>
       </c>
       <c r="F35" s="1">
-        <v>4.5162183000000002</v>
+        <v>13.548654900000001</v>
       </c>
       <c r="G35" s="1">
-        <v>3.9853670779999995</v>
+        <v>11.956101233999998</v>
       </c>
       <c r="H35" s="1">
-        <v>3.2985095616000009</v>
+        <v>9.8955286848000021</v>
       </c>
       <c r="I35" s="1">
-        <v>2.7712719496000005</v>
+        <v>8.3138158488000009</v>
       </c>
       <c r="J35" s="1">
-        <v>3.3198767184000002</v>
+        <v>9.9596301552000011</v>
       </c>
       <c r="K35" s="1">
-        <v>0.63812572208000029</v>
+        <v>1.9143771662400009</v>
       </c>
       <c r="L35" s="1">
-        <v>0.55593999999999999</v>
+        <v>1.6678199999999999</v>
       </c>
       <c r="M35" s="1">
-        <v>0.80221419277999984</v>
+        <v>2.4066425783399996</v>
       </c>
       <c r="N35" s="1">
-        <v>0.49616811090000007</v>
+        <v>1.4885043327000003</v>
       </c>
       <c r="O35" s="1">
-        <v>0.59638455557999992</v>
+        <v>1.7891536667399999</v>
       </c>
       <c r="P35" s="1">
-        <v>0.98779558185000027</v>
+        <v>2.9633867455500007</v>
       </c>
       <c r="Q35" s="1">
-        <v>1.7679718762199998</v>
+        <v>5.3039156286599995</v>
       </c>
       <c r="R35" s="1">
-        <v>1.9243707436799997</v>
+        <v>5.7731122310399989</v>
       </c>
       <c r="S35" s="1">
-        <v>1.7106000595199999</v>
+        <v>5.1318001785599998</v>
       </c>
       <c r="T35" s="1">
-        <v>1.061388735</v>
+        <v>3.1841662049999999</v>
       </c>
       <c r="U35" s="1">
-        <v>2.1379034060999995</v>
+        <v>6.4137102182999985</v>
       </c>
       <c r="V35" s="1">
-        <v>1.2298333132800001</v>
+        <v>3.6894999398400001</v>
       </c>
       <c r="W35" s="1">
-        <v>0.85689470393999978</v>
+        <v>2.5706841118199995</v>
       </c>
       <c r="X35" s="1">
-        <v>1.1994580224000002</v>
+        <v>3.5983740672000009</v>
       </c>
       <c r="Y35" s="1">
-        <v>0.77254566048000006</v>
+        <v>2.3176369814400002</v>
       </c>
       <c r="Z35" s="1">
-        <v>3.7464643319400004</v>
+        <v>11.239392995820001</v>
       </c>
       <c r="AA35" s="1">
-        <v>4.4278119270000005</v>
+        <v>13.283435781000001</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.2">
@@ -72190,76 +72190,76 @@
         <v>3</v>
       </c>
       <c r="D36" s="1">
-        <v>-11.491308081798431</v>
+        <v>-34.473924245395295</v>
       </c>
       <c r="E36" s="1">
-        <v>-13.194951140203669</v>
+        <v>-39.584853420611005</v>
       </c>
       <c r="F36" s="1">
-        <v>-10.124610883058489</v>
+        <v>-30.373832649175469</v>
       </c>
       <c r="G36" s="1">
-        <v>-13.234087288948061</v>
+        <v>-39.702261866844182</v>
       </c>
       <c r="H36" s="1">
-        <v>-19.072982252787739</v>
+        <v>-57.218946758363217</v>
       </c>
       <c r="I36" s="1">
-        <v>-17.216267662160398</v>
+        <v>-51.648802986481193</v>
       </c>
       <c r="J36" s="1">
-        <v>-14.86449206033237</v>
+        <v>-44.593476180997115</v>
       </c>
       <c r="K36" s="1">
-        <v>-17.933119068584393</v>
+        <v>-53.799357205753182</v>
       </c>
       <c r="L36" s="1">
-        <v>-17.955044179469137</v>
+        <v>-53.865132538407408</v>
       </c>
       <c r="M36" s="1">
-        <v>-22.248940380237677</v>
+        <v>-66.746821140713024</v>
       </c>
       <c r="N36" s="1">
-        <v>-21.771331842824804</v>
+        <v>-65.313995528474408</v>
       </c>
       <c r="O36" s="1">
-        <v>-24.337238956152245</v>
+        <v>-73.01171686845673</v>
       </c>
       <c r="P36" s="1">
-        <v>-18.891845915888229</v>
+        <v>-56.675537747664691</v>
       </c>
       <c r="Q36" s="1">
-        <v>-19.16473525988264</v>
+        <v>-57.49420577964792</v>
       </c>
       <c r="R36" s="1">
-        <v>-21.852751245588365</v>
+        <v>-65.558253736765096</v>
       </c>
       <c r="S36" s="1">
-        <v>-17.64744573848494</v>
+        <v>-52.94233721545482</v>
       </c>
       <c r="T36" s="1">
-        <v>-14.780962094354544</v>
+        <v>-44.342886283063635</v>
       </c>
       <c r="U36" s="1">
-        <v>-14.609571195287231</v>
+        <v>-43.828713585861692</v>
       </c>
       <c r="V36" s="1">
-        <v>-8.3082171415913812</v>
+        <v>-24.924651424774144</v>
       </c>
       <c r="W36" s="1">
-        <v>-11.166994270617963</v>
+        <v>-33.500982811853888</v>
       </c>
       <c r="X36" s="1">
-        <v>-11.083393715080987</v>
+        <v>-33.250181145242962</v>
       </c>
       <c r="Y36" s="1">
-        <v>-10.443967264744721</v>
+        <v>-31.331901794234163</v>
       </c>
       <c r="Z36" s="1">
-        <v>-9.3504804413324436</v>
+        <v>-28.051441323997331</v>
       </c>
       <c r="AA36" s="1">
-        <v>-10.341864678418714</v>
+        <v>-31.025594035256141</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.2">
@@ -72273,76 +72273,76 @@
         <v>3</v>
       </c>
       <c r="D37" s="1">
-        <v>8.0076370847513143</v>
+        <v>24.022911254253941</v>
       </c>
       <c r="E37" s="1">
-        <v>10.725035086982919</v>
+        <v>32.175105260948754</v>
       </c>
       <c r="F37" s="1">
-        <v>13.130045779607736</v>
+        <v>39.390137338823209</v>
       </c>
       <c r="G37" s="1">
-        <v>12.033620121471701</v>
+        <v>36.100860364415105</v>
       </c>
       <c r="H37" s="1">
-        <v>16.114025744894121</v>
+        <v>48.342077234682364</v>
       </c>
       <c r="I37" s="1">
-        <v>15.795882570611413</v>
+        <v>47.387647711834241</v>
       </c>
       <c r="J37" s="1">
-        <v>14.432354298402197</v>
+        <v>43.297062895206594</v>
       </c>
       <c r="K37" s="1">
-        <v>16.327219956135551</v>
+        <v>48.981659868406652</v>
       </c>
       <c r="L37" s="1">
-        <v>15.105433520970005</v>
+        <v>45.316300562910016</v>
       </c>
       <c r="M37" s="1">
-        <v>21.458793140984103</v>
+        <v>64.376379422952311</v>
       </c>
       <c r="N37" s="1">
-        <v>17.724750028361573</v>
+        <v>53.174250085084722</v>
       </c>
       <c r="O37" s="1">
-        <v>17.257463779515938</v>
+        <v>51.772391338547813</v>
       </c>
       <c r="P37" s="1">
-        <v>17.867058967211566</v>
+        <v>53.601176901634702</v>
       </c>
       <c r="Q37" s="1">
-        <v>15.939337332279408</v>
+        <v>47.818011996838223</v>
       </c>
       <c r="R37" s="1">
-        <v>14.641936574090682</v>
+        <v>43.925809722272049</v>
       </c>
       <c r="S37" s="1">
-        <v>12.178797607086672</v>
+        <v>36.536392821260016</v>
       </c>
       <c r="T37" s="1">
-        <v>13.46881349524994</v>
+        <v>40.406440485749819</v>
       </c>
       <c r="U37" s="1">
-        <v>10.873590409934371</v>
+        <v>32.620771229803111</v>
       </c>
       <c r="V37" s="1">
-        <v>11.727600228431108</v>
+        <v>35.182800685293323</v>
       </c>
       <c r="W37" s="1">
-        <v>11.666868206980888</v>
+        <v>35.000604620942667</v>
       </c>
       <c r="X37" s="1">
-        <v>10.114431811484108</v>
+        <v>30.343295434452322</v>
       </c>
       <c r="Y37" s="1">
-        <v>12.42648908282133</v>
+        <v>37.279467248463988</v>
       </c>
       <c r="Z37" s="1">
-        <v>8.1665688590504946</v>
+        <v>24.499706577151485</v>
       </c>
       <c r="AA37" s="1">
-        <v>9.888129266217236</v>
+        <v>29.66438779865171</v>
       </c>
     </row>
   </sheetData>
